--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="997">
   <si>
     <t>_id</t>
   </si>
@@ -3019,6 +3019,33 @@
     <t>3011</t>
   </si>
   <si>
+    <t>220032</t>
+  </si>
+  <si>
+    <t>220033</t>
+  </si>
+  <si>
+    <t>220034</t>
+  </si>
+  <si>
+    <t>220035</t>
+  </si>
+  <si>
+    <t>220036</t>
+  </si>
+  <si>
+    <t>等级丹</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>4014</t>
+  </si>
+  <si>
+    <t>220037</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
@@ -3134,15 +3161,6 @@
   </si>
   <si>
     <t>1006</t>
-  </si>
-  <si>
-    <t>等级丹</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>4014</t>
   </si>
   <si>
     <t>1007</t>
@@ -3590,12 +3608,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -10850,7 +10868,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H30"/>
+  <dimension ref="C1:H36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -11428,6 +11446,126 @@
       </c>
       <c r="H30" s="17" t="s">
         <v>867</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:8">
+      <c r="C31" s="18" t="s">
+        <v>868</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="F31" s="2">
+        <v>2</v>
+      </c>
+      <c r="G31" s="2">
+        <v>9</v>
+      </c>
+      <c r="H31" s="2">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:8">
+      <c r="C32" s="18" t="s">
+        <v>869</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="F32" s="2">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2">
+        <v>5</v>
+      </c>
+      <c r="H32" s="2">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:8">
+      <c r="C33" s="18" t="s">
+        <v>870</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="F33" s="2">
+        <v>200</v>
+      </c>
+      <c r="G33" s="2">
+        <v>5</v>
+      </c>
+      <c r="H33" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:8">
+      <c r="C34" s="18" t="s">
+        <v>871</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F34" s="2">
+        <v>100</v>
+      </c>
+      <c r="G34" s="2">
+        <v>5</v>
+      </c>
+      <c r="H34" s="2">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C35" s="18" t="s">
+        <v>872</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="F35" s="2">
+        <v>10</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>874</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C36" s="18" t="s">
+        <v>876</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="F36" s="2">
+        <v>15</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>874</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>875</v>
       </c>
     </row>
   </sheetData>
@@ -11527,13 +11665,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>869</v>
+        <v>878</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11542,18 +11680,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>872</v>
+        <v>881</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11562,18 +11700,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -11582,18 +11720,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -11602,18 +11740,18 @@
         <v>20</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -11622,18 +11760,18 @@
         <v>17</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="17" t="s">
-        <v>883</v>
+        <v>892</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -11642,18 +11780,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>884</v>
+        <v>893</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -11662,18 +11800,18 @@
         <v>17</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -11682,7 +11820,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -11693,176 +11831,176 @@
         <v>842</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>892</v>
+        <v>901</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>893</v>
+        <v>902</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>899</v>
+        <v>908</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="17" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="17" t="s">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>905</v>
+        <v>914</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="17" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>907</v>
+        <v>873</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>908</v>
+        <v>874</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>909</v>
+        <v>875</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="17" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="8:8">
@@ -11870,7 +12008,7 @@
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="17" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>842</v>
@@ -11890,7 +12028,7 @@
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="17" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>842</v>
@@ -11910,7 +12048,7 @@
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="17" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>842</v>
@@ -11939,7 +12077,7 @@
         <v>842</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>19</v>
@@ -11948,7 +12086,7 @@
         <v>844</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -11959,7 +12097,7 @@
         <v>842</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>19</v>
@@ -11968,18 +12106,18 @@
         <v>844</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>19</v>
@@ -11988,18 +12126,18 @@
         <v>844</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="17" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>19</v>
@@ -12008,18 +12146,18 @@
         <v>844</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>19</v>
@@ -12028,18 +12166,18 @@
         <v>844</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>19</v>
@@ -12048,18 +12186,18 @@
         <v>844</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>19</v>
@@ -12068,18 +12206,18 @@
         <v>844</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>19</v>
@@ -12088,18 +12226,18 @@
         <v>844</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>19</v>
@@ -12108,18 +12246,18 @@
         <v>844</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>19</v>
@@ -12128,18 +12266,18 @@
         <v>844</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="17" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>19</v>
@@ -12148,18 +12286,18 @@
         <v>844</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="17" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>19</v>
@@ -12168,7 +12306,7 @@
         <v>844</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="3:8">
@@ -12181,7 +12319,7 @@
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="17" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>842</v>
@@ -12201,7 +12339,7 @@
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>842</v>
@@ -12221,42 +12359,42 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:8">
@@ -12269,182 +12407,182 @@
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="10" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="10" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="10" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>963</v>
-      </c>
       <c r="H50" s="17" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="10" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="10" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="10" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="10" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="10" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="H55" s="21" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="10" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="D56" s="17" t="s">
         <v>51</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="H56" s="21" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12455,16 +12593,16 @@
         <v>100</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="H57" s="21" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="1012">
   <si>
     <t>_id</t>
   </si>
@@ -3181,13 +3181,58 @@
     <t>4016</t>
   </si>
   <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>第二批冠名图鉴</t>
+  </si>
+  <si>
+    <t>2000011,2000012,2000013</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>龙之二期</t>
+  </si>
+  <si>
+    <t>1999989,1999990,1999991,1999992</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>2001</t>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>金色图鉴1-4</t>
+  </si>
+  <si>
+    <t>1999001,1999002,1999003,1999004</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>金色图鉴5</t>
+  </si>
+  <si>
+    <t>1999005</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>金色图鉴6</t>
+  </si>
+  <si>
+    <t>1999006</t>
   </si>
   <si>
     <t>第一批白图鉴</t>
@@ -3608,12 +3653,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -11583,7 +11628,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H57"/>
+  <dimension ref="C1:H67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -12006,118 +12051,18 @@
     <row r="24" s="2" customFormat="1" customHeight="1" spans="8:8">
       <c r="H24" s="7"/>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C25" s="17" t="s">
-        <v>922</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>844</v>
-      </c>
-      <c r="H25" s="21" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C26" s="17" t="s">
-        <v>923</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>844</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C27" s="17" t="s">
-        <v>924</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>844</v>
-      </c>
-      <c r="H27" s="21" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="8:8">
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C29" s="17" t="s">
-        <v>829</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>844</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C30" s="17" t="s">
-        <v>864</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>844</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>928</v>
-      </c>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="8:8">
+      <c r="H25" s="7"/>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>930</v>
+        <v>847</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>19</v>
@@ -12125,19 +12070,19 @@
       <c r="G31" s="17" t="s">
         <v>844</v>
       </c>
-      <c r="H31" s="22" t="s">
-        <v>931</v>
+      <c r="H31" s="21" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="17" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>933</v>
+        <v>843</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>19</v>
@@ -12145,19 +12090,19 @@
       <c r="G32" s="17" t="s">
         <v>844</v>
       </c>
-      <c r="H32" s="19" t="s">
-        <v>934</v>
+      <c r="H32" s="21" t="s">
+        <v>845</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>935</v>
+        <v>924</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>936</v>
+        <v>925</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>19</v>
@@ -12166,18 +12111,18 @@
         <v>844</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>937</v>
+        <v>926</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>19</v>
@@ -12186,18 +12131,18 @@
         <v>844</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>940</v>
+        <v>929</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>941</v>
+        <v>930</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>942</v>
+        <v>850</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>19</v>
@@ -12206,18 +12151,18 @@
         <v>844</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>943</v>
+        <v>851</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>19</v>
@@ -12226,18 +12171,18 @@
         <v>844</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>946</v>
+        <v>933</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>19</v>
@@ -12246,18 +12191,18 @@
         <v>844</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>949</v>
+        <v>936</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>950</v>
+        <v>937</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>19</v>
@@ -12266,18 +12211,18 @@
         <v>844</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="17" t="s">
-        <v>953</v>
+        <v>829</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>954</v>
+        <v>940</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>19</v>
@@ -12285,19 +12230,19 @@
       <c r="G39" s="17" t="s">
         <v>844</v>
       </c>
-      <c r="H39" s="21" t="s">
-        <v>955</v>
+      <c r="H39" s="22" t="s">
+        <v>941</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="17" t="s">
-        <v>956</v>
+        <v>864</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>957</v>
+        <v>942</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>19</v>
@@ -12305,304 +12250,504 @@
       <c r="G40" s="17" t="s">
         <v>844</v>
       </c>
-      <c r="H40" s="21" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="3"/>
+      <c r="H40" s="19" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C41" s="17" t="s">
+        <v>944</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="H41" s="22" t="s">
+        <v>946</v>
+      </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="17" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>853</v>
+        <v>948</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>854</v>
-      </c>
-      <c r="H42" s="21" t="s">
-        <v>855</v>
+        <v>844</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>949</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>857</v>
+        <v>951</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:8">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C44" s="17" t="s">
+        <v>953</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="H44" s="21" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>962</v>
+      <c r="E45" s="2" t="s">
+        <v>957</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>899</v>
-      </c>
-      <c r="H45" s="23" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:8">
+        <v>844</v>
+      </c>
+      <c r="H45" s="21" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="H46" s="21" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C47" s="17" t="s">
+        <v>962</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="H47" s="21" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C48" s="17" t="s">
         <v>965</v>
       </c>
-      <c r="F46" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G46" s="17" t="s">
+      <c r="D48" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="H48" s="21" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C49" s="17" t="s">
+        <v>968</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="H49" s="21" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C50" s="17" t="s">
+        <v>971</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="H50" s="21" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C52" s="17" t="s">
+        <v>974</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>854</v>
+      </c>
+      <c r="H52" s="21" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C53" s="17" t="s">
+        <v>975</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="17" t="s">
+        <v>854</v>
+      </c>
+      <c r="H53" s="21" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:8">
+      <c r="C55" s="17" t="s">
+        <v>976</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="17" t="s">
         <v>899</v>
       </c>
-      <c r="H46" s="23" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C48" s="10" t="s">
-        <v>967</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="H55" s="23" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:8">
+      <c r="C56" s="17" t="s">
+        <v>979</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>899</v>
+      </c>
+      <c r="H56" s="23" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C58" s="10" t="s">
+        <v>982</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="H48" s="17" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C49" s="10" t="s">
-        <v>971</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="E58" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="H58" s="17" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C59" s="10" t="s">
+        <v>986</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>972</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="H49" s="17" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C50" s="10" t="s">
-        <v>974</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="E59" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C60" s="10" t="s">
+        <v>989</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>975</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="H50" s="17" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C51" s="10" t="s">
-        <v>977</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="E60" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="H60" s="17" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C61" s="10" t="s">
+        <v>992</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="H51" s="17" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C52" s="10" t="s">
-        <v>980</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="E61" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="H61" s="17" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C62" s="10" t="s">
+        <v>995</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="H52" s="17" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C53" s="10" t="s">
-        <v>983</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="E62" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="H62" s="17" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C63" s="10" t="s">
+        <v>998</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E63" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="H53" s="17" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C54" s="10" t="s">
-        <v>986</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="H63" s="17" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C64" s="10" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>987</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="H54" s="17" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C55" s="10" t="s">
-        <v>989</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="E64" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="H64" s="17" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C65" s="10" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>990</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="H55" s="21" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C56" s="10" t="s">
-        <v>992</v>
-      </c>
-      <c r="D56" s="17" t="s">
+      <c r="E65" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="H65" s="21" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C66" s="10" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D66" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>993</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="H56" s="21" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C57" s="10">
+      <c r="E66" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="H66" s="21" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C67" s="10">
         <v>300091</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D67" s="2">
         <v>100</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="H57" s="21" t="s">
-        <v>996</v>
+      <c r="E67" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="H67" s="21" t="s">
+        <v>1011</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -3199,13 +3199,13 @@
     <t>2005</t>
   </si>
   <si>
+    <t>2006</t>
+  </si>
+  <si>
     <t>龙之二期</t>
   </si>
   <si>
     <t>1999989,1999990,1999991,1999992</t>
-  </si>
-  <si>
-    <t>2006</t>
   </si>
   <si>
     <t>2007</t>
@@ -3653,12 +3653,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -12122,7 +12122,7 @@
         <v>842</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>928</v>
+        <v>850</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>19</v>
@@ -12131,18 +12131,18 @@
         <v>844</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>929</v>
+        <v>851</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>842</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>850</v>
+        <v>929</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>19</v>
@@ -12151,7 +12151,7 @@
         <v>844</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>851</v>
+        <v>930</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="1012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="1016">
   <si>
     <t>_id</t>
   </si>
@@ -2843,6 +2843,18 @@
   </si>
   <si>
     <t>极·卖身契</t>
+  </si>
+  <si>
+    <t>极·圣者遗物</t>
+  </si>
+  <si>
+    <t>极·副本契约</t>
+  </si>
+  <si>
+    <t>极·BOSS契约</t>
+  </si>
+  <si>
+    <t>极.财富契约</t>
   </si>
   <si>
     <t>220000</t>
@@ -10880,17 +10892,85 @@
         <v>180030</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C30" s="10"/>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C31" s="10"/>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C32" s="10"/>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C29" s="14">
+        <v>180031</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="2">
+        <v>18</v>
+      </c>
+      <c r="H29" s="14">
+        <v>180031</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C30" s="14">
+        <v>180032</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="2">
+        <v>18</v>
+      </c>
+      <c r="H30" s="14">
+        <v>180032</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C31" s="14">
+        <v>180033</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="2">
+        <v>18</v>
+      </c>
+      <c r="H31" s="14">
+        <v>180033</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C32" s="14">
+        <v>180034</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="2">
+        <v>18</v>
+      </c>
+      <c r="H32" s="14">
+        <v>180034</v>
+      </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:3">
       <c r="C33" s="10"/>
@@ -10995,13 +11075,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="18" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11015,13 +11095,13 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11035,13 +11115,13 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="F8" s="2">
         <v>50</v>
@@ -11055,13 +11135,13 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F9" s="2">
         <v>20</v>
@@ -11075,13 +11155,13 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -11095,13 +11175,13 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -11115,13 +11195,13 @@
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -11135,13 +11215,13 @@
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -11150,18 +11230,18 @@
         <v>3</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -11170,18 +11250,18 @@
         <v>3</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -11190,18 +11270,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="F16" s="2">
         <v>75</v>
@@ -11215,13 +11295,13 @@
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F17" s="2">
         <v>30</v>
@@ -11235,13 +11315,13 @@
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="F18" s="2">
         <v>100</v>
@@ -11255,13 +11335,13 @@
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F19" s="2">
         <v>40</v>
@@ -11275,13 +11355,13 @@
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -11295,13 +11375,13 @@
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="F21" s="2">
         <v>150</v>
@@ -11315,13 +11395,13 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F22" s="2">
         <v>60</v>
@@ -11335,113 +11415,113 @@
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
+        <v>850</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>842</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -11450,18 +11530,18 @@
         <v>3</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -11470,18 +11550,18 @@
         <v>3</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -11490,18 +11570,18 @@
         <v>3</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="F31" s="2">
         <v>2</v>
@@ -11515,13 +11595,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -11535,13 +11615,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="F33" s="2">
         <v>200</v>
@@ -11555,13 +11635,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="F34" s="2">
         <v>100</v>
@@ -11575,42 +11655,42 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="F36" s="2">
         <v>15</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
     </row>
   </sheetData>
@@ -11710,13 +11790,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11725,18 +11805,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11745,18 +11825,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -11765,18 +11845,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -11785,18 +11865,18 @@
         <v>20</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -11805,18 +11885,18 @@
         <v>17</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="17" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -11825,18 +11905,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
+        <v>898</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>894</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>890</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -11845,18 +11925,18 @@
         <v>17</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -11865,7 +11945,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -11873,179 +11953,179 @@
         <v>347</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="17" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="17" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="17" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="17" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="8:8">
@@ -12056,402 +12136,402 @@
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="17" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="17" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="17" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="17" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="17" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H44" s="21" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:8">
@@ -12464,82 +12544,82 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="17" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:8">
@@ -12552,182 +12632,182 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="10" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H65" s="21" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="D66" s="17" t="s">
         <v>51</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H66" s="21" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12738,16 +12818,16 @@
         <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="1016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="1018">
   <si>
     <t>_id</t>
   </si>
@@ -3056,6 +3056,12 @@
   </si>
   <si>
     <t>220037</t>
+  </si>
+  <si>
+    <t>220038</t>
+  </si>
+  <si>
+    <t>天赋秘籍</t>
   </si>
   <si>
     <t>101</t>
@@ -10993,7 +10999,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H36"/>
+  <dimension ref="C1:H37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -11691,6 +11697,26 @@
       </c>
       <c r="H36" s="21" t="s">
         <v>879</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C37" s="18" t="s">
+        <v>881</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="2">
+        <v>15</v>
+      </c>
+      <c r="H37" s="2">
+        <v>4020</v>
       </c>
     </row>
   </sheetData>
@@ -11790,13 +11816,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11805,18 +11831,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11825,18 +11851,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -11845,18 +11871,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -11865,18 +11891,18 @@
         <v>20</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -11885,18 +11911,18 @@
         <v>17</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="17" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -11905,18 +11931,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -11925,18 +11951,18 @@
         <v>17</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -11945,7 +11971,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -11956,121 +11982,121 @@
         <v>846</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="17" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="17" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="17" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>846</v>
@@ -12090,42 +12116,42 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="17" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="8:8">
@@ -12136,7 +12162,7 @@
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>846</v>
@@ -12156,7 +12182,7 @@
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="17" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>846</v>
@@ -12176,13 +12202,13 @@
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>19</v>
@@ -12191,12 +12217,12 @@
         <v>848</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>846</v>
@@ -12216,13 +12242,13 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>19</v>
@@ -12231,18 +12257,18 @@
         <v>848</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>19</v>
@@ -12251,18 +12277,18 @@
         <v>848</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>19</v>
@@ -12271,18 +12297,18 @@
         <v>848</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>19</v>
@@ -12291,7 +12317,7 @@
         <v>848</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12302,7 +12328,7 @@
         <v>846</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>19</v>
@@ -12311,7 +12337,7 @@
         <v>848</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12322,7 +12348,7 @@
         <v>846</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>19</v>
@@ -12331,18 +12357,18 @@
         <v>848</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="17" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>19</v>
@@ -12351,18 +12377,18 @@
         <v>848</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="17" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>19</v>
@@ -12371,18 +12397,18 @@
         <v>848</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>19</v>
@@ -12391,18 +12417,18 @@
         <v>848</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>19</v>
@@ -12411,18 +12437,18 @@
         <v>848</v>
       </c>
       <c r="H44" s="21" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>19</v>
@@ -12431,18 +12457,18 @@
         <v>848</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>19</v>
@@ -12451,18 +12477,18 @@
         <v>848</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>19</v>
@@ -12471,18 +12497,18 @@
         <v>848</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>19</v>
@@ -12491,18 +12517,18 @@
         <v>848</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>19</v>
@@ -12511,18 +12537,18 @@
         <v>848</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>19</v>
@@ -12531,7 +12557,7 @@
         <v>848</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:8">
@@ -12544,7 +12570,7 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="17" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>846</v>
@@ -12564,7 +12590,7 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>846</v>
@@ -12584,42 +12610,42 @@
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:8">
@@ -12632,182 +12658,182 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="10" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="H65" s="21" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D66" s="17" t="s">
         <v>51</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="H66" s="21" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12818,16 +12844,16 @@
         <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="1020">
   <si>
     <t>_id</t>
   </si>
@@ -3062,6 +3062,12 @@
   </si>
   <si>
     <t>天赋秘籍</t>
+  </si>
+  <si>
+    <t>220039</t>
+  </si>
+  <si>
+    <t>220040</t>
   </si>
   <si>
     <t>101</t>
@@ -3671,12 +3677,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -10999,7 +11005,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H37"/>
+  <dimension ref="C1:H39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -11290,7 +11296,7 @@
         <v>819</v>
       </c>
       <c r="F16" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G16" s="2">
         <v>5</v>
@@ -11310,7 +11316,7 @@
         <v>821</v>
       </c>
       <c r="F17" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G17" s="2">
         <v>5</v>
@@ -11330,7 +11336,7 @@
         <v>819</v>
       </c>
       <c r="F18" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G18" s="2">
         <v>5</v>
@@ -11350,7 +11356,7 @@
         <v>821</v>
       </c>
       <c r="F19" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2">
         <v>5</v>
@@ -11390,7 +11396,7 @@
         <v>819</v>
       </c>
       <c r="F21" s="2">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="G21" s="2">
         <v>5</v>
@@ -11410,7 +11416,7 @@
         <v>821</v>
       </c>
       <c r="F22" s="2">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="G22" s="2">
         <v>5</v>
@@ -11717,6 +11723,46 @@
       </c>
       <c r="H37" s="2">
         <v>4020</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:8">
+      <c r="C38" s="18" t="s">
+        <v>883</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G38" s="2">
+        <v>5</v>
+      </c>
+      <c r="H38" s="2">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:8">
+      <c r="C39" s="18" t="s">
+        <v>884</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="F39" s="2">
+        <v>300</v>
+      </c>
+      <c r="G39" s="2">
+        <v>5</v>
+      </c>
+      <c r="H39" s="2">
+        <v>4101</v>
       </c>
     </row>
   </sheetData>
@@ -11816,13 +11862,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11831,18 +11877,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11851,18 +11897,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -11871,18 +11917,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -11891,18 +11937,18 @@
         <v>20</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -11911,18 +11957,18 @@
         <v>17</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="17" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -11931,18 +11977,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -11951,18 +11997,18 @@
         <v>17</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -11971,7 +12017,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -11982,121 +12028,121 @@
         <v>846</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="17" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="17" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="17" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>846</v>
@@ -12116,42 +12162,42 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="17" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="8:8">
@@ -12162,7 +12208,7 @@
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>846</v>
@@ -12182,7 +12228,7 @@
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="17" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>846</v>
@@ -12202,13 +12248,13 @@
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>19</v>
@@ -12217,12 +12263,12 @@
         <v>848</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>846</v>
@@ -12242,13 +12288,13 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>19</v>
@@ -12257,18 +12303,18 @@
         <v>848</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>19</v>
@@ -12277,18 +12323,18 @@
         <v>848</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>19</v>
@@ -12297,18 +12343,18 @@
         <v>848</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>19</v>
@@ -12317,7 +12363,7 @@
         <v>848</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12328,7 +12374,7 @@
         <v>846</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>19</v>
@@ -12337,7 +12383,7 @@
         <v>848</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12348,7 +12394,7 @@
         <v>846</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>19</v>
@@ -12357,18 +12403,18 @@
         <v>848</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="17" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>19</v>
@@ -12377,18 +12423,18 @@
         <v>848</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="17" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>19</v>
@@ -12397,18 +12443,18 @@
         <v>848</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>19</v>
@@ -12417,18 +12463,18 @@
         <v>848</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>19</v>
@@ -12437,18 +12483,18 @@
         <v>848</v>
       </c>
       <c r="H44" s="21" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>19</v>
@@ -12457,18 +12503,18 @@
         <v>848</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>19</v>
@@ -12477,18 +12523,18 @@
         <v>848</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>19</v>
@@ -12497,18 +12543,18 @@
         <v>848</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>19</v>
@@ -12517,18 +12563,18 @@
         <v>848</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>19</v>
@@ -12537,18 +12583,18 @@
         <v>848</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>19</v>
@@ -12557,7 +12603,7 @@
         <v>848</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:8">
@@ -12570,7 +12616,7 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="17" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>846</v>
@@ -12590,7 +12636,7 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>846</v>
@@ -12610,42 +12656,42 @@
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>846</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:8">
@@ -12658,182 +12704,182 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="10" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H65" s="21" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D66" s="17" t="s">
         <v>51</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H66" s="21" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12844,16 +12890,16 @@
         <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="1025">
   <si>
     <t>_id</t>
   </si>
@@ -2857,6 +2857,12 @@
     <t>极.财富契约</t>
   </si>
   <si>
+    <t>极.魔法书</t>
+  </si>
+  <si>
+    <t>极.无限之魂</t>
+  </si>
+  <si>
     <t>220000</t>
   </si>
   <si>
@@ -3068,6 +3074,15 @@
   </si>
   <si>
     <t>220040</t>
+  </si>
+  <si>
+    <t>220041</t>
+  </si>
+  <si>
+    <t>改造石</t>
+  </si>
+  <si>
+    <t>4021</t>
   </si>
   <si>
     <t>101</t>
@@ -3677,12 +3692,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -10984,11 +10999,45 @@
         <v>180034</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C33" s="10"/>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C34" s="10"/>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C33" s="14">
+        <v>180035</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="2">
+        <v>18</v>
+      </c>
+      <c r="H33" s="14">
+        <v>180035</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C34" s="14">
+        <v>180036</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="2">
+        <v>18</v>
+      </c>
+      <c r="H34" s="14">
+        <v>180036</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -11005,7 +11054,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H39"/>
+  <dimension ref="C1:H40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -11087,13 +11136,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="18" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11107,13 +11156,13 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11127,13 +11176,13 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F8" s="2">
         <v>50</v>
@@ -11147,13 +11196,13 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F9" s="2">
         <v>20</v>
@@ -11167,13 +11216,13 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -11187,13 +11236,13 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -11207,13 +11256,13 @@
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -11227,13 +11276,13 @@
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -11242,18 +11291,18 @@
         <v>3</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -11262,18 +11311,18 @@
         <v>3</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -11282,18 +11331,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F16" s="2">
         <v>100</v>
@@ -11307,13 +11356,13 @@
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F17" s="2">
         <v>40</v>
@@ -11327,13 +11376,13 @@
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F18" s="2">
         <v>200</v>
@@ -11347,13 +11396,13 @@
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F19" s="2">
         <v>80</v>
@@ -11367,13 +11416,13 @@
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -11387,13 +11436,13 @@
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F21" s="2">
         <v>500</v>
@@ -11407,13 +11456,13 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F22" s="2">
         <v>200</v>
@@ -11427,113 +11476,113 @@
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -11542,18 +11591,18 @@
         <v>3</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -11562,18 +11611,18 @@
         <v>3</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -11582,18 +11631,18 @@
         <v>3</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="F31" s="2">
         <v>2</v>
@@ -11607,13 +11656,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -11627,13 +11676,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F33" s="2">
         <v>200</v>
@@ -11647,13 +11696,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F34" s="2">
         <v>100</v>
@@ -11667,53 +11716,53 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F36" s="2">
         <v>15</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>19</v>
@@ -11727,13 +11776,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F38" s="2">
         <v>1000</v>
@@ -11747,13 +11796,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F39" s="2">
         <v>300</v>
@@ -11763,6 +11812,26 @@
       </c>
       <c r="H39" s="2">
         <v>4101</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C40" s="18" t="s">
+        <v>887</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2">
+        <v>5</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -11862,13 +11931,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11877,18 +11946,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11897,18 +11966,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -11917,18 +11986,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -11937,18 +12006,18 @@
         <v>20</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -11957,18 +12026,18 @@
         <v>17</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="17" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -11977,18 +12046,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -11997,18 +12066,18 @@
         <v>17</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -12017,7 +12086,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12025,179 +12094,179 @@
         <v>347</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="17" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="17" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="17" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="17" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="8:8">
@@ -12208,402 +12277,402 @@
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="17" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="17" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="17" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="17" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="17" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H44" s="21" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:8">
@@ -12616,82 +12685,82 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="17" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:8">
@@ -12704,182 +12773,182 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="10" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H65" s="21" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
       <c r="D66" s="17" t="s">
         <v>51</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H66" s="21" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12890,16 +12959,16 @@
         <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -2974,7 +2974,7 @@
     <t>220025</t>
   </si>
   <si>
-    <t>守沙图鉴</t>
+    <t>龙城图鉴</t>
   </si>
   <si>
     <t>2000006,2000007,2000008,2000009,2000010</t>
@@ -3169,7 +3169,7 @@
     <t>1002</t>
   </si>
   <si>
-    <t>守沙100书页</t>
+    <t>龙城100书页</t>
   </si>
   <si>
     <t>1003</t>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="1025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="985">
   <si>
     <t>_id</t>
   </si>
@@ -535,70 +535,58 @@
     <t>60</t>
   </si>
   <si>
-    <t>60级装备</t>
+    <t>100级装备</t>
+  </si>
+  <si>
+    <t>21000501,21000502,22000501,22000502,23000501,23000502</t>
+  </si>
+  <si>
+    <t>200070</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>21000503,21000504,22000503,22000504,23000503,23000504</t>
+  </si>
+  <si>
+    <t>200080</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>21000505,21000507,22000505,22000507,23000505,23000507</t>
+  </si>
+  <si>
+    <t>200090</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>21000509,21000510,22000509,22000510,23000509,23000510</t>
+  </si>
+  <si>
+    <t>200100</t>
+  </si>
+  <si>
+    <t>100</t>
   </si>
   <si>
     <t>21000501,21000502,21000503,21000504,21000505,21000507,21000509,21000510,22000501,22000502,22000503,22000504,22000505,22000507,22000509,22000510,23000501,23000502,23000503,23000504,23000505,23000507,23000509,23000510</t>
   </si>
   <si>
-    <t>200070</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>70级装备</t>
-  </si>
-  <si>
-    <t>21000601,21000602,21000603,21000604,21000605,21000607,21000609,21000610,22000601,22000602,22000603,22000604,22000605,22000607,22000609,22000610,23000601,23000602,23000603,23000604,23000605,23000607,23000609,23000610</t>
-  </si>
-  <si>
-    <t>200080</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>80级装备</t>
-  </si>
-  <si>
-    <t>21000701,21000702,21000703,21000704,21000705,21000707,21000709,21000710,22000701,22000702,22000703,22000704,22000705,22000707,22000709,22000710,23000701,23000702,23000703,23000704,23000705,23000707,23000709,23000710</t>
-  </si>
-  <si>
-    <t>200090</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>90级装备</t>
-  </si>
-  <si>
-    <t>21000801,21000802,21000803,21000804,21000805,21000807,21000809,21000810,22000801,22000802,22000803,22000804,22000805,22000807,22000809,22000810,23000801,23000802,23000803,23000804,23000805,23000807,23000809,23000810</t>
-  </si>
-  <si>
-    <t>200100</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>100级装备</t>
-  </si>
-  <si>
-    <t>21000901,21000902,21000903,21000904,21000905,21000907,21000909,21000910,22000901,22000902,22000903,22000904,22000905,22000907,22000909,22000910,23000901,23000902,23000903,23000904,23000905,23000907,23000909,23000910</t>
-  </si>
-  <si>
     <t>200110</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>110级装备</t>
-  </si>
-  <si>
-    <t>21001001,21001002,21001003,21001004,21001005,21001007,21001009,21001010,22001001,22001002,22001003,22001004,22001005,22001007,22001009,22001010,23001001,23001002,23001003,23001004,23001005,23001007,23001009,23001010</t>
+    <t>150级装备</t>
+  </si>
+  <si>
+    <t>21001001,22001001,23001001,21001002,22001002,23001002</t>
   </si>
   <si>
     <t>200120</t>
@@ -607,10 +595,7 @@
     <t>120</t>
   </si>
   <si>
-    <t>120级装备</t>
-  </si>
-  <si>
-    <t>21001101,21001102,21001103,21001104,21001105,21001107,21001109,21001110,22001101,22001102,22001103,22001104,22001105,22001107,22001109,22001110,23001101,23001102,23001103,23001104,23001105,23001107,23001109,23001110</t>
+    <t>21001003,22001003,23001003,21001004,22001004,23001004</t>
   </si>
   <si>
     <t>200130</t>
@@ -619,10 +604,7 @@
     <t>130</t>
   </si>
   <si>
-    <t>130级装备</t>
-  </si>
-  <si>
-    <t>21001201,21001202,21001203,21001204,21001205,21001207,21001209,21001210,22001201,22001202,22001203,22001204,22001205,22001207,22001209,22001210,23001201,23001202,23001203,23001204,23001205,23001207,23001209,23001210</t>
+    <t>21001005,22001005,23001005,21001007,22001007,23001007</t>
   </si>
   <si>
     <t>200140</t>
@@ -631,10 +613,7 @@
     <t>140</t>
   </si>
   <si>
-    <t>140级装备</t>
-  </si>
-  <si>
-    <t>21001301,21001302,21001303,21001304,21001305,21001307,21001309,21001310,22001301,22001302,22001303,22001304,22001305,22001307,22001309,22001310,23001301,23001302,23001303,23001304,23001305,23001307,23001309,23001310</t>
+    <t>21001009,22001009,23001009,21001010,22001010,23001010</t>
   </si>
   <si>
     <t>200150</t>
@@ -643,10 +622,7 @@
     <t>150</t>
   </si>
   <si>
-    <t>150级装备</t>
-  </si>
-  <si>
-    <t>21001401,21001402,21001403,21001404,21001405,21001407,21001409,21001410,22001401,22001402,22001403,22001404,22001405,22001407,22001409,22001410,23001401,23001402,23001403,23001404,23001405,23001407,23001409,23001410</t>
+    <t>21001001,22001001,23001001,21001002,22001002,23001002,21001003,22001003,23001003,21001004,22001004,23001004,21001005,22001005,23001005,21001007,22001007,23001007,21001009,22001009,23001009,21001010,22001010,23001010</t>
   </si>
   <si>
     <t>200160</t>
@@ -655,10 +631,10 @@
     <t>160</t>
   </si>
   <si>
-    <t>160级装备</t>
-  </si>
-  <si>
-    <t>21001501,21001502,21001503,21001504,21001505,21001507,21001509,21001510,22001501,22001502,22001503,22001504,22001505,22001507,22001509,22001510,23001501,23001502,23001503,23001504,23001505,23001507,23001509,23001510</t>
+    <t>200级装备</t>
+  </si>
+  <si>
+    <t>21001501,22001501,23001501,21001502,22001502,23001502</t>
   </si>
   <si>
     <t>200170</t>
@@ -667,10 +643,7 @@
     <t>170</t>
   </si>
   <si>
-    <t>170级装备</t>
-  </si>
-  <si>
-    <t>21001601,21001602,21001603,21001604,21001605,21001607,21001609,21001610,22001601,22001602,22001603,22001604,22001605,22001607,22001609,22001610,23001601,23001602,23001603,23001604,23001605,23001607,23001609,23001610</t>
+    <t>21001503,22001503,23001503,21001504,22001504,23001504</t>
   </si>
   <si>
     <t>200180</t>
@@ -679,10 +652,7 @@
     <t>180</t>
   </si>
   <si>
-    <t>180级装备</t>
-  </si>
-  <si>
-    <t>21001701,21001702,21001703,21001704,21001705,21001707,21001709,21001710,22001701,22001702,22001703,22001704,22001705,22001707,22001709,22001710,23001701,23001702,23001703,23001704,23001705,23001707,23001709,23001710</t>
+    <t>21001505,22001505,23001505,21001507,22001507,23001507</t>
   </si>
   <si>
     <t>200190</t>
@@ -691,10 +661,7 @@
     <t>190</t>
   </si>
   <si>
-    <t>190级装备</t>
-  </si>
-  <si>
-    <t>21001801,21001802,21001803,21001804,21001805,21001807,21001809,21001810,22001801,22001802,22001803,22001804,22001805,22001807,22001809,22001810,23001801,23001802,23001803,23001804,23001805,23001807,23001809,23001810</t>
+    <t>21001509,22001509,23001509,21001510,22001510,23001510</t>
   </si>
   <si>
     <t>200200</t>
@@ -703,10 +670,7 @@
     <t>200</t>
   </si>
   <si>
-    <t>200级装备</t>
-  </si>
-  <si>
-    <t>21001901,21001902,21001903,21001904,21001905,21001907,21001909,21001910,22001901,22001902,22001903,22001904,22001905,22001907,22001909,22001910,23001901,23001902,23001903,23001904,23001905,23001907,23001909,23001910</t>
+    <t>21001501,22001501,23001501,21001502,22001502,23001502,21001503,22001503,23001503,21001504,22001504,23001504,21001505,22001505,23001505,21001507,22001507,23001507,21001509,22001509,23001509,21001510,22001510,23001510</t>
   </si>
   <si>
     <t>200210</t>
@@ -715,10 +679,10 @@
     <t>210</t>
   </si>
   <si>
-    <t>210级装备</t>
-  </si>
-  <si>
-    <t>21002001,21002002,21002003,21002004,21002005,21002007,21002009,21002010,22002001,22002002,22002003,22002004,22002005,22002007,22002009,22002010,23002001,23002002,23002003,23002004,23002005,23002007,23002009,23002010</t>
+    <t>250级装备</t>
+  </si>
+  <si>
+    <t>21002001,22002001,23002001,21002002,22002002,23002002</t>
   </si>
   <si>
     <t>200220</t>
@@ -727,10 +691,7 @@
     <t>220</t>
   </si>
   <si>
-    <t>220级装备</t>
-  </si>
-  <si>
-    <t>21002101,21002102,21002103,21002104,21002105,21002107,21002109,21002110,22002101,22002102,22002103,22002104,22002105,22002107,22002109,22002110,23002101,23002102,23002103,23002104,23002105,23002107,23002109,23002110</t>
+    <t>21002003,22002003,23002003,21002004,22002004,23002004</t>
   </si>
   <si>
     <t>200230</t>
@@ -739,10 +700,7 @@
     <t>230</t>
   </si>
   <si>
-    <t>230级装备</t>
-  </si>
-  <si>
-    <t>21002201,21002202,21002203,21002204,21002205,21002207,21002209,21002210,22002201,22002202,22002203,22002204,22002205,22002207,22002209,22002210,23002201,23002202,23002203,23002204,23002205,23002207,23002209,23002210</t>
+    <t>21002005,22002005,23002005,21002007,22002007,23002007</t>
   </si>
   <si>
     <t>200240</t>
@@ -751,10 +709,7 @@
     <t>240</t>
   </si>
   <si>
-    <t>240级装备</t>
-  </si>
-  <si>
-    <t>21002301,21002302,21002303,21002304,21002305,21002307,21002309,21002310,22002301,22002302,22002303,22002304,22002305,22002307,22002309,22002310,23002301,23002302,23002303,23002304,23002305,23002307,23002309,23002310</t>
+    <t>21002009,22002009,23002009,21002010,22002010,23002010</t>
   </si>
   <si>
     <t>200250</t>
@@ -763,10 +718,7 @@
     <t>250</t>
   </si>
   <si>
-    <t>250级装备</t>
-  </si>
-  <si>
-    <t>21002401,21002402,21002403,21002404,21002405,21002407,21002409,21002410,22002401,22002402,22002403,22002404,22002405,22002407,22002409,22002410,23002401,23002402,23002403,23002404,23002405,23002407,23002409,23002410</t>
+    <t>21002001,22002001,23002001,21002002,22002002,23002002,21002003,22002003,23002003,21002004,22002004,23002004,21002005,22002005,23002005,21002007,22002007,23002007,21002009,22002009,23002009,21002010,22002010,23002010</t>
   </si>
   <si>
     <t>200260</t>
@@ -775,10 +727,10 @@
     <t>260</t>
   </si>
   <si>
-    <t>260级装备</t>
-  </si>
-  <si>
-    <t>21002501,21002502,21002503,21002504,21002505,21002507,21002509,21002510,22002501,22002502,22002503,22002504,22002505,22002507,22002509,22002510,23002501,23002502,23002503,23002504,23002505,23002507,23002509,23002510</t>
+    <t>300级装备</t>
+  </si>
+  <si>
+    <t>21002501,22002501,23002501,21002502,22002502,23002502</t>
   </si>
   <si>
     <t>200270</t>
@@ -787,10 +739,7 @@
     <t>270</t>
   </si>
   <si>
-    <t>270级装备</t>
-  </si>
-  <si>
-    <t>21002601,21002602,21002603,21002604,21002605,21002607,21002609,21002610,22002601,22002602,22002603,22002604,22002605,22002607,22002609,22002610,23002601,23002602,23002603,23002604,23002605,23002607,23002609,23002610</t>
+    <t>21002503,22002503,23002503,21002504,22002504,23002504</t>
   </si>
   <si>
     <t>200280</t>
@@ -799,10 +748,7 @@
     <t>280</t>
   </si>
   <si>
-    <t>280级装备</t>
-  </si>
-  <si>
-    <t>21002701,21002702,21002703,21002704,21002705,21002707,21002709,21002710,22002701,22002702,22002703,22002704,22002705,22002707,22002709,22002710,23002701,23002702,23002703,23002704,23002705,23002707,23002709,23002710</t>
+    <t>21002505,22002505,23002505,21002507,22002507,23002507</t>
   </si>
   <si>
     <t>200290</t>
@@ -811,10 +757,7 @@
     <t>290</t>
   </si>
   <si>
-    <t>290级装备</t>
-  </si>
-  <si>
-    <t>21002801,21002802,21002803,21002804,21002805,21002807,21002809,21002810,22002801,22002802,22002803,22002804,22002805,22002807,22002809,22002810,23002801,23002802,23002803,23002804,23002805,23002807,23002809,23002810</t>
+    <t>21002509,22002509,23002509,21002510,22002510,23002510</t>
   </si>
   <si>
     <t>200300</t>
@@ -823,10 +766,7 @@
     <t>300</t>
   </si>
   <si>
-    <t>300级装备</t>
-  </si>
-  <si>
-    <t>21002901,21002902,21002903,21002904,21002905,21002907,21002909,21002910,22002901,22002902,22002903,22002904,22002905,22002907,22002909,22002910,23002901,23002902,23002903,23002904,23002905,23002907,23002909,23002910</t>
+    <t>21002501,22002501,23002501,21002502,22002502,23002502,21002503,22002503,23002503,21002504,22002504,23002504,21002505,22002505,23002505,21002507,22002507,23002507,21002509,22002509,23002509,21002510,22002510,23002510</t>
   </si>
   <si>
     <t>200310</t>
@@ -835,10 +775,10 @@
     <t>310</t>
   </si>
   <si>
-    <t>310级装备</t>
-  </si>
-  <si>
-    <t>21003001,21003002,21003003,21003004,21003005,21003007,21003009,21003010,22003001,22003002,22003003,22003004,22003005,22003007,22003009,22003010,23003001,23003002,23003003,23003004,23003005,23003007,23003009,23003010</t>
+    <t>350级装备</t>
+  </si>
+  <si>
+    <t>21003001,22003001,23003001,21003002,22003002,23003002</t>
   </si>
   <si>
     <t>200320</t>
@@ -847,10 +787,7 @@
     <t>320</t>
   </si>
   <si>
-    <t>320级装备</t>
-  </si>
-  <si>
-    <t>21003101,21003102,21003103,21003104,21003105,21003107,21003109,21003110,22003101,22003102,22003103,22003104,22003105,22003107,22003109,22003110,23003101,23003102,23003103,23003104,23003105,23003107,23003109,23003110</t>
+    <t>21003003,22003003,23003003,21003004,22003004,23003004</t>
   </si>
   <si>
     <t>200330</t>
@@ -859,10 +796,7 @@
     <t>330</t>
   </si>
   <si>
-    <t>330级装备</t>
-  </si>
-  <si>
-    <t>21003201,21003202,21003203,21003204,21003205,21003207,21003209,21003210,22003201,22003202,22003203,22003204,22003205,22003207,22003209,22003210,23003201,23003202,23003203,23003204,23003205,23003207,23003209,23003210</t>
+    <t>21003005,22003005,23003005,21003007,22003007,23003007</t>
   </si>
   <si>
     <t>200340</t>
@@ -871,10 +805,7 @@
     <t>340</t>
   </si>
   <si>
-    <t>340级装备</t>
-  </si>
-  <si>
-    <t>21003301,21003302,21003303,21003304,21003305,21003307,21003309,21003310,22003301,22003302,22003303,22003304,22003305,22003307,22003309,22003310,23003301,23003302,23003303,23003304,23003305,23003307,23003309,23003310</t>
+    <t>21003009,22003009,23003009,21003010,22003010,23003010</t>
   </si>
   <si>
     <t>200350</t>
@@ -883,10 +814,7 @@
     <t>350</t>
   </si>
   <si>
-    <t>350级装备</t>
-  </si>
-  <si>
-    <t>21003401,21003402,21003403,21003404,21003405,21003407,21003409,21003410,22003401,22003402,22003403,22003404,22003405,22003407,22003409,22003410,23003401,23003402,23003403,23003404,23003405,23003407,23003409,23003410</t>
+    <t>21003001,22003001,23003001,21003002,22003002,23003002,21003003,22003003,23003003,21003004,22003004,23003004,21003005,22003005,23003005,21003007,22003007,23003007,21003009,22003009,23003009,21003010,22003010,23003010</t>
   </si>
   <si>
     <t>200360</t>
@@ -895,10 +823,10 @@
     <t>360</t>
   </si>
   <si>
-    <t>360级装备</t>
-  </si>
-  <si>
-    <t>21003501,21003502,21003503,21003504,21003505,21003507,21003509,21003510,22003501,22003502,22003503,22003504,22003505,22003507,22003509,22003510,23003501,23003502,23003503,23003504,23003505,23003507,23003509,23003510</t>
+    <t>400级装备</t>
+  </si>
+  <si>
+    <t>21003501,22003501,23003501,21003502,22003502,23003502</t>
   </si>
   <si>
     <t>200370</t>
@@ -907,10 +835,7 @@
     <t>370</t>
   </si>
   <si>
-    <t>370级装备</t>
-  </si>
-  <si>
-    <t>21003601,21003602,21003603,21003604,21003605,21003607,21003609,21003610,22003601,22003602,22003603,22003604,22003605,22003607,22003609,22003610,23003601,23003602,23003603,23003604,23003605,23003607,23003609,23003610</t>
+    <t>21003503,22003503,23003503,21003504,22003504,23003504</t>
   </si>
   <si>
     <t>200380</t>
@@ -919,10 +844,7 @@
     <t>380</t>
   </si>
   <si>
-    <t>380级装备</t>
-  </si>
-  <si>
-    <t>21003701,21003702,21003703,21003704,21003705,21003707,21003709,21003710,22003701,22003702,22003703,22003704,22003705,22003707,22003709,22003710,23003701,23003702,23003703,23003704,23003705,23003707,23003709,23003710</t>
+    <t>21003505,22003505,23003505,21003507,22003507,23003507</t>
   </si>
   <si>
     <t>200390</t>
@@ -931,10 +853,7 @@
     <t>390</t>
   </si>
   <si>
-    <t>390级装备</t>
-  </si>
-  <si>
-    <t>21003801,21003802,21003803,21003804,21003805,21003807,21003809,21003810,22003801,22003802,22003803,22003804,22003805,22003807,22003809,22003810,23003801,23003802,23003803,23003804,23003805,23003807,23003809,23003810</t>
+    <t>21003509,22003509,23003509,21003510,22003510,23003510</t>
   </si>
   <si>
     <t>200400</t>
@@ -943,10 +862,7 @@
     <t>400</t>
   </si>
   <si>
-    <t>400级装备</t>
-  </si>
-  <si>
-    <t>21003901,21003902,21003903,21003904,21003905,21003907,21003909,21003910,22003901,22003902,22003903,22003904,22003905,22003907,22003909,22003910,23003901,23003902,23003903,23003904,23003905,23003907,23003909,23003910</t>
+    <t>21003501,22003501,23003501,21003502,22003502,23003502,21003503,22003503,23003503,21003504,22003504,23003504,21003505,22003505,23003505,21003507,22003507,23003507,21003509,22003509,23003509,21003510,22003510,23003510</t>
   </si>
   <si>
     <t>200410</t>
@@ -955,10 +871,10 @@
     <t>410</t>
   </si>
   <si>
-    <t>410级装备</t>
-  </si>
-  <si>
-    <t>21004001,21004002,21004003,21004004,21004005,21004007,21004009,21004010,22004001,22004002,22004003,22004004,22004005,22004007,22004009,22004010,23004001,23004002,23004003,23004004,23004005,23004007,23004009,23004010</t>
+    <t>450级装备</t>
+  </si>
+  <si>
+    <t>21004001,22004001,23004001,21004002,22004002,23004002</t>
   </si>
   <si>
     <t>200420</t>
@@ -967,10 +883,7 @@
     <t>420</t>
   </si>
   <si>
-    <t>420级装备</t>
-  </si>
-  <si>
-    <t>21004101,21004102,21004103,21004104,21004105,21004107,21004109,21004110,22004101,22004102,22004103,22004104,22004105,22004107,22004109,22004110,23004101,23004102,23004103,23004104,23004105,23004107,23004109,23004110</t>
+    <t>21004003,22004003,23004003,21004004,22004004,23004004</t>
   </si>
   <si>
     <t>200430</t>
@@ -979,10 +892,7 @@
     <t>430</t>
   </si>
   <si>
-    <t>430级装备</t>
-  </si>
-  <si>
-    <t>21004201,21004202,21004203,21004204,21004205,21004207,21004209,21004210,22004201,22004202,22004203,22004204,22004205,22004207,22004209,22004210,23004201,23004202,23004203,23004204,23004205,23004207,23004209,23004210</t>
+    <t>21004005,22004005,23004005,21004007,22004007,23004007</t>
   </si>
   <si>
     <t>200440</t>
@@ -991,10 +901,7 @@
     <t>440</t>
   </si>
   <si>
-    <t>440级装备</t>
-  </si>
-  <si>
-    <t>21004301,21004302,21004303,21004304,21004305,21004307,21004309,21004310,22004301,22004302,22004303,22004304,22004305,22004307,22004309,22004310,23004301,23004302,23004303,23004304,23004305,23004307,23004309,23004310</t>
+    <t>21004009,22004009,23004009,21004010,22004010,23004010</t>
   </si>
   <si>
     <t>200450</t>
@@ -1003,10 +910,7 @@
     <t>450</t>
   </si>
   <si>
-    <t>450级装备</t>
-  </si>
-  <si>
-    <t>21004401,21004402,21004403,21004404,21004405,21004407,21004409,21004410,22004401,22004402,22004403,22004404,22004405,22004407,22004409,22004410,23004401,23004402,23004403,23004404,23004405,23004407,23004409,23004410</t>
+    <t>21004001,22004001,23004001,21004002,22004002,23004002,21004003,22004003,23004003,21004004,22004004,23004004,21004005,22004005,23004005,21004007,22004007,23004007,21004009,22004009,23004009,21004010,22004010,23004010</t>
   </si>
   <si>
     <t>200460</t>
@@ -1015,10 +919,10 @@
     <t>460</t>
   </si>
   <si>
-    <t>460级装备</t>
-  </si>
-  <si>
-    <t>21004501,21004502,21004503,21004504,21004505,21004507,21004509,21004510,22004501,22004502,22004503,22004504,22004505,22004507,22004509,22004510,23004501,23004502,23004503,23004504,23004505,23004507,23004509,23004510</t>
+    <t>500级装备</t>
+  </si>
+  <si>
+    <t>21004501,22004501,23004501,21004502,22004502,23004502</t>
   </si>
   <si>
     <t>200470</t>
@@ -1027,10 +931,7 @@
     <t>470</t>
   </si>
   <si>
-    <t>470级装备</t>
-  </si>
-  <si>
-    <t>21004601,21004602,21004603,21004604,21004605,21004607,21004609,21004610,22004601,22004602,22004603,22004604,22004605,22004607,22004609,22004610,23004601,23004602,23004603,23004604,23004605,23004607,23004609,23004610</t>
+    <t>21004503,22004503,23004503,21004504,22004504,23004504</t>
   </si>
   <si>
     <t>200480</t>
@@ -1039,10 +940,7 @@
     <t>480</t>
   </si>
   <si>
-    <t>480级装备</t>
-  </si>
-  <si>
-    <t>21004701,21004702,21004703,21004704,21004705,21004707,21004709,21004710,22004701,22004702,22004703,22004704,22004705,22004707,22004709,22004710,23004701,23004702,23004703,23004704,23004705,23004707,23004709,23004710</t>
+    <t>21004505,22004505,23004505,21004507,22004507,23004507</t>
   </si>
   <si>
     <t>200490</t>
@@ -1051,10 +949,7 @@
     <t>490</t>
   </si>
   <si>
-    <t>490级装备</t>
-  </si>
-  <si>
-    <t>21004801,21004802,21004803,21004804,21004805,21004807,21004809,21004810,22004801,22004802,22004803,22004804,22004805,22004807,22004809,22004810,23004801,23004802,23004803,23004804,23004805,23004807,23004809,23004810</t>
+    <t>21004509,22004509,23004509,21004510,22004510,23004510</t>
   </si>
   <si>
     <t>200500</t>
@@ -1063,10 +958,7 @@
     <t>500</t>
   </si>
   <si>
-    <t>500级装备</t>
-  </si>
-  <si>
-    <t>21004901,21004902,21004903,21004904,21004905,21004907,21004909,21004910,22004901,22004902,22004903,22004904,22004905,22004907,22004909,22004910,23004901,23004902,23004903,23004904,23004905,23004907,23004909,23004910</t>
+    <t>21004501,22004501,23004501,21004502,22004502,23004502,21004503,22004503,23004503,21004504,22004504,23004504,21004505,22004505,23004505,21004507,22004507,23004507,21004509,22004509,23004509,21004510,22004510,23004510</t>
   </si>
   <si>
     <t>200510</t>
@@ -1075,10 +967,10 @@
     <t>510</t>
   </si>
   <si>
-    <t>510级装备</t>
-  </si>
-  <si>
-    <t>21005001,21005002,21005003,21005004,21005005,21005007,21005009,21005010,22005001,22005002,22005003,22005004,22005005,22005007,22005009,22005010,23005001,23005002,23005003,23005004,23005005,23005007,23005009,23005010</t>
+    <t>550级装备</t>
+  </si>
+  <si>
+    <t>21005001,22005001,23005001,21005002,22005002,23005002</t>
   </si>
   <si>
     <t>200520</t>
@@ -1087,10 +979,7 @@
     <t>520</t>
   </si>
   <si>
-    <t>520级装备</t>
-  </si>
-  <si>
-    <t>21005101,21005102,21005103,21005104,21005105,21005107,21005109,21005110,22005101,22005102,22005103,22005104,22005105,22005107,22005109,22005110,23005101,23005102,23005103,23005104,23005105,23005107,23005109,23005110</t>
+    <t>21005003,22005003,23005003,21005004,22005004,23005004</t>
   </si>
   <si>
     <t>200530</t>
@@ -1099,10 +988,7 @@
     <t>530</t>
   </si>
   <si>
-    <t>530级装备</t>
-  </si>
-  <si>
-    <t>21005201,21005202,21005203,21005204,21005205,21005207,21005209,21005210,22005201,22005202,22005203,22005204,22005205,22005207,22005209,22005210,23005201,23005202,23005203,23005204,23005205,23005207,23005209,23005210</t>
+    <t>21005005,22005005,23005005,21005007,22005007,23005007</t>
   </si>
   <si>
     <t>200540</t>
@@ -1111,10 +997,7 @@
     <t>540</t>
   </si>
   <si>
-    <t>540级装备</t>
-  </si>
-  <si>
-    <t>21005301,21005302,21005303,21005304,21005305,21005307,21005309,21005310,22005301,22005302,22005303,22005304,22005305,22005307,22005309,22005310,23005301,23005302,23005303,23005304,23005305,23005307,23005309,23005310</t>
+    <t>21005009,22005009,23005009,21005010,22005010,23005010</t>
   </si>
   <si>
     <t>200550</t>
@@ -1123,10 +1006,7 @@
     <t>550</t>
   </si>
   <si>
-    <t>550级装备</t>
-  </si>
-  <si>
-    <t>21005401,21005402,21005403,21005404,21005405,21005407,21005409,21005410,22005401,22005402,22005403,22005404,22005405,22005407,22005409,22005410,23005401,23005402,23005403,23005404,23005405,23005407,23005409,23005410</t>
+    <t>21005001,22005001,23005001,21005002,22005002,23005002,21005003,22005003,23005003,21005004,22005004,23005004,21005005,22005005,23005005,21005007,22005007,23005007,21005009,22005009,23005009,21005010,22005010,23005010</t>
   </si>
   <si>
     <t>200600</t>
@@ -4725,7 +4605,7 @@
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="17" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4737,7 +4617,7 @@
         <v>43</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -4745,19 +4625,19 @@
       <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>45</v>
+      <c r="I12" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:9">
       <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -4765,19 +4645,19 @@
       <c r="G13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>49</v>
+      <c r="I13" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:9">
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -4785,19 +4665,19 @@
       <c r="G14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>53</v>
+      <c r="I14" s="17" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:9">
       <c r="C15" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>19</v>
@@ -4805,19 +4685,19 @@
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>57</v>
+      <c r="I15" s="17" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:9">
       <c r="C16" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>19</v>
@@ -4825,19 +4705,19 @@
       <c r="G16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>61</v>
+      <c r="I16" s="17" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:9">
       <c r="C17" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>19</v>
@@ -4845,19 +4725,19 @@
       <c r="G17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>65</v>
+      <c r="I17" s="17" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:9">
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>19</v>
@@ -4865,19 +4745,19 @@
       <c r="G18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>69</v>
+      <c r="I18" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:9">
       <c r="C19" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>19</v>
@@ -4885,19 +4765,19 @@
       <c r="G19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>73</v>
+      <c r="I19" s="17" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:9">
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -4905,19 +4785,19 @@
       <c r="G20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>77</v>
+      <c r="I20" s="17" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:9">
       <c r="C21" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>19</v>
@@ -4925,19 +4805,19 @@
       <c r="G21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>81</v>
+      <c r="I21" s="17" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:9">
       <c r="C22" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>19</v>
@@ -4945,19 +4825,19 @@
       <c r="G22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>85</v>
+      <c r="I22" s="17" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:9">
       <c r="C23" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>19</v>
@@ -4965,19 +4845,19 @@
       <c r="G23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>89</v>
+      <c r="I23" s="17" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:9">
       <c r="C24" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>19</v>
@@ -4985,19 +4865,19 @@
       <c r="G24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>93</v>
+      <c r="I24" s="17" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:9">
       <c r="C25" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>19</v>
@@ -5005,19 +4885,19 @@
       <c r="G25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>97</v>
+      <c r="I25" s="17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:9">
       <c r="C26" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>19</v>
@@ -5025,19 +4905,19 @@
       <c r="G26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>101</v>
+      <c r="I26" s="17" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:9">
       <c r="C27" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>19</v>
@@ -5045,19 +4925,19 @@
       <c r="G27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>105</v>
+      <c r="I27" s="17" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:9">
       <c r="C28" s="2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -5065,19 +4945,19 @@
       <c r="G28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>109</v>
+      <c r="I28" s="17" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:9">
       <c r="C29" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -5085,19 +4965,19 @@
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>113</v>
+      <c r="I29" s="17" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:9">
       <c r="C30" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -5105,19 +4985,19 @@
       <c r="G30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>117</v>
+      <c r="I30" s="17" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:9">
       <c r="C31" s="2" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>19</v>
@@ -5125,19 +5005,19 @@
       <c r="G31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>121</v>
+      <c r="I31" s="17" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:9">
       <c r="C32" s="2" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>19</v>
@@ -5145,19 +5025,19 @@
       <c r="G32" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>125</v>
+      <c r="I32" s="17" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:9">
       <c r="C33" s="2" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>19</v>
@@ -5165,19 +5045,19 @@
       <c r="G33" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>129</v>
+      <c r="I33" s="17" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:9">
       <c r="C34" s="2" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>19</v>
@@ -5185,19 +5065,19 @@
       <c r="G34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>133</v>
+      <c r="I34" s="17" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:9">
       <c r="C35" s="2" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>19</v>
@@ -5205,19 +5085,19 @@
       <c r="G35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>137</v>
+      <c r="I35" s="17" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:9">
       <c r="C36" s="2" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>19</v>
@@ -5225,19 +5105,19 @@
       <c r="G36" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>141</v>
+      <c r="I36" s="17" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:9">
       <c r="C37" s="2" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>19</v>
@@ -5245,19 +5125,19 @@
       <c r="G37" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>145</v>
+      <c r="I37" s="17" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:9">
       <c r="C38" s="2" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>19</v>
@@ -5265,19 +5145,19 @@
       <c r="G38" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>149</v>
+      <c r="I38" s="17" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:9">
       <c r="C39" s="2" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>19</v>
@@ -5285,19 +5165,19 @@
       <c r="G39" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I39" s="2" t="s">
-        <v>153</v>
+      <c r="I39" s="17" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:9">
       <c r="C40" s="2" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>19</v>
@@ -5305,19 +5185,19 @@
       <c r="G40" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I40" s="2" t="s">
-        <v>157</v>
+      <c r="I40" s="17" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:9">
       <c r="C41" s="2" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>19</v>
@@ -5325,19 +5205,19 @@
       <c r="G41" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>161</v>
+      <c r="I41" s="17" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:9">
       <c r="C42" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>19</v>
@@ -5345,19 +5225,19 @@
       <c r="G42" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I42" s="2" t="s">
-        <v>165</v>
+      <c r="I42" s="17" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:9">
       <c r="C43" s="2" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>19</v>
@@ -5365,19 +5245,19 @@
       <c r="G43" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>169</v>
+      <c r="I43" s="17" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:9">
       <c r="C44" s="2" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>19</v>
@@ -5385,19 +5265,19 @@
       <c r="G44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>173</v>
+      <c r="I44" s="17" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:9">
       <c r="C45" s="2" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>19</v>
@@ -5405,19 +5285,19 @@
       <c r="G45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>177</v>
+      <c r="I45" s="17" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C46" s="2" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>19</v>
@@ -5425,19 +5305,19 @@
       <c r="G46" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I46" s="2" t="s">
-        <v>181</v>
+      <c r="I46" s="17" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C47" s="2" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>19</v>
@@ -5445,19 +5325,19 @@
       <c r="G47" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>185</v>
+      <c r="I47" s="17" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C48" s="2" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>19</v>
@@ -5465,19 +5345,19 @@
       <c r="G48" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>189</v>
+      <c r="I48" s="17" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C49" s="2" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>19</v>
@@ -5485,19 +5365,19 @@
       <c r="G49" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I49" s="2" t="s">
-        <v>193</v>
+      <c r="I49" s="17" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C50" s="2" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>19</v>
@@ -5505,19 +5385,19 @@
       <c r="G50" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>197</v>
+      <c r="I50" s="17" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C51" s="2" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>19</v>
@@ -5525,19 +5405,19 @@
       <c r="G51" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>201</v>
+      <c r="I51" s="17" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C52" s="2" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>19</v>
@@ -5545,19 +5425,19 @@
       <c r="G52" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>205</v>
+      <c r="I52" s="17" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C53" s="2" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>19</v>
@@ -5565,19 +5445,19 @@
       <c r="G53" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I53" s="2" t="s">
-        <v>209</v>
+      <c r="I53" s="17" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C54" s="2" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>212</v>
+        <v>168</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>19</v>
@@ -5585,19 +5465,19 @@
       <c r="G54" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I54" s="2" t="s">
-        <v>213</v>
+      <c r="I54" s="17" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C55" s="2" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>19</v>
@@ -5605,19 +5485,19 @@
       <c r="G55" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>217</v>
+      <c r="I55" s="17" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C56" s="2" t="s">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>19</v>
@@ -5625,19 +5505,19 @@
       <c r="G56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I56" s="2" t="s">
-        <v>221</v>
+      <c r="I56" s="17" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C57" s="2" t="s">
-        <v>222</v>
+        <v>186</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>19</v>
@@ -5645,19 +5525,19 @@
       <c r="G57" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>225</v>
+      <c r="I57" s="17" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C58" s="2" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
@@ -5665,19 +5545,19 @@
       <c r="G58" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>229</v>
+      <c r="I58" s="17" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C59" s="2" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>231</v>
+        <v>193</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>232</v>
+        <v>184</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
@@ -5685,19 +5565,19 @@
       <c r="G59" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I59" s="2" t="s">
-        <v>233</v>
+      <c r="I59" s="17" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C60" s="2" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
@@ -5705,19 +5585,19 @@
       <c r="G60" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I60" s="2" t="s">
-        <v>237</v>
+      <c r="I60" s="17" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C61" s="17" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
@@ -5726,19 +5606,19 @@
         <v>20</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="J61" s="7"/>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C62" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
@@ -5747,19 +5627,19 @@
         <v>20</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="J62" s="7"/>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C63" s="2" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
@@ -5768,18 +5648,18 @@
         <v>20</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C64" s="2" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
@@ -5788,18 +5668,18 @@
         <v>20</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C65" s="2" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
@@ -5808,18 +5688,18 @@
         <v>20</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C66" s="2" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
@@ -5828,18 +5708,18 @@
         <v>20</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>257</v>
+        <v>217</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C67" s="2" t="s">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>259</v>
+        <v>219</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
@@ -5848,18 +5728,18 @@
         <v>20</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C68" s="2" t="s">
-        <v>261</v>
+        <v>221</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>262</v>
+        <v>222</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>19</v>
@@ -5868,18 +5748,18 @@
         <v>20</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C69" s="2" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>19</v>
@@ -5888,18 +5768,18 @@
         <v>20</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C70" s="2" t="s">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>19</v>
@@ -5908,20 +5788,20 @@
         <v>20</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>269</v>
+        <v>229</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A71" s="10"/>
       <c r="B71" s="10"/>
       <c r="C71" s="10" t="s">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>19</v>
@@ -5931,7 +5811,7 @@
       </c>
       <c r="H71" s="10"/>
       <c r="I71" s="18" t="s">
-        <v>273</v>
+        <v>233</v>
       </c>
       <c r="J71" s="10"/>
     </row>
@@ -5939,13 +5819,13 @@
       <c r="A72" s="10"/>
       <c r="B72" s="10"/>
       <c r="C72" s="10" t="s">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>275</v>
+        <v>235</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="F72" s="10" t="s">
         <v>19</v>
@@ -5955,7 +5835,7 @@
       </c>
       <c r="H72" s="10"/>
       <c r="I72" s="18" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
       <c r="J72" s="10"/>
     </row>
@@ -5963,13 +5843,13 @@
       <c r="A73" s="10"/>
       <c r="B73" s="10"/>
       <c r="C73" s="10" t="s">
-        <v>277</v>
+        <v>237</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>278</v>
+        <v>238</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>19</v>
@@ -5979,7 +5859,7 @@
       </c>
       <c r="H73" s="10"/>
       <c r="I73" s="18" t="s">
-        <v>279</v>
+        <v>239</v>
       </c>
       <c r="J73" s="10"/>
     </row>
@@ -5987,13 +5867,13 @@
       <c r="A74" s="10"/>
       <c r="B74" s="10"/>
       <c r="C74" s="10" t="s">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="F74" s="10" t="s">
         <v>19</v>
@@ -6003,7 +5883,7 @@
       </c>
       <c r="H74" s="10"/>
       <c r="I74" s="18" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="J74" s="16"/>
     </row>
@@ -6011,13 +5891,13 @@
       <c r="A75" s="10"/>
       <c r="B75" s="10"/>
       <c r="C75" s="10" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>19</v>
@@ -6027,19 +5907,19 @@
       </c>
       <c r="H75" s="10"/>
       <c r="I75" s="18" t="s">
-        <v>285</v>
+        <v>245</v>
       </c>
       <c r="J75" s="16"/>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C76" s="18" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>287</v>
+        <v>247</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>19</v>
@@ -6048,18 +5928,18 @@
         <v>20</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>289</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C77" s="18" t="s">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>19</v>
@@ -6068,18 +5948,18 @@
         <v>20</v>
       </c>
       <c r="I77" s="17" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C78" s="18" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>19</v>
@@ -6088,18 +5968,18 @@
         <v>20</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>295</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C79" s="18" t="s">
-        <v>296</v>
+        <v>256</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>297</v>
+        <v>257</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>19</v>
@@ -6108,18 +5988,18 @@
         <v>20</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>298</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C80" s="18" t="s">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>19</v>
@@ -6128,18 +6008,18 @@
         <v>20</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>301</v>
+        <v>261</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C81" s="2" t="s">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>19</v>
@@ -6148,19 +6028,19 @@
         <v>20</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="J81" s="7"/>
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C82" s="2" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>19</v>
@@ -6169,19 +6049,19 @@
         <v>20</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>308</v>
+        <v>268</v>
       </c>
       <c r="J82" s="7"/>
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C83" s="2" t="s">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>19</v>
@@ -6190,18 +6070,18 @@
         <v>20</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>311</v>
+        <v>271</v>
       </c>
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C84" s="2" t="s">
-        <v>312</v>
+        <v>272</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>19</v>
@@ -6210,18 +6090,18 @@
         <v>20</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>314</v>
+        <v>274</v>
       </c>
     </row>
     <row r="85" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C85" s="2" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>316</v>
+        <v>276</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>19</v>
@@ -6230,7 +6110,7 @@
         <v>20</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>317</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86" s="2" customFormat="1" customHeight="1" spans="3:10">
@@ -6241,7 +6121,7 @@
         <v>810</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>19</v>
@@ -6250,7 +6130,7 @@
         <v>20</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>319</v>
+        <v>279</v>
       </c>
       <c r="J86" s="7"/>
     </row>
@@ -6262,7 +6142,7 @@
         <v>820</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>19</v>
@@ -6271,7 +6151,7 @@
         <v>20</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="J87" s="7"/>
     </row>
@@ -6283,7 +6163,7 @@
         <v>830</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>19</v>
@@ -6292,7 +6172,7 @@
         <v>20</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>321</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" customHeight="1" spans="3:9">
@@ -6303,7 +6183,7 @@
         <v>840</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>19</v>
@@ -6312,7 +6192,7 @@
         <v>20</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>322</v>
+        <v>282</v>
       </c>
     </row>
     <row r="90" s="2" customFormat="1" customHeight="1" spans="3:9">
@@ -6323,7 +6203,7 @@
         <v>850</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>19</v>
@@ -6332,7 +6212,7 @@
         <v>20</v>
       </c>
       <c r="I90" s="17" t="s">
-        <v>323</v>
+        <v>283</v>
       </c>
     </row>
     <row r="91" s="2" customFormat="1" customHeight="1" spans="3:10">
@@ -6343,7 +6223,7 @@
         <v>860</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>19</v>
@@ -6352,7 +6232,7 @@
         <v>20</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="J91" s="7"/>
     </row>
@@ -6364,7 +6244,7 @@
         <v>870</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>19</v>
@@ -6373,7 +6253,7 @@
         <v>20</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>326</v>
+        <v>286</v>
       </c>
       <c r="J92" s="7"/>
     </row>
@@ -6385,7 +6265,7 @@
         <v>880</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>19</v>
@@ -6394,7 +6274,7 @@
         <v>20</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>327</v>
+        <v>287</v>
       </c>
     </row>
     <row r="94" s="2" customFormat="1" customHeight="1" spans="3:9">
@@ -6405,7 +6285,7 @@
         <v>890</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>19</v>
@@ -6414,7 +6294,7 @@
         <v>20</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>328</v>
+        <v>288</v>
       </c>
     </row>
     <row r="95" s="2" customFormat="1" customHeight="1" spans="3:9">
@@ -6425,7 +6305,7 @@
         <v>900</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>19</v>
@@ -6434,18 +6314,18 @@
         <v>20</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>329</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C96" s="2" t="s">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>19</v>
@@ -6454,19 +6334,19 @@
         <v>20</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>333</v>
+        <v>293</v>
       </c>
       <c r="J96" s="7"/>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C97" s="2" t="s">
-        <v>334</v>
+        <v>294</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>19</v>
@@ -6475,19 +6355,19 @@
         <v>20</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="J97" s="7"/>
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C98" s="2" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>338</v>
+        <v>298</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>19</v>
@@ -6496,18 +6376,18 @@
         <v>20</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>339</v>
+        <v>299</v>
       </c>
     </row>
     <row r="99" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C99" s="2" t="s">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>341</v>
+        <v>301</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>19</v>
@@ -6516,18 +6396,18 @@
         <v>20</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>342</v>
+        <v>302</v>
       </c>
     </row>
     <row r="100" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C100" s="2" t="s">
-        <v>343</v>
+        <v>303</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>344</v>
+        <v>304</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>19</v>
@@ -6536,18 +6416,18 @@
         <v>20</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>345</v>
+        <v>305</v>
       </c>
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C101" s="2" t="s">
-        <v>346</v>
+        <v>306</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>347</v>
+        <v>307</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>19</v>
@@ -6556,19 +6436,19 @@
         <v>20</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>349</v>
+        <v>309</v>
       </c>
       <c r="J101" s="7"/>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C102" s="2" t="s">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>19</v>
@@ -6577,19 +6457,19 @@
         <v>20</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="J102" s="7"/>
     </row>
     <row r="103" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C103" s="2" t="s">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>354</v>
+        <v>314</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>19</v>
@@ -6598,18 +6478,18 @@
         <v>20</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
     </row>
     <row r="104" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C104" s="2" t="s">
-        <v>356</v>
+        <v>316</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>19</v>
@@ -6618,18 +6498,18 @@
         <v>20</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
     </row>
     <row r="105" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C105" s="2" t="s">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>348</v>
+        <v>308</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>19</v>
@@ -6638,18 +6518,18 @@
         <v>20</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>361</v>
+        <v>321</v>
       </c>
     </row>
     <row r="106" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C106" s="2" t="s">
-        <v>362</v>
+        <v>322</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>363</v>
+        <v>323</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>364</v>
+        <v>324</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>19</v>
@@ -6658,19 +6538,19 @@
         <v>20</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>365</v>
+        <v>325</v>
       </c>
       <c r="J106" s="7"/>
     </row>
     <row r="107" s="2" customFormat="1" customHeight="1" spans="3:10">
       <c r="C107" s="2" t="s">
-        <v>366</v>
+        <v>326</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>367</v>
+        <v>327</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>364</v>
+        <v>324</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>19</v>
@@ -6679,19 +6559,19 @@
         <v>20</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>368</v>
+        <v>328</v>
       </c>
       <c r="J107" s="7"/>
     </row>
     <row r="108" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C108" s="2" t="s">
-        <v>369</v>
+        <v>329</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>364</v>
+        <v>324</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>19</v>
@@ -6700,18 +6580,18 @@
         <v>20</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
     </row>
     <row r="109" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C109" s="2" t="s">
-        <v>372</v>
+        <v>332</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>373</v>
+        <v>333</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>364</v>
+        <v>324</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>19</v>
@@ -6720,18 +6600,18 @@
         <v>20</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>374</v>
+        <v>334</v>
       </c>
     </row>
     <row r="110" s="2" customFormat="1" customHeight="1" spans="3:9">
       <c r="C110" s="2" t="s">
-        <v>375</v>
+        <v>335</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>364</v>
+        <v>324</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>19</v>
@@ -6740,7 +6620,7 @@
         <v>20</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>377</v>
+        <v>337</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:9">
@@ -6748,10 +6628,10 @@
         <v>202001</v>
       </c>
       <c r="D111" s="2">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="F111" s="2">
         <v>1</v>
@@ -6763,7 +6643,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="14" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:9">
@@ -6771,10 +6651,10 @@
         <v>202002</v>
       </c>
       <c r="D112" s="2">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="F112" s="2">
         <v>1</v>
@@ -6786,7 +6666,7 @@
         <v>2</v>
       </c>
       <c r="I112" s="14" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:9">
@@ -6794,10 +6674,10 @@
         <v>202003</v>
       </c>
       <c r="D113" s="2">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>381</v>
+        <v>341</v>
       </c>
       <c r="F113" s="2">
         <v>1</v>
@@ -6809,7 +6689,7 @@
         <v>3</v>
       </c>
       <c r="I113" s="14" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:9">
@@ -6817,10 +6697,10 @@
         <v>202004</v>
       </c>
       <c r="D114" s="2">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>382</v>
+        <v>342</v>
       </c>
       <c r="F114" s="2">
         <v>1</v>
@@ -6832,7 +6712,7 @@
         <v>4</v>
       </c>
       <c r="I114" s="14" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:9">
@@ -6840,10 +6720,10 @@
         <v>202005</v>
       </c>
       <c r="D115" s="2">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
       <c r="F115" s="2">
         <v>1</v>
@@ -6855,7 +6735,7 @@
         <v>5</v>
       </c>
       <c r="I115" s="14" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:9">
@@ -6863,10 +6743,10 @@
         <v>202006</v>
       </c>
       <c r="D116" s="2">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="F116" s="2">
         <v>1</v>
@@ -6878,7 +6758,7 @@
         <v>6</v>
       </c>
       <c r="I116" s="14" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:9">
@@ -6886,10 +6766,10 @@
         <v>202007</v>
       </c>
       <c r="D117" s="2">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>385</v>
+        <v>345</v>
       </c>
       <c r="F117" s="2">
         <v>1</v>
@@ -6901,7 +6781,7 @@
         <v>7</v>
       </c>
       <c r="I117" s="14" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -7002,13 +6882,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="18" t="s">
-        <v>386</v>
+        <v>346</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>387</v>
+        <v>347</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -7017,18 +6897,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>388</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>389</v>
+        <v>349</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -7037,18 +6917,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>391</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>392</v>
+        <v>352</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>393</v>
+        <v>353</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -7057,18 +6937,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>394</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>395</v>
+        <v>355</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>396</v>
+        <v>356</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -7077,18 +6957,18 @@
         <v>20</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>397</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>398</v>
+        <v>358</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>399</v>
+        <v>359</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -7097,18 +6977,18 @@
         <v>20</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>400</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>401</v>
+        <v>361</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>402</v>
+        <v>362</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -7117,18 +6997,18 @@
         <v>20</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>403</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>404</v>
+        <v>364</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -7137,18 +7017,18 @@
         <v>20</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>406</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>407</v>
+        <v>367</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>408</v>
+        <v>368</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -7157,18 +7037,18 @@
         <v>20</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>409</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -7177,18 +7057,18 @@
         <v>20</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>412</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>413</v>
+        <v>373</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>414</v>
+        <v>374</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>19</v>
@@ -7197,18 +7077,18 @@
         <v>20</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>415</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>416</v>
+        <v>376</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>417</v>
+        <v>377</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>19</v>
@@ -7217,18 +7097,18 @@
         <v>5</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>418</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>419</v>
+        <v>379</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>19</v>
@@ -7237,18 +7117,18 @@
         <v>5</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>421</v>
+        <v>381</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>423</v>
+        <v>383</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>19</v>
@@ -7257,18 +7137,18 @@
         <v>5</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>424</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>425</v>
+        <v>385</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>19</v>
@@ -7277,18 +7157,18 @@
         <v>5</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -7297,18 +7177,18 @@
         <v>5</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>430</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>431</v>
+        <v>391</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>432</v>
+        <v>392</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>19</v>
@@ -7317,18 +7197,18 @@
         <v>5</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>433</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>19</v>
@@ -7337,18 +7217,18 @@
         <v>5</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>436</v>
+        <v>396</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>437</v>
+        <v>397</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>19</v>
@@ -7357,18 +7237,18 @@
         <v>5</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>439</v>
+        <v>399</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>441</v>
+        <v>401</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>19</v>
@@ -7377,18 +7257,18 @@
         <v>5</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>442</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>443</v>
+        <v>403</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>444</v>
+        <v>404</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>19</v>
@@ -7397,18 +7277,18 @@
         <v>5</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>445</v>
+        <v>405</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>446</v>
+        <v>406</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>447</v>
+        <v>407</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>19</v>
@@ -7417,18 +7297,18 @@
         <v>5</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>448</v>
+        <v>408</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>449</v>
+        <v>409</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>19</v>
@@ -7437,18 +7317,18 @@
         <v>5</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>451</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>452</v>
+        <v>412</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>453</v>
+        <v>413</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -7457,18 +7337,18 @@
         <v>5</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>454</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>455</v>
+        <v>415</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -7477,18 +7357,18 @@
         <v>5</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>457</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>458</v>
+        <v>418</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>459</v>
+        <v>419</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -7497,18 +7377,18 @@
         <v>5</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>460</v>
+        <v>420</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>461</v>
+        <v>421</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>462</v>
+        <v>422</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>19</v>
@@ -7517,18 +7397,18 @@
         <v>5</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>463</v>
+        <v>423</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>465</v>
+        <v>425</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>19</v>
@@ -7537,18 +7417,18 @@
         <v>5</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>466</v>
+        <v>426</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>467</v>
+        <v>427</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>19</v>
@@ -7557,18 +7437,18 @@
         <v>5</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>469</v>
+        <v>429</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>471</v>
+        <v>431</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>19</v>
@@ -7577,18 +7457,18 @@
         <v>5</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>472</v>
+        <v>432</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>473</v>
+        <v>433</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>474</v>
+        <v>434</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>19</v>
@@ -7597,18 +7477,18 @@
         <v>5</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>475</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>476</v>
+        <v>436</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>477</v>
+        <v>437</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>19</v>
@@ -7617,18 +7497,18 @@
         <v>5</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>478</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>479</v>
+        <v>439</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>19</v>
@@ -7637,18 +7517,18 @@
         <v>5</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>481</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>482</v>
+        <v>442</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>483</v>
+        <v>443</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>19</v>
@@ -7657,18 +7537,18 @@
         <v>5</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>484</v>
+        <v>444</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>485</v>
+        <v>445</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>486</v>
+        <v>446</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>19</v>
@@ -7677,18 +7557,18 @@
         <v>5</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>487</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>488</v>
+        <v>448</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>489</v>
+        <v>449</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>19</v>
@@ -7697,18 +7577,18 @@
         <v>5</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>491</v>
+        <v>451</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>492</v>
+        <v>452</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>19</v>
@@ -7717,18 +7597,18 @@
         <v>5</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>493</v>
+        <v>453</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>494</v>
+        <v>454</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>495</v>
+        <v>455</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>19</v>
@@ -7737,18 +7617,18 @@
         <v>5</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>496</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>497</v>
+        <v>457</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>498</v>
+        <v>458</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>19</v>
@@ -7757,18 +7637,18 @@
         <v>5</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>499</v>
+        <v>459</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>501</v>
+        <v>461</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>19</v>
@@ -7777,18 +7657,18 @@
         <v>5</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>502</v>
+        <v>462</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>503</v>
+        <v>463</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>504</v>
+        <v>464</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>19</v>
@@ -7797,18 +7677,18 @@
         <v>5</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>505</v>
+        <v>465</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>506</v>
+        <v>466</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>507</v>
+        <v>467</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>19</v>
@@ -7817,18 +7697,18 @@
         <v>5</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>508</v>
+        <v>468</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>509</v>
+        <v>469</v>
       </c>
       <c r="D47" s="2">
         <v>0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>19</v>
@@ -7837,18 +7717,18 @@
         <v>5</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>511</v>
+        <v>471</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>512</v>
+        <v>472</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>513</v>
+        <v>473</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>19</v>
@@ -7857,18 +7737,18 @@
         <v>5</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>514</v>
+        <v>474</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>515</v>
+        <v>475</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>516</v>
+        <v>476</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>19</v>
@@ -7877,18 +7757,18 @@
         <v>5</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>517</v>
+        <v>477</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>518</v>
+        <v>478</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>519</v>
+        <v>479</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>19</v>
@@ -7897,18 +7777,18 @@
         <v>5</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>521</v>
+        <v>481</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>522</v>
+        <v>482</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>19</v>
@@ -7917,18 +7797,18 @@
         <v>5</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>523</v>
+        <v>483</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>524</v>
+        <v>484</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>525</v>
+        <v>485</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>19</v>
@@ -7937,18 +7817,18 @@
         <v>5</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>526</v>
+        <v>486</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>527</v>
+        <v>487</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>528</v>
+        <v>488</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>19</v>
@@ -7957,18 +7837,18 @@
         <v>5</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>529</v>
+        <v>489</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>530</v>
+        <v>490</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>531</v>
+        <v>491</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>19</v>
@@ -7977,18 +7857,18 @@
         <v>5</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>532</v>
+        <v>492</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>533</v>
+        <v>493</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>534</v>
+        <v>494</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>19</v>
@@ -7997,18 +7877,18 @@
         <v>5</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>535</v>
+        <v>495</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>536</v>
+        <v>496</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>537</v>
+        <v>497</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>19</v>
@@ -8017,18 +7897,18 @@
         <v>5</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>538</v>
+        <v>498</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>539</v>
+        <v>499</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>19</v>
@@ -8037,18 +7917,18 @@
         <v>5</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>541</v>
+        <v>501</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>542</v>
+        <v>502</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>543</v>
+        <v>503</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
@@ -8057,18 +7937,18 @@
         <v>5</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>544</v>
+        <v>504</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>545</v>
+        <v>505</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>546</v>
+        <v>506</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
@@ -8077,18 +7957,18 @@
         <v>5</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>547</v>
+        <v>507</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>548</v>
+        <v>508</v>
       </c>
       <c r="D60" s="2">
         <v>0</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>549</v>
+        <v>509</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
@@ -8097,18 +7977,18 @@
         <v>5</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>550</v>
+        <v>510</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>551</v>
+        <v>511</v>
       </c>
       <c r="D61" s="2">
         <v>0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>552</v>
+        <v>512</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
@@ -8117,18 +7997,18 @@
         <v>5</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>553</v>
+        <v>513</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>554</v>
+        <v>514</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>555</v>
+        <v>515</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
@@ -8137,18 +8017,18 @@
         <v>5</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>556</v>
+        <v>516</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>557</v>
+        <v>517</v>
       </c>
       <c r="D63" s="2">
         <v>0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>558</v>
+        <v>518</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
@@ -8157,18 +8037,18 @@
         <v>5</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>559</v>
+        <v>519</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
       <c r="C64" s="18" t="s">
-        <v>560</v>
+        <v>520</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>561</v>
+        <v>521</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
@@ -8177,18 +8057,18 @@
         <v>5</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>562</v>
+        <v>522</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
       <c r="C65" s="18" t="s">
-        <v>563</v>
+        <v>523</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>564</v>
+        <v>524</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
@@ -8197,18 +8077,18 @@
         <v>5</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>565</v>
+        <v>525</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
       <c r="C66" s="18" t="s">
-        <v>566</v>
+        <v>526</v>
       </c>
       <c r="D66" s="2">
         <v>0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>567</v>
+        <v>527</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
@@ -8217,18 +8097,18 @@
         <v>5</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>568</v>
+        <v>528</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="18" t="s">
-        <v>569</v>
+        <v>529</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>570</v>
+        <v>530</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
@@ -8237,18 +8117,18 @@
         <v>5</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>571</v>
+        <v>531</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="18" t="s">
-        <v>572</v>
+        <v>532</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>573</v>
+        <v>533</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>19</v>
@@ -8257,18 +8137,18 @@
         <v>5</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>574</v>
+        <v>534</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
       <c r="C69" s="18" t="s">
-        <v>575</v>
+        <v>535</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>576</v>
+        <v>536</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>19</v>
@@ -8277,18 +8157,18 @@
         <v>5</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>577</v>
+        <v>537</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="18" t="s">
-        <v>578</v>
+        <v>538</v>
       </c>
       <c r="D70" s="2">
         <v>0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>579</v>
+        <v>539</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>19</v>
@@ -8297,18 +8177,18 @@
         <v>5</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="18" t="s">
-        <v>581</v>
+        <v>541</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>582</v>
+        <v>542</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>19</v>
@@ -8317,18 +8197,18 @@
         <v>5</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>583</v>
+        <v>543</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
       <c r="C72" s="18" t="s">
-        <v>584</v>
+        <v>544</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>585</v>
+        <v>545</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>19</v>
@@ -8337,18 +8217,18 @@
         <v>5</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>586</v>
+        <v>546</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
       <c r="C73" s="18" t="s">
-        <v>587</v>
+        <v>547</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>19</v>
@@ -8357,18 +8237,18 @@
         <v>5</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>589</v>
+        <v>549</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:8">
       <c r="C74" s="18" t="s">
-        <v>590</v>
+        <v>550</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>19</v>
@@ -8377,18 +8257,18 @@
         <v>5</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>592</v>
+        <v>552</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
       <c r="C75" s="18" t="s">
-        <v>593</v>
+        <v>553</v>
       </c>
       <c r="D75" s="2">
         <v>0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>594</v>
+        <v>554</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>19</v>
@@ -8397,18 +8277,18 @@
         <v>5</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>595</v>
+        <v>555</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
       <c r="C76" s="18" t="s">
-        <v>596</v>
+        <v>556</v>
       </c>
       <c r="D76" s="2">
         <v>0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>597</v>
+        <v>557</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>19</v>
@@ -8417,18 +8297,18 @@
         <v>5</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>598</v>
+        <v>558</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
       <c r="C77" s="18" t="s">
-        <v>599</v>
+        <v>559</v>
       </c>
       <c r="D77" s="2">
         <v>0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>19</v>
@@ -8437,18 +8317,18 @@
         <v>5</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>601</v>
+        <v>561</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:8">
       <c r="C78" s="18" t="s">
-        <v>602</v>
+        <v>562</v>
       </c>
       <c r="D78" s="2">
         <v>0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>603</v>
+        <v>563</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>19</v>
@@ -8457,18 +8337,18 @@
         <v>5</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>604</v>
+        <v>564</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:8">
       <c r="C79" s="18" t="s">
-        <v>605</v>
+        <v>565</v>
       </c>
       <c r="D79" s="2">
         <v>0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>606</v>
+        <v>566</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>19</v>
@@ -8477,18 +8357,18 @@
         <v>5</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>607</v>
+        <v>567</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="C80" s="18" t="s">
-        <v>608</v>
+        <v>568</v>
       </c>
       <c r="D80" s="2">
         <v>0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>609</v>
+        <v>569</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>19</v>
@@ -8497,7 +8377,7 @@
         <v>5</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>610</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -8597,13 +8477,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="18" t="s">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>612</v>
+        <v>572</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -8617,13 +8497,13 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>613</v>
+        <v>573</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>614</v>
+        <v>574</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -8637,13 +8517,13 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>616</v>
+        <v>576</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -8657,13 +8537,13 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>617</v>
+        <v>577</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>618</v>
+        <v>578</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -8677,13 +8557,13 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>619</v>
+        <v>579</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>620</v>
+        <v>580</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -8699,13 +8579,13 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="18" t="s">
-        <v>621</v>
+        <v>581</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>622</v>
+        <v>582</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -8720,13 +8600,13 @@
     </row>
     <row r="12" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>623</v>
+        <v>583</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>624</v>
+        <v>584</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -8740,13 +8620,13 @@
     </row>
     <row r="13" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>625</v>
+        <v>585</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>626</v>
+        <v>586</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -8760,13 +8640,13 @@
     </row>
     <row r="14" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>627</v>
+        <v>587</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>628</v>
+        <v>588</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -8780,13 +8660,13 @@
     </row>
     <row r="15" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>629</v>
+        <v>589</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>19</v>
@@ -8800,13 +8680,13 @@
     </row>
     <row r="16" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>631</v>
+        <v>591</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>632</v>
+        <v>592</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>19</v>
@@ -8820,13 +8700,13 @@
     </row>
     <row r="17" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>633</v>
+        <v>593</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>634</v>
+        <v>594</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>19</v>
@@ -8840,13 +8720,13 @@
     </row>
     <row r="18" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>636</v>
+        <v>596</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>19</v>
@@ -8860,13 +8740,13 @@
     </row>
     <row r="19" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>637</v>
+        <v>597</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>638</v>
+        <v>598</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>19</v>
@@ -8880,13 +8760,13 @@
     </row>
     <row r="20" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>639</v>
+        <v>599</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>640</v>
+        <v>600</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -8900,13 +8780,13 @@
     </row>
     <row r="21" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>641</v>
+        <v>601</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>642</v>
+        <v>602</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>19</v>
@@ -8920,13 +8800,13 @@
     </row>
     <row r="22" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>643</v>
+        <v>603</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>644</v>
+        <v>604</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>19</v>
@@ -8940,13 +8820,13 @@
     </row>
     <row r="23" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>645</v>
+        <v>605</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>646</v>
+        <v>606</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>19</v>
@@ -8960,13 +8840,13 @@
     </row>
     <row r="24" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>647</v>
+        <v>607</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>648</v>
+        <v>608</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>19</v>
@@ -8980,13 +8860,13 @@
     </row>
     <row r="25" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>649</v>
+        <v>609</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>650</v>
+        <v>610</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>19</v>
@@ -9000,13 +8880,13 @@
     </row>
     <row r="26" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>652</v>
+        <v>612</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>19</v>
@@ -9020,13 +8900,13 @@
     </row>
     <row r="27" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>653</v>
+        <v>613</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>654</v>
+        <v>614</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>19</v>
@@ -9040,13 +8920,13 @@
     </row>
     <row r="28" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>655</v>
+        <v>615</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>656</v>
+        <v>616</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -9060,13 +8940,13 @@
     </row>
     <row r="29" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>657</v>
+        <v>617</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>658</v>
+        <v>618</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -9080,13 +8960,13 @@
     </row>
     <row r="30" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>659</v>
+        <v>619</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>660</v>
+        <v>620</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -9100,13 +8980,13 @@
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>661</v>
+        <v>621</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>662</v>
+        <v>622</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>19</v>
@@ -9120,13 +9000,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>663</v>
+        <v>623</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>664</v>
+        <v>624</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>19</v>
@@ -9140,13 +9020,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>665</v>
+        <v>625</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>666</v>
+        <v>626</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>19</v>
@@ -9160,13 +9040,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>667</v>
+        <v>627</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>668</v>
+        <v>628</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>19</v>
@@ -9180,13 +9060,13 @@
     </row>
     <row r="35" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>669</v>
+        <v>629</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>670</v>
+        <v>630</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>19</v>
@@ -9200,13 +9080,13 @@
     </row>
     <row r="36" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>671</v>
+        <v>631</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>672</v>
+        <v>632</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>19</v>
@@ -9220,13 +9100,13 @@
     </row>
     <row r="37" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>673</v>
+        <v>633</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>19</v>
@@ -9240,13 +9120,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>675</v>
+        <v>635</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>676</v>
+        <v>636</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>19</v>
@@ -9260,13 +9140,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>677</v>
+        <v>637</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>678</v>
+        <v>638</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>19</v>
@@ -9280,13 +9160,13 @@
     </row>
     <row r="40" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>679</v>
+        <v>639</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>680</v>
+        <v>640</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>19</v>
@@ -9300,13 +9180,13 @@
     </row>
     <row r="41" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>681</v>
+        <v>641</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>682</v>
+        <v>642</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>19</v>
@@ -9320,13 +9200,13 @@
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>683</v>
+        <v>643</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>684</v>
+        <v>644</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>19</v>
@@ -9340,13 +9220,13 @@
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>685</v>
+        <v>645</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>686</v>
+        <v>646</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>19</v>
@@ -9360,13 +9240,13 @@
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>687</v>
+        <v>647</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>688</v>
+        <v>648</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>19</v>
@@ -9380,13 +9260,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>689</v>
+        <v>649</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>690</v>
+        <v>650</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>19</v>
@@ -9400,13 +9280,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>691</v>
+        <v>651</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>692</v>
+        <v>652</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>19</v>
@@ -9420,13 +9300,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>693</v>
+        <v>653</v>
       </c>
       <c r="D47" s="2">
         <v>0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>694</v>
+        <v>654</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>19</v>
@@ -9440,13 +9320,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>695</v>
+        <v>655</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>696</v>
+        <v>656</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>19</v>
@@ -9460,13 +9340,13 @@
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>697</v>
+        <v>657</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>698</v>
+        <v>658</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>19</v>
@@ -9480,13 +9360,13 @@
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>699</v>
+        <v>659</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>700</v>
+        <v>660</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>19</v>
@@ -9500,13 +9380,13 @@
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>701</v>
+        <v>661</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>702</v>
+        <v>662</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>19</v>
@@ -9520,13 +9400,13 @@
     </row>
     <row r="52" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>703</v>
+        <v>663</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>19</v>
@@ -9540,13 +9420,13 @@
     </row>
     <row r="53" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>705</v>
+        <v>665</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>706</v>
+        <v>666</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>19</v>
@@ -9560,13 +9440,13 @@
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>707</v>
+        <v>667</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>696</v>
+        <v>656</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>19</v>
@@ -9580,13 +9460,13 @@
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>708</v>
+        <v>668</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>709</v>
+        <v>669</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>19</v>
@@ -9600,13 +9480,13 @@
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>710</v>
+        <v>670</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>711</v>
+        <v>671</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>19</v>
@@ -9620,13 +9500,13 @@
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>712</v>
+        <v>672</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>713</v>
+        <v>673</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>19</v>
@@ -9640,13 +9520,13 @@
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>714</v>
+        <v>674</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>715</v>
+        <v>675</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
@@ -9660,13 +9540,13 @@
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>716</v>
+        <v>676</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>717</v>
+        <v>677</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
@@ -9680,13 +9560,13 @@
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>718</v>
+        <v>678</v>
       </c>
       <c r="D60" s="2">
         <v>0</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>719</v>
+        <v>679</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
@@ -9700,13 +9580,13 @@
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>720</v>
+        <v>680</v>
       </c>
       <c r="D61" s="2">
         <v>0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>721</v>
+        <v>681</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
@@ -9720,13 +9600,13 @@
     </row>
     <row r="62" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>722</v>
+        <v>682</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>723</v>
+        <v>683</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
@@ -9740,13 +9620,13 @@
     </row>
     <row r="63" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>724</v>
+        <v>684</v>
       </c>
       <c r="D63" s="2">
         <v>0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>725</v>
+        <v>685</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
@@ -9760,13 +9640,13 @@
     </row>
     <row r="64" customHeight="1" spans="3:8">
       <c r="C64" s="18" t="s">
-        <v>726</v>
+        <v>686</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>727</v>
+        <v>687</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
@@ -9780,13 +9660,13 @@
     </row>
     <row r="65" customHeight="1" spans="3:8">
       <c r="C65" s="18" t="s">
-        <v>728</v>
+        <v>688</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>729</v>
+        <v>689</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
@@ -9800,13 +9680,13 @@
     </row>
     <row r="66" customHeight="1" spans="3:8">
       <c r="C66" s="18" t="s">
-        <v>730</v>
+        <v>690</v>
       </c>
       <c r="D66" s="2">
         <v>0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>731</v>
+        <v>691</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
@@ -9820,13 +9700,13 @@
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="18" t="s">
-        <v>732</v>
+        <v>692</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>733</v>
+        <v>693</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
@@ -9840,13 +9720,13 @@
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="18" t="s">
-        <v>734</v>
+        <v>694</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>735</v>
+        <v>695</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>19</v>
@@ -9860,13 +9740,13 @@
     </row>
     <row r="69" customHeight="1" spans="3:8">
       <c r="C69" s="18" t="s">
-        <v>736</v>
+        <v>696</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>737</v>
+        <v>697</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>19</v>
@@ -9880,13 +9760,13 @@
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="18" t="s">
-        <v>738</v>
+        <v>698</v>
       </c>
       <c r="D70" s="2">
         <v>0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>19</v>
@@ -9900,13 +9780,13 @@
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="18" t="s">
-        <v>740</v>
+        <v>700</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>741</v>
+        <v>701</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>19</v>
@@ -9920,13 +9800,13 @@
     </row>
     <row r="72" customHeight="1" spans="3:8">
       <c r="C72" s="18" t="s">
-        <v>742</v>
+        <v>702</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>743</v>
+        <v>703</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>19</v>
@@ -9940,13 +9820,13 @@
     </row>
     <row r="73" customHeight="1" spans="3:8">
       <c r="C73" s="18" t="s">
-        <v>744</v>
+        <v>704</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>745</v>
+        <v>705</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>19</v>
@@ -9960,13 +9840,13 @@
     </row>
     <row r="74" customHeight="1" spans="3:8">
       <c r="C74" s="18" t="s">
-        <v>746</v>
+        <v>706</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>747</v>
+        <v>707</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>19</v>
@@ -9980,13 +9860,13 @@
     </row>
     <row r="75" customHeight="1" spans="3:8">
       <c r="C75" s="18" t="s">
-        <v>748</v>
+        <v>708</v>
       </c>
       <c r="D75" s="2">
         <v>0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>749</v>
+        <v>709</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>19</v>
@@ -10000,13 +9880,13 @@
     </row>
     <row r="76" customHeight="1" spans="3:8">
       <c r="C76" s="18" t="s">
-        <v>750</v>
+        <v>710</v>
       </c>
       <c r="D76" s="2">
         <v>0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>751</v>
+        <v>711</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>19</v>
@@ -10020,13 +9900,13 @@
     </row>
     <row r="77" customHeight="1" spans="3:8">
       <c r="C77" s="18" t="s">
-        <v>752</v>
+        <v>712</v>
       </c>
       <c r="D77" s="2">
         <v>0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>753</v>
+        <v>713</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>19</v>
@@ -10040,13 +9920,13 @@
     </row>
     <row r="78" customHeight="1" spans="3:8">
       <c r="C78" s="18" t="s">
-        <v>754</v>
+        <v>714</v>
       </c>
       <c r="D78" s="2">
         <v>0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>755</v>
+        <v>715</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>19</v>
@@ -10060,13 +9940,13 @@
     </row>
     <row r="79" customHeight="1" spans="3:8">
       <c r="C79" s="18" t="s">
-        <v>756</v>
+        <v>716</v>
       </c>
       <c r="D79" s="2">
         <v>0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>757</v>
+        <v>717</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>19</v>
@@ -10080,13 +9960,13 @@
     </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="C80" s="18" t="s">
-        <v>758</v>
+        <v>718</v>
       </c>
       <c r="D80" s="2">
         <v>0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>759</v>
+        <v>719</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>19</v>
@@ -10100,13 +9980,13 @@
     </row>
     <row r="81" customHeight="1" spans="3:8">
       <c r="C81" s="18" t="s">
-        <v>760</v>
+        <v>720</v>
       </c>
       <c r="D81" s="2">
         <v>0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>761</v>
+        <v>721</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>19</v>
@@ -10120,13 +10000,13 @@
     </row>
     <row r="82" customHeight="1" spans="3:8">
       <c r="C82" s="18" t="s">
-        <v>762</v>
+        <v>722</v>
       </c>
       <c r="D82" s="2">
         <v>0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>763</v>
+        <v>723</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>19</v>
@@ -10140,13 +10020,13 @@
     </row>
     <row r="83" customHeight="1" spans="3:8">
       <c r="C83" s="18" t="s">
-        <v>764</v>
+        <v>724</v>
       </c>
       <c r="D83" s="2">
         <v>0</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>765</v>
+        <v>725</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>19</v>
@@ -10160,13 +10040,13 @@
     </row>
     <row r="84" customHeight="1" spans="3:8">
       <c r="C84" s="18" t="s">
-        <v>766</v>
+        <v>726</v>
       </c>
       <c r="D84" s="2">
         <v>0</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>767</v>
+        <v>727</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>19</v>
@@ -10180,13 +10060,13 @@
     </row>
     <row r="85" customHeight="1" spans="3:8">
       <c r="C85" s="18" t="s">
-        <v>768</v>
+        <v>728</v>
       </c>
       <c r="D85" s="2">
         <v>0</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>769</v>
+        <v>729</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>19</v>
@@ -10200,13 +10080,13 @@
     </row>
     <row r="86" customHeight="1" spans="3:8">
       <c r="C86" s="18" t="s">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="D86" s="2">
         <v>0</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>771</v>
+        <v>731</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>19</v>
@@ -10220,13 +10100,13 @@
     </row>
     <row r="87" customHeight="1" spans="3:8">
       <c r="C87" s="18" t="s">
-        <v>772</v>
+        <v>732</v>
       </c>
       <c r="D87" s="2">
         <v>0</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>773</v>
+        <v>733</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>19</v>
@@ -10240,13 +10120,13 @@
     </row>
     <row r="88" customHeight="1" spans="3:8">
       <c r="C88" s="18" t="s">
-        <v>774</v>
+        <v>734</v>
       </c>
       <c r="D88" s="2">
         <v>0</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>775</v>
+        <v>735</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>19</v>
@@ -10260,13 +10140,13 @@
     </row>
     <row r="89" customHeight="1" spans="3:8">
       <c r="C89" s="18" t="s">
-        <v>776</v>
+        <v>736</v>
       </c>
       <c r="D89" s="2">
         <v>0</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>777</v>
+        <v>737</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>19</v>
@@ -10280,13 +10160,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:8">
       <c r="C90" s="18" t="s">
-        <v>778</v>
+        <v>738</v>
       </c>
       <c r="D90" s="2">
         <v>0</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>779</v>
+        <v>739</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>19</v>
@@ -10300,13 +10180,13 @@
     </row>
     <row r="91" customHeight="1" spans="3:8">
       <c r="C91" s="18" t="s">
-        <v>780</v>
+        <v>740</v>
       </c>
       <c r="D91" s="2">
         <v>0</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>781</v>
+        <v>741</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>19</v>
@@ -10320,13 +10200,13 @@
     </row>
     <row r="92" customHeight="1" spans="3:8">
       <c r="C92" s="18" t="s">
-        <v>782</v>
+        <v>742</v>
       </c>
       <c r="D92" s="2">
         <v>0</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>783</v>
+        <v>743</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>19</v>
@@ -10340,13 +10220,13 @@
     </row>
     <row r="93" customHeight="1" spans="3:8">
       <c r="C93" s="18" t="s">
-        <v>784</v>
+        <v>744</v>
       </c>
       <c r="D93" s="2">
         <v>0</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>785</v>
+        <v>745</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>19</v>
@@ -10360,13 +10240,13 @@
     </row>
     <row r="94" customHeight="1" spans="3:8">
       <c r="C94" s="18" t="s">
-        <v>786</v>
+        <v>746</v>
       </c>
       <c r="D94" s="2">
         <v>0</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>787</v>
+        <v>747</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>19</v>
@@ -10481,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>788</v>
+        <v>748</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -10501,7 +10381,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>789</v>
+        <v>749</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -10521,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>790</v>
+        <v>750</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -10541,7 +10421,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>791</v>
+        <v>751</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -10561,7 +10441,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>792</v>
+        <v>752</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -10583,7 +10463,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>793</v>
+        <v>753</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -10604,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>794</v>
+        <v>754</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -10624,7 +10504,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>795</v>
+        <v>755</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -10644,7 +10524,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>796</v>
+        <v>756</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -10664,7 +10544,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>797</v>
+        <v>757</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>19</v>
@@ -10684,7 +10564,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>798</v>
+        <v>758</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>19</v>
@@ -10704,7 +10584,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>799</v>
+        <v>759</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>19</v>
@@ -10724,7 +10604,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>19</v>
@@ -10744,7 +10624,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>801</v>
+        <v>761</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>19</v>
@@ -10764,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>802</v>
+        <v>762</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -10784,7 +10664,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>803</v>
+        <v>763</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>19</v>
@@ -10804,7 +10684,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>804</v>
+        <v>764</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>19</v>
@@ -10824,7 +10704,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>805</v>
+        <v>765</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>19</v>
@@ -10844,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>806</v>
+        <v>766</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>19</v>
@@ -10864,7 +10744,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>807</v>
+        <v>767</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>19</v>
@@ -10884,7 +10764,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>808</v>
+        <v>768</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>19</v>
@@ -10907,7 +10787,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>809</v>
+        <v>769</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -10927,7 +10807,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>810</v>
+        <v>770</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -10947,7 +10827,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>811</v>
+        <v>771</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -10967,7 +10847,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>812</v>
+        <v>772</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>19</v>
@@ -10987,7 +10867,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>813</v>
+        <v>773</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>19</v>
@@ -11007,7 +10887,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>814</v>
+        <v>774</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>19</v>
@@ -11027,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>815</v>
+        <v>775</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>19</v>
@@ -11136,13 +11016,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="18" t="s">
-        <v>816</v>
+        <v>776</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>817</v>
+        <v>777</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11156,13 +11036,13 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>818</v>
+        <v>778</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>819</v>
+        <v>779</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11176,13 +11056,13 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>820</v>
+        <v>780</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>821</v>
+        <v>781</v>
       </c>
       <c r="F8" s="2">
         <v>50</v>
@@ -11196,13 +11076,13 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>822</v>
+        <v>782</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>823</v>
+        <v>783</v>
       </c>
       <c r="F9" s="2">
         <v>20</v>
@@ -11216,13 +11096,13 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>824</v>
+        <v>784</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>825</v>
+        <v>785</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -11236,13 +11116,13 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>826</v>
+        <v>786</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>827</v>
+        <v>787</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -11251,18 +11131,18 @@
         <v>3</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>351</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>828</v>
+        <v>788</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>829</v>
+        <v>789</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -11276,13 +11156,13 @@
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>830</v>
+        <v>790</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>831</v>
+        <v>791</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -11291,18 +11171,18 @@
         <v>3</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>832</v>
+        <v>792</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>833</v>
+        <v>793</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>834</v>
+        <v>794</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -11311,18 +11191,18 @@
         <v>3</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>835</v>
+        <v>795</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>836</v>
+        <v>796</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>837</v>
+        <v>797</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -11331,18 +11211,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>838</v>
+        <v>798</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>839</v>
+        <v>799</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>821</v>
+        <v>781</v>
       </c>
       <c r="F16" s="2">
         <v>100</v>
@@ -11356,13 +11236,13 @@
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>840</v>
+        <v>800</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>823</v>
+        <v>783</v>
       </c>
       <c r="F17" s="2">
         <v>40</v>
@@ -11376,13 +11256,13 @@
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>841</v>
+        <v>801</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>821</v>
+        <v>781</v>
       </c>
       <c r="F18" s="2">
         <v>200</v>
@@ -11396,13 +11276,13 @@
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>842</v>
+        <v>802</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>823</v>
+        <v>783</v>
       </c>
       <c r="F19" s="2">
         <v>80</v>
@@ -11416,13 +11296,13 @@
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>843</v>
+        <v>803</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>844</v>
+        <v>804</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -11436,13 +11316,13 @@
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>845</v>
+        <v>805</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>821</v>
+        <v>781</v>
       </c>
       <c r="F21" s="2">
         <v>500</v>
@@ -11456,13 +11336,13 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>846</v>
+        <v>806</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>823</v>
+        <v>783</v>
       </c>
       <c r="F22" s="2">
         <v>200</v>
@@ -11476,113 +11356,113 @@
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>847</v>
+        <v>807</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>849</v>
+        <v>809</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>851</v>
+        <v>811</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>852</v>
+        <v>812</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>853</v>
+        <v>813</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>854</v>
+        <v>814</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>855</v>
+        <v>815</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>856</v>
+        <v>816</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>857</v>
+        <v>817</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>858</v>
+        <v>818</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>859</v>
+        <v>819</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>860</v>
+        <v>820</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>861</v>
+        <v>821</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>862</v>
+        <v>822</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>863</v>
+        <v>823</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>860</v>
+        <v>820</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>864</v>
+        <v>824</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>865</v>
+        <v>825</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>866</v>
+        <v>826</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -11591,18 +11471,18 @@
         <v>3</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>867</v>
+        <v>827</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>868</v>
+        <v>828</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>869</v>
+        <v>829</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -11611,18 +11491,18 @@
         <v>3</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>870</v>
+        <v>830</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>871</v>
+        <v>831</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>872</v>
+        <v>832</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -11631,18 +11511,18 @@
         <v>3</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>873</v>
+        <v>833</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>874</v>
+        <v>834</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>817</v>
+        <v>777</v>
       </c>
       <c r="F31" s="2">
         <v>2</v>
@@ -11656,13 +11536,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>875</v>
+        <v>835</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>819</v>
+        <v>779</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -11676,13 +11556,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>876</v>
+        <v>836</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>821</v>
+        <v>781</v>
       </c>
       <c r="F33" s="2">
         <v>200</v>
@@ -11696,13 +11576,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>823</v>
+        <v>783</v>
       </c>
       <c r="F34" s="2">
         <v>100</v>
@@ -11716,53 +11596,53 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>878</v>
+        <v>838</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>881</v>
+        <v>841</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>882</v>
+        <v>842</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="F36" s="2">
         <v>15</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>881</v>
+        <v>841</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>883</v>
+        <v>843</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>884</v>
+        <v>844</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>19</v>
@@ -11776,13 +11656,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>885</v>
+        <v>845</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>821</v>
+        <v>781</v>
       </c>
       <c r="F38" s="2">
         <v>1000</v>
@@ -11796,13 +11676,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>886</v>
+        <v>846</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>823</v>
+        <v>783</v>
       </c>
       <c r="F39" s="2">
         <v>300</v>
@@ -11816,13 +11696,13 @@
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>887</v>
+        <v>847</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>848</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>888</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -11831,7 +11711,7 @@
         <v>5</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>889</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -11931,13 +11811,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>890</v>
+        <v>850</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>891</v>
+        <v>851</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11946,18 +11826,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>892</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>893</v>
+        <v>853</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>894</v>
+        <v>854</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11966,18 +11846,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>895</v>
+        <v>855</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>896</v>
+        <v>856</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>897</v>
+        <v>857</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -11986,18 +11866,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>898</v>
+        <v>858</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>899</v>
+        <v>859</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>900</v>
+        <v>860</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -12006,18 +11886,18 @@
         <v>20</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>901</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>902</v>
+        <v>862</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>903</v>
+        <v>863</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -12026,18 +11906,18 @@
         <v>17</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>904</v>
+        <v>864</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="17" t="s">
-        <v>905</v>
+        <v>865</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>903</v>
+        <v>863</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -12046,18 +11926,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>906</v>
+        <v>866</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
-        <v>907</v>
+        <v>867</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>903</v>
+        <v>863</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -12066,18 +11946,18 @@
         <v>17</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>908</v>
+        <v>868</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>909</v>
+        <v>869</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>903</v>
+        <v>863</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -12086,187 +11966,187 @@
         <v>17</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>910</v>
+        <v>870</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="17" t="s">
-        <v>347</v>
+        <v>307</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>911</v>
+        <v>871</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>913</v>
+        <v>873</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>914</v>
+        <v>874</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>915</v>
+        <v>875</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>916</v>
+        <v>876</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>917</v>
+        <v>877</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>918</v>
+        <v>878</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>916</v>
+        <v>876</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>919</v>
+        <v>879</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>920</v>
+        <v>880</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>921</v>
+        <v>881</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="17" t="s">
-        <v>922</v>
+        <v>882</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>923</v>
+        <v>883</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>924</v>
+        <v>884</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="17" t="s">
-        <v>925</v>
+        <v>885</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>926</v>
+        <v>886</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>927</v>
+        <v>887</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="17" t="s">
-        <v>928</v>
+        <v>888</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>879</v>
+        <v>839</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>880</v>
+        <v>840</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>881</v>
+        <v>841</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="17" t="s">
-        <v>929</v>
+        <v>889</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>930</v>
+        <v>890</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>931</v>
+        <v>891</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>932</v>
+        <v>892</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>933</v>
+        <v>893</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>934</v>
+        <v>894</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="8:8">
@@ -12277,402 +12157,402 @@
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>935</v>
+        <v>895</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>853</v>
+        <v>813</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>854</v>
+        <v>814</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="17" t="s">
-        <v>936</v>
+        <v>896</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>849</v>
+        <v>809</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>851</v>
+        <v>811</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>937</v>
+        <v>897</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>938</v>
+        <v>898</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>939</v>
+        <v>899</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>856</v>
+        <v>816</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>857</v>
+        <v>817</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>941</v>
+        <v>901</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>942</v>
+        <v>902</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>943</v>
+        <v>903</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>944</v>
+        <v>904</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>945</v>
+        <v>905</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>946</v>
+        <v>906</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>947</v>
+        <v>907</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>948</v>
+        <v>908</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>949</v>
+        <v>909</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>951</v>
+        <v>911</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>952</v>
+        <v>912</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="17" t="s">
-        <v>835</v>
+        <v>795</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>953</v>
+        <v>913</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>954</v>
+        <v>914</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="17" t="s">
-        <v>870</v>
+        <v>830</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>955</v>
+        <v>915</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>956</v>
+        <v>916</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="17" t="s">
-        <v>957</v>
+        <v>917</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>958</v>
+        <v>918</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>959</v>
+        <v>919</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="17" t="s">
-        <v>960</v>
+        <v>920</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>961</v>
+        <v>921</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>962</v>
+        <v>922</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>963</v>
+        <v>923</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>964</v>
+        <v>924</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>965</v>
+        <v>925</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>967</v>
+        <v>927</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H44" s="21" t="s">
-        <v>968</v>
+        <v>928</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>969</v>
+        <v>929</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>970</v>
+        <v>930</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>971</v>
+        <v>931</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>972</v>
+        <v>932</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>973</v>
+        <v>933</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>974</v>
+        <v>934</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>975</v>
+        <v>935</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>976</v>
+        <v>936</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>977</v>
+        <v>937</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>978</v>
+        <v>938</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>979</v>
+        <v>939</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>981</v>
+        <v>941</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>982</v>
+        <v>942</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>983</v>
+        <v>943</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>984</v>
+        <v>944</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>985</v>
+        <v>945</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>986</v>
+        <v>946</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:8">
@@ -12685,82 +12565,82 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="17" t="s">
-        <v>987</v>
+        <v>947</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>859</v>
+        <v>819</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>860</v>
+        <v>820</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>861</v>
+        <v>821</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>988</v>
+        <v>948</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>863</v>
+        <v>823</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>860</v>
+        <v>820</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>864</v>
+        <v>824</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>989</v>
+        <v>949</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>990</v>
+        <v>950</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>991</v>
+        <v>951</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>992</v>
+        <v>952</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>993</v>
+        <v>953</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>912</v>
+        <v>872</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>994</v>
+        <v>954</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:8">
@@ -12773,182 +12653,182 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="10" t="s">
-        <v>995</v>
+        <v>955</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>996</v>
+        <v>956</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>998</v>
+        <v>958</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>999</v>
+        <v>959</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>1001</v>
+        <v>961</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>1002</v>
+        <v>962</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1003</v>
+        <v>963</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>1004</v>
+        <v>964</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>1005</v>
+        <v>965</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1006</v>
+        <v>966</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>1007</v>
+        <v>967</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>1008</v>
+        <v>968</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1009</v>
+        <v>969</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>1010</v>
+        <v>970</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>1011</v>
+        <v>971</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1012</v>
+        <v>972</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>1013</v>
+        <v>973</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>1014</v>
+        <v>974</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1015</v>
+        <v>975</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>1016</v>
+        <v>976</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1017</v>
+        <v>977</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1018</v>
+        <v>978</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="H65" s="21" t="s">
-        <v>1019</v>
+        <v>979</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1020</v>
+        <v>980</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1021</v>
+        <v>981</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="H66" s="21" t="s">
-        <v>1022</v>
+        <v>982</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12959,16 +12839,16 @@
         <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1023</v>
+        <v>983</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>997</v>
+        <v>957</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>1024</v>
+        <v>984</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="988">
   <si>
     <t>_id</t>
   </si>
@@ -3098,6 +3098,15 @@
   </si>
   <si>
     <t>4016</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>口粮</t>
+  </si>
+  <si>
+    <t>4022</t>
   </si>
   <si>
     <t>2000</t>
@@ -12149,15 +12158,32 @@
         <v>894</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="8:8">
-      <c r="H24" s="7"/>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C24" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>872</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>897</v>
+      </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="8:8">
       <c r="H25" s="7"/>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>808</v>
@@ -12177,7 +12203,7 @@
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="17" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>808</v>
@@ -12197,13 +12223,13 @@
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>19</v>
@@ -12212,12 +12238,12 @@
         <v>810</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>808</v>
@@ -12237,13 +12263,13 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>19</v>
@@ -12252,18 +12278,18 @@
         <v>810</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>19</v>
@@ -12272,18 +12298,18 @@
         <v>810</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>19</v>
@@ -12292,18 +12318,18 @@
         <v>810</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>19</v>
@@ -12312,7 +12338,7 @@
         <v>810</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12323,7 +12349,7 @@
         <v>808</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>19</v>
@@ -12332,7 +12358,7 @@
         <v>810</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12343,7 +12369,7 @@
         <v>808</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>19</v>
@@ -12352,18 +12378,18 @@
         <v>810</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="17" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="F41" s="17" t="s">
         <v>19</v>
@@ -12372,18 +12398,18 @@
         <v>810</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="17" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>19</v>
@@ -12392,18 +12418,18 @@
         <v>810</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>19</v>
@@ -12412,18 +12438,18 @@
         <v>810</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>19</v>
@@ -12432,18 +12458,18 @@
         <v>810</v>
       </c>
       <c r="H44" s="21" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>19</v>
@@ -12452,18 +12478,18 @@
         <v>810</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>19</v>
@@ -12472,18 +12498,18 @@
         <v>810</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>19</v>
@@ -12492,18 +12518,18 @@
         <v>810</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>19</v>
@@ -12512,18 +12538,18 @@
         <v>810</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>19</v>
@@ -12532,18 +12558,18 @@
         <v>810</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>19</v>
@@ -12552,7 +12578,7 @@
         <v>810</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:8">
@@ -12565,7 +12591,7 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="17" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>808</v>
@@ -12585,7 +12611,7 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>808</v>
@@ -12605,13 +12631,13 @@
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>19</v>
@@ -12620,18 +12646,18 @@
         <v>872</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>19</v>
@@ -12640,7 +12666,7 @@
         <v>872</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:8">
@@ -12653,182 +12679,182 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="10" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>957</v>
-      </c>
       <c r="H59" s="17" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H65" s="21" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D66" s="17" t="s">
         <v>49</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H66" s="21" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12839,16 +12865,16 @@
         <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="1009">
   <si>
     <t>_id</t>
   </si>
@@ -2963,6 +2963,69 @@
   </si>
   <si>
     <t>4021</t>
+  </si>
+  <si>
+    <t>220101</t>
+  </si>
+  <si>
+    <t>白色宠物</t>
+  </si>
+  <si>
+    <t>4201</t>
+  </si>
+  <si>
+    <t>220102</t>
+  </si>
+  <si>
+    <t>绿色宠物</t>
+  </si>
+  <si>
+    <t>4202</t>
+  </si>
+  <si>
+    <t>220103</t>
+  </si>
+  <si>
+    <t>蓝色宠物</t>
+  </si>
+  <si>
+    <t>4203</t>
+  </si>
+  <si>
+    <t>220104</t>
+  </si>
+  <si>
+    <t>紫色宠物</t>
+  </si>
+  <si>
+    <t>4204</t>
+  </si>
+  <si>
+    <t>220105</t>
+  </si>
+  <si>
+    <t>橙色宠物</t>
+  </si>
+  <si>
+    <t>4205</t>
+  </si>
+  <si>
+    <t>220106</t>
+  </si>
+  <si>
+    <t>红色宠物</t>
+  </si>
+  <si>
+    <t>4206</t>
+  </si>
+  <si>
+    <t>220107</t>
+  </si>
+  <si>
+    <t>金色宠物</t>
+  </si>
+  <si>
+    <t>4207</t>
   </si>
   <si>
     <t>101</t>
@@ -3389,7 +3452,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3435,6 +3498,12 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF05073B"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -3922,16 +3991,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3940,119 +4006,122 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4082,6 +4151,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
@@ -4614,7 +4684,7 @@
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="18" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4634,7 +4704,7 @@
       <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="18" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4654,7 +4724,7 @@
       <c r="G13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="18" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4674,7 +4744,7 @@
       <c r="G14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="18" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4694,7 +4764,7 @@
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="I15" s="18" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4714,7 +4784,7 @@
       <c r="G16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="18" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4734,7 +4804,7 @@
       <c r="G17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="18" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4754,7 +4824,7 @@
       <c r="G18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I18" s="18" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4774,7 +4844,7 @@
       <c r="G19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I19" s="18" t="s">
         <v>66</v>
       </c>
     </row>
@@ -4794,7 +4864,7 @@
       <c r="G20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="18" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4814,7 +4884,7 @@
       <c r="G21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="18" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4834,7 +4904,7 @@
       <c r="G22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I22" s="18" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4854,7 +4924,7 @@
       <c r="G23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="17" t="s">
+      <c r="I23" s="18" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4874,7 +4944,7 @@
       <c r="G24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I24" s="17" t="s">
+      <c r="I24" s="18" t="s">
         <v>82</v>
       </c>
     </row>
@@ -4894,7 +4964,7 @@
       <c r="G25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="I25" s="18" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4914,7 +4984,7 @@
       <c r="G26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="17" t="s">
+      <c r="I26" s="18" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4934,7 +5004,7 @@
       <c r="G27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="17" t="s">
+      <c r="I27" s="18" t="s">
         <v>92</v>
       </c>
     </row>
@@ -4954,7 +5024,7 @@
       <c r="G28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="17" t="s">
+      <c r="I28" s="18" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4974,7 +5044,7 @@
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I29" s="17" t="s">
+      <c r="I29" s="18" t="s">
         <v>98</v>
       </c>
     </row>
@@ -4994,7 +5064,7 @@
       <c r="G30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I30" s="17" t="s">
+      <c r="I30" s="18" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5014,7 +5084,7 @@
       <c r="G31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I31" s="18" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5034,7 +5104,7 @@
       <c r="G32" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I32" s="17" t="s">
+      <c r="I32" s="18" t="s">
         <v>108</v>
       </c>
     </row>
@@ -5054,7 +5124,7 @@
       <c r="G33" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="18" t="s">
         <v>111</v>
       </c>
     </row>
@@ -5074,7 +5144,7 @@
       <c r="G34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I34" s="17" t="s">
+      <c r="I34" s="18" t="s">
         <v>114</v>
       </c>
     </row>
@@ -5094,7 +5164,7 @@
       <c r="G35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="I35" s="18" t="s">
         <v>117</v>
       </c>
     </row>
@@ -5114,7 +5184,7 @@
       <c r="G36" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I36" s="17" t="s">
+      <c r="I36" s="18" t="s">
         <v>121</v>
       </c>
     </row>
@@ -5134,7 +5204,7 @@
       <c r="G37" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I37" s="17" t="s">
+      <c r="I37" s="18" t="s">
         <v>124</v>
       </c>
     </row>
@@ -5154,7 +5224,7 @@
       <c r="G38" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I38" s="17" t="s">
+      <c r="I38" s="18" t="s">
         <v>127</v>
       </c>
     </row>
@@ -5174,7 +5244,7 @@
       <c r="G39" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I39" s="17" t="s">
+      <c r="I39" s="18" t="s">
         <v>130</v>
       </c>
     </row>
@@ -5194,7 +5264,7 @@
       <c r="G40" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I40" s="17" t="s">
+      <c r="I40" s="18" t="s">
         <v>133</v>
       </c>
     </row>
@@ -5214,7 +5284,7 @@
       <c r="G41" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I41" s="17" t="s">
+      <c r="I41" s="18" t="s">
         <v>137</v>
       </c>
     </row>
@@ -5234,7 +5304,7 @@
       <c r="G42" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I42" s="17" t="s">
+      <c r="I42" s="18" t="s">
         <v>140</v>
       </c>
     </row>
@@ -5254,7 +5324,7 @@
       <c r="G43" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I43" s="17" t="s">
+      <c r="I43" s="18" t="s">
         <v>143</v>
       </c>
     </row>
@@ -5274,7 +5344,7 @@
       <c r="G44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="17" t="s">
+      <c r="I44" s="18" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5294,7 +5364,7 @@
       <c r="G45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I45" s="17" t="s">
+      <c r="I45" s="18" t="s">
         <v>149</v>
       </c>
     </row>
@@ -5314,7 +5384,7 @@
       <c r="G46" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I46" s="17" t="s">
+      <c r="I46" s="18" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5334,7 +5404,7 @@
       <c r="G47" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I47" s="17" t="s">
+      <c r="I47" s="18" t="s">
         <v>156</v>
       </c>
     </row>
@@ -5354,7 +5424,7 @@
       <c r="G48" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I48" s="17" t="s">
+      <c r="I48" s="18" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5374,7 +5444,7 @@
       <c r="G49" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I49" s="17" t="s">
+      <c r="I49" s="18" t="s">
         <v>162</v>
       </c>
     </row>
@@ -5394,7 +5464,7 @@
       <c r="G50" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I50" s="17" t="s">
+      <c r="I50" s="18" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5414,7 +5484,7 @@
       <c r="G51" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="I51" s="18" t="s">
         <v>169</v>
       </c>
     </row>
@@ -5434,7 +5504,7 @@
       <c r="G52" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I52" s="17" t="s">
+      <c r="I52" s="18" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5454,7 +5524,7 @@
       <c r="G53" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I53" s="17" t="s">
+      <c r="I53" s="18" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5474,7 +5544,7 @@
       <c r="G54" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I54" s="17" t="s">
+      <c r="I54" s="18" t="s">
         <v>178</v>
       </c>
     </row>
@@ -5494,7 +5564,7 @@
       <c r="G55" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I55" s="17" t="s">
+      <c r="I55" s="18" t="s">
         <v>181</v>
       </c>
     </row>
@@ -5514,7 +5584,7 @@
       <c r="G56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I56" s="17" t="s">
+      <c r="I56" s="18" t="s">
         <v>185</v>
       </c>
     </row>
@@ -5534,7 +5604,7 @@
       <c r="G57" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I57" s="17" t="s">
+      <c r="I57" s="18" t="s">
         <v>188</v>
       </c>
     </row>
@@ -5554,7 +5624,7 @@
       <c r="G58" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I58" s="17" t="s">
+      <c r="I58" s="18" t="s">
         <v>191</v>
       </c>
     </row>
@@ -5574,7 +5644,7 @@
       <c r="G59" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I59" s="17" t="s">
+      <c r="I59" s="18" t="s">
         <v>194</v>
       </c>
     </row>
@@ -5594,15 +5664,15 @@
       <c r="G60" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I60" s="17" t="s">
+      <c r="I60" s="18" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="18" t="s">
         <v>199</v>
       </c>
       <c r="E61" s="2" t="s">
@@ -5623,7 +5693,7 @@
       <c r="C62" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="18" t="s">
         <v>203</v>
       </c>
       <c r="E62" s="2" t="s">
@@ -5644,7 +5714,7 @@
       <c r="C63" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="18" t="s">
         <v>206</v>
       </c>
       <c r="E63" s="2" t="s">
@@ -5664,7 +5734,7 @@
       <c r="C64" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="18" t="s">
         <v>209</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -5704,7 +5774,7 @@
       <c r="C66" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="18" t="s">
         <v>215</v>
       </c>
       <c r="E66" s="2" t="s">
@@ -5724,7 +5794,7 @@
       <c r="C67" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="18" t="s">
         <v>219</v>
       </c>
       <c r="E67" s="2" t="s">
@@ -5744,7 +5814,7 @@
       <c r="C68" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="18" t="s">
         <v>222</v>
       </c>
       <c r="E68" s="2" t="s">
@@ -5764,7 +5834,7 @@
       <c r="C69" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="18" t="s">
         <v>225</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -5784,7 +5854,7 @@
       <c r="C70" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="18" t="s">
         <v>228</v>
       </c>
       <c r="E70" s="2" t="s">
@@ -5806,7 +5876,7 @@
       <c r="C71" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="D71" s="17" t="s">
+      <c r="D71" s="18" t="s">
         <v>231</v>
       </c>
       <c r="E71" s="10" t="s">
@@ -5819,7 +5889,7 @@
         <v>20</v>
       </c>
       <c r="H71" s="10"/>
-      <c r="I71" s="18" t="s">
+      <c r="I71" s="19" t="s">
         <v>233</v>
       </c>
       <c r="J71" s="10"/>
@@ -5830,7 +5900,7 @@
       <c r="C72" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="18" t="s">
         <v>235</v>
       </c>
       <c r="E72" s="10" t="s">
@@ -5843,7 +5913,7 @@
         <v>20</v>
       </c>
       <c r="H72" s="10"/>
-      <c r="I72" s="18" t="s">
+      <c r="I72" s="19" t="s">
         <v>236</v>
       </c>
       <c r="J72" s="10"/>
@@ -5854,7 +5924,7 @@
       <c r="C73" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="D73" s="17" t="s">
+      <c r="D73" s="18" t="s">
         <v>238</v>
       </c>
       <c r="E73" s="10" t="s">
@@ -5867,7 +5937,7 @@
         <v>20</v>
       </c>
       <c r="H73" s="10"/>
-      <c r="I73" s="18" t="s">
+      <c r="I73" s="19" t="s">
         <v>239</v>
       </c>
       <c r="J73" s="10"/>
@@ -5878,7 +5948,7 @@
       <c r="C74" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="D74" s="17" t="s">
+      <c r="D74" s="18" t="s">
         <v>241</v>
       </c>
       <c r="E74" s="10" t="s">
@@ -5891,10 +5961,10 @@
         <v>20</v>
       </c>
       <c r="H74" s="10"/>
-      <c r="I74" s="18" t="s">
+      <c r="I74" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="J74" s="16"/>
+      <c r="J74" s="17"/>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A75" s="10"/>
@@ -5902,7 +5972,7 @@
       <c r="C75" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="D75" s="17" t="s">
+      <c r="D75" s="18" t="s">
         <v>244</v>
       </c>
       <c r="E75" s="10" t="s">
@@ -5915,16 +5985,16 @@
         <v>20</v>
       </c>
       <c r="H75" s="10"/>
-      <c r="I75" s="18" t="s">
+      <c r="I75" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="J75" s="16"/>
+      <c r="J75" s="17"/>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C76" s="18" t="s">
+      <c r="C76" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="D76" s="17" t="s">
+      <c r="D76" s="18" t="s">
         <v>247</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -5936,15 +6006,15 @@
       <c r="G76" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I76" s="17" t="s">
+      <c r="I76" s="18" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C77" s="18" t="s">
+      <c r="C77" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="D77" s="17" t="s">
+      <c r="D77" s="18" t="s">
         <v>251</v>
       </c>
       <c r="E77" s="2" t="s">
@@ -5956,15 +6026,15 @@
       <c r="G77" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I77" s="17" t="s">
+      <c r="I77" s="18" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C78" s="18" t="s">
+      <c r="C78" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="D78" s="17" t="s">
+      <c r="D78" s="18" t="s">
         <v>254</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -5976,15 +6046,15 @@
       <c r="G78" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I78" s="17" t="s">
+      <c r="I78" s="18" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C79" s="18" t="s">
+      <c r="C79" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D79" s="18" t="s">
         <v>257</v>
       </c>
       <c r="E79" s="2" t="s">
@@ -5996,15 +6066,15 @@
       <c r="G79" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I79" s="17" t="s">
+      <c r="I79" s="18" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C80" s="18" t="s">
+      <c r="C80" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="D80" s="17" t="s">
+      <c r="D80" s="18" t="s">
         <v>260</v>
       </c>
       <c r="E80" s="2" t="s">
@@ -6016,7 +6086,7 @@
       <c r="G80" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I80" s="17" t="s">
+      <c r="I80" s="18" t="s">
         <v>261</v>
       </c>
     </row>
@@ -6024,7 +6094,7 @@
       <c r="C81" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D81" s="17" t="s">
+      <c r="D81" s="18" t="s">
         <v>263</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -6036,7 +6106,7 @@
       <c r="G81" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I81" s="17" t="s">
+      <c r="I81" s="18" t="s">
         <v>265</v>
       </c>
       <c r="J81" s="7"/>
@@ -6045,7 +6115,7 @@
       <c r="C82" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D82" s="17" t="s">
+      <c r="D82" s="18" t="s">
         <v>267</v>
       </c>
       <c r="E82" s="2" t="s">
@@ -6057,7 +6127,7 @@
       <c r="G82" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I82" s="17" t="s">
+      <c r="I82" s="18" t="s">
         <v>268</v>
       </c>
       <c r="J82" s="7"/>
@@ -6066,7 +6136,7 @@
       <c r="C83" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="D83" s="17" t="s">
+      <c r="D83" s="18" t="s">
         <v>270</v>
       </c>
       <c r="E83" s="2" t="s">
@@ -6078,7 +6148,7 @@
       <c r="G83" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I83" s="17" t="s">
+      <c r="I83" s="18" t="s">
         <v>271</v>
       </c>
     </row>
@@ -6086,7 +6156,7 @@
       <c r="C84" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="18" t="s">
         <v>273</v>
       </c>
       <c r="E84" s="2" t="s">
@@ -6098,7 +6168,7 @@
       <c r="G84" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I84" s="17" t="s">
+      <c r="I84" s="18" t="s">
         <v>274</v>
       </c>
     </row>
@@ -6106,7 +6176,7 @@
       <c r="C85" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D85" s="17" t="s">
+      <c r="D85" s="18" t="s">
         <v>276</v>
       </c>
       <c r="E85" s="2" t="s">
@@ -6118,7 +6188,7 @@
       <c r="G85" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I85" s="17" t="s">
+      <c r="I85" s="18" t="s">
         <v>277</v>
       </c>
     </row>
@@ -6138,7 +6208,7 @@
       <c r="G86" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I86" s="17" t="s">
+      <c r="I86" s="18" t="s">
         <v>279</v>
       </c>
       <c r="J86" s="7"/>
@@ -6159,7 +6229,7 @@
       <c r="G87" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I87" s="17" t="s">
+      <c r="I87" s="18" t="s">
         <v>280</v>
       </c>
       <c r="J87" s="7"/>
@@ -6180,7 +6250,7 @@
       <c r="G88" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I88" s="17" t="s">
+      <c r="I88" s="18" t="s">
         <v>281</v>
       </c>
     </row>
@@ -6200,7 +6270,7 @@
       <c r="G89" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I89" s="17" t="s">
+      <c r="I89" s="18" t="s">
         <v>282</v>
       </c>
     </row>
@@ -6220,7 +6290,7 @@
       <c r="G90" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I90" s="17" t="s">
+      <c r="I90" s="18" t="s">
         <v>283</v>
       </c>
     </row>
@@ -6240,7 +6310,7 @@
       <c r="G91" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I91" s="17" t="s">
+      <c r="I91" s="18" t="s">
         <v>285</v>
       </c>
       <c r="J91" s="7"/>
@@ -6261,7 +6331,7 @@
       <c r="G92" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I92" s="17" t="s">
+      <c r="I92" s="18" t="s">
         <v>286</v>
       </c>
       <c r="J92" s="7"/>
@@ -6282,7 +6352,7 @@
       <c r="G93" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I93" s="17" t="s">
+      <c r="I93" s="18" t="s">
         <v>287</v>
       </c>
     </row>
@@ -6302,7 +6372,7 @@
       <c r="G94" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I94" s="17" t="s">
+      <c r="I94" s="18" t="s">
         <v>288</v>
       </c>
     </row>
@@ -6322,7 +6392,7 @@
       <c r="G95" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I95" s="17" t="s">
+      <c r="I95" s="18" t="s">
         <v>289</v>
       </c>
     </row>
@@ -6890,7 +6960,7 @@
       </c>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>346</v>
       </c>
       <c r="D6" s="2">
@@ -6905,12 +6975,12 @@
       <c r="G6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="18" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>349</v>
       </c>
       <c r="D7" s="2">
@@ -6925,12 +6995,12 @@
       <c r="G7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="18" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>352</v>
       </c>
       <c r="D8" s="2">
@@ -6945,12 +7015,12 @@
       <c r="G8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="18" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>355</v>
       </c>
       <c r="D9" s="2">
@@ -6965,12 +7035,12 @@
       <c r="G9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="18" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>358</v>
       </c>
       <c r="D10" s="2">
@@ -6985,12 +7055,12 @@
       <c r="G10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="18" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>361</v>
       </c>
       <c r="D11" s="2">
@@ -7005,12 +7075,12 @@
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="18" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>364</v>
       </c>
       <c r="D12" s="2">
@@ -7025,12 +7095,12 @@
       <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="18" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>367</v>
       </c>
       <c r="D13" s="2">
@@ -7045,12 +7115,12 @@
       <c r="G13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="18" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="19" t="s">
         <v>370</v>
       </c>
       <c r="D14" s="2">
@@ -7065,12 +7135,12 @@
       <c r="G14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="18" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="19" t="s">
         <v>373</v>
       </c>
       <c r="D15" s="2">
@@ -7085,12 +7155,12 @@
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="18" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>376</v>
       </c>
       <c r="D16" s="2">
@@ -7105,12 +7175,12 @@
       <c r="G16" s="2">
         <v>5</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="18" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="19" t="s">
         <v>379</v>
       </c>
       <c r="D17" s="2">
@@ -7125,12 +7195,12 @@
       <c r="G17" s="2">
         <v>5</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="18" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:8">
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>382</v>
       </c>
       <c r="D18" s="2">
@@ -7145,12 +7215,12 @@
       <c r="G18" s="2">
         <v>5</v>
       </c>
-      <c r="H18" s="17" t="s">
+      <c r="H18" s="18" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:8">
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="19" t="s">
         <v>385</v>
       </c>
       <c r="D19" s="2">
@@ -7165,12 +7235,12 @@
       <c r="G19" s="2">
         <v>5</v>
       </c>
-      <c r="H19" s="17" t="s">
+      <c r="H19" s="18" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:8">
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="19" t="s">
         <v>388</v>
       </c>
       <c r="D20" s="2">
@@ -7185,12 +7255,12 @@
       <c r="G20" s="2">
         <v>5</v>
       </c>
-      <c r="H20" s="17" t="s">
+      <c r="H20" s="18" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:8">
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="19" t="s">
         <v>391</v>
       </c>
       <c r="D21" s="2">
@@ -7205,12 +7275,12 @@
       <c r="G21" s="2">
         <v>5</v>
       </c>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="18" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:8">
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="19" t="s">
         <v>394</v>
       </c>
       <c r="D22" s="2">
@@ -7225,12 +7295,12 @@
       <c r="G22" s="2">
         <v>5</v>
       </c>
-      <c r="H22" s="17" t="s">
+      <c r="H22" s="18" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:8">
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="19" t="s">
         <v>397</v>
       </c>
       <c r="D23" s="2">
@@ -7245,12 +7315,12 @@
       <c r="G23" s="2">
         <v>5</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="18" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:8">
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="19" t="s">
         <v>400</v>
       </c>
       <c r="D24" s="2">
@@ -7265,12 +7335,12 @@
       <c r="G24" s="2">
         <v>5</v>
       </c>
-      <c r="H24" s="17" t="s">
+      <c r="H24" s="18" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:8">
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="19" t="s">
         <v>403</v>
       </c>
       <c r="D25" s="2">
@@ -7285,12 +7355,12 @@
       <c r="G25" s="2">
         <v>5</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="H25" s="18" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:8">
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="19" t="s">
         <v>406</v>
       </c>
       <c r="D26" s="2">
@@ -7305,12 +7375,12 @@
       <c r="G26" s="2">
         <v>5</v>
       </c>
-      <c r="H26" s="17" t="s">
+      <c r="H26" s="18" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="19" t="s">
         <v>409</v>
       </c>
       <c r="D27" s="2">
@@ -7325,12 +7395,12 @@
       <c r="G27" s="2">
         <v>5</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="18" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="19" t="s">
         <v>412</v>
       </c>
       <c r="D28" s="2">
@@ -7345,12 +7415,12 @@
       <c r="G28" s="2">
         <v>5</v>
       </c>
-      <c r="H28" s="17" t="s">
+      <c r="H28" s="18" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="19" t="s">
         <v>415</v>
       </c>
       <c r="D29" s="2">
@@ -7365,12 +7435,12 @@
       <c r="G29" s="2">
         <v>5</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="18" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="19" t="s">
         <v>418</v>
       </c>
       <c r="D30" s="2">
@@ -7385,12 +7455,12 @@
       <c r="G30" s="2">
         <v>5</v>
       </c>
-      <c r="H30" s="17" t="s">
+      <c r="H30" s="18" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="19" t="s">
         <v>421</v>
       </c>
       <c r="D31" s="2">
@@ -7405,12 +7475,12 @@
       <c r="G31" s="2">
         <v>5</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H31" s="18" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="19" t="s">
         <v>424</v>
       </c>
       <c r="D32" s="2">
@@ -7425,12 +7495,12 @@
       <c r="G32" s="2">
         <v>5</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="18" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="19" t="s">
         <v>427</v>
       </c>
       <c r="D33" s="2">
@@ -7445,12 +7515,12 @@
       <c r="G33" s="2">
         <v>5</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="H33" s="18" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="19" t="s">
         <v>430</v>
       </c>
       <c r="D34" s="2">
@@ -7465,12 +7535,12 @@
       <c r="G34" s="2">
         <v>5</v>
       </c>
-      <c r="H34" s="17" t="s">
+      <c r="H34" s="18" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="19" t="s">
         <v>433</v>
       </c>
       <c r="D35" s="2">
@@ -7485,12 +7555,12 @@
       <c r="G35" s="2">
         <v>5</v>
       </c>
-      <c r="H35" s="17" t="s">
+      <c r="H35" s="18" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="19" t="s">
         <v>436</v>
       </c>
       <c r="D36" s="2">
@@ -7505,12 +7575,12 @@
       <c r="G36" s="2">
         <v>5</v>
       </c>
-      <c r="H36" s="17" t="s">
+      <c r="H36" s="18" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="19" t="s">
         <v>439</v>
       </c>
       <c r="D37" s="2">
@@ -7525,12 +7595,12 @@
       <c r="G37" s="2">
         <v>5</v>
       </c>
-      <c r="H37" s="17" t="s">
+      <c r="H37" s="18" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="19" t="s">
         <v>442</v>
       </c>
       <c r="D38" s="2">
@@ -7545,12 +7615,12 @@
       <c r="G38" s="2">
         <v>5</v>
       </c>
-      <c r="H38" s="17" t="s">
+      <c r="H38" s="18" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="19" t="s">
         <v>445</v>
       </c>
       <c r="D39" s="2">
@@ -7565,12 +7635,12 @@
       <c r="G39" s="2">
         <v>5</v>
       </c>
-      <c r="H39" s="17" t="s">
+      <c r="H39" s="18" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="19" t="s">
         <v>448</v>
       </c>
       <c r="D40" s="2">
@@ -7585,12 +7655,12 @@
       <c r="G40" s="2">
         <v>5</v>
       </c>
-      <c r="H40" s="17" t="s">
+      <c r="H40" s="18" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="19" t="s">
         <v>451</v>
       </c>
       <c r="D41" s="2">
@@ -7605,12 +7675,12 @@
       <c r="G41" s="2">
         <v>5</v>
       </c>
-      <c r="H41" s="17" t="s">
+      <c r="H41" s="18" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="19" t="s">
         <v>454</v>
       </c>
       <c r="D42" s="2">
@@ -7625,12 +7695,12 @@
       <c r="G42" s="2">
         <v>5</v>
       </c>
-      <c r="H42" s="17" t="s">
+      <c r="H42" s="18" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="19" t="s">
         <v>457</v>
       </c>
       <c r="D43" s="2">
@@ -7645,12 +7715,12 @@
       <c r="G43" s="2">
         <v>5</v>
       </c>
-      <c r="H43" s="17" t="s">
+      <c r="H43" s="18" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="19" t="s">
         <v>460</v>
       </c>
       <c r="D44" s="2">
@@ -7665,12 +7735,12 @@
       <c r="G44" s="2">
         <v>5</v>
       </c>
-      <c r="H44" s="17" t="s">
+      <c r="H44" s="18" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="19" t="s">
         <v>463</v>
       </c>
       <c r="D45" s="2">
@@ -7685,12 +7755,12 @@
       <c r="G45" s="2">
         <v>5</v>
       </c>
-      <c r="H45" s="17" t="s">
+      <c r="H45" s="18" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="19" t="s">
         <v>466</v>
       </c>
       <c r="D46" s="2">
@@ -7705,12 +7775,12 @@
       <c r="G46" s="2">
         <v>5</v>
       </c>
-      <c r="H46" s="19" t="s">
+      <c r="H46" s="20" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="19" t="s">
         <v>469</v>
       </c>
       <c r="D47" s="2">
@@ -7725,12 +7795,12 @@
       <c r="G47" s="2">
         <v>5</v>
       </c>
-      <c r="H47" s="19" t="s">
+      <c r="H47" s="20" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="19" t="s">
         <v>472</v>
       </c>
       <c r="D48" s="2">
@@ -7745,12 +7815,12 @@
       <c r="G48" s="2">
         <v>5</v>
       </c>
-      <c r="H48" s="19" t="s">
+      <c r="H48" s="20" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="19" t="s">
         <v>475</v>
       </c>
       <c r="D49" s="2">
@@ -7765,12 +7835,12 @@
       <c r="G49" s="2">
         <v>5</v>
       </c>
-      <c r="H49" s="19" t="s">
+      <c r="H49" s="20" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="19" t="s">
         <v>478</v>
       </c>
       <c r="D50" s="2">
@@ -7785,12 +7855,12 @@
       <c r="G50" s="2">
         <v>5</v>
       </c>
-      <c r="H50" s="19" t="s">
+      <c r="H50" s="20" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="19" t="s">
         <v>481</v>
       </c>
       <c r="D51" s="2">
@@ -7805,12 +7875,12 @@
       <c r="G51" s="2">
         <v>5</v>
       </c>
-      <c r="H51" s="19" t="s">
+      <c r="H51" s="20" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="19" t="s">
         <v>484</v>
       </c>
       <c r="D52" s="2">
@@ -7825,12 +7895,12 @@
       <c r="G52" s="2">
         <v>5</v>
       </c>
-      <c r="H52" s="19" t="s">
+      <c r="H52" s="20" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="19" t="s">
         <v>487</v>
       </c>
       <c r="D53" s="2">
@@ -7845,12 +7915,12 @@
       <c r="G53" s="2">
         <v>5</v>
       </c>
-      <c r="H53" s="19" t="s">
+      <c r="H53" s="20" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="19" t="s">
         <v>490</v>
       </c>
       <c r="D54" s="2">
@@ -7865,12 +7935,12 @@
       <c r="G54" s="2">
         <v>5</v>
       </c>
-      <c r="H54" s="19" t="s">
+      <c r="H54" s="20" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="19" t="s">
         <v>493</v>
       </c>
       <c r="D55" s="2">
@@ -7885,12 +7955,12 @@
       <c r="G55" s="2">
         <v>5</v>
       </c>
-      <c r="H55" s="19" t="s">
+      <c r="H55" s="20" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
-      <c r="C56" s="18" t="s">
+      <c r="C56" s="19" t="s">
         <v>496</v>
       </c>
       <c r="D56" s="2">
@@ -7905,12 +7975,12 @@
       <c r="G56" s="2">
         <v>5</v>
       </c>
-      <c r="H56" s="19" t="s">
+      <c r="H56" s="20" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="19" t="s">
         <v>499</v>
       </c>
       <c r="D57" s="2">
@@ -7925,12 +7995,12 @@
       <c r="G57" s="2">
         <v>5</v>
       </c>
-      <c r="H57" s="19" t="s">
+      <c r="H57" s="20" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="19" t="s">
         <v>502</v>
       </c>
       <c r="D58" s="2">
@@ -7945,12 +8015,12 @@
       <c r="G58" s="2">
         <v>5</v>
       </c>
-      <c r="H58" s="19" t="s">
+      <c r="H58" s="20" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="19" t="s">
         <v>505</v>
       </c>
       <c r="D59" s="2">
@@ -7965,12 +8035,12 @@
       <c r="G59" s="2">
         <v>5</v>
       </c>
-      <c r="H59" s="19" t="s">
+      <c r="H59" s="20" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="19" t="s">
         <v>508</v>
       </c>
       <c r="D60" s="2">
@@ -7985,12 +8055,12 @@
       <c r="G60" s="2">
         <v>5</v>
       </c>
-      <c r="H60" s="19" t="s">
+      <c r="H60" s="20" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="19" t="s">
         <v>511</v>
       </c>
       <c r="D61" s="2">
@@ -8005,12 +8075,12 @@
       <c r="G61" s="2">
         <v>5</v>
       </c>
-      <c r="H61" s="19" t="s">
+      <c r="H61" s="20" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:8">
-      <c r="C62" s="18" t="s">
+      <c r="C62" s="19" t="s">
         <v>514</v>
       </c>
       <c r="D62" s="2">
@@ -8025,12 +8095,12 @@
       <c r="G62" s="2">
         <v>5</v>
       </c>
-      <c r="H62" s="19" t="s">
+      <c r="H62" s="20" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="19" t="s">
         <v>517</v>
       </c>
       <c r="D63" s="2">
@@ -8045,12 +8115,12 @@
       <c r="G63" s="2">
         <v>5</v>
       </c>
-      <c r="H63" s="19" t="s">
+      <c r="H63" s="20" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="19" t="s">
         <v>520</v>
       </c>
       <c r="D64" s="2">
@@ -8065,12 +8135,12 @@
       <c r="G64" s="2">
         <v>5</v>
       </c>
-      <c r="H64" s="19" t="s">
+      <c r="H64" s="20" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
-      <c r="C65" s="18" t="s">
+      <c r="C65" s="19" t="s">
         <v>523</v>
       </c>
       <c r="D65" s="2">
@@ -8085,12 +8155,12 @@
       <c r="G65" s="2">
         <v>5</v>
       </c>
-      <c r="H65" s="19" t="s">
+      <c r="H65" s="20" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="19" t="s">
         <v>526</v>
       </c>
       <c r="D66" s="2">
@@ -8105,12 +8175,12 @@
       <c r="G66" s="2">
         <v>5</v>
       </c>
-      <c r="H66" s="19" t="s">
+      <c r="H66" s="20" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="19" t="s">
         <v>529</v>
       </c>
       <c r="D67" s="2">
@@ -8125,12 +8195,12 @@
       <c r="G67" s="2">
         <v>5</v>
       </c>
-      <c r="H67" s="19" t="s">
+      <c r="H67" s="20" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
-      <c r="C68" s="18" t="s">
+      <c r="C68" s="19" t="s">
         <v>532</v>
       </c>
       <c r="D68" s="2">
@@ -8145,12 +8215,12 @@
       <c r="G68" s="2">
         <v>5</v>
       </c>
-      <c r="H68" s="19" t="s">
+      <c r="H68" s="20" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
-      <c r="C69" s="18" t="s">
+      <c r="C69" s="19" t="s">
         <v>535</v>
       </c>
       <c r="D69" s="2">
@@ -8165,12 +8235,12 @@
       <c r="G69" s="2">
         <v>5</v>
       </c>
-      <c r="H69" s="19" t="s">
+      <c r="H69" s="20" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="19" t="s">
         <v>538</v>
       </c>
       <c r="D70" s="2">
@@ -8185,12 +8255,12 @@
       <c r="G70" s="2">
         <v>5</v>
       </c>
-      <c r="H70" s="19" t="s">
+      <c r="H70" s="20" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="19" t="s">
         <v>541</v>
       </c>
       <c r="D71" s="2">
@@ -8205,12 +8275,12 @@
       <c r="G71" s="2">
         <v>5</v>
       </c>
-      <c r="H71" s="19" t="s">
+      <c r="H71" s="20" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
-      <c r="C72" s="18" t="s">
+      <c r="C72" s="19" t="s">
         <v>544</v>
       </c>
       <c r="D72" s="2">
@@ -8225,12 +8295,12 @@
       <c r="G72" s="2">
         <v>5</v>
       </c>
-      <c r="H72" s="19" t="s">
+      <c r="H72" s="20" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="19" t="s">
         <v>547</v>
       </c>
       <c r="D73" s="2">
@@ -8245,12 +8315,12 @@
       <c r="G73" s="2">
         <v>5</v>
       </c>
-      <c r="H73" s="19" t="s">
+      <c r="H73" s="20" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:8">
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="19" t="s">
         <v>550</v>
       </c>
       <c r="D74" s="2">
@@ -8265,12 +8335,12 @@
       <c r="G74" s="2">
         <v>5</v>
       </c>
-      <c r="H74" s="19" t="s">
+      <c r="H74" s="20" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
-      <c r="C75" s="18" t="s">
+      <c r="C75" s="19" t="s">
         <v>553</v>
       </c>
       <c r="D75" s="2">
@@ -8285,12 +8355,12 @@
       <c r="G75" s="2">
         <v>5</v>
       </c>
-      <c r="H75" s="19" t="s">
+      <c r="H75" s="20" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
-      <c r="C76" s="18" t="s">
+      <c r="C76" s="19" t="s">
         <v>556</v>
       </c>
       <c r="D76" s="2">
@@ -8305,12 +8375,12 @@
       <c r="G76" s="2">
         <v>5</v>
       </c>
-      <c r="H76" s="19" t="s">
+      <c r="H76" s="20" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
-      <c r="C77" s="18" t="s">
+      <c r="C77" s="19" t="s">
         <v>559</v>
       </c>
       <c r="D77" s="2">
@@ -8325,12 +8395,12 @@
       <c r="G77" s="2">
         <v>5</v>
       </c>
-      <c r="H77" s="19" t="s">
+      <c r="H77" s="20" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:8">
-      <c r="C78" s="18" t="s">
+      <c r="C78" s="19" t="s">
         <v>562</v>
       </c>
       <c r="D78" s="2">
@@ -8345,12 +8415,12 @@
       <c r="G78" s="2">
         <v>5</v>
       </c>
-      <c r="H78" s="19" t="s">
+      <c r="H78" s="20" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:8">
-      <c r="C79" s="18" t="s">
+      <c r="C79" s="19" t="s">
         <v>565</v>
       </c>
       <c r="D79" s="2">
@@ -8365,12 +8435,12 @@
       <c r="G79" s="2">
         <v>5</v>
       </c>
-      <c r="H79" s="19" t="s">
+      <c r="H79" s="20" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:8">
-      <c r="C80" s="18" t="s">
+      <c r="C80" s="19" t="s">
         <v>568</v>
       </c>
       <c r="D80" s="2">
@@ -8385,7 +8455,7 @@
       <c r="G80" s="2">
         <v>5</v>
       </c>
-      <c r="H80" s="19" t="s">
+      <c r="H80" s="20" t="s">
         <v>570</v>
       </c>
     </row>
@@ -8485,7 +8555,7 @@
       </c>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>571</v>
       </c>
       <c r="D6" s="2">
@@ -8505,7 +8575,7 @@
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>573</v>
       </c>
       <c r="D7" s="2">
@@ -8525,7 +8595,7 @@
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>575</v>
       </c>
       <c r="D8" s="2">
@@ -8545,7 +8615,7 @@
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>577</v>
       </c>
       <c r="D9" s="2">
@@ -8565,7 +8635,7 @@
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>579</v>
       </c>
       <c r="D10" s="2">
@@ -8587,7 +8657,7 @@
     <row r="11" s="2" customFormat="1" customHeight="1" spans="1:9">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>581</v>
       </c>
       <c r="D11" s="2">
@@ -8608,7 +8678,7 @@
       <c r="I11" s="10"/>
     </row>
     <row r="12" customHeight="1" spans="3:8">
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>583</v>
       </c>
       <c r="D12" s="2">
@@ -8628,7 +8698,7 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:8">
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>585</v>
       </c>
       <c r="D13" s="2">
@@ -8648,7 +8718,7 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:8">
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="19" t="s">
         <v>587</v>
       </c>
       <c r="D14" s="2">
@@ -8668,7 +8738,7 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:8">
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="19" t="s">
         <v>589</v>
       </c>
       <c r="D15" s="2">
@@ -8688,7 +8758,7 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:8">
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>591</v>
       </c>
       <c r="D16" s="2">
@@ -8708,7 +8778,7 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="19" t="s">
         <v>593</v>
       </c>
       <c r="D17" s="2">
@@ -8728,7 +8798,7 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:8">
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>595</v>
       </c>
       <c r="D18" s="2">
@@ -8748,7 +8818,7 @@
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:8">
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="19" t="s">
         <v>597</v>
       </c>
       <c r="D19" s="2">
@@ -8768,7 +8838,7 @@
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:8">
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="19" t="s">
         <v>599</v>
       </c>
       <c r="D20" s="2">
@@ -8788,7 +8858,7 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:8">
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="19" t="s">
         <v>601</v>
       </c>
       <c r="D21" s="2">
@@ -8808,7 +8878,7 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:8">
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="19" t="s">
         <v>603</v>
       </c>
       <c r="D22" s="2">
@@ -8828,7 +8898,7 @@
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:8">
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="19" t="s">
         <v>605</v>
       </c>
       <c r="D23" s="2">
@@ -8848,7 +8918,7 @@
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:8">
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="19" t="s">
         <v>607</v>
       </c>
       <c r="D24" s="2">
@@ -8868,7 +8938,7 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:8">
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="19" t="s">
         <v>609</v>
       </c>
       <c r="D25" s="2">
@@ -8888,7 +8958,7 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:8">
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="19" t="s">
         <v>611</v>
       </c>
       <c r="D26" s="2">
@@ -8908,7 +8978,7 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="19" t="s">
         <v>613</v>
       </c>
       <c r="D27" s="2">
@@ -8928,7 +8998,7 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="19" t="s">
         <v>615</v>
       </c>
       <c r="D28" s="2">
@@ -8948,7 +9018,7 @@
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="19" t="s">
         <v>617</v>
       </c>
       <c r="D29" s="2">
@@ -8968,7 +9038,7 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="19" t="s">
         <v>619</v>
       </c>
       <c r="D30" s="2">
@@ -8988,7 +9058,7 @@
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="19" t="s">
         <v>621</v>
       </c>
       <c r="D31" s="2">
@@ -9008,7 +9078,7 @@
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="19" t="s">
         <v>623</v>
       </c>
       <c r="D32" s="2">
@@ -9028,7 +9098,7 @@
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="19" t="s">
         <v>625</v>
       </c>
       <c r="D33" s="2">
@@ -9048,7 +9118,7 @@
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="19" t="s">
         <v>627</v>
       </c>
       <c r="D34" s="2">
@@ -9068,7 +9138,7 @@
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="19" t="s">
         <v>629</v>
       </c>
       <c r="D35" s="2">
@@ -9088,7 +9158,7 @@
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="19" t="s">
         <v>631</v>
       </c>
       <c r="D36" s="2">
@@ -9108,7 +9178,7 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="19" t="s">
         <v>633</v>
       </c>
       <c r="D37" s="2">
@@ -9128,7 +9198,7 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="19" t="s">
         <v>635</v>
       </c>
       <c r="D38" s="2">
@@ -9148,7 +9218,7 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="19" t="s">
         <v>637</v>
       </c>
       <c r="D39" s="2">
@@ -9168,7 +9238,7 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="19" t="s">
         <v>639</v>
       </c>
       <c r="D40" s="2">
@@ -9188,7 +9258,7 @@
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="19" t="s">
         <v>641</v>
       </c>
       <c r="D41" s="2">
@@ -9208,7 +9278,7 @@
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="19" t="s">
         <v>643</v>
       </c>
       <c r="D42" s="2">
@@ -9228,7 +9298,7 @@
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="19" t="s">
         <v>645</v>
       </c>
       <c r="D43" s="2">
@@ -9248,7 +9318,7 @@
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="19" t="s">
         <v>647</v>
       </c>
       <c r="D44" s="2">
@@ -9268,7 +9338,7 @@
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="19" t="s">
         <v>649</v>
       </c>
       <c r="D45" s="2">
@@ -9288,7 +9358,7 @@
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="19" t="s">
         <v>651</v>
       </c>
       <c r="D46" s="2">
@@ -9308,7 +9378,7 @@
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="19" t="s">
         <v>653</v>
       </c>
       <c r="D47" s="2">
@@ -9328,7 +9398,7 @@
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="19" t="s">
         <v>655</v>
       </c>
       <c r="D48" s="2">
@@ -9348,7 +9418,7 @@
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="19" t="s">
         <v>657</v>
       </c>
       <c r="D49" s="2">
@@ -9368,7 +9438,7 @@
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="19" t="s">
         <v>659</v>
       </c>
       <c r="D50" s="2">
@@ -9388,7 +9458,7 @@
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="19" t="s">
         <v>661</v>
       </c>
       <c r="D51" s="2">
@@ -9408,7 +9478,7 @@
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="19" t="s">
         <v>663</v>
       </c>
       <c r="D52" s="2">
@@ -9428,7 +9498,7 @@
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="19" t="s">
         <v>665</v>
       </c>
       <c r="D53" s="2">
@@ -9448,7 +9518,7 @@
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="19" t="s">
         <v>667</v>
       </c>
       <c r="D54" s="2">
@@ -9468,7 +9538,7 @@
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="19" t="s">
         <v>668</v>
       </c>
       <c r="D55" s="2">
@@ -9488,7 +9558,7 @@
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
-      <c r="C56" s="18" t="s">
+      <c r="C56" s="19" t="s">
         <v>670</v>
       </c>
       <c r="D56" s="2">
@@ -9508,7 +9578,7 @@
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="19" t="s">
         <v>672</v>
       </c>
       <c r="D57" s="2">
@@ -9528,7 +9598,7 @@
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="19" t="s">
         <v>674</v>
       </c>
       <c r="D58" s="2">
@@ -9548,7 +9618,7 @@
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="19" t="s">
         <v>676</v>
       </c>
       <c r="D59" s="2">
@@ -9568,13 +9638,13 @@
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="19" t="s">
         <v>678</v>
       </c>
       <c r="D60" s="2">
         <v>0</v>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E60" s="16" t="s">
         <v>679</v>
       </c>
       <c r="F60" s="2" t="s">
@@ -9588,7 +9658,7 @@
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="19" t="s">
         <v>680</v>
       </c>
       <c r="D61" s="2">
@@ -9608,7 +9678,7 @@
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:8">
-      <c r="C62" s="18" t="s">
+      <c r="C62" s="19" t="s">
         <v>682</v>
       </c>
       <c r="D62" s="2">
@@ -9628,7 +9698,7 @@
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="19" t="s">
         <v>684</v>
       </c>
       <c r="D63" s="2">
@@ -9648,7 +9718,7 @@
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="19" t="s">
         <v>686</v>
       </c>
       <c r="D64" s="2">
@@ -9668,7 +9738,7 @@
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
-      <c r="C65" s="18" t="s">
+      <c r="C65" s="19" t="s">
         <v>688</v>
       </c>
       <c r="D65" s="2">
@@ -9688,7 +9758,7 @@
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="19" t="s">
         <v>690</v>
       </c>
       <c r="D66" s="2">
@@ -9708,7 +9778,7 @@
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="19" t="s">
         <v>692</v>
       </c>
       <c r="D67" s="2">
@@ -9728,7 +9798,7 @@
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
-      <c r="C68" s="18" t="s">
+      <c r="C68" s="19" t="s">
         <v>694</v>
       </c>
       <c r="D68" s="2">
@@ -9748,7 +9818,7 @@
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
-      <c r="C69" s="18" t="s">
+      <c r="C69" s="19" t="s">
         <v>696</v>
       </c>
       <c r="D69" s="2">
@@ -9768,7 +9838,7 @@
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="19" t="s">
         <v>698</v>
       </c>
       <c r="D70" s="2">
@@ -9788,7 +9858,7 @@
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="19" t="s">
         <v>700</v>
       </c>
       <c r="D71" s="2">
@@ -9808,7 +9878,7 @@
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
-      <c r="C72" s="18" t="s">
+      <c r="C72" s="19" t="s">
         <v>702</v>
       </c>
       <c r="D72" s="2">
@@ -9828,7 +9898,7 @@
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="19" t="s">
         <v>704</v>
       </c>
       <c r="D73" s="2">
@@ -9848,7 +9918,7 @@
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:8">
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="19" t="s">
         <v>706</v>
       </c>
       <c r="D74" s="2">
@@ -9868,7 +9938,7 @@
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
-      <c r="C75" s="18" t="s">
+      <c r="C75" s="19" t="s">
         <v>708</v>
       </c>
       <c r="D75" s="2">
@@ -9888,7 +9958,7 @@
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
-      <c r="C76" s="18" t="s">
+      <c r="C76" s="19" t="s">
         <v>710</v>
       </c>
       <c r="D76" s="2">
@@ -9908,7 +9978,7 @@
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
-      <c r="C77" s="18" t="s">
+      <c r="C77" s="19" t="s">
         <v>712</v>
       </c>
       <c r="D77" s="2">
@@ -9928,7 +9998,7 @@
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:8">
-      <c r="C78" s="18" t="s">
+      <c r="C78" s="19" t="s">
         <v>714</v>
       </c>
       <c r="D78" s="2">
@@ -9948,7 +10018,7 @@
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:8">
-      <c r="C79" s="18" t="s">
+      <c r="C79" s="19" t="s">
         <v>716</v>
       </c>
       <c r="D79" s="2">
@@ -9968,7 +10038,7 @@
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:8">
-      <c r="C80" s="18" t="s">
+      <c r="C80" s="19" t="s">
         <v>718</v>
       </c>
       <c r="D80" s="2">
@@ -9988,7 +10058,7 @@
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:8">
-      <c r="C81" s="18" t="s">
+      <c r="C81" s="19" t="s">
         <v>720</v>
       </c>
       <c r="D81" s="2">
@@ -10008,7 +10078,7 @@
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:8">
-      <c r="C82" s="18" t="s">
+      <c r="C82" s="19" t="s">
         <v>722</v>
       </c>
       <c r="D82" s="2">
@@ -10028,7 +10098,7 @@
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:8">
-      <c r="C83" s="18" t="s">
+      <c r="C83" s="19" t="s">
         <v>724</v>
       </c>
       <c r="D83" s="2">
@@ -10048,7 +10118,7 @@
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:8">
-      <c r="C84" s="18" t="s">
+      <c r="C84" s="19" t="s">
         <v>726</v>
       </c>
       <c r="D84" s="2">
@@ -10068,7 +10138,7 @@
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:8">
-      <c r="C85" s="18" t="s">
+      <c r="C85" s="19" t="s">
         <v>728</v>
       </c>
       <c r="D85" s="2">
@@ -10088,7 +10158,7 @@
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:8">
-      <c r="C86" s="18" t="s">
+      <c r="C86" s="19" t="s">
         <v>730</v>
       </c>
       <c r="D86" s="2">
@@ -10108,7 +10178,7 @@
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:8">
-      <c r="C87" s="18" t="s">
+      <c r="C87" s="19" t="s">
         <v>732</v>
       </c>
       <c r="D87" s="2">
@@ -10128,7 +10198,7 @@
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:8">
-      <c r="C88" s="18" t="s">
+      <c r="C88" s="19" t="s">
         <v>734</v>
       </c>
       <c r="D88" s="2">
@@ -10148,7 +10218,7 @@
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:8">
-      <c r="C89" s="18" t="s">
+      <c r="C89" s="19" t="s">
         <v>736</v>
       </c>
       <c r="D89" s="2">
@@ -10168,7 +10238,7 @@
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:8">
-      <c r="C90" s="18" t="s">
+      <c r="C90" s="19" t="s">
         <v>738</v>
       </c>
       <c r="D90" s="2">
@@ -10188,7 +10258,7 @@
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:8">
-      <c r="C91" s="18" t="s">
+      <c r="C91" s="19" t="s">
         <v>740</v>
       </c>
       <c r="D91" s="2">
@@ -10208,7 +10278,7 @@
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:8">
-      <c r="C92" s="18" t="s">
+      <c r="C92" s="19" t="s">
         <v>742</v>
       </c>
       <c r="D92" s="2">
@@ -10228,7 +10298,7 @@
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:8">
-      <c r="C93" s="18" t="s">
+      <c r="C93" s="19" t="s">
         <v>744</v>
       </c>
       <c r="D93" s="2">
@@ -10248,7 +10318,7 @@
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:8">
-      <c r="C94" s="18" t="s">
+      <c r="C94" s="19" t="s">
         <v>746</v>
       </c>
       <c r="D94" s="2">
@@ -10943,7 +11013,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H40"/>
+  <dimension ref="C1:H48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -11024,7 +11094,7 @@
       </c>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>776</v>
       </c>
       <c r="D6" s="2">
@@ -11044,7 +11114,7 @@
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>778</v>
       </c>
       <c r="D7" s="2">
@@ -11064,7 +11134,7 @@
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>780</v>
       </c>
       <c r="D8" s="2">
@@ -11084,7 +11154,7 @@
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>782</v>
       </c>
       <c r="D9" s="2">
@@ -11104,7 +11174,7 @@
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>784</v>
       </c>
       <c r="D10" s="2">
@@ -11119,12 +11189,12 @@
       <c r="G10" s="2">
         <v>15</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>786</v>
       </c>
       <c r="D11" s="2">
@@ -11139,12 +11209,12 @@
       <c r="G11" s="2">
         <v>3</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="18" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>788</v>
       </c>
       <c r="D12" s="2">
@@ -11164,7 +11234,7 @@
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>790</v>
       </c>
       <c r="D13" s="2">
@@ -11179,12 +11249,12 @@
       <c r="G13" s="2">
         <v>3</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="18" t="s">
         <v>792</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="19" t="s">
         <v>793</v>
       </c>
       <c r="D14" s="2">
@@ -11199,12 +11269,12 @@
       <c r="G14" s="2">
         <v>3</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="18" t="s">
         <v>795</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="19" t="s">
         <v>796</v>
       </c>
       <c r="D15" s="2">
@@ -11219,12 +11289,12 @@
       <c r="G15" s="2">
         <v>19</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="21" t="s">
         <v>798</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="19" t="s">
         <v>799</v>
       </c>
       <c r="D16" s="2">
@@ -11244,7 +11314,7 @@
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="19" t="s">
         <v>800</v>
       </c>
       <c r="D17" s="2">
@@ -11264,7 +11334,7 @@
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>801</v>
       </c>
       <c r="D18" s="2">
@@ -11284,7 +11354,7 @@
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="19" t="s">
         <v>802</v>
       </c>
       <c r="D19" s="2">
@@ -11304,7 +11374,7 @@
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="19" t="s">
         <v>803</v>
       </c>
       <c r="D20" s="2">
@@ -11324,7 +11394,7 @@
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="19" t="s">
         <v>805</v>
       </c>
       <c r="D21" s="2">
@@ -11344,7 +11414,7 @@
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="19" t="s">
         <v>806</v>
       </c>
       <c r="D22" s="2">
@@ -11364,7 +11434,7 @@
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="19" t="s">
         <v>807</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -11373,18 +11443,18 @@
       <c r="E23" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="17" t="s">
+      <c r="G23" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H23" s="21" t="s">
+      <c r="H23" s="22" t="s">
         <v>811</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="19" t="s">
         <v>812</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -11393,18 +11463,18 @@
       <c r="E24" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H24" s="21" t="s">
+      <c r="H24" s="22" t="s">
         <v>814</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="19" t="s">
         <v>815</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -11413,18 +11483,18 @@
       <c r="E25" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="G25" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="H25" s="22" t="s">
         <v>817</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="19" t="s">
         <v>818</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -11433,18 +11503,18 @@
       <c r="E26" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="G26" s="18" t="s">
         <v>820</v>
       </c>
-      <c r="H26" s="21" t="s">
+      <c r="H26" s="22" t="s">
         <v>821</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="19" t="s">
         <v>822</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -11453,18 +11523,18 @@
       <c r="E27" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="17" t="s">
+      <c r="G27" s="18" t="s">
         <v>820</v>
       </c>
-      <c r="H27" s="21" t="s">
+      <c r="H27" s="22" t="s">
         <v>824</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="19" t="s">
         <v>825</v>
       </c>
       <c r="D28" s="2">
@@ -11479,12 +11549,12 @@
       <c r="G28" s="2">
         <v>3</v>
       </c>
-      <c r="H28" s="17" t="s">
+      <c r="H28" s="18" t="s">
         <v>827</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="19" t="s">
         <v>828</v>
       </c>
       <c r="D29" s="2">
@@ -11499,12 +11569,12 @@
       <c r="G29" s="2">
         <v>3</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="18" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="19" t="s">
         <v>831</v>
       </c>
       <c r="D30" s="2">
@@ -11519,12 +11589,12 @@
       <c r="G30" s="2">
         <v>3</v>
       </c>
-      <c r="H30" s="17" t="s">
+      <c r="H30" s="18" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="19" t="s">
         <v>834</v>
       </c>
       <c r="D31" s="2">
@@ -11544,7 +11614,7 @@
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="19" t="s">
         <v>835</v>
       </c>
       <c r="D32" s="2">
@@ -11564,7 +11634,7 @@
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="19" t="s">
         <v>836</v>
       </c>
       <c r="D33" s="2">
@@ -11584,7 +11654,7 @@
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="19" t="s">
         <v>837</v>
       </c>
       <c r="D34" s="2">
@@ -11604,7 +11674,7 @@
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="19" t="s">
         <v>838</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -11616,15 +11686,15 @@
       <c r="F35" s="2">
         <v>10</v>
       </c>
-      <c r="G35" s="17" t="s">
+      <c r="G35" s="18" t="s">
         <v>840</v>
       </c>
-      <c r="H35" s="21" t="s">
+      <c r="H35" s="22" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="19" t="s">
         <v>842</v>
       </c>
       <c r="D36" s="2" t="s">
@@ -11636,15 +11706,15 @@
       <c r="F36" s="2">
         <v>15</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G36" s="18" t="s">
         <v>840</v>
       </c>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="22" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="19" t="s">
         <v>843</v>
       </c>
       <c r="D37" s="2">
@@ -11664,7 +11734,7 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="19" t="s">
         <v>845</v>
       </c>
       <c r="D38" s="2">
@@ -11684,7 +11754,7 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="19" t="s">
         <v>846</v>
       </c>
       <c r="D39" s="2">
@@ -11704,7 +11774,7 @@
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="19" t="s">
         <v>847</v>
       </c>
       <c r="D40" s="2" t="s">
@@ -11719,8 +11789,148 @@
       <c r="G40" s="2">
         <v>5</v>
       </c>
-      <c r="H40" s="21" t="s">
+      <c r="H40" s="22" t="s">
         <v>849</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:8">
+      <c r="C42" s="19" t="s">
+        <v>850</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>851</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2">
+        <v>16</v>
+      </c>
+      <c r="H42" s="22" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:8">
+      <c r="C43" s="19" t="s">
+        <v>853</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>854</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>16</v>
+      </c>
+      <c r="H43" s="22" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:8">
+      <c r="C44" s="19" t="s">
+        <v>856</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>857</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2">
+        <v>16</v>
+      </c>
+      <c r="H44" s="22" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:8">
+      <c r="C45" s="19" t="s">
+        <v>859</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>860</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2">
+        <v>16</v>
+      </c>
+      <c r="H45" s="22" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:8">
+      <c r="C46" s="19" t="s">
+        <v>862</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>863</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2">
+        <v>16</v>
+      </c>
+      <c r="H46" s="22" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:8">
+      <c r="C47" s="19" t="s">
+        <v>865</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>866</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2">
+        <v>16</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:8">
+      <c r="C48" s="19" t="s">
+        <v>868</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>869</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2">
+        <v>16</v>
+      </c>
+      <c r="H48" s="22" t="s">
+        <v>870</v>
       </c>
     </row>
   </sheetData>
@@ -11820,13 +12030,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11835,18 +12045,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C7" s="17" t="s">
-        <v>853</v>
+      <c r="C7" s="18" t="s">
+        <v>874</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11854,19 +12064,19 @@
       <c r="G7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="21" t="s">
-        <v>855</v>
+      <c r="H7" s="22" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C8" s="17" t="s">
-        <v>856</v>
+      <c r="C8" s="18" t="s">
+        <v>877</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>857</v>
+        <v>878</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -11874,19 +12084,19 @@
       <c r="G8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>858</v>
+      <c r="H8" s="22" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C9" s="17" t="s">
-        <v>859</v>
+      <c r="C9" s="18" t="s">
+        <v>880</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -11894,213 +12104,213 @@
       <c r="G9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="21" t="s">
-        <v>861</v>
+      <c r="H9" s="22" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C10" s="17" t="s">
-        <v>862</v>
+      <c r="C10" s="18" t="s">
+        <v>883</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="21" t="s">
-        <v>864</v>
+      <c r="H10" s="22" t="s">
+        <v>885</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C11" s="17" t="s">
-        <v>865</v>
+      <c r="C11" s="18" t="s">
+        <v>886</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="G11" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="21" t="s">
-        <v>866</v>
+      <c r="H11" s="22" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C12" s="17" t="s">
-        <v>867</v>
+      <c r="C12" s="18" t="s">
+        <v>888</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="21" t="s">
-        <v>868</v>
+      <c r="H12" s="22" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C13" s="17" t="s">
-        <v>869</v>
+      <c r="C13" s="18" t="s">
+        <v>890</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="21" t="s">
-        <v>870</v>
+      <c r="H13" s="22" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="18" t="s">
         <v>307</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="F15" s="17" t="s">
+        <v>892</v>
+      </c>
+      <c r="F15" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>873</v>
+      <c r="G15" s="18" t="s">
+        <v>893</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C16" s="17" t="s">
-        <v>874</v>
+      <c r="C16" s="18" t="s">
+        <v>895</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>876</v>
+        <v>896</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>893</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C17" s="17" t="s">
-        <v>877</v>
+      <c r="C17" s="18" t="s">
+        <v>898</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="F17" s="17" t="s">
+        <v>899</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>876</v>
+      <c r="G17" s="18" t="s">
+        <v>893</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C18" s="17" t="s">
-        <v>879</v>
+      <c r="C18" s="18" t="s">
+        <v>900</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>881</v>
+        <v>901</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>893</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C19" s="17" t="s">
-        <v>882</v>
+      <c r="C19" s="18" t="s">
+        <v>903</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>884</v>
+        <v>904</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>893</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>905</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C20" s="17" t="s">
-        <v>885</v>
+      <c r="C20" s="18" t="s">
+        <v>906</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>887</v>
+        <v>907</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>893</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>908</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C21" s="17" t="s">
-        <v>888</v>
+      <c r="C21" s="18" t="s">
+        <v>909</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>808</v>
@@ -12108,82 +12318,82 @@
       <c r="E21" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="G21" s="18" t="s">
         <v>840</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="H21" s="22" t="s">
         <v>841</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C22" s="17" t="s">
-        <v>889</v>
+      <c r="C22" s="18" t="s">
+        <v>910</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H22" s="21" t="s">
-        <v>891</v>
+        <v>911</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>893</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C23" s="17" t="s">
-        <v>892</v>
+      <c r="C23" s="18" t="s">
+        <v>913</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="18" t="s">
         <v>893</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H23" s="21" t="s">
-        <v>894</v>
+      <c r="H23" s="22" t="s">
+        <v>915</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C24" s="17" t="s">
-        <v>895</v>
+      <c r="C24" s="18" t="s">
+        <v>916</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H24" s="21" t="s">
-        <v>897</v>
+        <v>917</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>893</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>918</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="8:8">
       <c r="H25" s="7"/>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C31" s="17" t="s">
-        <v>898</v>
+      <c r="C31" s="18" t="s">
+        <v>919</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>808</v>
@@ -12191,19 +12401,19 @@
       <c r="E31" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="F31" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="17" t="s">
+      <c r="F31" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H31" s="21" t="s">
+      <c r="H31" s="22" t="s">
         <v>814</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C32" s="17" t="s">
-        <v>899</v>
+      <c r="C32" s="18" t="s">
+        <v>920</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>808</v>
@@ -12211,39 +12421,39 @@
       <c r="E32" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="F32" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="17" t="s">
+      <c r="F32" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="H32" s="22" t="s">
         <v>811</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C33" s="17" t="s">
-        <v>900</v>
+      <c r="C33" s="18" t="s">
+        <v>921</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H33" s="21" t="s">
-        <v>902</v>
+      <c r="H33" s="22" t="s">
+        <v>923</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C34" s="17" t="s">
-        <v>903</v>
+      <c r="C34" s="18" t="s">
+        <v>924</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>808</v>
@@ -12251,334 +12461,334 @@
       <c r="E34" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="F34" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" s="17" t="s">
+      <c r="F34" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H34" s="21" t="s">
+      <c r="H34" s="22" t="s">
         <v>817</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C35" s="17" t="s">
-        <v>904</v>
+      <c r="C35" s="18" t="s">
+        <v>925</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="17" t="s">
+        <v>926</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H35" s="21" t="s">
-        <v>906</v>
+      <c r="H35" s="22" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C36" s="17" t="s">
-        <v>907</v>
+      <c r="C36" s="18" t="s">
+        <v>928</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="F36" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="17" t="s">
+        <v>929</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H36" s="21" t="s">
-        <v>909</v>
+      <c r="H36" s="22" t="s">
+        <v>930</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C37" s="17" t="s">
-        <v>910</v>
+      <c r="C37" s="18" t="s">
+        <v>931</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37" s="17" t="s">
+        <v>932</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H37" s="21" t="s">
-        <v>912</v>
+      <c r="H37" s="22" t="s">
+        <v>933</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C38" s="17" t="s">
-        <v>913</v>
+      <c r="C38" s="18" t="s">
+        <v>934</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>914</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G38" s="17" t="s">
+        <v>935</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H38" s="21" t="s">
-        <v>915</v>
+      <c r="H38" s="22" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="18" t="s">
         <v>795</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G39" s="17" t="s">
+        <v>937</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H39" s="22" t="s">
-        <v>917</v>
+      <c r="H39" s="23" t="s">
+        <v>938</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="18" t="s">
         <v>830</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>918</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G40" s="17" t="s">
+        <v>939</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H40" s="19" t="s">
-        <v>919</v>
+      <c r="H40" s="20" t="s">
+        <v>940</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C41" s="17" t="s">
-        <v>920</v>
+      <c r="C41" s="18" t="s">
+        <v>941</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G41" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H41" s="22" t="s">
-        <v>922</v>
+      <c r="H41" s="23" t="s">
+        <v>943</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C42" s="17" t="s">
-        <v>923</v>
+      <c r="C42" s="18" t="s">
+        <v>944</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G42" s="17" t="s">
+        <v>945</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H42" s="19" t="s">
-        <v>925</v>
+      <c r="H42" s="20" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C43" s="17" t="s">
-        <v>926</v>
+      <c r="C43" s="18" t="s">
+        <v>947</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G43" s="17" t="s">
+        <v>948</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H43" s="21" t="s">
-        <v>928</v>
+      <c r="H43" s="22" t="s">
+        <v>949</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C44" s="17" t="s">
-        <v>929</v>
+      <c r="C44" s="18" t="s">
+        <v>950</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H44" s="21" t="s">
-        <v>931</v>
+      <c r="H44" s="22" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C45" s="17" t="s">
-        <v>932</v>
+      <c r="C45" s="18" t="s">
+        <v>953</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>933</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" s="17" t="s">
+        <v>954</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H45" s="21" t="s">
-        <v>934</v>
+      <c r="H45" s="22" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C46" s="17" t="s">
-        <v>935</v>
+      <c r="C46" s="18" t="s">
+        <v>956</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G46" s="17" t="s">
+        <v>957</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H46" s="21" t="s">
-        <v>937</v>
+      <c r="H46" s="22" t="s">
+        <v>958</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C47" s="17" t="s">
-        <v>938</v>
+      <c r="C47" s="18" t="s">
+        <v>959</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G47" s="17" t="s">
+        <v>960</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H47" s="21" t="s">
-        <v>940</v>
+      <c r="H47" s="22" t="s">
+        <v>961</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C48" s="17" t="s">
-        <v>941</v>
+      <c r="C48" s="18" t="s">
+        <v>962</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>942</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" s="17" t="s">
+        <v>963</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H48" s="21" t="s">
-        <v>943</v>
+      <c r="H48" s="22" t="s">
+        <v>964</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C49" s="17" t="s">
-        <v>944</v>
+      <c r="C49" s="18" t="s">
+        <v>965</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>945</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G49" s="17" t="s">
+        <v>966</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H49" s="21" t="s">
-        <v>946</v>
+      <c r="H49" s="22" t="s">
+        <v>967</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C50" s="17" t="s">
-        <v>947</v>
+      <c r="C50" s="18" t="s">
+        <v>968</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G50" s="17" t="s">
+        <v>969</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="18" t="s">
         <v>810</v>
       </c>
-      <c r="H50" s="21" t="s">
-        <v>949</v>
+      <c r="H50" s="22" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:8">
@@ -12590,8 +12800,8 @@
       <c r="H51" s="3"/>
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C52" s="17" t="s">
-        <v>950</v>
+      <c r="C52" s="18" t="s">
+        <v>971</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>808</v>
@@ -12599,19 +12809,19 @@
       <c r="E52" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="F52" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G52" s="17" t="s">
+      <c r="F52" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="18" t="s">
         <v>820</v>
       </c>
-      <c r="H52" s="21" t="s">
+      <c r="H52" s="22" t="s">
         <v>821</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C53" s="17" t="s">
-        <v>951</v>
+      <c r="C53" s="18" t="s">
+        <v>972</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>808</v>
@@ -12619,54 +12829,54 @@
       <c r="E53" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="F53" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" s="17" t="s">
+      <c r="F53" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="18" t="s">
         <v>820</v>
       </c>
-      <c r="H53" s="21" t="s">
+      <c r="H53" s="22" t="s">
         <v>824</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
-      <c r="C55" s="17" t="s">
-        <v>952</v>
+      <c r="C55" s="18" t="s">
+        <v>973</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>953</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H55" s="23" t="s">
-        <v>954</v>
+        <v>974</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>893</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>975</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
-      <c r="C56" s="17" t="s">
-        <v>955</v>
+      <c r="C56" s="18" t="s">
+        <v>976</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>956</v>
-      </c>
-      <c r="F56" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G56" s="17" t="s">
-        <v>872</v>
-      </c>
-      <c r="H56" s="23" t="s">
-        <v>957</v>
+        <v>977</v>
+      </c>
+      <c r="F56" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="18" t="s">
+        <v>893</v>
+      </c>
+      <c r="H56" s="24" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:8">
@@ -12679,182 +12889,182 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="10" t="s">
-        <v>958</v>
+        <v>979</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H58" s="17" t="s">
-        <v>961</v>
+        <v>981</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>982</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>962</v>
+        <v>983</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>963</v>
+        <v>984</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H59" s="17" t="s">
-        <v>964</v>
+        <v>981</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>985</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>965</v>
+        <v>986</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>966</v>
+        <v>987</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H60" s="17" t="s">
-        <v>967</v>
+        <v>981</v>
+      </c>
+      <c r="H60" s="18" t="s">
+        <v>988</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>968</v>
+        <v>989</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>969</v>
+        <v>990</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H61" s="17" t="s">
-        <v>970</v>
+        <v>981</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>991</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>971</v>
+        <v>992</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H62" s="17" t="s">
-        <v>973</v>
+        <v>981</v>
+      </c>
+      <c r="H62" s="18" t="s">
+        <v>994</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>974</v>
+        <v>995</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>975</v>
+        <v>996</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H63" s="17" t="s">
-        <v>976</v>
+        <v>981</v>
+      </c>
+      <c r="H63" s="18" t="s">
+        <v>997</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>977</v>
+        <v>998</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>978</v>
+        <v>999</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H64" s="17" t="s">
-        <v>979</v>
+        <v>981</v>
+      </c>
+      <c r="H64" s="18" t="s">
+        <v>1000</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E65" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H65" s="21" t="s">
-        <v>982</v>
+      <c r="H65" s="22" t="s">
+        <v>1003</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>983</v>
-      </c>
-      <c r="D66" s="17" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D66" s="18" t="s">
         <v>49</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>984</v>
+        <v>1005</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H66" s="21" t="s">
-        <v>985</v>
+        <v>981</v>
+      </c>
+      <c r="H66" s="22" t="s">
+        <v>1006</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12865,16 +13075,16 @@
         <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>986</v>
+        <v>1007</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="H67" s="21" t="s">
-        <v>987</v>
+        <v>981</v>
+      </c>
+      <c r="H67" s="22" t="s">
+        <v>1008</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="1002">
   <si>
     <t>_id</t>
   </si>
@@ -2971,61 +2971,40 @@
     <t>白色宠物</t>
   </si>
   <si>
-    <t>4201</t>
-  </si>
-  <si>
     <t>220102</t>
   </si>
   <si>
     <t>绿色宠物</t>
   </si>
   <si>
-    <t>4202</t>
-  </si>
-  <si>
     <t>220103</t>
   </si>
   <si>
     <t>蓝色宠物</t>
   </si>
   <si>
-    <t>4203</t>
-  </si>
-  <si>
     <t>220104</t>
   </si>
   <si>
     <t>紫色宠物</t>
   </si>
   <si>
-    <t>4204</t>
-  </si>
-  <si>
     <t>220105</t>
   </si>
   <si>
     <t>橙色宠物</t>
   </si>
   <si>
-    <t>4205</t>
-  </si>
-  <si>
     <t>220106</t>
   </si>
   <si>
     <t>红色宠物</t>
   </si>
   <si>
-    <t>4206</t>
-  </si>
-  <si>
     <t>220107</t>
   </si>
   <si>
     <t>金色宠物</t>
-  </si>
-  <si>
-    <t>4207</t>
   </si>
   <si>
     <t>101</t>
@@ -11809,19 +11788,19 @@
       <c r="G42" s="2">
         <v>16</v>
       </c>
-      <c r="H42" s="22" t="s">
-        <v>852</v>
+      <c r="H42" s="2">
+        <v>8201</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="19" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F43" s="2">
         <v>1</v>
@@ -11829,19 +11808,19 @@
       <c r="G43" s="2">
         <v>16</v>
       </c>
-      <c r="H43" s="22" t="s">
-        <v>855</v>
+      <c r="H43" s="2">
+        <v>8202</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="19" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F44" s="2">
         <v>1</v>
@@ -11849,19 +11828,19 @@
       <c r="G44" s="2">
         <v>16</v>
       </c>
-      <c r="H44" s="22" t="s">
-        <v>858</v>
+      <c r="H44" s="2">
+        <v>8203</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="19" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="F45" s="2">
         <v>1</v>
@@ -11869,19 +11848,19 @@
       <c r="G45" s="2">
         <v>16</v>
       </c>
-      <c r="H45" s="22" t="s">
-        <v>861</v>
+      <c r="H45" s="2">
+        <v>8204</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="19" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
@@ -11889,19 +11868,19 @@
       <c r="G46" s="2">
         <v>16</v>
       </c>
-      <c r="H46" s="22" t="s">
-        <v>864</v>
+      <c r="H46" s="2">
+        <v>8205</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="19" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -11909,19 +11888,19 @@
       <c r="G47" s="2">
         <v>16</v>
       </c>
-      <c r="H47" s="22" t="s">
-        <v>867</v>
+      <c r="H47" s="2">
+        <v>8206</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="19" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -11929,8 +11908,8 @@
       <c r="G48" s="2">
         <v>16</v>
       </c>
-      <c r="H48" s="22" t="s">
-        <v>870</v>
+      <c r="H48" s="2">
+        <v>8207</v>
       </c>
     </row>
   </sheetData>
@@ -12030,13 +12009,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -12045,18 +12024,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -12065,18 +12044,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -12085,18 +12064,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -12105,18 +12084,18 @@
         <v>20</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -12125,18 +12104,18 @@
         <v>17</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -12145,18 +12124,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -12165,18 +12144,18 @@
         <v>17</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -12185,7 +12164,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12196,121 +12175,121 @@
         <v>808</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>808</v>
@@ -12330,62 +12309,62 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="8:8">
@@ -12393,7 +12372,7 @@
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>808</v>
@@ -12413,7 +12392,7 @@
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>808</v>
@@ -12433,13 +12412,13 @@
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>19</v>
@@ -12448,12 +12427,12 @@
         <v>810</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>808</v>
@@ -12473,13 +12452,13 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>19</v>
@@ -12488,18 +12467,18 @@
         <v>810</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>19</v>
@@ -12508,18 +12487,18 @@
         <v>810</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>19</v>
@@ -12528,18 +12507,18 @@
         <v>810</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>19</v>
@@ -12548,7 +12527,7 @@
         <v>810</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12559,7 +12538,7 @@
         <v>808</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>19</v>
@@ -12568,7 +12547,7 @@
         <v>810</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -12579,7 +12558,7 @@
         <v>808</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>19</v>
@@ -12588,18 +12567,18 @@
         <v>810</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>19</v>
@@ -12608,18 +12587,18 @@
         <v>810</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>19</v>
@@ -12628,18 +12607,18 @@
         <v>810</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>19</v>
@@ -12648,18 +12627,18 @@
         <v>810</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>950</v>
+        <v>943</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>951</v>
+        <v>944</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>19</v>
@@ -12668,18 +12647,18 @@
         <v>810</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>952</v>
+        <v>945</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>19</v>
@@ -12688,18 +12667,18 @@
         <v>810</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>19</v>
@@ -12708,18 +12687,18 @@
         <v>810</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>19</v>
@@ -12728,18 +12707,18 @@
         <v>810</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>19</v>
@@ -12748,18 +12727,18 @@
         <v>810</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>19</v>
@@ -12768,18 +12747,18 @@
         <v>810</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>19</v>
@@ -12788,7 +12767,7 @@
         <v>810</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:8">
@@ -12801,7 +12780,7 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>808</v>
@@ -12821,7 +12800,7 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>808</v>
@@ -12841,42 +12820,42 @@
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>808</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:8">
@@ -12889,182 +12868,182 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="10" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="H60" s="18" t="s">
         <v>981</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="D66" s="18" t="s">
         <v>49</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13075,16 +13054,16 @@
         <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="1002">
   <si>
     <t>_id</t>
   </si>
@@ -10331,7 +10331,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -10834,38 +10834,38 @@
         <v>180021</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C27" s="10"/>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C28" s="14">
-        <v>180030</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" s="2">
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C27" s="14">
+        <v>180022</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="2">
         <v>18</v>
       </c>
-      <c r="H28" s="14">
-        <v>180030</v>
-      </c>
+      <c r="H27" s="14">
+        <v>180022</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:3">
+      <c r="C28" s="10"/>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="14">
-        <v>180031</v>
+        <v>180030</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -10874,18 +10874,18 @@
         <v>18</v>
       </c>
       <c r="H29" s="14">
-        <v>180031</v>
+        <v>180030</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="14">
-        <v>180032</v>
+        <v>180031</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -10894,18 +10894,18 @@
         <v>18</v>
       </c>
       <c r="H30" s="14">
-        <v>180032</v>
+        <v>180031</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="14">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>19</v>
@@ -10914,18 +10914,18 @@
         <v>18</v>
       </c>
       <c r="H31" s="14">
-        <v>180033</v>
+        <v>180032</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="14">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>19</v>
@@ -10934,18 +10934,18 @@
         <v>18</v>
       </c>
       <c r="H32" s="14">
-        <v>180034</v>
+        <v>180033</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="14">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>19</v>
@@ -10954,18 +10954,18 @@
         <v>18</v>
       </c>
       <c r="H33" s="14">
-        <v>180035</v>
+        <v>180034</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="14">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>19</v>
@@ -10974,7 +10974,47 @@
         <v>18</v>
       </c>
       <c r="H34" s="14">
+        <v>180035</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C35" s="14">
         <v>180036</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="2">
+        <v>18</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180036</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C36" s="14">
+        <v>180037</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="2">
+        <v>18</v>
+      </c>
+      <c r="H36" s="14">
+        <v>180037</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="1107">
   <si>
     <t>_id</t>
   </si>
@@ -1435,22 +1435,55 @@
     <t>21010001,21010002,21010003,21010004,21010005,21010007,21010009,21010010,22010001,22010002,22010003,22010004,22010005,22010007,22010009,22010010,23010001,23010002,23010003,23010004,23010005,23010007,23010009,23010010</t>
   </si>
   <si>
-    <t>2阶1100级装备</t>
-  </si>
-  <si>
-    <t>3阶1100级装备</t>
-  </si>
-  <si>
-    <t>4阶1100级装备</t>
-  </si>
-  <si>
-    <t>5阶1100级装备</t>
-  </si>
-  <si>
-    <t>6阶1100级装备</t>
-  </si>
-  <si>
-    <t>7阶1100级装备</t>
+    <t>1阶1450级装备</t>
+  </si>
+  <si>
+    <t>21020001,21020002,21020003,21020004,21020005,21020007,21020009,21020010,22020001,22020002,22020003,22020004,22020005,22020007,22020009,22020010,23020001,23020002,23020003,23020004,23020005,23020007,23020009,23020010</t>
+  </si>
+  <si>
+    <t>209990</t>
+  </si>
+  <si>
+    <t>1介暗金装1</t>
+  </si>
+  <si>
+    <t>21305801,21305802,22305801,22305802,23305801,23305802</t>
+  </si>
+  <si>
+    <t>209991</t>
+  </si>
+  <si>
+    <t>1介暗金装2</t>
+  </si>
+  <si>
+    <t>21305803,21305804,22305803,22305804,23305803,23305804</t>
+  </si>
+  <si>
+    <t>209992</t>
+  </si>
+  <si>
+    <t>1介暗金装3</t>
+  </si>
+  <si>
+    <t>21305805,21305807,22305805,22305807,23305805,23305807</t>
+  </si>
+  <si>
+    <t>209993</t>
+  </si>
+  <si>
+    <t>1介暗金装4</t>
+  </si>
+  <si>
+    <t>21305809,21305810,22305809,22305810,23305809,23305810</t>
+  </si>
+  <si>
+    <t>209994</t>
+  </si>
+  <si>
+    <t>1介暗金装5</t>
+  </si>
+  <si>
+    <t>21305801,21305802,21305803,21305804,21305805,21305807,21305809,21305810,22305801,22305802,22305803,22305804,22305805,22305807,22305809,22305810,23305801,23305802,23305803,23305804,23305805,23305807,23305809,23305810</t>
   </si>
   <si>
     <t>209995</t>
@@ -2128,6 +2161,69 @@
     <t>50000097,50000098,50000099,50000100,50000101,50000102,50000103,50000104</t>
   </si>
   <si>
+    <t>210070</t>
+  </si>
+  <si>
+    <t>十五阶升阶石</t>
+  </si>
+  <si>
+    <t>50000105</t>
+  </si>
+  <si>
+    <t>210071</t>
+  </si>
+  <si>
+    <t>十六阶升阶石</t>
+  </si>
+  <si>
+    <t>50000106</t>
+  </si>
+  <si>
+    <t>210072</t>
+  </si>
+  <si>
+    <t>十七阶升阶石</t>
+  </si>
+  <si>
+    <t>50000107</t>
+  </si>
+  <si>
+    <t>210073</t>
+  </si>
+  <si>
+    <t>十八阶升阶石</t>
+  </si>
+  <si>
+    <t>50000108</t>
+  </si>
+  <si>
+    <t>210074</t>
+  </si>
+  <si>
+    <t>十九阶升阶石</t>
+  </si>
+  <si>
+    <t>50000109</t>
+  </si>
+  <si>
+    <t>210075</t>
+  </si>
+  <si>
+    <t>二十阶升阶石</t>
+  </si>
+  <si>
+    <t>50000110</t>
+  </si>
+  <si>
+    <t>210076</t>
+  </si>
+  <si>
+    <t>二一阶升阶石</t>
+  </si>
+  <si>
+    <t>50000111</t>
+  </si>
+  <si>
     <t>1400000</t>
   </si>
   <si>
@@ -2659,6 +2755,216 @@
     <t>地狱龙爪</t>
   </si>
   <si>
+    <t>1400089</t>
+  </si>
+  <si>
+    <t>深渊鸡爪</t>
+  </si>
+  <si>
+    <t>1400090</t>
+  </si>
+  <si>
+    <t>深渊鹿茸</t>
+  </si>
+  <si>
+    <t>1400091</t>
+  </si>
+  <si>
+    <t>深渊草帽</t>
+  </si>
+  <si>
+    <t>1400092</t>
+  </si>
+  <si>
+    <t>深渊猫爪</t>
+  </si>
+  <si>
+    <t>1400093</t>
+  </si>
+  <si>
+    <t>深渊花朵</t>
+  </si>
+  <si>
+    <t>1400094</t>
+  </si>
+  <si>
+    <t>深渊冰晶</t>
+  </si>
+  <si>
+    <t>1400095</t>
+  </si>
+  <si>
+    <t>深渊蝠翼</t>
+  </si>
+  <si>
+    <t>1400096</t>
+  </si>
+  <si>
+    <t>深渊魂火</t>
+  </si>
+  <si>
+    <t>1400097</t>
+  </si>
+  <si>
+    <t>深渊腐肉</t>
+  </si>
+  <si>
+    <t>1400098</t>
+  </si>
+  <si>
+    <t>深渊蛇胆</t>
+  </si>
+  <si>
+    <t>1400099</t>
+  </si>
+  <si>
+    <t>深渊狼爪</t>
+  </si>
+  <si>
+    <t>1400100</t>
+  </si>
+  <si>
+    <t>深渊虫皮</t>
+  </si>
+  <si>
+    <t>1400101</t>
+  </si>
+  <si>
+    <t>深渊鹰羽</t>
+  </si>
+  <si>
+    <t>1400102</t>
+  </si>
+  <si>
+    <t>深渊虫角</t>
+  </si>
+  <si>
+    <t>1400103</t>
+  </si>
+  <si>
+    <t>深渊蜈膏</t>
+  </si>
+  <si>
+    <t>1400104</t>
+  </si>
+  <si>
+    <t>深渊虫心</t>
+  </si>
+  <si>
+    <t>1400105</t>
+  </si>
+  <si>
+    <t>深渊龙皮</t>
+  </si>
+  <si>
+    <t>1400106</t>
+  </si>
+  <si>
+    <t>深渊猪皮</t>
+  </si>
+  <si>
+    <t>1400107</t>
+  </si>
+  <si>
+    <t>深渊猪心</t>
+  </si>
+  <si>
+    <t>1400108</t>
+  </si>
+  <si>
+    <t>深渊蝎皮</t>
+  </si>
+  <si>
+    <t>1400109</t>
+  </si>
+  <si>
+    <t>深渊宝甲</t>
+  </si>
+  <si>
+    <t>1400110</t>
+  </si>
+  <si>
+    <t>深渊号角</t>
+  </si>
+  <si>
+    <t>1400111</t>
+  </si>
+  <si>
+    <t>深渊雕像</t>
+  </si>
+  <si>
+    <t>1400112</t>
+  </si>
+  <si>
+    <t>深渊神像</t>
+  </si>
+  <si>
+    <t>1400113</t>
+  </si>
+  <si>
+    <t>深渊獠牙</t>
+  </si>
+  <si>
+    <t>1400114</t>
+  </si>
+  <si>
+    <t>深渊树心</t>
+  </si>
+  <si>
+    <t>1400115</t>
+  </si>
+  <si>
+    <t>深渊魔心</t>
+  </si>
+  <si>
+    <t>1400116</t>
+  </si>
+  <si>
+    <t>深渊尸心</t>
+  </si>
+  <si>
+    <t>1400117</t>
+  </si>
+  <si>
+    <t>深渊法杖</t>
+  </si>
+  <si>
+    <t>1400118</t>
+  </si>
+  <si>
+    <t>深渊权杖</t>
+  </si>
+  <si>
+    <t>1400119</t>
+  </si>
+  <si>
+    <t>深渊战锤</t>
+  </si>
+  <si>
+    <t>1400120</t>
+  </si>
+  <si>
+    <t>深渊血核</t>
+  </si>
+  <si>
+    <t>1400121</t>
+  </si>
+  <si>
+    <t>深渊魔核</t>
+  </si>
+  <si>
+    <t>1400122</t>
+  </si>
+  <si>
+    <t>深渊龙甲</t>
+  </si>
+  <si>
+    <t>1400123</t>
+  </si>
+  <si>
+    <t>深渊龙爪</t>
+  </si>
+  <si>
     <t>BOSS杀手</t>
   </si>
   <si>
@@ -3041,6 +3347,15 @@
   </si>
   <si>
     <t>104,204,304,404</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>五阶四格</t>
+  </si>
+  <si>
+    <t>105,205,305,405</t>
   </si>
   <si>
     <t>501</t>
@@ -4135,8 +4450,8 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment wrapText="1"/>
@@ -6700,7 +7015,7 @@
       <c r="H111" s="2">
         <v>1</v>
       </c>
-      <c r="I111" s="14" t="s">
+      <c r="I111" s="20" t="s">
         <v>339</v>
       </c>
     </row>
@@ -6709,7 +7024,7 @@
         <v>202002</v>
       </c>
       <c r="D112" s="2">
-        <v>1100</v>
+        <v>1450</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>340</v>
@@ -6723,124 +7038,24 @@
       <c r="H112" s="2">
         <v>2</v>
       </c>
-      <c r="I112" s="14" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" spans="3:9">
-      <c r="C113" s="2">
-        <v>202003</v>
-      </c>
-      <c r="D113" s="2">
-        <v>1100</v>
-      </c>
-      <c r="E113" s="2" t="s">
+      <c r="I112" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="F113" s="2">
-        <v>1</v>
-      </c>
-      <c r="G113" s="2">
-        <v>2</v>
-      </c>
-      <c r="H113" s="2">
-        <v>3</v>
-      </c>
-      <c r="I113" s="14" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="114" customHeight="1" spans="3:9">
-      <c r="C114" s="2">
-        <v>202004</v>
-      </c>
-      <c r="D114" s="2">
-        <v>1100</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F114" s="2">
-        <v>1</v>
-      </c>
-      <c r="G114" s="2">
-        <v>2</v>
-      </c>
-      <c r="H114" s="2">
-        <v>4</v>
-      </c>
-      <c r="I114" s="14" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" spans="3:9">
-      <c r="C115" s="2">
-        <v>202005</v>
-      </c>
-      <c r="D115" s="2">
-        <v>1100</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="F115" s="2">
-        <v>1</v>
-      </c>
-      <c r="G115" s="2">
-        <v>2</v>
-      </c>
-      <c r="H115" s="2">
-        <v>5</v>
-      </c>
-      <c r="I115" s="14" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" spans="3:9">
-      <c r="C116" s="2">
-        <v>202006</v>
-      </c>
-      <c r="D116" s="2">
-        <v>1100</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="F116" s="2">
-        <v>1</v>
-      </c>
-      <c r="G116" s="2">
-        <v>2</v>
-      </c>
-      <c r="H116" s="2">
-        <v>6</v>
-      </c>
-      <c r="I116" s="14" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" spans="3:9">
-      <c r="C117" s="2">
-        <v>202007</v>
-      </c>
-      <c r="D117" s="2">
-        <v>1100</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F117" s="2">
-        <v>1</v>
-      </c>
-      <c r="G117" s="2">
-        <v>2</v>
-      </c>
-      <c r="H117" s="2">
-        <v>7</v>
-      </c>
-      <c r="I117" s="14" t="s">
-        <v>339</v>
-      </c>
+    </row>
+    <row r="113" customHeight="1" spans="9:9">
+      <c r="I113" s="14"/>
+    </row>
+    <row r="114" customHeight="1" spans="9:9">
+      <c r="I114" s="14"/>
+    </row>
+    <row r="115" customHeight="1" spans="9:9">
+      <c r="I115" s="14"/>
+    </row>
+    <row r="116" customHeight="1" spans="9:9">
+      <c r="I116" s="14"/>
+    </row>
+    <row r="117" customHeight="1" spans="9:9">
+      <c r="I117" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6858,7 +7073,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H80"/>
+  <dimension ref="C1:H93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -6940,13 +7155,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="19" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -6955,18 +7170,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="19" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -6975,18 +7190,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="19" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -6995,18 +7210,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="19" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -7015,18 +7230,18 @@
         <v>20</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="19" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -7035,18 +7250,18 @@
         <v>20</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="19" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -7055,18 +7270,18 @@
         <v>20</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="19" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -7075,18 +7290,18 @@
         <v>20</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="19" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -7095,18 +7310,18 @@
         <v>20</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="19" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -7115,18 +7330,18 @@
         <v>20</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="19" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>19</v>
@@ -7135,118 +7350,118 @@
         <v>20</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C17" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="18" t="s">
         <v>377</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="2">
-        <v>5</v>
-      </c>
-      <c r="H16" s="18" t="s">
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C18" s="19" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:8">
-      <c r="C17" s="19" t="s">
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="18" t="s">
         <v>380</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="2">
-        <v>5</v>
-      </c>
-      <c r="H17" s="18" t="s">
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C19" s="19" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:8">
-      <c r="C18" s="19" t="s">
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="2">
-        <v>5</v>
-      </c>
-      <c r="H18" s="18" t="s">
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C20" s="19" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:8">
-      <c r="C19" s="19" t="s">
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="2">
-        <v>5</v>
-      </c>
-      <c r="H19" s="18" t="s">
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C21" s="19" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:8">
-      <c r="C20" s="19" t="s">
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="2">
-        <v>5</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:8">
-      <c r="C21" s="19" t="s">
-        <v>391</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>19</v>
@@ -7255,18 +7470,18 @@
         <v>5</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:8">
       <c r="C22" s="19" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>19</v>
@@ -7275,18 +7490,18 @@
         <v>5</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:8">
       <c r="C23" s="19" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>19</v>
@@ -7295,18 +7510,18 @@
         <v>5</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:8">
       <c r="C24" s="19" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>19</v>
@@ -7315,18 +7530,18 @@
         <v>5</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:8">
       <c r="C25" s="19" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>19</v>
@@ -7335,18 +7550,18 @@
         <v>5</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:8">
       <c r="C26" s="19" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>19</v>
@@ -7355,18 +7570,18 @@
         <v>5</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
       <c r="C27" s="19" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>19</v>
@@ -7375,18 +7590,18 @@
         <v>5</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
       <c r="C28" s="19" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -7395,18 +7610,18 @@
         <v>5</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
       <c r="C29" s="19" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -7415,18 +7630,18 @@
         <v>5</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
       <c r="C30" s="19" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -7435,18 +7650,18 @@
         <v>5</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="19" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>19</v>
@@ -7455,18 +7670,18 @@
         <v>5</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="19" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>19</v>
@@ -7475,18 +7690,18 @@
         <v>5</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="19" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>19</v>
@@ -7495,18 +7710,18 @@
         <v>5</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="19" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>19</v>
@@ -7515,18 +7730,18 @@
         <v>5</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
       <c r="C35" s="19" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>19</v>
@@ -7535,18 +7750,18 @@
         <v>5</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
       <c r="C36" s="19" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>19</v>
@@ -7555,18 +7770,18 @@
         <v>5</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
       <c r="C37" s="19" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>19</v>
@@ -7575,18 +7790,18 @@
         <v>5</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="19" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>19</v>
@@ -7595,18 +7810,18 @@
         <v>5</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="19" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>19</v>
@@ -7615,18 +7830,18 @@
         <v>5</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
       <c r="C40" s="19" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>19</v>
@@ -7635,18 +7850,18 @@
         <v>5</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
       <c r="C41" s="19" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>19</v>
@@ -7655,18 +7870,18 @@
         <v>5</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="19" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>19</v>
@@ -7675,18 +7890,18 @@
         <v>5</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="19" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>19</v>
@@ -7695,18 +7910,18 @@
         <v>5</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="19" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>19</v>
@@ -7715,18 +7930,18 @@
         <v>5</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="19" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>19</v>
@@ -7735,18 +7950,18 @@
         <v>5</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="19" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>19</v>
@@ -7754,19 +7969,19 @@
       <c r="G46" s="2">
         <v>5</v>
       </c>
-      <c r="H46" s="20" t="s">
-        <v>468</v>
+      <c r="H46" s="18" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="19" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D47" s="2">
         <v>0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>19</v>
@@ -7774,19 +7989,19 @@
       <c r="G47" s="2">
         <v>5</v>
       </c>
-      <c r="H47" s="20" t="s">
-        <v>471</v>
+      <c r="H47" s="18" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="19" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>19</v>
@@ -7794,19 +8009,19 @@
       <c r="G48" s="2">
         <v>5</v>
       </c>
-      <c r="H48" s="20" t="s">
-        <v>474</v>
+      <c r="H48" s="18" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="19" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>19</v>
@@ -7814,19 +8029,19 @@
       <c r="G49" s="2">
         <v>5</v>
       </c>
-      <c r="H49" s="20" t="s">
-        <v>477</v>
+      <c r="H49" s="18" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="19" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>19</v>
@@ -7834,19 +8049,19 @@
       <c r="G50" s="2">
         <v>5</v>
       </c>
-      <c r="H50" s="20" t="s">
-        <v>480</v>
+      <c r="H50" s="18" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="19" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>19</v>
@@ -7854,19 +8069,19 @@
       <c r="G51" s="2">
         <v>5</v>
       </c>
-      <c r="H51" s="20" t="s">
-        <v>483</v>
+      <c r="H51" s="21" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
       <c r="C52" s="19" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>19</v>
@@ -7874,19 +8089,19 @@
       <c r="G52" s="2">
         <v>5</v>
       </c>
-      <c r="H52" s="20" t="s">
-        <v>486</v>
+      <c r="H52" s="21" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
       <c r="C53" s="19" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>19</v>
@@ -7894,19 +8109,19 @@
       <c r="G53" s="2">
         <v>5</v>
       </c>
-      <c r="H53" s="20" t="s">
-        <v>489</v>
+      <c r="H53" s="21" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="19" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>19</v>
@@ -7914,19 +8129,19 @@
       <c r="G54" s="2">
         <v>5</v>
       </c>
-      <c r="H54" s="20" t="s">
-        <v>492</v>
+      <c r="H54" s="21" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="19" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>19</v>
@@ -7934,19 +8149,19 @@
       <c r="G55" s="2">
         <v>5</v>
       </c>
-      <c r="H55" s="20" t="s">
-        <v>495</v>
+      <c r="H55" s="21" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="19" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>19</v>
@@ -7954,19 +8169,19 @@
       <c r="G56" s="2">
         <v>5</v>
       </c>
-      <c r="H56" s="20" t="s">
-        <v>498</v>
+      <c r="H56" s="21" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="19" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>19</v>
@@ -7974,19 +8189,19 @@
       <c r="G57" s="2">
         <v>5</v>
       </c>
-      <c r="H57" s="20" t="s">
-        <v>501</v>
+      <c r="H57" s="21" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="19" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
@@ -7994,19 +8209,19 @@
       <c r="G58" s="2">
         <v>5</v>
       </c>
-      <c r="H58" s="20" t="s">
-        <v>504</v>
+      <c r="H58" s="21" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="19" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
@@ -8014,19 +8229,19 @@
       <c r="G59" s="2">
         <v>5</v>
       </c>
-      <c r="H59" s="20" t="s">
-        <v>507</v>
+      <c r="H59" s="21" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="19" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D60" s="2">
         <v>0</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
@@ -8034,19 +8249,19 @@
       <c r="G60" s="2">
         <v>5</v>
       </c>
-      <c r="H60" s="20" t="s">
-        <v>510</v>
+      <c r="H60" s="21" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="19" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D61" s="2">
         <v>0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
@@ -8054,19 +8269,19 @@
       <c r="G61" s="2">
         <v>5</v>
       </c>
-      <c r="H61" s="20" t="s">
-        <v>513</v>
+      <c r="H61" s="21" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:8">
       <c r="C62" s="19" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
@@ -8074,19 +8289,19 @@
       <c r="G62" s="2">
         <v>5</v>
       </c>
-      <c r="H62" s="20" t="s">
-        <v>516</v>
+      <c r="H62" s="21" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
       <c r="C63" s="19" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="D63" s="2">
         <v>0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
@@ -8094,19 +8309,19 @@
       <c r="G63" s="2">
         <v>5</v>
       </c>
-      <c r="H63" s="20" t="s">
-        <v>519</v>
+      <c r="H63" s="21" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
       <c r="C64" s="19" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
@@ -8114,19 +8329,19 @@
       <c r="G64" s="2">
         <v>5</v>
       </c>
-      <c r="H64" s="20" t="s">
-        <v>522</v>
+      <c r="H64" s="21" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
       <c r="C65" s="19" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
@@ -8134,19 +8349,19 @@
       <c r="G65" s="2">
         <v>5</v>
       </c>
-      <c r="H65" s="20" t="s">
-        <v>525</v>
+      <c r="H65" s="21" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
       <c r="C66" s="19" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D66" s="2">
         <v>0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
@@ -8154,19 +8369,19 @@
       <c r="G66" s="2">
         <v>5</v>
       </c>
-      <c r="H66" s="20" t="s">
-        <v>528</v>
+      <c r="H66" s="21" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="19" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
@@ -8174,19 +8389,19 @@
       <c r="G67" s="2">
         <v>5</v>
       </c>
-      <c r="H67" s="20" t="s">
-        <v>531</v>
+      <c r="H67" s="21" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="19" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>19</v>
@@ -8194,19 +8409,19 @@
       <c r="G68" s="2">
         <v>5</v>
       </c>
-      <c r="H68" s="20" t="s">
-        <v>534</v>
+      <c r="H68" s="21" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
       <c r="C69" s="19" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>19</v>
@@ -8214,19 +8429,19 @@
       <c r="G69" s="2">
         <v>5</v>
       </c>
-      <c r="H69" s="20" t="s">
-        <v>537</v>
+      <c r="H69" s="21" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="19" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D70" s="2">
         <v>0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>19</v>
@@ -8234,19 +8449,19 @@
       <c r="G70" s="2">
         <v>5</v>
       </c>
-      <c r="H70" s="20" t="s">
-        <v>540</v>
+      <c r="H70" s="21" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="19" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>19</v>
@@ -8254,19 +8469,19 @@
       <c r="G71" s="2">
         <v>5</v>
       </c>
-      <c r="H71" s="20" t="s">
-        <v>543</v>
+      <c r="H71" s="21" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
       <c r="C72" s="19" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>19</v>
@@ -8274,19 +8489,19 @@
       <c r="G72" s="2">
         <v>5</v>
       </c>
-      <c r="H72" s="20" t="s">
-        <v>546</v>
+      <c r="H72" s="21" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
       <c r="C73" s="19" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>19</v>
@@ -8294,19 +8509,19 @@
       <c r="G73" s="2">
         <v>5</v>
       </c>
-      <c r="H73" s="20" t="s">
-        <v>549</v>
+      <c r="H73" s="21" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:8">
       <c r="C74" s="19" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>19</v>
@@ -8314,19 +8529,19 @@
       <c r="G74" s="2">
         <v>5</v>
       </c>
-      <c r="H74" s="20" t="s">
-        <v>552</v>
+      <c r="H74" s="21" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
       <c r="C75" s="19" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D75" s="2">
         <v>0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>19</v>
@@ -8334,19 +8549,19 @@
       <c r="G75" s="2">
         <v>5</v>
       </c>
-      <c r="H75" s="20" t="s">
-        <v>555</v>
+      <c r="H75" s="21" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
       <c r="C76" s="19" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="D76" s="2">
         <v>0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>19</v>
@@ -8354,19 +8569,19 @@
       <c r="G76" s="2">
         <v>5</v>
       </c>
-      <c r="H76" s="20" t="s">
-        <v>558</v>
+      <c r="H76" s="21" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
       <c r="C77" s="19" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="D77" s="2">
         <v>0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>19</v>
@@ -8374,19 +8589,19 @@
       <c r="G77" s="2">
         <v>5</v>
       </c>
-      <c r="H77" s="20" t="s">
-        <v>561</v>
+      <c r="H77" s="21" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:8">
       <c r="C78" s="19" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="D78" s="2">
         <v>0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>19</v>
@@ -8394,19 +8609,19 @@
       <c r="G78" s="2">
         <v>5</v>
       </c>
-      <c r="H78" s="20" t="s">
-        <v>564</v>
+      <c r="H78" s="21" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:8">
       <c r="C79" s="19" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D79" s="2">
         <v>0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>19</v>
@@ -8414,19 +8629,19 @@
       <c r="G79" s="2">
         <v>5</v>
       </c>
-      <c r="H79" s="20" t="s">
-        <v>567</v>
+      <c r="H79" s="21" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="C80" s="19" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="D80" s="2">
         <v>0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>19</v>
@@ -8434,9 +8649,252 @@
       <c r="G80" s="2">
         <v>5</v>
       </c>
-      <c r="H80" s="20" t="s">
+      <c r="H80" s="21" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:8">
+      <c r="C81" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="D81" s="2">
+        <v>0</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="2">
+        <v>5</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:8">
+      <c r="C82" s="19" t="s">
         <v>570</v>
       </c>
+      <c r="D82" s="2">
+        <v>0</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G82" s="2">
+        <v>5</v>
+      </c>
+      <c r="H82" s="21" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:8">
+      <c r="C83" s="19" t="s">
+        <v>573</v>
+      </c>
+      <c r="D83" s="2">
+        <v>0</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="2">
+        <v>5</v>
+      </c>
+      <c r="H83" s="21" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:8">
+      <c r="C84" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="D84" s="2">
+        <v>0</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G84" s="2">
+        <v>5</v>
+      </c>
+      <c r="H84" s="21" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:8">
+      <c r="C85" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="D85" s="2">
+        <v>0</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85" s="2">
+        <v>5</v>
+      </c>
+      <c r="H85" s="21" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:8">
+      <c r="C86" s="19" t="s">
+        <v>582</v>
+      </c>
+      <c r="D86" s="2">
+        <v>0</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86" s="2">
+        <v>5</v>
+      </c>
+      <c r="H86" s="21" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:8">
+      <c r="C87" s="19" t="s">
+        <v>585</v>
+      </c>
+      <c r="D87" s="2">
+        <v>0</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G87" s="2">
+        <v>5</v>
+      </c>
+      <c r="H87" s="21" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:8">
+      <c r="C88" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="D88" s="2">
+        <v>0</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G88" s="2">
+        <v>5</v>
+      </c>
+      <c r="H88" s="21" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:8">
+      <c r="C89" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="D89" s="2">
+        <v>0</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" s="2">
+        <v>5</v>
+      </c>
+      <c r="H89" s="21" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:8">
+      <c r="C90" s="19" t="s">
+        <v>594</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G90" s="2">
+        <v>5</v>
+      </c>
+      <c r="H90" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:8">
+      <c r="C91" s="19" t="s">
+        <v>597</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91" s="2">
+        <v>5</v>
+      </c>
+      <c r="H91" s="21" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:8">
+      <c r="C92" s="19" t="s">
+        <v>600</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" s="2">
+        <v>5</v>
+      </c>
+      <c r="H92" s="21" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:3">
+      <c r="C93" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -8453,7 +8911,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -8535,13 +8993,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="19" t="s">
-        <v>571</v>
+        <v>603</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>572</v>
+        <v>604</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -8555,13 +9013,13 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="19" t="s">
-        <v>573</v>
+        <v>605</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>574</v>
+        <v>606</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -8575,13 +9033,13 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="19" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>576</v>
+        <v>608</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -8595,13 +9053,13 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="19" t="s">
-        <v>577</v>
+        <v>609</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>578</v>
+        <v>610</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -8615,13 +9073,13 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="19" t="s">
-        <v>579</v>
+        <v>611</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>580</v>
+        <v>612</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -8637,13 +9095,13 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="19" t="s">
-        <v>581</v>
+        <v>613</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>582</v>
+        <v>614</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -8658,13 +9116,13 @@
     </row>
     <row r="12" customHeight="1" spans="3:8">
       <c r="C12" s="19" t="s">
-        <v>583</v>
+        <v>615</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>584</v>
+        <v>616</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -8678,13 +9136,13 @@
     </row>
     <row r="13" customHeight="1" spans="3:8">
       <c r="C13" s="19" t="s">
-        <v>585</v>
+        <v>617</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>586</v>
+        <v>618</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -8698,13 +9156,13 @@
     </row>
     <row r="14" customHeight="1" spans="3:8">
       <c r="C14" s="19" t="s">
-        <v>587</v>
+        <v>619</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>588</v>
+        <v>620</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -8718,13 +9176,13 @@
     </row>
     <row r="15" customHeight="1" spans="3:8">
       <c r="C15" s="19" t="s">
-        <v>589</v>
+        <v>621</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>590</v>
+        <v>622</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>19</v>
@@ -8738,13 +9196,13 @@
     </row>
     <row r="16" customHeight="1" spans="3:8">
       <c r="C16" s="19" t="s">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>592</v>
+        <v>624</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>19</v>
@@ -8758,13 +9216,13 @@
     </row>
     <row r="17" customHeight="1" spans="3:8">
       <c r="C17" s="19" t="s">
-        <v>593</v>
+        <v>625</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>594</v>
+        <v>626</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>19</v>
@@ -8778,13 +9236,13 @@
     </row>
     <row r="18" customHeight="1" spans="3:8">
       <c r="C18" s="19" t="s">
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>596</v>
+        <v>628</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>19</v>
@@ -8798,13 +9256,13 @@
     </row>
     <row r="19" customHeight="1" spans="3:8">
       <c r="C19" s="19" t="s">
-        <v>597</v>
+        <v>629</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>598</v>
+        <v>630</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>19</v>
@@ -8818,13 +9276,13 @@
     </row>
     <row r="20" customHeight="1" spans="3:8">
       <c r="C20" s="19" t="s">
-        <v>599</v>
+        <v>631</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -8838,13 +9296,13 @@
     </row>
     <row r="21" customHeight="1" spans="3:8">
       <c r="C21" s="19" t="s">
-        <v>601</v>
+        <v>633</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>19</v>
@@ -8858,13 +9316,13 @@
     </row>
     <row r="22" customHeight="1" spans="3:8">
       <c r="C22" s="19" t="s">
-        <v>603</v>
+        <v>635</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>604</v>
+        <v>636</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>19</v>
@@ -8878,13 +9336,13 @@
     </row>
     <row r="23" customHeight="1" spans="3:8">
       <c r="C23" s="19" t="s">
-        <v>605</v>
+        <v>637</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>606</v>
+        <v>638</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>19</v>
@@ -8898,13 +9356,13 @@
     </row>
     <row r="24" customHeight="1" spans="3:8">
       <c r="C24" s="19" t="s">
-        <v>607</v>
+        <v>639</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>608</v>
+        <v>640</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>19</v>
@@ -8918,13 +9376,13 @@
     </row>
     <row r="25" customHeight="1" spans="3:8">
       <c r="C25" s="19" t="s">
-        <v>609</v>
+        <v>641</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>19</v>
@@ -8938,13 +9396,13 @@
     </row>
     <row r="26" customHeight="1" spans="3:8">
       <c r="C26" s="19" t="s">
-        <v>611</v>
+        <v>643</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>612</v>
+        <v>644</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>19</v>
@@ -8958,13 +9416,13 @@
     </row>
     <row r="27" customHeight="1" spans="3:8">
       <c r="C27" s="19" t="s">
-        <v>613</v>
+        <v>645</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>614</v>
+        <v>646</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>19</v>
@@ -8978,13 +9436,13 @@
     </row>
     <row r="28" customHeight="1" spans="3:8">
       <c r="C28" s="19" t="s">
-        <v>615</v>
+        <v>647</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>616</v>
+        <v>648</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -8998,13 +9456,13 @@
     </row>
     <row r="29" customHeight="1" spans="3:8">
       <c r="C29" s="19" t="s">
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>618</v>
+        <v>650</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -9018,13 +9476,13 @@
     </row>
     <row r="30" customHeight="1" spans="3:8">
       <c r="C30" s="19" t="s">
-        <v>619</v>
+        <v>651</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>620</v>
+        <v>652</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -9038,13 +9496,13 @@
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="19" t="s">
-        <v>621</v>
+        <v>653</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>622</v>
+        <v>654</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>19</v>
@@ -9058,13 +9516,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="19" t="s">
-        <v>623</v>
+        <v>655</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>624</v>
+        <v>656</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>19</v>
@@ -9078,13 +9536,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="19" t="s">
-        <v>625</v>
+        <v>657</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>626</v>
+        <v>658</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>19</v>
@@ -9098,13 +9556,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="19" t="s">
-        <v>627</v>
+        <v>659</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>628</v>
+        <v>660</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>19</v>
@@ -9118,13 +9576,13 @@
     </row>
     <row r="35" customHeight="1" spans="3:8">
       <c r="C35" s="19" t="s">
-        <v>629</v>
+        <v>661</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>630</v>
+        <v>662</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>19</v>
@@ -9138,13 +9596,13 @@
     </row>
     <row r="36" customHeight="1" spans="3:8">
       <c r="C36" s="19" t="s">
-        <v>631</v>
+        <v>663</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>19</v>
@@ -9158,13 +9616,13 @@
     </row>
     <row r="37" customHeight="1" spans="3:8">
       <c r="C37" s="19" t="s">
-        <v>633</v>
+        <v>665</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>19</v>
@@ -9178,13 +9636,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="19" t="s">
-        <v>635</v>
+        <v>667</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>636</v>
+        <v>668</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>19</v>
@@ -9198,13 +9656,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="19" t="s">
-        <v>637</v>
+        <v>669</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>638</v>
+        <v>670</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>19</v>
@@ -9218,13 +9676,13 @@
     </row>
     <row r="40" customHeight="1" spans="3:8">
       <c r="C40" s="19" t="s">
-        <v>639</v>
+        <v>671</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>19</v>
@@ -9238,13 +9696,13 @@
     </row>
     <row r="41" customHeight="1" spans="3:8">
       <c r="C41" s="19" t="s">
-        <v>641</v>
+        <v>673</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>642</v>
+        <v>674</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>19</v>
@@ -9258,13 +9716,13 @@
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="19" t="s">
-        <v>643</v>
+        <v>675</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>644</v>
+        <v>676</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>19</v>
@@ -9278,13 +9736,13 @@
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="19" t="s">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>19</v>
@@ -9298,13 +9756,13 @@
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="19" t="s">
-        <v>647</v>
+        <v>679</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>19</v>
@@ -9318,13 +9776,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="19" t="s">
-        <v>649</v>
+        <v>681</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>19</v>
@@ -9338,13 +9796,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="19" t="s">
-        <v>651</v>
+        <v>683</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>652</v>
+        <v>684</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>19</v>
@@ -9358,13 +9816,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="19" t="s">
-        <v>653</v>
+        <v>685</v>
       </c>
       <c r="D47" s="2">
         <v>0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>654</v>
+        <v>686</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>19</v>
@@ -9378,13 +9836,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="19" t="s">
-        <v>655</v>
+        <v>687</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>656</v>
+        <v>688</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>19</v>
@@ -9398,13 +9856,13 @@
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="19" t="s">
-        <v>657</v>
+        <v>689</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>19</v>
@@ -9418,13 +9876,13 @@
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="19" t="s">
-        <v>659</v>
+        <v>691</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>660</v>
+        <v>692</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>19</v>
@@ -9438,13 +9896,13 @@
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="19" t="s">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>662</v>
+        <v>694</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>19</v>
@@ -9458,13 +9916,13 @@
     </row>
     <row r="52" customHeight="1" spans="3:8">
       <c r="C52" s="19" t="s">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>664</v>
+        <v>696</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>19</v>
@@ -9478,13 +9936,13 @@
     </row>
     <row r="53" customHeight="1" spans="3:8">
       <c r="C53" s="19" t="s">
-        <v>665</v>
+        <v>697</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>666</v>
+        <v>698</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>19</v>
@@ -9498,13 +9956,13 @@
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="19" t="s">
-        <v>667</v>
+        <v>699</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>656</v>
+        <v>688</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>19</v>
@@ -9518,13 +9976,13 @@
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="19" t="s">
-        <v>668</v>
+        <v>700</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>19</v>
@@ -9538,13 +9996,13 @@
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="19" t="s">
-        <v>670</v>
+        <v>702</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>671</v>
+        <v>703</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>19</v>
@@ -9558,13 +10016,13 @@
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="19" t="s">
-        <v>672</v>
+        <v>704</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>673</v>
+        <v>705</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>19</v>
@@ -9578,13 +10036,13 @@
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="19" t="s">
-        <v>674</v>
+        <v>706</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>675</v>
+        <v>707</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
@@ -9598,13 +10056,13 @@
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="19" t="s">
-        <v>676</v>
+        <v>708</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>677</v>
+        <v>709</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
@@ -9618,13 +10076,13 @@
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="19" t="s">
-        <v>678</v>
+        <v>710</v>
       </c>
       <c r="D60" s="2">
         <v>0</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>679</v>
+        <v>711</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
@@ -9638,13 +10096,13 @@
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="19" t="s">
-        <v>680</v>
+        <v>712</v>
       </c>
       <c r="D61" s="2">
         <v>0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>681</v>
+        <v>713</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
@@ -9658,13 +10116,13 @@
     </row>
     <row r="62" customHeight="1" spans="3:8">
       <c r="C62" s="19" t="s">
-        <v>682</v>
+        <v>714</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>683</v>
+        <v>715</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
@@ -9678,13 +10136,13 @@
     </row>
     <row r="63" customHeight="1" spans="3:8">
       <c r="C63" s="19" t="s">
-        <v>684</v>
+        <v>716</v>
       </c>
       <c r="D63" s="2">
         <v>0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>685</v>
+        <v>717</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
@@ -9698,13 +10156,13 @@
     </row>
     <row r="64" customHeight="1" spans="3:8">
       <c r="C64" s="19" t="s">
-        <v>686</v>
+        <v>718</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>687</v>
+        <v>719</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
@@ -9718,13 +10176,13 @@
     </row>
     <row r="65" customHeight="1" spans="3:8">
       <c r="C65" s="19" t="s">
-        <v>688</v>
+        <v>720</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>689</v>
+        <v>721</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
@@ -9738,13 +10196,13 @@
     </row>
     <row r="66" customHeight="1" spans="3:8">
       <c r="C66" s="19" t="s">
-        <v>690</v>
+        <v>722</v>
       </c>
       <c r="D66" s="2">
         <v>0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>691</v>
+        <v>723</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
@@ -9758,13 +10216,13 @@
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="19" t="s">
-        <v>692</v>
+        <v>724</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>693</v>
+        <v>725</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
@@ -9778,13 +10236,13 @@
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="19" t="s">
-        <v>694</v>
+        <v>726</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>695</v>
+        <v>727</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>19</v>
@@ -9798,13 +10256,13 @@
     </row>
     <row r="69" customHeight="1" spans="3:8">
       <c r="C69" s="19" t="s">
-        <v>696</v>
+        <v>728</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>697</v>
+        <v>729</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>19</v>
@@ -9818,13 +10276,13 @@
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="19" t="s">
-        <v>698</v>
+        <v>730</v>
       </c>
       <c r="D70" s="2">
         <v>0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>699</v>
+        <v>731</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>19</v>
@@ -9838,13 +10296,13 @@
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="19" t="s">
-        <v>700</v>
+        <v>732</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>701</v>
+        <v>733</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>19</v>
@@ -9858,13 +10316,13 @@
     </row>
     <row r="72" customHeight="1" spans="3:8">
       <c r="C72" s="19" t="s">
-        <v>702</v>
+        <v>734</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>703</v>
+        <v>735</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>19</v>
@@ -9878,13 +10336,13 @@
     </row>
     <row r="73" customHeight="1" spans="3:8">
       <c r="C73" s="19" t="s">
-        <v>704</v>
+        <v>736</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>705</v>
+        <v>737</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>19</v>
@@ -9898,13 +10356,13 @@
     </row>
     <row r="74" customHeight="1" spans="3:8">
       <c r="C74" s="19" t="s">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>707</v>
+        <v>739</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>19</v>
@@ -9918,13 +10376,13 @@
     </row>
     <row r="75" customHeight="1" spans="3:8">
       <c r="C75" s="19" t="s">
-        <v>708</v>
+        <v>740</v>
       </c>
       <c r="D75" s="2">
         <v>0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>709</v>
+        <v>741</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>19</v>
@@ -9938,13 +10396,13 @@
     </row>
     <row r="76" customHeight="1" spans="3:8">
       <c r="C76" s="19" t="s">
-        <v>710</v>
+        <v>742</v>
       </c>
       <c r="D76" s="2">
         <v>0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>711</v>
+        <v>743</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>19</v>
@@ -9958,13 +10416,13 @@
     </row>
     <row r="77" customHeight="1" spans="3:8">
       <c r="C77" s="19" t="s">
-        <v>712</v>
+        <v>744</v>
       </c>
       <c r="D77" s="2">
         <v>0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>713</v>
+        <v>745</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>19</v>
@@ -9978,13 +10436,13 @@
     </row>
     <row r="78" customHeight="1" spans="3:8">
       <c r="C78" s="19" t="s">
-        <v>714</v>
+        <v>746</v>
       </c>
       <c r="D78" s="2">
         <v>0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>715</v>
+        <v>747</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>19</v>
@@ -9998,13 +10456,13 @@
     </row>
     <row r="79" customHeight="1" spans="3:8">
       <c r="C79" s="19" t="s">
-        <v>716</v>
+        <v>748</v>
       </c>
       <c r="D79" s="2">
         <v>0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>717</v>
+        <v>749</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>19</v>
@@ -10018,13 +10476,13 @@
     </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="C80" s="19" t="s">
-        <v>718</v>
+        <v>750</v>
       </c>
       <c r="D80" s="2">
         <v>0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>719</v>
+        <v>751</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>19</v>
@@ -10038,13 +10496,13 @@
     </row>
     <row r="81" customHeight="1" spans="3:8">
       <c r="C81" s="19" t="s">
-        <v>720</v>
+        <v>752</v>
       </c>
       <c r="D81" s="2">
         <v>0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>721</v>
+        <v>753</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>19</v>
@@ -10058,13 +10516,13 @@
     </row>
     <row r="82" customHeight="1" spans="3:8">
       <c r="C82" s="19" t="s">
-        <v>722</v>
+        <v>754</v>
       </c>
       <c r="D82" s="2">
         <v>0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>723</v>
+        <v>755</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>19</v>
@@ -10078,13 +10536,13 @@
     </row>
     <row r="83" customHeight="1" spans="3:8">
       <c r="C83" s="19" t="s">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="D83" s="2">
         <v>0</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>725</v>
+        <v>757</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>19</v>
@@ -10098,13 +10556,13 @@
     </row>
     <row r="84" customHeight="1" spans="3:8">
       <c r="C84" s="19" t="s">
-        <v>726</v>
+        <v>758</v>
       </c>
       <c r="D84" s="2">
         <v>0</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>727</v>
+        <v>759</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>19</v>
@@ -10118,13 +10576,13 @@
     </row>
     <row r="85" customHeight="1" spans="3:8">
       <c r="C85" s="19" t="s">
-        <v>728</v>
+        <v>760</v>
       </c>
       <c r="D85" s="2">
         <v>0</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>19</v>
@@ -10138,13 +10596,13 @@
     </row>
     <row r="86" customHeight="1" spans="3:8">
       <c r="C86" s="19" t="s">
-        <v>730</v>
+        <v>762</v>
       </c>
       <c r="D86" s="2">
         <v>0</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>731</v>
+        <v>763</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>19</v>
@@ -10158,13 +10616,13 @@
     </row>
     <row r="87" customHeight="1" spans="3:8">
       <c r="C87" s="19" t="s">
-        <v>732</v>
+        <v>764</v>
       </c>
       <c r="D87" s="2">
         <v>0</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>733</v>
+        <v>765</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>19</v>
@@ -10178,13 +10636,13 @@
     </row>
     <row r="88" customHeight="1" spans="3:8">
       <c r="C88" s="19" t="s">
-        <v>734</v>
+        <v>766</v>
       </c>
       <c r="D88" s="2">
         <v>0</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>735</v>
+        <v>767</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>19</v>
@@ -10198,13 +10656,13 @@
     </row>
     <row r="89" customHeight="1" spans="3:8">
       <c r="C89" s="19" t="s">
-        <v>736</v>
+        <v>768</v>
       </c>
       <c r="D89" s="2">
         <v>0</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>737</v>
+        <v>769</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>19</v>
@@ -10218,13 +10676,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:8">
       <c r="C90" s="19" t="s">
-        <v>738</v>
+        <v>770</v>
       </c>
       <c r="D90" s="2">
         <v>0</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>739</v>
+        <v>771</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>19</v>
@@ -10238,13 +10696,13 @@
     </row>
     <row r="91" customHeight="1" spans="3:8">
       <c r="C91" s="19" t="s">
-        <v>740</v>
+        <v>772</v>
       </c>
       <c r="D91" s="2">
         <v>0</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>741</v>
+        <v>773</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>19</v>
@@ -10258,13 +10716,13 @@
     </row>
     <row r="92" customHeight="1" spans="3:8">
       <c r="C92" s="19" t="s">
-        <v>742</v>
+        <v>774</v>
       </c>
       <c r="D92" s="2">
         <v>0</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>743</v>
+        <v>775</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>19</v>
@@ -10278,13 +10736,13 @@
     </row>
     <row r="93" customHeight="1" spans="3:8">
       <c r="C93" s="19" t="s">
-        <v>744</v>
+        <v>776</v>
       </c>
       <c r="D93" s="2">
         <v>0</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>745</v>
+        <v>777</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>19</v>
@@ -10298,13 +10756,13 @@
     </row>
     <row r="94" customHeight="1" spans="3:8">
       <c r="C94" s="19" t="s">
-        <v>746</v>
+        <v>778</v>
       </c>
       <c r="D94" s="2">
         <v>0</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>747</v>
+        <v>779</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>19</v>
@@ -10314,6 +10772,706 @@
       </c>
       <c r="H94" s="2">
         <v>40000139</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:8">
+      <c r="C95" s="19" t="s">
+        <v>780</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0</v>
+      </c>
+      <c r="E95" s="16" t="s">
+        <v>781</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G95" s="2">
+        <v>14</v>
+      </c>
+      <c r="H95" s="2">
+        <v>40000140</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:8">
+      <c r="C96" s="19" t="s">
+        <v>782</v>
+      </c>
+      <c r="D96" s="2">
+        <v>0</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G96" s="2">
+        <v>14</v>
+      </c>
+      <c r="H96" s="2">
+        <v>40000141</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:8">
+      <c r="C97" s="19" t="s">
+        <v>784</v>
+      </c>
+      <c r="D97" s="2">
+        <v>0</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G97" s="2">
+        <v>14</v>
+      </c>
+      <c r="H97" s="2">
+        <v>40000142</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:8">
+      <c r="C98" s="19" t="s">
+        <v>786</v>
+      </c>
+      <c r="D98" s="2">
+        <v>0</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G98" s="2">
+        <v>14</v>
+      </c>
+      <c r="H98" s="2">
+        <v>40000143</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:8">
+      <c r="C99" s="19" t="s">
+        <v>788</v>
+      </c>
+      <c r="D99" s="2">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G99" s="2">
+        <v>14</v>
+      </c>
+      <c r="H99" s="2">
+        <v>40000144</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:8">
+      <c r="C100" s="19" t="s">
+        <v>790</v>
+      </c>
+      <c r="D100" s="2">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G100" s="2">
+        <v>14</v>
+      </c>
+      <c r="H100" s="2">
+        <v>40000145</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:8">
+      <c r="C101" s="19" t="s">
+        <v>792</v>
+      </c>
+      <c r="D101" s="2">
+        <v>0</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G101" s="2">
+        <v>14</v>
+      </c>
+      <c r="H101" s="2">
+        <v>40000146</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:8">
+      <c r="C102" s="19" t="s">
+        <v>794</v>
+      </c>
+      <c r="D102" s="2">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G102" s="2">
+        <v>14</v>
+      </c>
+      <c r="H102" s="2">
+        <v>40000147</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:8">
+      <c r="C103" s="19" t="s">
+        <v>796</v>
+      </c>
+      <c r="D103" s="2">
+        <v>0</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G103" s="2">
+        <v>14</v>
+      </c>
+      <c r="H103" s="2">
+        <v>40000148</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:8">
+      <c r="C104" s="19" t="s">
+        <v>798</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G104" s="2">
+        <v>14</v>
+      </c>
+      <c r="H104" s="2">
+        <v>40000149</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:8">
+      <c r="C105" s="19" t="s">
+        <v>800</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G105" s="2">
+        <v>14</v>
+      </c>
+      <c r="H105" s="2">
+        <v>40000150</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:8">
+      <c r="C106" s="19" t="s">
+        <v>802</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G106" s="2">
+        <v>14</v>
+      </c>
+      <c r="H106" s="2">
+        <v>40000151</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:8">
+      <c r="C107" s="19" t="s">
+        <v>804</v>
+      </c>
+      <c r="D107" s="2">
+        <v>0</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G107" s="2">
+        <v>14</v>
+      </c>
+      <c r="H107" s="2">
+        <v>40000152</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:8">
+      <c r="C108" s="19" t="s">
+        <v>806</v>
+      </c>
+      <c r="D108" s="2">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G108" s="2">
+        <v>14</v>
+      </c>
+      <c r="H108" s="2">
+        <v>40000153</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:8">
+      <c r="C109" s="19" t="s">
+        <v>808</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G109" s="2">
+        <v>14</v>
+      </c>
+      <c r="H109" s="2">
+        <v>40000154</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:8">
+      <c r="C110" s="19" t="s">
+        <v>810</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G110" s="2">
+        <v>14</v>
+      </c>
+      <c r="H110" s="2">
+        <v>40000155</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:8">
+      <c r="C111" s="19" t="s">
+        <v>812</v>
+      </c>
+      <c r="D111" s="2">
+        <v>0</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G111" s="2">
+        <v>14</v>
+      </c>
+      <c r="H111" s="2">
+        <v>40000156</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:8">
+      <c r="C112" s="19" t="s">
+        <v>814</v>
+      </c>
+      <c r="D112" s="2">
+        <v>0</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G112" s="2">
+        <v>14</v>
+      </c>
+      <c r="H112" s="2">
+        <v>40000157</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:8">
+      <c r="C113" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="D113" s="2">
+        <v>0</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G113" s="2">
+        <v>14</v>
+      </c>
+      <c r="H113" s="2">
+        <v>40000158</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:8">
+      <c r="C114" s="19" t="s">
+        <v>818</v>
+      </c>
+      <c r="D114" s="2">
+        <v>0</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G114" s="2">
+        <v>14</v>
+      </c>
+      <c r="H114" s="2">
+        <v>40000159</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:8">
+      <c r="C115" s="19" t="s">
+        <v>820</v>
+      </c>
+      <c r="D115" s="2">
+        <v>0</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G115" s="2">
+        <v>14</v>
+      </c>
+      <c r="H115" s="2">
+        <v>40000160</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:8">
+      <c r="C116" s="19" t="s">
+        <v>822</v>
+      </c>
+      <c r="D116" s="2">
+        <v>0</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G116" s="2">
+        <v>14</v>
+      </c>
+      <c r="H116" s="2">
+        <v>40000161</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:8">
+      <c r="C117" s="19" t="s">
+        <v>824</v>
+      </c>
+      <c r="D117" s="2">
+        <v>0</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G117" s="2">
+        <v>14</v>
+      </c>
+      <c r="H117" s="2">
+        <v>40000162</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:8">
+      <c r="C118" s="19" t="s">
+        <v>826</v>
+      </c>
+      <c r="D118" s="2">
+        <v>0</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G118" s="2">
+        <v>14</v>
+      </c>
+      <c r="H118" s="2">
+        <v>40000163</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:8">
+      <c r="C119" s="19" t="s">
+        <v>828</v>
+      </c>
+      <c r="D119" s="2">
+        <v>0</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G119" s="2">
+        <v>14</v>
+      </c>
+      <c r="H119" s="2">
+        <v>40000164</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:8">
+      <c r="C120" s="19" t="s">
+        <v>830</v>
+      </c>
+      <c r="D120" s="2">
+        <v>0</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G120" s="2">
+        <v>14</v>
+      </c>
+      <c r="H120" s="2">
+        <v>40000165</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:8">
+      <c r="C121" s="19" t="s">
+        <v>832</v>
+      </c>
+      <c r="D121" s="2">
+        <v>0</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G121" s="2">
+        <v>14</v>
+      </c>
+      <c r="H121" s="2">
+        <v>40000166</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:8">
+      <c r="C122" s="19" t="s">
+        <v>834</v>
+      </c>
+      <c r="D122" s="2">
+        <v>0</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G122" s="2">
+        <v>14</v>
+      </c>
+      <c r="H122" s="2">
+        <v>40000167</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:8">
+      <c r="C123" s="19" t="s">
+        <v>836</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123" s="2">
+        <v>14</v>
+      </c>
+      <c r="H123" s="2">
+        <v>40000168</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:8">
+      <c r="C124" s="19" t="s">
+        <v>838</v>
+      </c>
+      <c r="D124" s="2">
+        <v>0</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G124" s="2">
+        <v>14</v>
+      </c>
+      <c r="H124" s="2">
+        <v>40000169</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:8">
+      <c r="C125" s="19" t="s">
+        <v>840</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G125" s="2">
+        <v>14</v>
+      </c>
+      <c r="H125" s="2">
+        <v>40000170</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:8">
+      <c r="C126" s="19" t="s">
+        <v>842</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G126" s="2">
+        <v>14</v>
+      </c>
+      <c r="H126" s="2">
+        <v>40000171</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:8">
+      <c r="C127" s="19" t="s">
+        <v>844</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G127" s="2">
+        <v>14</v>
+      </c>
+      <c r="H127" s="2">
+        <v>40000172</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:8">
+      <c r="C128" s="19" t="s">
+        <v>846</v>
+      </c>
+      <c r="D128" s="2">
+        <v>0</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G128" s="2">
+        <v>14</v>
+      </c>
+      <c r="H128" s="2">
+        <v>40000173</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:8">
+      <c r="C129" s="19" t="s">
+        <v>848</v>
+      </c>
+      <c r="D129" s="2">
+        <v>0</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129" s="2">
+        <v>14</v>
+      </c>
+      <c r="H129" s="2">
+        <v>40000174</v>
       </c>
     </row>
   </sheetData>
@@ -10419,7 +11577,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>748</v>
+        <v>850</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -10439,7 +11597,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>749</v>
+        <v>851</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -10459,7 +11617,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>750</v>
+        <v>852</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -10479,7 +11637,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>751</v>
+        <v>853</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -10499,7 +11657,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>752</v>
+        <v>854</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -10521,7 +11679,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>753</v>
+        <v>855</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -10542,7 +11700,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>754</v>
+        <v>856</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -10562,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>755</v>
+        <v>857</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -10582,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>756</v>
+        <v>858</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -10602,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>757</v>
+        <v>859</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>19</v>
@@ -10622,7 +11780,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>758</v>
+        <v>860</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>19</v>
@@ -10642,7 +11800,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>759</v>
+        <v>861</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>19</v>
@@ -10662,7 +11820,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>760</v>
+        <v>862</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>19</v>
@@ -10682,7 +11840,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>761</v>
+        <v>863</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>19</v>
@@ -10702,7 +11860,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>762</v>
+        <v>864</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -10722,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>763</v>
+        <v>865</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>19</v>
@@ -10742,7 +11900,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>764</v>
+        <v>866</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>19</v>
@@ -10762,7 +11920,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>765</v>
+        <v>867</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>19</v>
@@ -10782,7 +11940,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>766</v>
+        <v>868</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>19</v>
@@ -10802,7 +11960,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>767</v>
+        <v>869</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>19</v>
@@ -10822,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>768</v>
+        <v>870</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>19</v>
@@ -10842,7 +12000,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>768</v>
+        <v>870</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>19</v>
@@ -10865,7 +12023,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>769</v>
+        <v>871</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -10885,7 +12043,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>770</v>
+        <v>872</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -10905,7 +12063,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>771</v>
+        <v>873</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>19</v>
@@ -10925,7 +12083,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>772</v>
+        <v>874</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>19</v>
@@ -10945,7 +12103,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>773</v>
+        <v>875</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>19</v>
@@ -10965,7 +12123,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>774</v>
+        <v>876</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>19</v>
@@ -10985,7 +12143,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>775</v>
+        <v>877</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>19</v>
@@ -11005,7 +12163,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>775</v>
+        <v>877</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>19</v>
@@ -11114,13 +12272,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="19" t="s">
-        <v>776</v>
+        <v>878</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>777</v>
+        <v>879</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -11134,13 +12292,13 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="19" t="s">
-        <v>778</v>
+        <v>880</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>779</v>
+        <v>881</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -11154,13 +12312,13 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="19" t="s">
-        <v>780</v>
+        <v>882</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>781</v>
+        <v>883</v>
       </c>
       <c r="F8" s="2">
         <v>50</v>
@@ -11174,13 +12332,13 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="19" t="s">
-        <v>782</v>
+        <v>884</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>783</v>
+        <v>885</v>
       </c>
       <c r="F9" s="2">
         <v>20</v>
@@ -11194,13 +12352,13 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="19" t="s">
-        <v>784</v>
+        <v>886</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>785</v>
+        <v>887</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -11214,13 +12372,13 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="19" t="s">
-        <v>786</v>
+        <v>888</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>787</v>
+        <v>889</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -11234,13 +12392,13 @@
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="19" t="s">
-        <v>788</v>
+        <v>890</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>789</v>
+        <v>891</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -11254,13 +12412,13 @@
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="19" t="s">
-        <v>790</v>
+        <v>892</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>791</v>
+        <v>893</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -11269,18 +12427,18 @@
         <v>3</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>792</v>
+        <v>894</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="19" t="s">
-        <v>793</v>
+        <v>895</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>794</v>
+        <v>896</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -11289,18 +12447,18 @@
         <v>3</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>795</v>
+        <v>897</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="19" t="s">
-        <v>796</v>
+        <v>898</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>797</v>
+        <v>899</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -11308,19 +12466,19 @@
       <c r="G15" s="2">
         <v>19</v>
       </c>
-      <c r="H15" s="21" t="s">
-        <v>798</v>
+      <c r="H15" s="20" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="19" t="s">
-        <v>799</v>
+        <v>901</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>781</v>
+        <v>883</v>
       </c>
       <c r="F16" s="2">
         <v>100</v>
@@ -11334,13 +12492,13 @@
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="19" t="s">
-        <v>800</v>
+        <v>902</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>783</v>
+        <v>885</v>
       </c>
       <c r="F17" s="2">
         <v>40</v>
@@ -11354,13 +12512,13 @@
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="19" t="s">
-        <v>801</v>
+        <v>903</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>781</v>
+        <v>883</v>
       </c>
       <c r="F18" s="2">
         <v>200</v>
@@ -11374,13 +12532,13 @@
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="19" t="s">
-        <v>802</v>
+        <v>904</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>783</v>
+        <v>885</v>
       </c>
       <c r="F19" s="2">
         <v>80</v>
@@ -11394,13 +12552,13 @@
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="19" t="s">
-        <v>803</v>
+        <v>905</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>804</v>
+        <v>906</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -11414,13 +12572,13 @@
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="19" t="s">
-        <v>805</v>
+        <v>907</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>781</v>
+        <v>883</v>
       </c>
       <c r="F21" s="2">
         <v>500</v>
@@ -11434,13 +12592,13 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="19" t="s">
-        <v>806</v>
+        <v>908</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>783</v>
+        <v>885</v>
       </c>
       <c r="F22" s="2">
         <v>200</v>
@@ -11454,113 +12612,113 @@
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="19" t="s">
-        <v>807</v>
+        <v>909</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>809</v>
+        <v>911</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>811</v>
+        <v>913</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="19" t="s">
-        <v>812</v>
+        <v>914</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>813</v>
+        <v>915</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>814</v>
+        <v>916</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="19" t="s">
-        <v>815</v>
+        <v>917</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>816</v>
+        <v>918</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>817</v>
+        <v>919</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="19" t="s">
-        <v>818</v>
+        <v>920</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>819</v>
+        <v>921</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>820</v>
+        <v>922</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>821</v>
+        <v>923</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="19" t="s">
-        <v>822</v>
+        <v>924</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>823</v>
+        <v>925</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>820</v>
+        <v>922</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>824</v>
+        <v>926</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="19" t="s">
-        <v>825</v>
+        <v>927</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>826</v>
+        <v>928</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -11569,18 +12727,18 @@
         <v>3</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>827</v>
+        <v>929</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="19" t="s">
-        <v>828</v>
+        <v>930</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>829</v>
+        <v>931</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -11589,18 +12747,18 @@
         <v>3</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>830</v>
+        <v>932</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="19" t="s">
-        <v>831</v>
+        <v>933</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>832</v>
+        <v>934</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -11609,18 +12767,18 @@
         <v>3</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>833</v>
+        <v>935</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="19" t="s">
-        <v>834</v>
+        <v>936</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>777</v>
+        <v>879</v>
       </c>
       <c r="F31" s="2">
         <v>2</v>
@@ -11634,13 +12792,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="19" t="s">
-        <v>835</v>
+        <v>937</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>779</v>
+        <v>881</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -11654,13 +12812,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="19" t="s">
-        <v>836</v>
+        <v>938</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>781</v>
+        <v>883</v>
       </c>
       <c r="F33" s="2">
         <v>200</v>
@@ -11674,13 +12832,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="19" t="s">
-        <v>837</v>
+        <v>939</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>783</v>
+        <v>885</v>
       </c>
       <c r="F34" s="2">
         <v>100</v>
@@ -11694,53 +12852,53 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="19" t="s">
-        <v>838</v>
+        <v>940</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>839</v>
+        <v>941</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>840</v>
+        <v>942</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>841</v>
+        <v>943</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="19" t="s">
-        <v>842</v>
+        <v>944</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>839</v>
+        <v>941</v>
       </c>
       <c r="F36" s="2">
         <v>15</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>840</v>
+        <v>942</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>841</v>
+        <v>943</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="19" t="s">
-        <v>843</v>
+        <v>945</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>844</v>
+        <v>946</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>19</v>
@@ -11754,13 +12912,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="19" t="s">
-        <v>845</v>
+        <v>947</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>781</v>
+        <v>883</v>
       </c>
       <c r="F38" s="2">
         <v>1000</v>
@@ -11774,13 +12932,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="19" t="s">
-        <v>846</v>
+        <v>948</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>783</v>
+        <v>885</v>
       </c>
       <c r="F39" s="2">
         <v>300</v>
@@ -11794,13 +12952,13 @@
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="19" t="s">
-        <v>847</v>
+        <v>949</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>848</v>
+        <v>950</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -11809,18 +12967,18 @@
         <v>5</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>849</v>
+        <v>951</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="19" t="s">
-        <v>850</v>
+        <v>952</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>851</v>
+        <v>953</v>
       </c>
       <c r="F42" s="2">
         <v>1</v>
@@ -11834,13 +12992,13 @@
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="19" t="s">
-        <v>852</v>
+        <v>954</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>853</v>
+        <v>955</v>
       </c>
       <c r="F43" s="2">
         <v>1</v>
@@ -11854,13 +13012,13 @@
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="19" t="s">
-        <v>854</v>
+        <v>956</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>855</v>
+        <v>957</v>
       </c>
       <c r="F44" s="2">
         <v>1</v>
@@ -11874,13 +13032,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="19" t="s">
-        <v>856</v>
+        <v>958</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>857</v>
+        <v>959</v>
       </c>
       <c r="F45" s="2">
         <v>1</v>
@@ -11894,13 +13052,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="19" t="s">
-        <v>858</v>
+        <v>960</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>859</v>
+        <v>961</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
@@ -11914,13 +13072,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="19" t="s">
-        <v>860</v>
+        <v>962</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>861</v>
+        <v>963</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -11934,13 +13092,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="19" t="s">
-        <v>862</v>
+        <v>964</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>863</v>
+        <v>965</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -11967,7 +13125,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H67"/>
+  <dimension ref="C1:H68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -12049,13 +13207,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>864</v>
+        <v>966</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>865</v>
+        <v>967</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -12064,18 +13222,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>866</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>867</v>
+        <v>969</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>868</v>
+        <v>970</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -12084,18 +13242,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>869</v>
+        <v>971</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>870</v>
+        <v>972</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>871</v>
+        <v>973</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -12104,18 +13262,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>872</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>873</v>
+        <v>975</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>874</v>
+        <v>976</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -12124,38 +13282,38 @@
         <v>20</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>875</v>
+        <v>977</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>876</v>
+        <v>978</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>877</v>
+        <v>979</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="18" t="s">
-        <v>17</v>
+      <c r="G10" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>878</v>
+        <v>980</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>879</v>
+        <v>981</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>877</v>
+        <v>982</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -12164,18 +13322,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>880</v>
+        <v>983</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>881</v>
+        <v>984</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>877</v>
+        <v>982</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -12184,18 +13342,18 @@
         <v>17</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>882</v>
+        <v>985</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>883</v>
+        <v>986</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>877</v>
+        <v>982</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -12204,906 +13362,926 @@
         <v>17</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C15" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>885</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>886</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>887</v>
+        <v>987</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C14" s="18" t="s">
+        <v>988</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>989</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>888</v>
+        <v>307</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>889</v>
+        <v>990</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>886</v>
+        <v>991</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>890</v>
+        <v>992</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>891</v>
+        <v>993</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>892</v>
+        <v>994</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>886</v>
+        <v>991</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>890</v>
+        <v>995</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>893</v>
+        <v>996</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>894</v>
+        <v>997</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>886</v>
+        <v>991</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>895</v>
+        <v>995</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>896</v>
+        <v>998</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>897</v>
+        <v>999</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>886</v>
+        <v>991</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>898</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>899</v>
+        <v>1001</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>900</v>
+        <v>1002</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>886</v>
+        <v>991</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>901</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>902</v>
+        <v>1004</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>839</v>
+        <v>1005</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>840</v>
+        <v>991</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>841</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>903</v>
+        <v>1007</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>904</v>
+        <v>941</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>886</v>
+        <v>942</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>905</v>
+        <v>943</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>906</v>
+        <v>1008</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>907</v>
+        <v>1009</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>886</v>
+        <v>991</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>908</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>909</v>
+        <v>1011</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>991</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C25" s="18" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>910</v>
       </c>
-      <c r="F24" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>886</v>
-      </c>
-      <c r="H24" s="22" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="8:8">
-      <c r="H25" s="7"/>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C31" s="18" t="s">
-        <v>912</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>810</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>814</v>
-      </c>
+      <c r="E25" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>991</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="8:8">
+      <c r="H26" s="7"/>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>913</v>
+        <v>1017</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>809</v>
+        <v>915</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>811</v>
+        <v>916</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>914</v>
+        <v>1018</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>917</v>
+        <v>1019</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>816</v>
+        <v>1020</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>817</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>918</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>912</v>
+      </c>
+      <c r="H35" s="22" t="s">
         <v>919</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>810</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>921</v>
+        <v>1023</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>922</v>
+        <v>1024</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>923</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>924</v>
+        <v>1026</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>925</v>
+        <v>1027</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>926</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>927</v>
+        <v>1029</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>928</v>
+        <v>1030</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>929</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>795</v>
+        <v>1032</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>930</v>
+        <v>1033</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>810</v>
-      </c>
-      <c r="H39" s="23" t="s">
-        <v>931</v>
+        <v>912</v>
+      </c>
+      <c r="H39" s="22" t="s">
+        <v>1034</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>830</v>
+        <v>897</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>932</v>
+        <v>1035</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>810</v>
-      </c>
-      <c r="H40" s="20" t="s">
-        <v>933</v>
+        <v>912</v>
+      </c>
+      <c r="H40" s="23" t="s">
+        <v>1036</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>935</v>
+        <v>1037</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>810</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>936</v>
+        <v>912</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>1038</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>937</v>
+        <v>1039</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>938</v>
+        <v>1040</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>810</v>
-      </c>
-      <c r="H42" s="20" t="s">
-        <v>939</v>
+        <v>912</v>
+      </c>
+      <c r="H42" s="23" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>940</v>
+        <v>1042</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>941</v>
+        <v>1043</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>810</v>
-      </c>
-      <c r="H43" s="22" t="s">
-        <v>942</v>
+        <v>912</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>1044</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>943</v>
+        <v>1045</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>944</v>
+        <v>1046</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>945</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>946</v>
+        <v>1048</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>947</v>
+        <v>1049</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>948</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>949</v>
+        <v>1051</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>950</v>
+        <v>1052</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>951</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>952</v>
+        <v>1054</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>953</v>
+        <v>1055</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>954</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>955</v>
+        <v>1057</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>956</v>
+        <v>1058</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>957</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>958</v>
+        <v>1060</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>959</v>
+        <v>1061</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>960</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>961</v>
+        <v>1063</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>962</v>
+        <v>1064</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="18" t="s">
-        <v>810</v>
+        <v>912</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C52" s="18" t="s">
-        <v>964</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="F52" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G52" s="18" t="s">
-        <v>820</v>
-      </c>
-      <c r="H52" s="22" t="s">
-        <v>821</v>
-      </c>
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C51" s="18" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="18" t="s">
+        <v>912</v>
+      </c>
+      <c r="H51" s="22" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="3"/>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>965</v>
+        <v>1069</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>823</v>
+        <v>921</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>820</v>
+        <v>922</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:8">
-      <c r="C55" s="18" t="s">
-        <v>966</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="F55" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="18" t="s">
-        <v>886</v>
-      </c>
-      <c r="H55" s="24" t="s">
-        <v>968</v>
+        <v>923</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C54" s="18" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="18" t="s">
+        <v>922</v>
+      </c>
+      <c r="H54" s="22" t="s">
+        <v>926</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>969</v>
+        <v>1071</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>808</v>
+        <v>910</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>970</v>
+        <v>1072</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>886</v>
+        <v>991</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="57" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C58" s="10" t="s">
-        <v>972</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="H58" s="18" t="s">
-        <v>975</v>
-      </c>
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:8">
+      <c r="C57" s="18" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>991</v>
+      </c>
+      <c r="H57" s="24" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="3"/>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>976</v>
+        <v>1077</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>977</v>
+        <v>1078</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>974</v>
+        <v>1079</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>978</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>979</v>
+        <v>1081</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>980</v>
+        <v>1082</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>974</v>
+        <v>1079</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>981</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>982</v>
+        <v>1084</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>983</v>
+        <v>1085</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>974</v>
+        <v>1079</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>984</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>985</v>
+        <v>1087</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>986</v>
+        <v>1088</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>974</v>
+        <v>1079</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>987</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>988</v>
+        <v>1090</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>989</v>
+        <v>1091</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>974</v>
+        <v>1079</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>990</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>991</v>
+        <v>1093</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>992</v>
+        <v>1094</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>974</v>
+        <v>1079</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>993</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>994</v>
+        <v>1096</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>995</v>
+        <v>1097</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="H65" s="22" t="s">
-        <v>996</v>
+        <v>1079</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>1098</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>997</v>
-      </c>
-      <c r="D66" s="18" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H66" s="22" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C67" s="10" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D67" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="H66" s="22" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C67" s="10">
+      <c r="E67" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H67" s="22" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C68" s="10">
         <v>300091</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D68" s="2">
         <v>100</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="H67" s="22" t="s">
-        <v>1001</v>
+      <c r="E68" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>1106</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1975" uniqueCount="1107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="1111">
   <si>
     <t>_id</t>
   </si>
@@ -3464,6 +3464,18 @@
   </si>
   <si>
     <t>4022</t>
+  </si>
+  <si>
+    <t>金装精华</t>
+  </si>
+  <si>
+    <t>4025</t>
+  </si>
+  <si>
+    <t>暗金精华</t>
+  </si>
+  <si>
+    <t>4026</t>
   </si>
   <si>
     <t>2000</t>
@@ -13585,12 +13597,49 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="8:8">
-      <c r="H26" s="7"/>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C26" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>991</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C27" s="18" t="s">
+        <v>929</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>991</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>1020</v>
+      </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>910</v>
@@ -13610,7 +13659,7 @@
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>910</v>
@@ -13630,13 +13679,13 @@
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>19</v>
@@ -13645,12 +13694,12 @@
         <v>912</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>910</v>
@@ -13670,13 +13719,13 @@
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>19</v>
@@ -13685,18 +13734,18 @@
         <v>912</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>19</v>
@@ -13705,18 +13754,18 @@
         <v>912</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>19</v>
@@ -13725,18 +13774,18 @@
         <v>912</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>19</v>
@@ -13745,7 +13794,7 @@
         <v>912</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13756,7 +13805,7 @@
         <v>910</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>19</v>
@@ -13765,7 +13814,7 @@
         <v>912</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13776,7 +13825,7 @@
         <v>910</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>19</v>
@@ -13785,18 +13834,18 @@
         <v>912</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>19</v>
@@ -13805,18 +13854,18 @@
         <v>912</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>19</v>
@@ -13825,18 +13874,18 @@
         <v>912</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>19</v>
@@ -13845,18 +13894,18 @@
         <v>912</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>19</v>
@@ -13865,18 +13914,18 @@
         <v>912</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>19</v>
@@ -13885,18 +13934,18 @@
         <v>912</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>19</v>
@@ -13905,18 +13954,18 @@
         <v>912</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>19</v>
@@ -13925,18 +13974,18 @@
         <v>912</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>19</v>
@@ -13945,18 +13994,18 @@
         <v>912</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>19</v>
@@ -13965,18 +14014,18 @@
         <v>912</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>19</v>
@@ -13985,7 +14034,7 @@
         <v>912</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:8">
@@ -13998,7 +14047,7 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>910</v>
@@ -14018,7 +14067,7 @@
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>910</v>
@@ -14038,13 +14087,13 @@
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>19</v>
@@ -14053,18 +14102,18 @@
         <v>991</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>910</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>19</v>
@@ -14073,7 +14122,7 @@
         <v>991</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:8">
@@ -14086,182 +14135,182 @@
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C67" s="10" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="D67" s="18" t="s">
         <v>49</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14272,16 +14321,16 @@
         <v>100</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="5"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -3469,7 +3469,7 @@
     <t>金装精华</t>
   </si>
   <si>
-    <t>4025</t>
+    <t>4019</t>
   </si>
   <si>
     <t>暗金精华</t>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="1113">
   <si>
     <t>_id</t>
   </si>
@@ -3047,6 +3047,12 @@
   </si>
   <si>
     <t>极.无限之魂</t>
+  </si>
+  <si>
+    <t>极·万界图</t>
+  </si>
+  <si>
+    <t>极·金蛟剪</t>
   </si>
   <si>
     <t>220000</t>
@@ -11501,7 +11507,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -12185,6 +12191,46 @@
       </c>
       <c r="H36" s="14">
         <v>180037</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C37" s="14">
+        <v>180038</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="2">
+        <v>18</v>
+      </c>
+      <c r="H37" s="14">
+        <v>180038</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C38" s="14">
+        <v>180039</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="2">
+        <v>18</v>
+      </c>
+      <c r="H38" s="14">
+        <v>180039</v>
       </c>
     </row>
   </sheetData>
@@ -12284,13 +12330,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="19" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -12304,13 +12350,13 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="19" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -12324,13 +12370,13 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="19" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F8" s="2">
         <v>50</v>
@@ -12344,13 +12390,13 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="19" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F9" s="2">
         <v>20</v>
@@ -12364,13 +12410,13 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="19" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -12384,13 +12430,13 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="19" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -12404,13 +12450,13 @@
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="19" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -12424,13 +12470,13 @@
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="19" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -12439,18 +12485,18 @@
         <v>3</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="19" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -12459,18 +12505,18 @@
         <v>3</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="19" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -12479,18 +12525,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="19" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F16" s="2">
         <v>100</v>
@@ -12504,13 +12550,13 @@
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="19" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F17" s="2">
         <v>40</v>
@@ -12524,13 +12570,13 @@
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F18" s="2">
         <v>200</v>
@@ -12544,13 +12590,13 @@
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="19" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F19" s="2">
         <v>80</v>
@@ -12564,13 +12610,13 @@
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="19" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>19</v>
@@ -12584,13 +12630,13 @@
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="19" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F21" s="2">
         <v>500</v>
@@ -12604,13 +12650,13 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="19" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F22" s="2">
         <v>200</v>
@@ -12624,113 +12670,113 @@
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="19" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="19" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="19" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="19" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="19" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
@@ -12739,18 +12785,18 @@
         <v>3</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="19" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>19</v>
@@ -12759,18 +12805,18 @@
         <v>3</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="19" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -12779,18 +12825,18 @@
         <v>3</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="19" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="F31" s="2">
         <v>2</v>
@@ -12804,13 +12850,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="19" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -12824,13 +12870,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="19" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F33" s="2">
         <v>200</v>
@@ -12844,13 +12890,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="19" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F34" s="2">
         <v>100</v>
@@ -12864,53 +12910,53 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="19" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="19" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="F36" s="2">
         <v>15</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="19" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>19</v>
@@ -12924,13 +12970,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="19" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F38" s="2">
         <v>1000</v>
@@ -12944,13 +12990,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="19" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F39" s="2">
         <v>300</v>
@@ -12964,13 +13010,13 @@
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="19" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -12979,18 +13025,18 @@
         <v>5</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="19" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="F42" s="2">
         <v>1</v>
@@ -13004,13 +13050,13 @@
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="19" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="F43" s="2">
         <v>1</v>
@@ -13024,13 +13070,13 @@
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="19" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="F44" s="2">
         <v>1</v>
@@ -13044,13 +13090,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="19" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="F45" s="2">
         <v>1</v>
@@ -13064,13 +13110,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="19" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
@@ -13084,13 +13130,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="19" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -13104,13 +13150,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="19" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -13219,13 +13265,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>19</v>
@@ -13234,18 +13280,18 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
@@ -13254,18 +13300,18 @@
         <v>20</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -13274,18 +13320,18 @@
         <v>20</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>19</v>
@@ -13294,18 +13340,18 @@
         <v>20</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -13314,18 +13360,18 @@
         <v>20</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>19</v>
@@ -13334,18 +13380,18 @@
         <v>17</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
+        <v>986</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>984</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>982</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>19</v>
@@ -13354,18 +13400,18 @@
         <v>17</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>19</v>
@@ -13374,18 +13420,18 @@
         <v>17</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>19</v>
@@ -13394,7 +13440,7 @@
         <v>17</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13402,199 +13448,199 @@
         <v>307</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
+        <v>995</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="18" t="s">
         <v>993</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>991</v>
-      </c>
       <c r="H17" s="22" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>23</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13602,439 +13648,439 @@
         <v>311</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:8">
@@ -14047,82 +14093,82 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="F54" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:8">
@@ -14135,182 +14181,182 @@
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C67" s="10" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="D67" s="18" t="s">
         <v>49</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14321,16 +14367,16 @@
         <v>100</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -13183,7 +13183,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H68"/>
+  <dimension ref="C1:H67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -13191,7 +13191,7 @@
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="142.125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="85.5833333333333" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -13683,15 +13683,35 @@
         <v>1022</v>
       </c>
     </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C31" s="18" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>914</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>918</v>
+      </c>
+    </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>19</v>
@@ -13700,18 +13720,18 @@
         <v>914</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>913</v>
+        <v>1026</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>19</v>
@@ -13720,18 +13740,18 @@
         <v>914</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>915</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1026</v>
+        <v>920</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>19</v>
@@ -13740,18 +13760,18 @@
         <v>914</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>1027</v>
+        <v>921</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>920</v>
+        <v>1030</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>19</v>
@@ -13760,18 +13780,18 @@
         <v>914</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>921</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>19</v>
@@ -13780,18 +13800,18 @@
         <v>914</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>19</v>
@@ -13800,18 +13820,18 @@
         <v>914</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>19</v>
@@ -13820,18 +13840,18 @@
         <v>914</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1038</v>
+        <v>899</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>19</v>
@@ -13839,19 +13859,19 @@
       <c r="G39" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H39" s="22" t="s">
-        <v>1040</v>
+      <c r="H39" s="23" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>899</v>
+        <v>934</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>19</v>
@@ -13859,19 +13879,19 @@
       <c r="G40" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H40" s="23" t="s">
-        <v>1042</v>
+      <c r="H40" s="21" t="s">
+        <v>1044</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>934</v>
+        <v>1045</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>19</v>
@@ -13879,19 +13899,19 @@
       <c r="G41" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H41" s="21" t="s">
-        <v>1044</v>
+      <c r="H41" s="23" t="s">
+        <v>1047</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>19</v>
@@ -13899,19 +13919,19 @@
       <c r="G42" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H42" s="23" t="s">
-        <v>1047</v>
+      <c r="H42" s="21" t="s">
+        <v>1050</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>19</v>
@@ -13919,19 +13939,19 @@
       <c r="G43" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H43" s="21" t="s">
-        <v>1050</v>
+      <c r="H43" s="22" t="s">
+        <v>1053</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>19</v>
@@ -13940,18 +13960,18 @@
         <v>914</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>19</v>
@@ -13960,18 +13980,18 @@
         <v>914</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>19</v>
@@ -13980,18 +14000,18 @@
         <v>914</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>19</v>
@@ -14000,18 +14020,18 @@
         <v>914</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>19</v>
@@ -14020,18 +14040,18 @@
         <v>914</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>19</v>
@@ -14040,18 +14060,18 @@
         <v>914</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>19</v>
@@ -14060,46 +14080,46 @@
         <v>914</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C51" s="18" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D51" s="2" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C52" s="18" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F51" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" s="18" t="s">
-        <v>914</v>
-      </c>
-      <c r="H51" s="22" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="3"/>
+      <c r="E52" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="18" t="s">
+        <v>924</v>
+      </c>
+      <c r="H52" s="22" t="s">
+        <v>925</v>
+      </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>19</v>
@@ -14108,38 +14128,38 @@
         <v>924</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C54" s="18" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D54" s="2" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:8">
+      <c r="C55" s="18" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G54" s="18" t="s">
-        <v>924</v>
-      </c>
-      <c r="H54" s="22" t="s">
-        <v>928</v>
+      <c r="E55" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>993</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>1079</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>19</v>
@@ -14148,46 +14168,46 @@
         <v>993</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:8">
-      <c r="C57" s="18" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F57" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G57" s="18" t="s">
-        <v>993</v>
-      </c>
-      <c r="H57" s="24" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="58" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="3"/>
+    <row r="57" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C58" s="10" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>19</v>
@@ -14196,18 +14216,18 @@
         <v>1085</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
@@ -14216,18 +14236,18 @@
         <v>1085</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
@@ -14236,18 +14256,18 @@
         <v>1085</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
@@ -14256,18 +14276,18 @@
         <v>1085</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
@@ -14276,18 +14296,18 @@
         <v>1085</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
@@ -14296,18 +14316,18 @@
         <v>1085</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
@@ -14315,19 +14335,19 @@
       <c r="G65" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="H65" s="18" t="s">
-        <v>1104</v>
+      <c r="H65" s="22" t="s">
+        <v>1107</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>46</v>
+        <v>1108</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
@@ -14336,18 +14356,18 @@
         <v>1085</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C67" s="10" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D67" s="18" t="s">
-        <v>49</v>
+      <c r="C67" s="10">
+        <v>300091</v>
+      </c>
+      <c r="D67" s="2">
+        <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
@@ -14356,26 +14376,6 @@
         <v>1085</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C68" s="10">
-        <v>300091</v>
-      </c>
-      <c r="D68" s="2">
-        <v>100</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="H68" s="22" t="s">
         <v>1112</v>
       </c>
     </row>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="1113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="1116">
   <si>
     <t>_id</t>
   </si>
@@ -3482,6 +3482,15 @@
   </si>
   <si>
     <t>4026</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>开孔石</t>
+  </si>
+  <si>
+    <t>4027</t>
   </si>
   <si>
     <t>2000</t>
@@ -12248,7 +12257,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H48"/>
+  <dimension ref="C1:H49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -13028,35 +13037,16 @@
         <v>953</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:8">
-      <c r="C42" s="19" t="s">
-        <v>954</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>955</v>
-      </c>
-      <c r="F42" s="2">
-        <v>1</v>
-      </c>
-      <c r="G42" s="2">
-        <v>16</v>
-      </c>
-      <c r="H42" s="2">
-        <v>8201</v>
-      </c>
-    </row>
+    <row r="41" customFormat="1" customHeight="1"/>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="19" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F43" s="2">
         <v>1</v>
@@ -13065,18 +13055,18 @@
         <v>16</v>
       </c>
       <c r="H43" s="2">
-        <v>8202</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="19" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="F44" s="2">
         <v>1</v>
@@ -13085,18 +13075,18 @@
         <v>16</v>
       </c>
       <c r="H44" s="2">
-        <v>8203</v>
+        <v>8202</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="19" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="F45" s="2">
         <v>1</v>
@@ -13105,18 +13095,18 @@
         <v>16</v>
       </c>
       <c r="H45" s="2">
-        <v>8204</v>
+        <v>8203</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="19" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
@@ -13125,18 +13115,18 @@
         <v>16</v>
       </c>
       <c r="H46" s="2">
-        <v>8205</v>
+        <v>8204</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="19" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -13145,18 +13135,18 @@
         <v>16</v>
       </c>
       <c r="H47" s="2">
-        <v>8206</v>
+        <v>8205</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="19" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -13165,6 +13155,26 @@
         <v>16</v>
       </c>
       <c r="H48" s="2">
+        <v>8206</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:8">
+      <c r="C49" s="19" t="s">
+        <v>966</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>967</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2">
+        <v>16</v>
+      </c>
+      <c r="H49" s="2">
         <v>8207</v>
       </c>
     </row>
@@ -13683,9 +13693,29 @@
         <v>1022</v>
       </c>
     </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C28" s="18" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>993</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>1025</v>
+      </c>
+    </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>912</v>
@@ -13705,7 +13735,7 @@
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>912</v>
@@ -13725,13 +13755,13 @@
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>19</v>
@@ -13740,12 +13770,12 @@
         <v>914</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>912</v>
@@ -13765,13 +13795,13 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>19</v>
@@ -13780,18 +13810,18 @@
         <v>914</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>19</v>
@@ -13800,18 +13830,18 @@
         <v>914</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>19</v>
@@ -13820,18 +13850,18 @@
         <v>914</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>19</v>
@@ -13840,7 +13870,7 @@
         <v>914</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13851,7 +13881,7 @@
         <v>912</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>19</v>
@@ -13860,7 +13890,7 @@
         <v>914</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13871,7 +13901,7 @@
         <v>912</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>19</v>
@@ -13880,18 +13910,18 @@
         <v>914</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>19</v>
@@ -13900,18 +13930,18 @@
         <v>914</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>19</v>
@@ -13920,18 +13950,18 @@
         <v>914</v>
       </c>
       <c r="H42" s="21" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>19</v>
@@ -13940,18 +13970,18 @@
         <v>914</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>19</v>
@@ -13960,18 +13990,18 @@
         <v>914</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>19</v>
@@ -13980,18 +14010,18 @@
         <v>914</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>19</v>
@@ -14000,18 +14030,18 @@
         <v>914</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>19</v>
@@ -14020,18 +14050,18 @@
         <v>914</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>19</v>
@@ -14040,18 +14070,18 @@
         <v>914</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>19</v>
@@ -14060,18 +14090,18 @@
         <v>914</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>19</v>
@@ -14080,7 +14110,7 @@
         <v>914</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="3:8">
@@ -14093,7 +14123,7 @@
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>912</v>
@@ -14113,7 +14143,7 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>912</v>
@@ -14133,13 +14163,13 @@
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>19</v>
@@ -14148,18 +14178,18 @@
         <v>993</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>19</v>
@@ -14168,7 +14198,7 @@
         <v>993</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:8">
@@ -14181,182 +14211,182 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="10" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>1085</v>
-      </c>
       <c r="H59" s="18" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="10" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="D66" s="18" t="s">
         <v>49</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14367,16 +14397,16 @@
         <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="5"/>
+    <workbookView windowWidth="27952" windowHeight="12255" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="1119">
   <si>
     <t>_id</t>
   </si>
@@ -3647,6 +3647,15 @@
   </si>
   <si>
     <t>2000327,2000328,2000329</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>暗金图鉴</t>
+  </si>
+  <si>
+    <t>1998001,1998002,1998003,1998004,1998005</t>
   </si>
   <si>
     <t>3001</t>
@@ -4807,12 +4816,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="8.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="40.375" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8.75221238938053" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.8761061946903" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.2477876106195" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.2477876106195" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.87610619469027" style="2" customWidth="1"/>
+    <col min="9" max="9" width="40.3716814159292" style="9" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -7104,11 +7113,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="8.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="40.375" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8.75221238938053" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.8761061946903" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.2477876106195" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.2477876106195" style="2" customWidth="1"/>
+    <col min="8" max="8" width="40.3716814159292" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -8942,11 +8951,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="8.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.25" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8.75221238938053" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.8761061946903" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.2477876106195" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.2477876106195" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.2477876106195" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -11520,11 +11529,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="8.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="27.125" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8.75221238938053" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.8761061946903" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.2477876106195" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.2477876106195" style="2" customWidth="1"/>
+    <col min="8" max="8" width="27.1238938053097" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -12261,11 +12270,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="8.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="32.75" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8.75221238938053" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.8761061946903" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.2477876106195" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.2477876106195" style="2" customWidth="1"/>
+    <col min="8" max="8" width="32.7522123893805" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -13193,15 +13202,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H67"/>
+  <dimension ref="C1:H68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="4" width="8.75" style="1" customWidth="1"/>
+    <col min="3" max="4" width="8.75221238938053" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="85.5833333333333" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.2477876106195" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.2477876106195" style="1" customWidth="1"/>
+    <col min="8" max="8" width="85.5840707964602" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -14113,43 +14122,43 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="51" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C52" s="18" t="s">
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C51" s="18" t="s">
         <v>1078</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="F52" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G52" s="18" t="s">
-        <v>924</v>
-      </c>
-      <c r="H52" s="22" t="s">
-        <v>925</v>
-      </c>
+      <c r="E51" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="18" t="s">
+        <v>914</v>
+      </c>
+      <c r="H51" s="22" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="3"/>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>19</v>
@@ -14158,27 +14167,27 @@
         <v>924</v>
       </c>
       <c r="H53" s="22" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C54" s="18" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="18" t="s">
+        <v>924</v>
+      </c>
+      <c r="H54" s="22" t="s">
         <v>928</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:8">
-      <c r="C55" s="18" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F55" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="18" t="s">
-        <v>993</v>
-      </c>
-      <c r="H55" s="24" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
@@ -14201,49 +14210,49 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="57" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C58" s="10" t="s">
+    <row r="57" customHeight="1" spans="3:8">
+      <c r="C57" s="18" t="s">
         <v>1086</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="D57" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G58" s="2" t="s">
+      <c r="F57" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>993</v>
+      </c>
+      <c r="H57" s="24" t="s">
         <v>1088</v>
       </c>
-      <c r="H58" s="18" t="s">
-        <v>1089</v>
-      </c>
+    </row>
+    <row r="58" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="3"/>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="10" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E59" s="2" t="s">
+      <c r="F59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>1091</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>1088</v>
       </c>
       <c r="H59" s="18" t="s">
         <v>1092</v>
@@ -14254,7 +14263,7 @@
         <v>1093</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>1094</v>
@@ -14263,7 +14272,7 @@
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="H60" s="18" t="s">
         <v>1095</v>
@@ -14274,7 +14283,7 @@
         <v>1096</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>1097</v>
@@ -14283,7 +14292,7 @@
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>1098</v>
@@ -14294,7 +14303,7 @@
         <v>1099</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>1100</v>
@@ -14303,7 +14312,7 @@
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="H62" s="18" t="s">
         <v>1101</v>
@@ -14314,7 +14323,7 @@
         <v>1102</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>1103</v>
@@ -14323,7 +14332,7 @@
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>1104</v>
@@ -14334,7 +14343,7 @@
         <v>1105</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>1106</v>
@@ -14343,7 +14352,7 @@
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>1107</v>
@@ -14354,7 +14363,7 @@
         <v>1108</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>1109</v>
@@ -14363,9 +14372,9 @@
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="H65" s="22" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H65" s="18" t="s">
         <v>1110</v>
       </c>
     </row>
@@ -14373,8 +14382,8 @@
       <c r="C66" s="10" t="s">
         <v>1111</v>
       </c>
-      <c r="D66" s="18" t="s">
-        <v>49</v>
+      <c r="D66" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>1112</v>
@@ -14383,30 +14392,50 @@
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="H66" s="22" t="s">
         <v>1113</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C67" s="10">
+      <c r="C67" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H67" s="22" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C68" s="10">
         <v>300091</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D68" s="2">
         <v>100</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="H67" s="22" t="s">
-        <v>1115</v>
+      <c r="E68" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>1118</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="1125">
   <si>
     <t>_id</t>
   </si>
@@ -3662,6 +3662,24 @@
   </si>
   <si>
     <t>3002</t>
+  </si>
+  <si>
+    <t>3003</t>
+  </si>
+  <si>
+    <t>第三批时装</t>
+  </si>
+  <si>
+    <t>3000049,3000050,3000051,3000052,3000053,3000054,3000055,3000056</t>
+  </si>
+  <si>
+    <t>3004</t>
+  </si>
+  <si>
+    <t>第四批时装</t>
+  </si>
+  <si>
+    <t>3000057,3000058,3000059,3000060,3000061,3000062,3000063,3000064</t>
   </si>
   <si>
     <t>4001</t>
@@ -13202,7 +13220,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H68"/>
+  <dimension ref="C1:H70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -14190,109 +14208,109 @@
         <v>928</v>
       </c>
     </row>
+    <row r="55" customHeight="1" spans="3:8">
+      <c r="C55" s="18" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>924</v>
+      </c>
+      <c r="H55" s="24" t="s">
+        <v>1085</v>
+      </c>
+    </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>1084</v>
+      <c r="E56" s="2" t="s">
+        <v>1087</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G56" s="18" t="s">
+        <v>924</v>
+      </c>
+      <c r="H56" s="24" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:8">
+      <c r="C58" s="18" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="18" t="s">
         <v>993</v>
       </c>
-      <c r="H56" s="24" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:8">
-      <c r="C57" s="18" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D57" s="2" t="s">
+      <c r="H58" s="24" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:8">
+      <c r="C59" s="18" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F57" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G57" s="18" t="s">
+      <c r="E59" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="18" t="s">
         <v>993</v>
       </c>
-      <c r="H57" s="24" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="3"/>
-    </row>
-    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C59" s="10" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="H59" s="18" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C60" s="10" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E60" s="2" t="s">
+      <c r="H59" s="24" t="s">
         <v>1094</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>1095</v>
-      </c>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="3"/>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>1096</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E61" s="2" t="s">
+      <c r="F61" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>1097</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>1091</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>1098</v>
@@ -14303,7 +14321,7 @@
         <v>1099</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>1100</v>
@@ -14312,7 +14330,7 @@
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="H62" s="18" t="s">
         <v>1101</v>
@@ -14323,7 +14341,7 @@
         <v>1102</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>1103</v>
@@ -14332,7 +14350,7 @@
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>1104</v>
@@ -14343,7 +14361,7 @@
         <v>1105</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>1106</v>
@@ -14352,7 +14370,7 @@
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>1107</v>
@@ -14363,7 +14381,7 @@
         <v>1108</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>1109</v>
@@ -14372,7 +14390,7 @@
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>1110</v>
@@ -14383,7 +14401,7 @@
         <v>1111</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>1112</v>
@@ -14392,9 +14410,9 @@
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="H66" s="22" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H66" s="18" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -14402,8 +14420,8 @@
       <c r="C67" s="10" t="s">
         <v>1114</v>
       </c>
-      <c r="D67" s="18" t="s">
-        <v>49</v>
+      <c r="D67" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>1115</v>
@@ -14412,30 +14430,70 @@
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="H67" s="22" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H67" s="18" t="s">
         <v>1116</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C68" s="10">
+      <c r="C68" s="10" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C69" s="10" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H69" s="22" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C70" s="10">
         <v>300091</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D70" s="2">
         <v>100</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="H68" s="22" t="s">
-        <v>1118</v>
+      <c r="E70" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H70" s="22" t="s">
+        <v>1124</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="1125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="1128">
   <si>
     <t>_id</t>
   </si>
@@ -3491,6 +3491,15 @@
   </si>
   <si>
     <t>4027</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>时装精华</t>
+  </si>
+  <si>
+    <t>4034</t>
   </si>
   <si>
     <t>2000</t>
@@ -13740,9 +13749,29 @@
         <v>1025</v>
       </c>
     </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C29" s="18" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>993</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>1028</v>
+      </c>
+    </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>912</v>
@@ -13762,7 +13791,7 @@
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>912</v>
@@ -13782,13 +13811,13 @@
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>19</v>
@@ -13797,12 +13826,12 @@
         <v>914</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>912</v>
@@ -13822,13 +13851,13 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>19</v>
@@ -13837,18 +13866,18 @@
         <v>914</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>19</v>
@@ -13857,18 +13886,18 @@
         <v>914</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>19</v>
@@ -13877,18 +13906,18 @@
         <v>914</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>19</v>
@@ -13897,7 +13926,7 @@
         <v>914</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13908,7 +13937,7 @@
         <v>912</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>19</v>
@@ -13917,7 +13946,7 @@
         <v>914</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13928,7 +13957,7 @@
         <v>912</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>19</v>
@@ -13937,18 +13966,18 @@
         <v>914</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>19</v>
@@ -13957,18 +13986,18 @@
         <v>914</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>19</v>
@@ -13977,18 +14006,18 @@
         <v>914</v>
       </c>
       <c r="H42" s="21" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>19</v>
@@ -13997,18 +14026,18 @@
         <v>914</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>19</v>
@@ -14017,18 +14046,18 @@
         <v>914</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>19</v>
@@ -14037,18 +14066,18 @@
         <v>914</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>19</v>
@@ -14057,18 +14086,18 @@
         <v>914</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>19</v>
@@ -14077,18 +14106,18 @@
         <v>914</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>19</v>
@@ -14097,18 +14126,18 @@
         <v>914</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>19</v>
@@ -14117,18 +14146,18 @@
         <v>914</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>19</v>
@@ -14137,18 +14166,18 @@
         <v>914</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>19</v>
@@ -14157,7 +14186,7 @@
         <v>914</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="3:8">
@@ -14170,7 +14199,7 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>912</v>
@@ -14190,7 +14219,7 @@
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>912</v>
@@ -14210,13 +14239,13 @@
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>19</v>
@@ -14225,18 +14254,18 @@
         <v>924</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>19</v>
@@ -14245,18 +14274,18 @@
         <v>924</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>19</v>
@@ -14265,18 +14294,18 @@
         <v>993</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>19</v>
@@ -14285,7 +14314,7 @@
         <v>993</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="3:8">
@@ -14298,182 +14327,182 @@
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="10" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="10" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E62" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>1097</v>
-      </c>
       <c r="H62" s="18" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="10" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C67" s="10" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C68" s="10" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C69" s="10" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="D69" s="18" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="H69" s="22" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14484,16 +14513,16 @@
         <v>100</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255" activeTab="5"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="1137">
   <si>
     <t>_id</t>
   </si>
@@ -3389,6 +3389,33 @@
   </si>
   <si>
     <t>1,2,3,4,5,6</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>传奇专属</t>
+  </si>
+  <si>
+    <t>7,8,9,10,11,12</t>
+  </si>
+  <si>
+    <t>506</t>
+  </si>
+  <si>
+    <t>不朽专属</t>
+  </si>
+  <si>
+    <t>13,14,15,16,17,18</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>永恒专属</t>
+  </si>
+  <si>
+    <t>19,20,21,22,23,24</t>
   </si>
   <si>
     <t>特殊图鉴碎片</t>
@@ -4843,12 +4870,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="8.75221238938053" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.8761061946903" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.2477876106195" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.2477876106195" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.87610619469027" style="2" customWidth="1"/>
-    <col min="9" max="9" width="40.3716814159292" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="40.375" style="9" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -7140,11 +7167,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="8.75221238938053" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.8761061946903" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.2477876106195" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.2477876106195" style="2" customWidth="1"/>
-    <col min="8" max="8" width="40.3716814159292" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="40.375" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -8978,11 +9005,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="8.75221238938053" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.8761061946903" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.2477876106195" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.2477876106195" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.2477876106195" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.25" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -11556,11 +11583,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="8.75221238938053" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.8761061946903" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.2477876106195" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.2477876106195" style="2" customWidth="1"/>
-    <col min="8" max="8" width="27.1238938053097" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="27.125" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -12297,11 +12324,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="8.75221238938053" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.8761061946903" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.2477876106195" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.2477876106195" style="2" customWidth="1"/>
-    <col min="8" max="8" width="32.7522123893805" style="9" customWidth="1"/>
+    <col min="3" max="4" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="32.75" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -13229,15 +13256,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H70"/>
+  <dimension ref="C1:H73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="4" width="8.75221238938053" style="1" customWidth="1"/>
+    <col min="3" max="4" width="8.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.2477876106195" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.2477876106195" style="1" customWidth="1"/>
-    <col min="8" max="8" width="85.5840707964602" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="85.5833333333333" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -13489,69 +13516,77 @@
         <v>991</v>
       </c>
     </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C15" s="18" t="s">
+        <v>992</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>994</v>
+      </c>
+    </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>307</v>
+        <v>995</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>992</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>20</v>
+        <v>996</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>993</v>
+        <v>17</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="F17" s="18" t="s">
+        <v>999</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>993</v>
+        <v>17</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C18" s="18" t="s">
-        <v>998</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>993</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>997</v>
-      </c>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="3"/>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>1000</v>
+        <v>307</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>912</v>
@@ -13560,53 +13595,53 @@
         <v>1001</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13617,227 +13652,227 @@
         <v>912</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>943</v>
+        <v>1010</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>944</v>
+        <v>1002</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>945</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1017</v>
+        <v>943</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>993</v>
+        <v>944</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>1018</v>
+        <v>945</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>311</v>
+        <v>1019</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>931</v>
+        <v>1022</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="F28" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>993</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>1025</v>
+        <v>1002</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>1027</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>1026</v>
+        <v>311</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>993</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>1028</v>
+        <v>1002</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C30" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H30" s="22" t="s">
+        <v>1031</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>917</v>
+        <v>1033</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>914</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>918</v>
+        <v>1002</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>1034</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>913</v>
+        <v>1036</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>914</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C33" s="18" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>914</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>1033</v>
+        <v>1002</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>1037</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>19</v>
@@ -13846,18 +13881,18 @@
         <v>914</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1036</v>
+        <v>913</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>19</v>
@@ -13866,18 +13901,18 @@
         <v>914</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>1037</v>
+        <v>915</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>19</v>
@@ -13886,18 +13921,18 @@
         <v>914</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1042</v>
+        <v>920</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>19</v>
@@ -13906,7 +13941,7 @@
         <v>914</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>1043</v>
+        <v>921</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13931,13 +13966,13 @@
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>899</v>
+        <v>1047</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>19</v>
@@ -13945,19 +13980,19 @@
       <c r="G39" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H39" s="23" t="s">
-        <v>1048</v>
+      <c r="H39" s="22" t="s">
+        <v>1049</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>934</v>
+        <v>1050</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>19</v>
@@ -13965,19 +14000,19 @@
       <c r="G40" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H40" s="21" t="s">
-        <v>1050</v>
+      <c r="H40" s="22" t="s">
+        <v>1052</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>19</v>
@@ -13985,19 +14020,19 @@
       <c r="G41" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H41" s="23" t="s">
-        <v>1053</v>
+      <c r="H41" s="22" t="s">
+        <v>1055</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1054</v>
+        <v>899</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>19</v>
@@ -14005,13 +14040,13 @@
       <c r="G42" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H42" s="21" t="s">
-        <v>1056</v>
+      <c r="H42" s="23" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>1057</v>
+        <v>934</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>912</v>
@@ -14025,7 +14060,7 @@
       <c r="G43" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H43" s="22" t="s">
+      <c r="H43" s="21" t="s">
         <v>1059</v>
       </c>
     </row>
@@ -14045,7 +14080,7 @@
       <c r="G44" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H44" s="22" t="s">
+      <c r="H44" s="23" t="s">
         <v>1062</v>
       </c>
     </row>
@@ -14065,7 +14100,7 @@
       <c r="G45" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H45" s="22" t="s">
+      <c r="H45" s="21" t="s">
         <v>1065</v>
       </c>
     </row>
@@ -14189,83 +14224,83 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="52" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="3"/>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C52" s="18" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="18" t="s">
+        <v>914</v>
+      </c>
+      <c r="H52" s="22" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>923</v>
+        <v>1088</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>924</v>
+        <v>914</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>925</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>927</v>
+        <v>1091</v>
       </c>
       <c r="F54" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>924</v>
+        <v>914</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:8">
-      <c r="C55" s="18" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F55" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="18" t="s">
-        <v>924</v>
-      </c>
-      <c r="H55" s="24" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:8">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1090</v>
+        <v>923</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>19</v>
@@ -14273,133 +14308,133 @@
       <c r="G56" s="18" t="s">
         <v>924</v>
       </c>
-      <c r="H56" s="24" t="s">
-        <v>1091</v>
+      <c r="H56" s="22" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C57" s="18" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>924</v>
+      </c>
+      <c r="H57" s="22" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>1093</v>
+      <c r="E58" s="2" t="s">
+        <v>1096</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>993</v>
+        <v>924</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>1096</v>
+      <c r="E59" s="2" t="s">
+        <v>1099</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>19</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>993</v>
+        <v>924</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C61" s="10" t="s">
-        <v>1098</v>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:8">
+      <c r="C61" s="18" t="s">
+        <v>1101</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H61" s="18" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C62" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>1102</v>
       </c>
+      <c r="F61" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H61" s="24" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:8">
+      <c r="C62" s="18" t="s">
+        <v>1104</v>
+      </c>
       <c r="D62" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H62" s="18" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C63" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="F62" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="18" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H62" s="24" t="s">
         <v>1106</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H63" s="18" t="s">
-        <v>1107</v>
-      </c>
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="3"/>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="10" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="F64" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>1109</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>1100</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>1110</v>
@@ -14410,7 +14445,7 @@
         <v>1111</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>1112</v>
@@ -14419,7 +14454,7 @@
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>1113</v>
@@ -14430,7 +14465,7 @@
         <v>1114</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>1115</v>
@@ -14439,7 +14474,7 @@
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="H66" s="18" t="s">
         <v>1116</v>
@@ -14450,7 +14485,7 @@
         <v>1117</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>1118</v>
@@ -14459,7 +14494,7 @@
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>1119</v>
@@ -14470,7 +14505,7 @@
         <v>1120</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>1121</v>
@@ -14479,9 +14514,9 @@
         <v>19</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H68" s="22" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H68" s="18" t="s">
         <v>1122</v>
       </c>
     </row>
@@ -14489,8 +14524,8 @@
       <c r="C69" s="10" t="s">
         <v>1123</v>
       </c>
-      <c r="D69" s="18" t="s">
-        <v>49</v>
+      <c r="D69" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>1124</v>
@@ -14499,30 +14534,90 @@
         <v>19</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H69" s="22" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H69" s="18" t="s">
         <v>1125</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C70" s="10">
+      <c r="C70" s="10" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H70" s="18" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C71" s="10" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H71" s="22" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C72" s="10" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H72" s="22" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C73" s="10">
         <v>300091</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D73" s="2">
         <v>100</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H70" s="22" t="s">
-        <v>1127</v>
+      <c r="E73" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H73" s="22" t="s">
+        <v>1136</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="1137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="1140">
   <si>
     <t>_id</t>
   </si>
@@ -3527,6 +3527,15 @@
   </si>
   <si>
     <t>4034</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>超级书页</t>
+  </si>
+  <si>
+    <t>4112</t>
   </si>
   <si>
     <t>2000</t>
@@ -13256,7 +13265,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H73"/>
+  <dimension ref="C1:H74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -13864,35 +13873,43 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C34" s="18" t="s">
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C33" s="18" t="s">
         <v>1038</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>914</v>
-      </c>
-      <c r="H34" s="22" t="s">
-        <v>918</v>
-      </c>
+      <c r="E33" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="3"/>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>19</v>
@@ -13901,18 +13918,18 @@
         <v>914</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1041</v>
+        <v>913</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>19</v>
@@ -13921,7 +13938,7 @@
         <v>914</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>1042</v>
+        <v>915</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -13932,7 +13949,7 @@
         <v>912</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>920</v>
+        <v>1044</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>19</v>
@@ -13941,18 +13958,18 @@
         <v>914</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>921</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1045</v>
+        <v>920</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>19</v>
@@ -13961,7 +13978,7 @@
         <v>914</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>1046</v>
+        <v>921</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14026,13 +14043,13 @@
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>899</v>
+        <v>1056</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>19</v>
@@ -14040,19 +14057,19 @@
       <c r="G42" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H42" s="23" t="s">
-        <v>1057</v>
+      <c r="H42" s="22" t="s">
+        <v>1058</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>934</v>
+        <v>899</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>19</v>
@@ -14060,13 +14077,13 @@
       <c r="G43" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H43" s="21" t="s">
-        <v>1059</v>
+      <c r="H43" s="23" t="s">
+        <v>1060</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1060</v>
+        <v>934</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>912</v>
@@ -14080,7 +14097,7 @@
       <c r="G44" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H44" s="23" t="s">
+      <c r="H44" s="21" t="s">
         <v>1062</v>
       </c>
     </row>
@@ -14100,7 +14117,7 @@
       <c r="G45" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H45" s="21" t="s">
+      <c r="H45" s="23" t="s">
         <v>1065</v>
       </c>
     </row>
@@ -14120,7 +14137,7 @@
       <c r="G46" s="18" t="s">
         <v>914</v>
       </c>
-      <c r="H46" s="22" t="s">
+      <c r="H46" s="21" t="s">
         <v>1068</v>
       </c>
     </row>
@@ -14284,43 +14301,43 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="55" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="3"/>
-    </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C56" s="18" t="s">
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C55" s="18" t="s">
         <v>1093</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="F56" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G56" s="18" t="s">
-        <v>924</v>
-      </c>
-      <c r="H56" s="22" t="s">
-        <v>925</v>
-      </c>
+      <c r="E55" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>914</v>
+      </c>
+      <c r="H55" s="22" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="3"/>
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>19</v>
@@ -14329,18 +14346,18 @@
         <v>924</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:8">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>912</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1096</v>
+        <v>927</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>19</v>
@@ -14348,8 +14365,8 @@
       <c r="G58" s="18" t="s">
         <v>924</v>
       </c>
-      <c r="H58" s="24" t="s">
-        <v>1097</v>
+      <c r="H58" s="22" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
@@ -14372,23 +14389,23 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="3:8">
-      <c r="C61" s="18" t="s">
+    <row r="60" customHeight="1" spans="3:8">
+      <c r="C60" s="18" t="s">
         <v>1101</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E60" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="F61" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G61" s="18" t="s">
-        <v>1002</v>
-      </c>
-      <c r="H61" s="24" t="s">
+      <c r="F60" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" s="18" t="s">
+        <v>924</v>
+      </c>
+      <c r="H60" s="24" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -14412,49 +14429,49 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="63" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="3"/>
-    </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C64" s="10" t="s">
+    <row r="63" customHeight="1" spans="3:8">
+      <c r="C63" s="18" t="s">
         <v>1107</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="D63" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G64" s="2" t="s">
+      <c r="F63" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="18" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H63" s="24" t="s">
         <v>1109</v>
       </c>
-      <c r="H64" s="18" t="s">
-        <v>1110</v>
-      </c>
+    </row>
+    <row r="64" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="3"/>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="10" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>1112</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>1109</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>1113</v>
@@ -14465,7 +14482,7 @@
         <v>1114</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>1115</v>
@@ -14474,7 +14491,7 @@
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="H66" s="18" t="s">
         <v>1116</v>
@@ -14485,7 +14502,7 @@
         <v>1117</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>1118</v>
@@ -14494,7 +14511,7 @@
         <v>19</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>1119</v>
@@ -14505,7 +14522,7 @@
         <v>1120</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>1121</v>
@@ -14514,7 +14531,7 @@
         <v>19</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>1122</v>
@@ -14525,7 +14542,7 @@
         <v>1123</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>1124</v>
@@ -14534,7 +14551,7 @@
         <v>19</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="H69" s="18" t="s">
         <v>1125</v>
@@ -14545,7 +14562,7 @@
         <v>1126</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>1127</v>
@@ -14554,7 +14571,7 @@
         <v>19</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="H70" s="18" t="s">
         <v>1128</v>
@@ -14565,7 +14582,7 @@
         <v>1129</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>1130</v>
@@ -14574,9 +14591,9 @@
         <v>19</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="H71" s="22" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H71" s="18" t="s">
         <v>1131</v>
       </c>
     </row>
@@ -14584,8 +14601,8 @@
       <c r="C72" s="10" t="s">
         <v>1132</v>
       </c>
-      <c r="D72" s="18" t="s">
-        <v>49</v>
+      <c r="D72" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>1133</v>
@@ -14594,30 +14611,50 @@
         <v>19</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="H72" s="22" t="s">
         <v>1134</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C73" s="10">
+      <c r="C73" s="10" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H73" s="22" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C74" s="10">
         <v>300091</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D74" s="2">
         <v>100</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="H73" s="22" t="s">
-        <v>1136</v>
+      <c r="E74" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H74" s="22" t="s">
+        <v>1139</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2183" uniqueCount="1234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="1242">
   <si>
     <t>_id</t>
   </si>
@@ -1438,10 +1438,34 @@
     <t>21020001,21020002,21020003,21020004,21020005,21020007,21020009,21020010,22020001,22020002,22020003,22020004,22020005,22020007,22020009,22020010,23020001,23020002,23020003,23020004,23020005,23020007,23020009,23020010</t>
   </si>
   <si>
-    <t>混沌装备</t>
+    <t>混沌装备-全</t>
   </si>
   <si>
     <t>21405801,21405802,21405803,21405804,21405805,21405807,21405809,21405810,22405801,22405802,22405803,22405804,22405805,22405807,22405809,22405810,23405801,23405802,23405803,23405804,23405805,23405807,23405809,23405810</t>
+  </si>
+  <si>
+    <t>混沌装备-剑甲</t>
+  </si>
+  <si>
+    <t>21405801,21405802,22405801,22405802,23405801,23405802</t>
+  </si>
+  <si>
+    <t>混沌装备-项链头盔</t>
+  </si>
+  <si>
+    <t>21405803,21405804,22405803,22405804,23405803,23405804</t>
+  </si>
+  <si>
+    <t>混沌装备-手镯戒指</t>
+  </si>
+  <si>
+    <t>21405805,21405807,22405805,22405807,23405805,23405807</t>
+  </si>
+  <si>
+    <t>混沌装备-鞋子腰带</t>
+  </si>
+  <si>
+    <t>21405809,21405810,22405809,22405810,23405809,23405810</t>
   </si>
   <si>
     <t>209990</t>
@@ -4331,12 +4355,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7432,17 +7456,85 @@
         <v>342</v>
       </c>
     </row>
-    <row r="114" customHeight="1" spans="8:8">
-      <c r="H114" s="14"/>
-    </row>
-    <row r="115" customHeight="1" spans="8:8">
-      <c r="H115" s="14"/>
-    </row>
-    <row r="116" customHeight="1" spans="8:8">
-      <c r="H116" s="14"/>
-    </row>
-    <row r="117" customHeight="1" spans="8:8">
-      <c r="H117" s="14"/>
+    <row r="114" customHeight="1" spans="3:8">
+      <c r="C114" s="2">
+        <v>202004</v>
+      </c>
+      <c r="D114" s="2">
+        <v>1450</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F114" s="2">
+        <v>1</v>
+      </c>
+      <c r="G114" s="2">
+        <v>2</v>
+      </c>
+      <c r="H114" s="23" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:8">
+      <c r="C115" s="2">
+        <v>202005</v>
+      </c>
+      <c r="D115" s="2">
+        <v>1450</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F115" s="2">
+        <v>1</v>
+      </c>
+      <c r="G115" s="2">
+        <v>2</v>
+      </c>
+      <c r="H115" s="23" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:8">
+      <c r="C116" s="2">
+        <v>202006</v>
+      </c>
+      <c r="D116" s="2">
+        <v>1450</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F116" s="2">
+        <v>1</v>
+      </c>
+      <c r="G116" s="2">
+        <v>2</v>
+      </c>
+      <c r="H116" s="23" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:8">
+      <c r="C117" s="2">
+        <v>202007</v>
+      </c>
+      <c r="D117" s="2">
+        <v>1450</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F117" s="2">
+        <v>1</v>
+      </c>
+      <c r="G117" s="2">
+        <v>2</v>
+      </c>
+      <c r="H117" s="23" t="s">
+        <v>350</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -7542,13 +7634,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="21" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>18</v>
@@ -7557,18 +7649,18 @@
         <v>19</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="21" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>18</v>
@@ -7577,18 +7669,18 @@
         <v>19</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="21" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -7597,18 +7689,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="21" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>
@@ -7617,18 +7709,18 @@
         <v>19</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="21" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>18</v>
@@ -7637,18 +7729,18 @@
         <v>19</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="21" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>18</v>
@@ -7657,18 +7749,18 @@
         <v>19</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="21" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>18</v>
@@ -7677,18 +7769,18 @@
         <v>19</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="21" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>18</v>
@@ -7697,18 +7789,18 @@
         <v>19</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="21" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>18</v>
@@ -7717,18 +7809,18 @@
         <v>19</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="21" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>18</v>
@@ -7737,18 +7829,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="21" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>18</v>
@@ -7757,18 +7849,18 @@
         <v>19</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="21" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>18</v>
@@ -7777,18 +7869,18 @@
         <v>19</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="21" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>18</v>
@@ -7797,18 +7889,18 @@
         <v>19</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="21" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>18</v>
@@ -7817,18 +7909,18 @@
         <v>19</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="21" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>18</v>
@@ -7837,18 +7929,18 @@
         <v>19</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="21" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>18</v>
@@ -7857,18 +7949,18 @@
         <v>5</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:8">
       <c r="C22" s="21" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>18</v>
@@ -7877,18 +7969,18 @@
         <v>5</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:8">
       <c r="C23" s="21" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>18</v>
@@ -7897,18 +7989,18 @@
         <v>5</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:8">
       <c r="C24" s="21" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>18</v>
@@ -7917,18 +8009,18 @@
         <v>5</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:8">
       <c r="C25" s="21" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>18</v>
@@ -7937,18 +8029,18 @@
         <v>5</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:8">
       <c r="C26" s="21" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>18</v>
@@ -7957,18 +8049,18 @@
         <v>5</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
       <c r="C27" s="21" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>18</v>
@@ -7977,18 +8069,18 @@
         <v>5</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
       <c r="C28" s="21" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>18</v>
@@ -7997,18 +8089,18 @@
         <v>5</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
       <c r="C29" s="21" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>18</v>
@@ -8017,18 +8109,18 @@
         <v>5</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
       <c r="C30" s="21" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>18</v>
@@ -8037,18 +8129,18 @@
         <v>5</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="21" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>18</v>
@@ -8057,18 +8149,18 @@
         <v>5</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="21" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>18</v>
@@ -8077,18 +8169,18 @@
         <v>5</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="21" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>18</v>
@@ -8097,18 +8189,18 @@
         <v>5</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="21" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>18</v>
@@ -8117,18 +8209,18 @@
         <v>5</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
       <c r="C35" s="21" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>18</v>
@@ -8137,18 +8229,18 @@
         <v>5</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
       <c r="C36" s="21" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>18</v>
@@ -8157,18 +8249,18 @@
         <v>5</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
       <c r="C37" s="21" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>18</v>
@@ -8177,18 +8269,18 @@
         <v>5</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="21" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>18</v>
@@ -8197,18 +8289,18 @@
         <v>5</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="21" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>18</v>
@@ -8217,18 +8309,18 @@
         <v>5</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
       <c r="C40" s="21" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>18</v>
@@ -8237,18 +8329,18 @@
         <v>5</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
       <c r="C41" s="21" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>18</v>
@@ -8257,18 +8349,18 @@
         <v>5</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="21" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>18</v>
@@ -8277,18 +8369,18 @@
         <v>5</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="21" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>18</v>
@@ -8297,18 +8389,18 @@
         <v>5</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="21" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>18</v>
@@ -8317,18 +8409,18 @@
         <v>5</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="21" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>18</v>
@@ -8337,18 +8429,18 @@
         <v>5</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="21" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>18</v>
@@ -8357,18 +8449,18 @@
         <v>5</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="21" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="D47" s="2">
         <v>0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>18</v>
@@ -8377,18 +8469,18 @@
         <v>5</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="21" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>18</v>
@@ -8397,18 +8489,18 @@
         <v>5</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="21" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>18</v>
@@ -8417,18 +8509,18 @@
         <v>5</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="21" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>18</v>
@@ -8437,18 +8529,18 @@
         <v>5</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="21" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>18</v>
@@ -8457,18 +8549,18 @@
         <v>5</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
       <c r="C52" s="21" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>18</v>
@@ -8477,18 +8569,18 @@
         <v>5</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
       <c r="C53" s="21" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>18</v>
@@ -8497,18 +8589,18 @@
         <v>5</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="21" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>18</v>
@@ -8517,18 +8609,18 @@
         <v>5</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="21" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>18</v>
@@ -8537,18 +8629,18 @@
         <v>5</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="21" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>18</v>
@@ -8557,18 +8649,18 @@
         <v>5</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="21" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>18</v>
@@ -8577,18 +8669,18 @@
         <v>5</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="21" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>18</v>
@@ -8597,18 +8689,18 @@
         <v>5</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="21" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>18</v>
@@ -8617,18 +8709,18 @@
         <v>5</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="21" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D60" s="2">
         <v>0</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>18</v>
@@ -8637,18 +8729,18 @@
         <v>5</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="21" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="D61" s="2">
         <v>0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>18</v>
@@ -8657,18 +8749,18 @@
         <v>5</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:8">
       <c r="C62" s="21" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>18</v>
@@ -8677,18 +8769,18 @@
         <v>5</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
       <c r="C63" s="21" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D63" s="2">
         <v>0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>18</v>
@@ -8697,18 +8789,18 @@
         <v>5</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
       <c r="C64" s="21" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>18</v>
@@ -8717,18 +8809,18 @@
         <v>5</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
       <c r="C65" s="21" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>18</v>
@@ -8737,18 +8829,18 @@
         <v>5</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
       <c r="C66" s="21" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D66" s="2">
         <v>0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>18</v>
@@ -8757,18 +8849,18 @@
         <v>5</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="21" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>18</v>
@@ -8777,18 +8869,18 @@
         <v>5</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="21" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>18</v>
@@ -8797,18 +8889,18 @@
         <v>5</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
       <c r="C69" s="21" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>18</v>
@@ -8817,18 +8909,18 @@
         <v>5</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="21" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D70" s="2">
         <v>0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>18</v>
@@ -8837,18 +8929,18 @@
         <v>5</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="21" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>18</v>
@@ -8857,18 +8949,18 @@
         <v>5</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
       <c r="C72" s="21" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>18</v>
@@ -8877,18 +8969,18 @@
         <v>5</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
       <c r="C73" s="21" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>18</v>
@@ -8897,18 +8989,18 @@
         <v>5</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:8">
       <c r="C74" s="21" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>18</v>
@@ -8917,18 +9009,18 @@
         <v>5</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
       <c r="C75" s="21" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="D75" s="2">
         <v>0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>18</v>
@@ -8937,18 +9029,18 @@
         <v>5</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
       <c r="C76" s="21" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="D76" s="2">
         <v>0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>18</v>
@@ -8957,18 +9049,18 @@
         <v>5</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
       <c r="C77" s="21" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="D77" s="2">
         <v>0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>18</v>
@@ -8977,18 +9069,18 @@
         <v>5</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:8">
       <c r="C78" s="21" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D78" s="2">
         <v>0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>18</v>
@@ -8997,18 +9089,18 @@
         <v>5</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:8">
       <c r="C79" s="21" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="D79" s="2">
         <v>0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>18</v>
@@ -9017,18 +9109,18 @@
         <v>5</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="C80" s="21" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="D80" s="2">
         <v>0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>18</v>
@@ -9037,18 +9129,18 @@
         <v>5</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:8">
       <c r="C81" s="21" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D81" s="2">
         <v>0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>18</v>
@@ -9057,18 +9149,18 @@
         <v>5</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:8">
       <c r="C82" s="21" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="D82" s="2">
         <v>0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>18</v>
@@ -9077,18 +9169,18 @@
         <v>5</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:8">
       <c r="C83" s="21" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="D83" s="2">
         <v>0</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>18</v>
@@ -9097,18 +9189,18 @@
         <v>5</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:8">
       <c r="C84" s="21" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="D84" s="2">
         <v>0</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>18</v>
@@ -9117,18 +9209,18 @@
         <v>5</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:8">
       <c r="C85" s="21" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="D85" s="2">
         <v>0</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>18</v>
@@ -9137,18 +9229,18 @@
         <v>5</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:8">
       <c r="C86" s="21" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="D86" s="2">
         <v>0</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>18</v>
@@ -9157,18 +9249,18 @@
         <v>5</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:8">
       <c r="C87" s="21" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="D87" s="2">
         <v>0</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>18</v>
@@ -9177,18 +9269,18 @@
         <v>5</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:8">
       <c r="C88" s="21" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D88" s="2">
         <v>0</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>18</v>
@@ -9197,18 +9289,18 @@
         <v>5</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:8">
       <c r="C89" s="21" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="D89" s="2">
         <v>0</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>18</v>
@@ -9217,18 +9309,18 @@
         <v>5</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:8">
       <c r="C90" s="21" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="D90" s="2">
         <v>0</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>18</v>
@@ -9237,18 +9329,18 @@
         <v>5</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:8">
       <c r="C91" s="21" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="D91" s="2">
         <v>0</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>18</v>
@@ -9257,18 +9349,18 @@
         <v>5</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:8">
       <c r="C92" s="21" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="D92" s="2">
         <v>0</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>18</v>
@@ -9277,18 +9369,18 @@
         <v>5</v>
       </c>
       <c r="H92" s="24" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:8">
       <c r="C93" s="21" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="D93" s="2">
         <v>0</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>18</v>
@@ -9297,18 +9389,18 @@
         <v>5</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:8">
       <c r="C94" s="21" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="D94" s="2">
         <v>0</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>18</v>
@@ -9317,18 +9409,18 @@
         <v>5</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:8">
       <c r="C95" s="21" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="D95" s="2">
         <v>0</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>18</v>
@@ -9337,18 +9429,18 @@
         <v>5</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:8">
       <c r="C96" s="21" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="D96" s="2">
         <v>0</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>18</v>
@@ -9357,18 +9449,18 @@
         <v>5</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:8">
       <c r="C97" s="21" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="D97" s="2">
         <v>0</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>18</v>
@@ -9377,18 +9469,18 @@
         <v>5</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:8">
       <c r="C98" s="21" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D98" s="2">
         <v>0</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>18</v>
@@ -9397,18 +9489,18 @@
         <v>5</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:8">
       <c r="C99" s="21" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="D99" s="2">
         <v>0</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>18</v>
@@ -9417,7 +9509,7 @@
         <v>5</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:3">
@@ -9520,13 +9612,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="21" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>18</v>
@@ -9540,13 +9632,13 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="21" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>18</v>
@@ -9560,13 +9652,13 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="21" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -9580,13 +9672,13 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="21" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>
@@ -9600,13 +9692,13 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="21" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>18</v>
@@ -9622,13 +9714,13 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="21" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>18</v>
@@ -9643,13 +9735,13 @@
     </row>
     <row r="12" customHeight="1" spans="3:8">
       <c r="C12" s="21" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>18</v>
@@ -9663,13 +9755,13 @@
     </row>
     <row r="13" customHeight="1" spans="3:8">
       <c r="C13" s="21" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>18</v>
@@ -9683,13 +9775,13 @@
     </row>
     <row r="14" customHeight="1" spans="3:8">
       <c r="C14" s="21" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>18</v>
@@ -9703,13 +9795,13 @@
     </row>
     <row r="15" customHeight="1" spans="3:8">
       <c r="C15" s="21" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>18</v>
@@ -9723,13 +9815,13 @@
     </row>
     <row r="16" customHeight="1" spans="3:8">
       <c r="C16" s="21" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>18</v>
@@ -9743,13 +9835,13 @@
     </row>
     <row r="17" customHeight="1" spans="3:8">
       <c r="C17" s="21" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>18</v>
@@ -9763,13 +9855,13 @@
     </row>
     <row r="18" customHeight="1" spans="3:8">
       <c r="C18" s="21" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>18</v>
@@ -9783,13 +9875,13 @@
     </row>
     <row r="19" customHeight="1" spans="3:8">
       <c r="C19" s="21" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>18</v>
@@ -9803,13 +9895,13 @@
     </row>
     <row r="20" customHeight="1" spans="3:8">
       <c r="C20" s="21" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>18</v>
@@ -9823,13 +9915,13 @@
     </row>
     <row r="21" customHeight="1" spans="3:8">
       <c r="C21" s="21" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>18</v>
@@ -9843,13 +9935,13 @@
     </row>
     <row r="22" customHeight="1" spans="3:8">
       <c r="C22" s="21" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>18</v>
@@ -9863,13 +9955,13 @@
     </row>
     <row r="23" customHeight="1" spans="3:8">
       <c r="C23" s="21" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>18</v>
@@ -9883,13 +9975,13 @@
     </row>
     <row r="24" customHeight="1" spans="3:8">
       <c r="C24" s="21" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>18</v>
@@ -9903,13 +9995,13 @@
     </row>
     <row r="25" customHeight="1" spans="3:8">
       <c r="C25" s="21" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>18</v>
@@ -9923,13 +10015,13 @@
     </row>
     <row r="26" customHeight="1" spans="3:8">
       <c r="C26" s="21" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>18</v>
@@ -9943,13 +10035,13 @@
     </row>
     <row r="27" customHeight="1" spans="3:8">
       <c r="C27" s="21" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>18</v>
@@ -9963,13 +10055,13 @@
     </row>
     <row r="28" customHeight="1" spans="3:8">
       <c r="C28" s="21" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>18</v>
@@ -9983,13 +10075,13 @@
     </row>
     <row r="29" customHeight="1" spans="3:8">
       <c r="C29" s="21" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>18</v>
@@ -10003,13 +10095,13 @@
     </row>
     <row r="30" customHeight="1" spans="3:8">
       <c r="C30" s="21" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>18</v>
@@ -10023,13 +10115,13 @@
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="21" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>18</v>
@@ -10043,13 +10135,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="21" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>18</v>
@@ -10063,13 +10155,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="21" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>18</v>
@@ -10083,13 +10175,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="21" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>18</v>
@@ -10103,13 +10195,13 @@
     </row>
     <row r="35" customHeight="1" spans="3:8">
       <c r="C35" s="21" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>18</v>
@@ -10123,13 +10215,13 @@
     </row>
     <row r="36" customHeight="1" spans="3:8">
       <c r="C36" s="21" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>18</v>
@@ -10143,13 +10235,13 @@
     </row>
     <row r="37" customHeight="1" spans="3:8">
       <c r="C37" s="21" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>18</v>
@@ -10163,13 +10255,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="21" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>18</v>
@@ -10183,13 +10275,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="21" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>18</v>
@@ -10203,13 +10295,13 @@
     </row>
     <row r="40" customHeight="1" spans="3:8">
       <c r="C40" s="21" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>18</v>
@@ -10223,13 +10315,13 @@
     </row>
     <row r="41" customHeight="1" spans="3:8">
       <c r="C41" s="21" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>18</v>
@@ -10243,13 +10335,13 @@
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="21" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>18</v>
@@ -10263,13 +10355,13 @@
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="21" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>18</v>
@@ -10283,13 +10375,13 @@
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="21" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>18</v>
@@ -10303,13 +10395,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="21" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>18</v>
@@ -10323,13 +10415,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="21" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>18</v>
@@ -10343,13 +10435,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="21" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="D47" s="2">
         <v>0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>18</v>
@@ -10363,13 +10455,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="21" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>18</v>
@@ -10383,13 +10475,13 @@
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="21" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>18</v>
@@ -10403,13 +10495,13 @@
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="21" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="D50" s="2">
         <v>0</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>18</v>
@@ -10423,13 +10515,13 @@
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="21" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>18</v>
@@ -10443,13 +10535,13 @@
     </row>
     <row r="52" customHeight="1" spans="3:8">
       <c r="C52" s="21" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>18</v>
@@ -10463,13 +10555,13 @@
     </row>
     <row r="53" customHeight="1" spans="3:8">
       <c r="C53" s="21" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="D53" s="2">
         <v>0</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>18</v>
@@ -10483,13 +10575,13 @@
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="21" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>18</v>
@@ -10503,13 +10595,13 @@
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="21" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>18</v>
@@ -10523,13 +10615,13 @@
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="21" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="D56" s="2">
         <v>0</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>18</v>
@@ -10543,13 +10635,13 @@
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="21" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>18</v>
@@ -10563,13 +10655,13 @@
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="21" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>18</v>
@@ -10583,13 +10675,13 @@
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="21" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>18</v>
@@ -10603,13 +10695,13 @@
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="21" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="D60" s="2">
         <v>0</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>18</v>
@@ -10623,13 +10715,13 @@
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="21" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="D61" s="2">
         <v>0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>18</v>
@@ -10643,13 +10735,13 @@
     </row>
     <row r="62" customHeight="1" spans="3:8">
       <c r="C62" s="21" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>18</v>
@@ -10663,13 +10755,13 @@
     </row>
     <row r="63" customHeight="1" spans="3:8">
       <c r="C63" s="21" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="D63" s="2">
         <v>0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>18</v>
@@ -10683,13 +10775,13 @@
     </row>
     <row r="64" customHeight="1" spans="3:8">
       <c r="C64" s="21" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>18</v>
@@ -10703,13 +10795,13 @@
     </row>
     <row r="65" customHeight="1" spans="3:8">
       <c r="C65" s="21" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>18</v>
@@ -10723,13 +10815,13 @@
     </row>
     <row r="66" customHeight="1" spans="3:8">
       <c r="C66" s="21" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="D66" s="2">
         <v>0</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>18</v>
@@ -10743,13 +10835,13 @@
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="21" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>18</v>
@@ -10763,13 +10855,13 @@
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="21" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>18</v>
@@ -10783,13 +10875,13 @@
     </row>
     <row r="69" customHeight="1" spans="3:8">
       <c r="C69" s="21" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>18</v>
@@ -10803,13 +10895,13 @@
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="21" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="D70" s="2">
         <v>0</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>18</v>
@@ -10823,13 +10915,13 @@
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="21" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>18</v>
@@ -10843,13 +10935,13 @@
     </row>
     <row r="72" customHeight="1" spans="3:8">
       <c r="C72" s="21" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>18</v>
@@ -10863,13 +10955,13 @@
     </row>
     <row r="73" customHeight="1" spans="3:8">
       <c r="C73" s="21" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>18</v>
@@ -10883,13 +10975,13 @@
     </row>
     <row r="74" customHeight="1" spans="3:8">
       <c r="C74" s="21" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>18</v>
@@ -10903,13 +10995,13 @@
     </row>
     <row r="75" customHeight="1" spans="3:8">
       <c r="C75" s="21" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="D75" s="2">
         <v>0</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>18</v>
@@ -10923,13 +11015,13 @@
     </row>
     <row r="76" customHeight="1" spans="3:8">
       <c r="C76" s="21" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="D76" s="2">
         <v>0</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>18</v>
@@ -10943,13 +11035,13 @@
     </row>
     <row r="77" customHeight="1" spans="3:8">
       <c r="C77" s="21" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="D77" s="2">
         <v>0</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>18</v>
@@ -10963,13 +11055,13 @@
     </row>
     <row r="78" customHeight="1" spans="3:8">
       <c r="C78" s="21" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="D78" s="2">
         <v>0</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>18</v>
@@ -10983,13 +11075,13 @@
     </row>
     <row r="79" customHeight="1" spans="3:8">
       <c r="C79" s="21" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="D79" s="2">
         <v>0</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>18</v>
@@ -11003,13 +11095,13 @@
     </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="C80" s="21" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="D80" s="2">
         <v>0</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>18</v>
@@ -11023,13 +11115,13 @@
     </row>
     <row r="81" customHeight="1" spans="3:8">
       <c r="C81" s="21" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="D81" s="2">
         <v>0</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>18</v>
@@ -11043,13 +11135,13 @@
     </row>
     <row r="82" customHeight="1" spans="3:8">
       <c r="C82" s="21" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="D82" s="2">
         <v>0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>18</v>
@@ -11063,13 +11155,13 @@
     </row>
     <row r="83" customHeight="1" spans="3:8">
       <c r="C83" s="21" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="D83" s="2">
         <v>0</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>18</v>
@@ -11083,13 +11175,13 @@
     </row>
     <row r="84" customHeight="1" spans="3:8">
       <c r="C84" s="21" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="D84" s="2">
         <v>0</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>18</v>
@@ -11103,13 +11195,13 @@
     </row>
     <row r="85" customHeight="1" spans="3:8">
       <c r="C85" s="21" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="D85" s="2">
         <v>0</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>18</v>
@@ -11123,13 +11215,13 @@
     </row>
     <row r="86" customHeight="1" spans="3:8">
       <c r="C86" s="21" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="D86" s="2">
         <v>0</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>18</v>
@@ -11143,13 +11235,13 @@
     </row>
     <row r="87" customHeight="1" spans="3:8">
       <c r="C87" s="21" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="D87" s="2">
         <v>0</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>18</v>
@@ -11163,13 +11255,13 @@
     </row>
     <row r="88" customHeight="1" spans="3:8">
       <c r="C88" s="21" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="D88" s="2">
         <v>0</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>18</v>
@@ -11183,13 +11275,13 @@
     </row>
     <row r="89" customHeight="1" spans="3:8">
       <c r="C89" s="21" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="D89" s="2">
         <v>0</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>18</v>
@@ -11203,13 +11295,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:8">
       <c r="C90" s="21" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="D90" s="2">
         <v>0</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>18</v>
@@ -11223,13 +11315,13 @@
     </row>
     <row r="91" customHeight="1" spans="3:8">
       <c r="C91" s="21" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="D91" s="2">
         <v>0</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>18</v>
@@ -11243,13 +11335,13 @@
     </row>
     <row r="92" customHeight="1" spans="3:8">
       <c r="C92" s="21" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="D92" s="2">
         <v>0</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>18</v>
@@ -11263,13 +11355,13 @@
     </row>
     <row r="93" customHeight="1" spans="3:8">
       <c r="C93" s="21" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="D93" s="2">
         <v>0</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>18</v>
@@ -11283,13 +11375,13 @@
     </row>
     <row r="94" customHeight="1" spans="3:8">
       <c r="C94" s="21" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="D94" s="2">
         <v>0</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>18</v>
@@ -11303,13 +11395,13 @@
     </row>
     <row r="95" s="16" customFormat="1" customHeight="1" spans="3:8">
       <c r="C95" s="25" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="D95" s="16">
         <v>0</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="F95" s="16" t="s">
         <v>18</v>
@@ -11323,13 +11415,13 @@
     </row>
     <row r="96" customHeight="1" spans="3:8">
       <c r="C96" s="21" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="D96" s="2">
         <v>0</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>18</v>
@@ -11343,13 +11435,13 @@
     </row>
     <row r="97" customHeight="1" spans="3:8">
       <c r="C97" s="21" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="D97" s="2">
         <v>0</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>18</v>
@@ -11363,13 +11455,13 @@
     </row>
     <row r="98" customHeight="1" spans="3:8">
       <c r="C98" s="21" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="D98" s="2">
         <v>0</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>18</v>
@@ -11383,13 +11475,13 @@
     </row>
     <row r="99" customHeight="1" spans="3:8">
       <c r="C99" s="21" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="D99" s="2">
         <v>0</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>18</v>
@@ -11403,13 +11495,13 @@
     </row>
     <row r="100" customHeight="1" spans="3:8">
       <c r="C100" s="21" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="D100" s="2">
         <v>0</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>18</v>
@@ -11423,13 +11515,13 @@
     </row>
     <row r="101" customHeight="1" spans="3:8">
       <c r="C101" s="21" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="D101" s="2">
         <v>0</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>18</v>
@@ -11443,13 +11535,13 @@
     </row>
     <row r="102" customHeight="1" spans="3:8">
       <c r="C102" s="21" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="D102" s="2">
         <v>0</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>18</v>
@@ -11463,13 +11555,13 @@
     </row>
     <row r="103" customHeight="1" spans="3:8">
       <c r="C103" s="21" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="D103" s="2">
         <v>0</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>18</v>
@@ -11483,13 +11575,13 @@
     </row>
     <row r="104" customHeight="1" spans="3:8">
       <c r="C104" s="21" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="D104" s="2">
         <v>0</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>18</v>
@@ -11503,13 +11595,13 @@
     </row>
     <row r="105" customHeight="1" spans="3:8">
       <c r="C105" s="21" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="D105" s="2">
         <v>0</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>18</v>
@@ -11523,13 +11615,13 @@
     </row>
     <row r="106" customHeight="1" spans="3:8">
       <c r="C106" s="21" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="D106" s="2">
         <v>0</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>18</v>
@@ -11543,13 +11635,13 @@
     </row>
     <row r="107" customHeight="1" spans="3:8">
       <c r="C107" s="21" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="D107" s="2">
         <v>0</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>18</v>
@@ -11563,13 +11655,13 @@
     </row>
     <row r="108" customHeight="1" spans="3:8">
       <c r="C108" s="21" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="D108" s="2">
         <v>0</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>18</v>
@@ -11583,13 +11675,13 @@
     </row>
     <row r="109" customHeight="1" spans="3:8">
       <c r="C109" s="21" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="D109" s="2">
         <v>0</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>18</v>
@@ -11603,13 +11695,13 @@
     </row>
     <row r="110" customHeight="1" spans="3:8">
       <c r="C110" s="21" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="D110" s="2">
         <v>0</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>18</v>
@@ -11623,13 +11715,13 @@
     </row>
     <row r="111" customHeight="1" spans="3:8">
       <c r="C111" s="21" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="D111" s="2">
         <v>0</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>18</v>
@@ -11643,13 +11735,13 @@
     </row>
     <row r="112" customHeight="1" spans="3:8">
       <c r="C112" s="21" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="D112" s="2">
         <v>0</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>18</v>
@@ -11663,13 +11755,13 @@
     </row>
     <row r="113" customHeight="1" spans="3:8">
       <c r="C113" s="21" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="D113" s="2">
         <v>0</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>18</v>
@@ -11683,13 +11775,13 @@
     </row>
     <row r="114" customHeight="1" spans="3:8">
       <c r="C114" s="21" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D114" s="2">
         <v>0</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>18</v>
@@ -11703,13 +11795,13 @@
     </row>
     <row r="115" customHeight="1" spans="3:8">
       <c r="C115" s="21" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="D115" s="2">
         <v>0</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>18</v>
@@ -11723,13 +11815,13 @@
     </row>
     <row r="116" customHeight="1" spans="3:8">
       <c r="C116" s="21" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="D116" s="2">
         <v>0</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>18</v>
@@ -11743,13 +11835,13 @@
     </row>
     <row r="117" customHeight="1" spans="3:8">
       <c r="C117" s="21" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="D117" s="2">
         <v>0</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>18</v>
@@ -11763,13 +11855,13 @@
     </row>
     <row r="118" customHeight="1" spans="3:8">
       <c r="C118" s="21" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="D118" s="2">
         <v>0</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>18</v>
@@ -11783,13 +11875,13 @@
     </row>
     <row r="119" customHeight="1" spans="3:8">
       <c r="C119" s="21" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="D119" s="2">
         <v>0</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>18</v>
@@ -11803,13 +11895,13 @@
     </row>
     <row r="120" customHeight="1" spans="3:8">
       <c r="C120" s="21" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="D120" s="2">
         <v>0</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>18</v>
@@ -11823,13 +11915,13 @@
     </row>
     <row r="121" customHeight="1" spans="3:8">
       <c r="C121" s="21" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="D121" s="2">
         <v>0</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>18</v>
@@ -11843,13 +11935,13 @@
     </row>
     <row r="122" customHeight="1" spans="3:8">
       <c r="C122" s="21" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="D122" s="2">
         <v>0</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>18</v>
@@ -11863,13 +11955,13 @@
     </row>
     <row r="123" customHeight="1" spans="3:8">
       <c r="C123" s="21" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="D123" s="2">
         <v>0</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>18</v>
@@ -11883,13 +11975,13 @@
     </row>
     <row r="124" customHeight="1" spans="3:8">
       <c r="C124" s="21" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="D124" s="2">
         <v>0</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>18</v>
@@ -11903,13 +11995,13 @@
     </row>
     <row r="125" customHeight="1" spans="3:8">
       <c r="C125" s="21" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="D125" s="2">
         <v>0</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>18</v>
@@ -11923,13 +12015,13 @@
     </row>
     <row r="126" customHeight="1" spans="3:8">
       <c r="C126" s="21" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="D126" s="2">
         <v>0</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>18</v>
@@ -11943,13 +12035,13 @@
     </row>
     <row r="127" customHeight="1" spans="3:8">
       <c r="C127" s="21" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="D127" s="2">
         <v>0</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>18</v>
@@ -11963,13 +12055,13 @@
     </row>
     <row r="128" customHeight="1" spans="3:8">
       <c r="C128" s="21" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="D128" s="2">
         <v>0</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>18</v>
@@ -11983,13 +12075,13 @@
     </row>
     <row r="129" customHeight="1" spans="3:8">
       <c r="C129" s="21" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="D129" s="2">
         <v>0</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>18</v>
@@ -12003,13 +12095,13 @@
     </row>
     <row r="130" s="16" customFormat="1" customHeight="1" spans="3:8">
       <c r="C130" s="25" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="D130" s="16">
         <v>0</v>
       </c>
       <c r="E130" s="16" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="F130" s="16" t="s">
         <v>18</v>
@@ -12023,13 +12115,13 @@
     </row>
     <row r="131" customHeight="1" spans="3:8">
       <c r="C131" s="21" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="D131" s="2">
         <v>0</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>18</v>
@@ -12043,13 +12135,13 @@
     </row>
     <row r="132" customHeight="1" spans="3:8">
       <c r="C132" s="21" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="D132" s="2">
         <v>0</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>18</v>
@@ -12063,13 +12155,13 @@
     </row>
     <row r="133" customHeight="1" spans="3:8">
       <c r="C133" s="21" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="D133" s="2">
         <v>0</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>18</v>
@@ -12083,13 +12175,13 @@
     </row>
     <row r="134" customHeight="1" spans="3:8">
       <c r="C134" s="21" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D134" s="2">
         <v>0</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>18</v>
@@ -12103,13 +12195,13 @@
     </row>
     <row r="135" customHeight="1" spans="3:8">
       <c r="C135" s="21" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="D135" s="2">
         <v>0</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>18</v>
@@ -12123,13 +12215,13 @@
     </row>
     <row r="136" customHeight="1" spans="3:8">
       <c r="C136" s="21" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D136" s="2">
         <v>0</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>18</v>
@@ -12143,13 +12235,13 @@
     </row>
     <row r="137" customHeight="1" spans="3:8">
       <c r="C137" s="21" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="D137" s="2">
         <v>0</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>18</v>
@@ -12163,13 +12255,13 @@
     </row>
     <row r="138" customHeight="1" spans="3:8">
       <c r="C138" s="21" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="D138" s="2">
         <v>0</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>18</v>
@@ -12183,13 +12275,13 @@
     </row>
     <row r="139" customHeight="1" spans="3:8">
       <c r="C139" s="21" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="D139" s="2">
         <v>0</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>18</v>
@@ -12203,13 +12295,13 @@
     </row>
     <row r="140" customHeight="1" spans="3:8">
       <c r="C140" s="21" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="D140" s="2">
         <v>0</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>18</v>
@@ -12223,13 +12315,13 @@
     </row>
     <row r="141" customHeight="1" spans="3:8">
       <c r="C141" s="21" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="D141" s="2">
         <v>0</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>18</v>
@@ -12243,13 +12335,13 @@
     </row>
     <row r="142" customHeight="1" spans="3:8">
       <c r="C142" s="21" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="D142" s="2">
         <v>0</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>18</v>
@@ -12263,13 +12355,13 @@
     </row>
     <row r="143" customHeight="1" spans="3:8">
       <c r="C143" s="21" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="D143" s="2">
         <v>0</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>18</v>
@@ -12283,13 +12375,13 @@
     </row>
     <row r="144" customHeight="1" spans="3:8">
       <c r="C144" s="21" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="D144" s="2">
         <v>0</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>18</v>
@@ -12303,13 +12395,13 @@
     </row>
     <row r="145" customHeight="1" spans="3:8">
       <c r="C145" s="21" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="D145" s="2">
         <v>0</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>18</v>
@@ -12323,13 +12415,13 @@
     </row>
     <row r="146" customHeight="1" spans="3:8">
       <c r="C146" s="21" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="D146" s="2">
         <v>0</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>18</v>
@@ -12343,13 +12435,13 @@
     </row>
     <row r="147" customHeight="1" spans="3:8">
       <c r="C147" s="21" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="D147" s="2">
         <v>0</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>18</v>
@@ -12363,13 +12455,13 @@
     </row>
     <row r="148" customHeight="1" spans="3:8">
       <c r="C148" s="21" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="D148" s="2">
         <v>0</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>18</v>
@@ -12383,13 +12475,13 @@
     </row>
     <row r="149" customHeight="1" spans="3:8">
       <c r="C149" s="21" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="D149" s="2">
         <v>0</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>18</v>
@@ -12403,13 +12495,13 @@
     </row>
     <row r="150" customHeight="1" spans="3:8">
       <c r="C150" s="21" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="D150" s="2">
         <v>0</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>18</v>
@@ -12423,13 +12515,13 @@
     </row>
     <row r="151" customHeight="1" spans="3:8">
       <c r="C151" s="21" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="D151" s="2">
         <v>0</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>18</v>
@@ -12443,13 +12535,13 @@
     </row>
     <row r="152" customHeight="1" spans="3:8">
       <c r="C152" s="21" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="D152" s="2">
         <v>0</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>18</v>
@@ -12463,13 +12555,13 @@
     </row>
     <row r="153" customHeight="1" spans="3:8">
       <c r="C153" s="21" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="D153" s="2">
         <v>0</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>18</v>
@@ -12483,13 +12575,13 @@
     </row>
     <row r="154" customHeight="1" spans="3:8">
       <c r="C154" s="21" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="D154" s="2">
         <v>0</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>18</v>
@@ -12503,13 +12595,13 @@
     </row>
     <row r="155" customHeight="1" spans="3:8">
       <c r="C155" s="21" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="D155" s="2">
         <v>0</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>18</v>
@@ -12523,13 +12615,13 @@
     </row>
     <row r="156" customHeight="1" spans="3:8">
       <c r="C156" s="21" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="D156" s="2">
         <v>0</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>18</v>
@@ -12543,13 +12635,13 @@
     </row>
     <row r="157" customHeight="1" spans="3:8">
       <c r="C157" s="21" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="D157" s="2">
         <v>0</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>18</v>
@@ -12563,13 +12655,13 @@
     </row>
     <row r="158" customHeight="1" spans="3:8">
       <c r="C158" s="21" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="D158" s="2">
         <v>0</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>18</v>
@@ -12583,13 +12675,13 @@
     </row>
     <row r="159" customHeight="1" spans="3:8">
       <c r="C159" s="21" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="D159" s="2">
         <v>0</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>18</v>
@@ -12603,13 +12695,13 @@
     </row>
     <row r="160" customHeight="1" spans="3:8">
       <c r="C160" s="21" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="D160" s="2">
         <v>0</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>18</v>
@@ -12623,13 +12715,13 @@
     </row>
     <row r="161" customHeight="1" spans="3:8">
       <c r="C161" s="21" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="D161" s="2">
         <v>0</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>18</v>
@@ -12643,13 +12735,13 @@
     </row>
     <row r="162" customHeight="1" spans="3:8">
       <c r="C162" s="21" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="D162" s="2">
         <v>0</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>18</v>
@@ -12663,13 +12755,13 @@
     </row>
     <row r="163" customHeight="1" spans="3:8">
       <c r="C163" s="21" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="D163" s="2">
         <v>0</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>18</v>
@@ -12683,13 +12775,13 @@
     </row>
     <row r="164" customHeight="1" spans="3:8">
       <c r="C164" s="21" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="D164" s="2">
         <v>0</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>18</v>
@@ -12807,7 +12899,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>18</v>
@@ -12827,7 +12919,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>18</v>
@@ -12847,7 +12939,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -12867,7 +12959,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>
@@ -12887,7 +12979,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>18</v>
@@ -12909,7 +13001,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>18</v>
@@ -12930,7 +13022,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>18</v>
@@ -12950,7 +13042,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>18</v>
@@ -12970,7 +13062,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>18</v>
@@ -12990,7 +13082,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>18</v>
@@ -13010,7 +13102,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>18</v>
@@ -13030,7 +13122,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>18</v>
@@ -13050,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>18</v>
@@ -13070,7 +13162,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>18</v>
@@ -13090,7 +13182,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>18</v>
@@ -13110,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>18</v>
@@ -13130,7 +13222,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>18</v>
@@ -13150,7 +13242,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>18</v>
@@ -13170,7 +13262,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>18</v>
@@ -13190,7 +13282,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>18</v>
@@ -13210,7 +13302,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>18</v>
@@ -13230,7 +13322,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>18</v>
@@ -13253,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>18</v>
@@ -13273,7 +13365,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>18</v>
@@ -13293,7 +13385,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>18</v>
@@ -13313,7 +13405,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>18</v>
@@ -13333,7 +13425,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>18</v>
@@ -13353,7 +13445,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>18</v>
@@ -13373,7 +13465,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>18</v>
@@ -13393,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>18</v>
@@ -13413,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>18</v>
@@ -13433,7 +13525,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>18</v>
@@ -13542,13 +13634,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="21" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>18</v>
@@ -13562,13 +13654,13 @@
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="21" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>18</v>
@@ -13582,13 +13674,13 @@
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="21" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="F8" s="2">
         <v>50</v>
@@ -13602,13 +13694,13 @@
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="21" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="F9" s="2">
         <v>20</v>
@@ -13622,13 +13714,13 @@
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="21" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>18</v>
@@ -13642,13 +13734,13 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="21" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>18</v>
@@ -13662,13 +13754,13 @@
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="21" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>18</v>
@@ -13682,13 +13774,13 @@
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="21" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>18</v>
@@ -13697,18 +13789,18 @@
         <v>3</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="21" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>18</v>
@@ -13717,18 +13809,18 @@
         <v>3</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="21" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -13737,18 +13829,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="21" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="F16" s="2">
         <v>100</v>
@@ -13762,13 +13854,13 @@
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="21" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="F17" s="2">
         <v>40</v>
@@ -13782,13 +13874,13 @@
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="21" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="F18" s="2">
         <v>200</v>
@@ -13802,13 +13894,13 @@
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="21" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="F19" s="2">
         <v>80</v>
@@ -13822,13 +13914,13 @@
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="21" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>18</v>
@@ -13842,13 +13934,13 @@
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="21" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="F21" s="2">
         <v>500</v>
@@ -13862,13 +13954,13 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="21" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="F22" s="2">
         <v>200</v>
@@ -13882,113 +13974,113 @@
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="21" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="21" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="21" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="21" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>19</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="21" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>19</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="21" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>18</v>
@@ -13997,18 +14089,18 @@
         <v>3</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="21" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>18</v>
@@ -14017,18 +14109,18 @@
         <v>3</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="21" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>18</v>
@@ -14037,18 +14129,18 @@
         <v>3</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="21" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="F31" s="2">
         <v>2</v>
@@ -14062,13 +14154,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="21" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -14082,13 +14174,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="21" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="F33" s="2">
         <v>200</v>
@@ -14102,13 +14194,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="21" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="F34" s="2">
         <v>100</v>
@@ -14122,53 +14214,53 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="21" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="F35" s="2">
         <v>10</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="21" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="F36" s="2">
         <v>15</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="21" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>18</v>
@@ -14182,13 +14274,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="21" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="F38" s="2">
         <v>1000</v>
@@ -14202,13 +14294,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="21" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="F39" s="2">
         <v>300</v>
@@ -14222,13 +14314,13 @@
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="21" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -14237,19 +14329,19 @@
         <v>5</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="41" customFormat="1" customHeight="1"/>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="21" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="F43" s="2">
         <v>1</v>
@@ -14263,13 +14355,13 @@
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="21" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="F44" s="2">
         <v>1</v>
@@ -14283,13 +14375,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="21" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="F45" s="2">
         <v>1</v>
@@ -14303,13 +14395,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="21" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
@@ -14323,13 +14415,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="21" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -14343,13 +14435,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="21" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -14363,13 +14455,13 @@
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="21" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="F49" s="2">
         <v>1</v>
@@ -14478,13 +14570,13 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="2" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>18</v>
@@ -14493,18 +14585,18 @@
         <v>19</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="20" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>18</v>
@@ -14513,18 +14605,18 @@
         <v>19</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="20" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>18</v>
@@ -14533,18 +14625,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="20" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>18</v>
@@ -14553,18 +14645,18 @@
         <v>19</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="20" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>18</v>
@@ -14573,7 +14665,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14581,10 +14673,10 @@
         <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>18</v>
@@ -14593,18 +14685,18 @@
         <v>19</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="20" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>18</v>
@@ -14613,18 +14705,18 @@
         <v>16</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="20" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>18</v>
@@ -14633,18 +14725,18 @@
         <v>16</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="20" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>18</v>
@@ -14653,18 +14745,18 @@
         <v>16</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="20" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>18</v>
@@ -14673,18 +14765,18 @@
         <v>16</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="20" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>18</v>
@@ -14693,18 +14785,18 @@
         <v>16</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="20" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>18</v>
@@ -14713,18 +14805,18 @@
         <v>16</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="20" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>18</v>
@@ -14733,7 +14825,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="19" customFormat="1" customHeight="1" spans="3:8">
@@ -14749,199 +14841,199 @@
         <v>306</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="20" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="20" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="20" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="20" t="s">
         <v>1104</v>
       </c>
-      <c r="F23" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>1096</v>
-      </c>
       <c r="H23" s="26" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="20" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="20" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="20" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="F26" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="20" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="20" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="20" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14949,99 +15041,99 @@
         <v>310</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="F30" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H30" s="26" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="20" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="F31" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="20" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="F32" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="20" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="F33" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="20" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="35" customFormat="1" customHeight="1" spans="3:8">
@@ -15054,422 +15146,422 @@
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="20" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="20" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="F37" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="20" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="F38" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="20" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="F39" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="20" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="20" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="F41" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="20" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="F42" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="20" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="F43" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="20" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="F44" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H44" s="27" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="20" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="F45" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="20" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="F46" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H46" s="27" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="20" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="F47" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="20" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="F48" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="20" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="F49" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="20" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="F50" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H50" s="26" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="20" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="F51" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H51" s="26" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="20" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="F52" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H52" s="26" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="20" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="F53" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H53" s="26" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="20" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="F54" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G54" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="20" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="F55" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G55" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="20" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="F56" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="H56" s="26" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="3:8">
@@ -15482,122 +15574,122 @@
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="20" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="F58" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G58" s="20" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="H58" s="26" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="20" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="F59" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="H59" s="26" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="20" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="F60" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="H60" s="28" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="20" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="F61" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="H61" s="28" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
       <c r="C63" s="20" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="F63" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H63" s="28" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
       <c r="C64" s="20" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F64" s="20" t="s">
         <v>18</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H64" s="28" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="3:8">
@@ -15610,182 +15702,182 @@
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="10" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C67" s="10" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C68" s="10" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C69" s="10" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C70" s="10" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C71" s="10" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>38</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C72" s="10" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="H72" s="20" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C73" s="10" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="H73" s="26" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C74" s="10" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="D74" s="20" t="s">
         <v>48</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15796,16 +15888,16 @@
         <v>100</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="H75" s="26" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="1254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="1256">
   <si>
     <t>_id</t>
   </si>
@@ -3722,6 +3722,12 @@
   </si>
   <si>
     <t>19,20,21,22,23,24</t>
+  </si>
+  <si>
+    <t>宝石随机</t>
+  </si>
+  <si>
+    <t>60000001,60000002,60000003,60000004,60000005,60000006,60000007,60000008,60000009,60000010</t>
   </si>
   <si>
     <t>特殊图鉴碎片</t>
@@ -14507,7 +14513,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H79"/>
+  <dimension ref="C1:H82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -14855,463 +14861,439 @@
       <c r="G19" s="1"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C20" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>1012</v>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C20" s="1">
+        <v>601</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>1103</v>
       </c>
-      <c r="F20" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="17" t="s">
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>5</v>
+      </c>
+      <c r="H20" s="21" t="s">
         <v>1104</v>
       </c>
-      <c r="H20" s="23" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C21" s="17" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>1104</v>
-      </c>
-      <c r="H21" s="23" t="s">
-        <v>1108</v>
-      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="17" t="s">
-        <v>1109</v>
+        <v>306</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="17" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="17" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="17" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1043</v>
+        <v>1117</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>1044</v>
+        <v>1106</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>1045</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="17" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="17" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1125</v>
+        <v>1043</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>1104</v>
+        <v>1044</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>1126</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="17" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="17" t="s">
-        <v>310</v>
+        <v>1126</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>1031</v>
+        <v>1129</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="17" t="s">
-        <v>1134</v>
+        <v>310</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>1104</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>1136</v>
+        <v>1106</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>1133</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>1137</v>
+        <v>1031</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>1104</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>1139</v>
+        <v>1106</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:8">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>1144</v>
+      <c r="E35" s="1" t="s">
+        <v>1140</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:8">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>1147</v>
+      <c r="E36" s="1" t="s">
+        <v>1143</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E38" s="8" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C39" s="17" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H39" s="17" t="s">
         <v>1153</v>
       </c>
-      <c r="F38" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>1104</v>
-      </c>
-      <c r="H38" s="3" t="s">
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C40" s="17" t="s">
         <v>1154</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C40" s="17" t="s">
-        <v>1155</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>1017</v>
+      <c r="E40" s="8" t="s">
+        <v>1155</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1014</v>
-      </c>
-      <c r="H40" s="23" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C41" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>1156</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" s="17" t="s">
-        <v>1014</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C42" s="17" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G42" s="17" t="s">
-        <v>1014</v>
-      </c>
-      <c r="H42" s="23" t="s">
-        <v>1159</v>
-      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="3"/>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>18</v>
@@ -15320,18 +15302,18 @@
         <v>1014</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1162</v>
+        <v>1013</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>18</v>
@@ -15340,18 +15322,18 @@
         <v>1014</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>1163</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>18</v>
@@ -15360,18 +15342,18 @@
         <v>1014</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1168</v>
+        <v>1020</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>18</v>
@@ -15380,18 +15362,18 @@
         <v>1014</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>1169</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>1170</v>
+        <v>1163</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1171</v>
+        <v>1164</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>18</v>
@@ -15400,18 +15382,18 @@
         <v>1014</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>1172</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>999</v>
+        <v>1166</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>18</v>
@@ -15419,19 +15401,19 @@
       <c r="G48" s="17" t="s">
         <v>1014</v>
       </c>
-      <c r="H48" s="24" t="s">
-        <v>1174</v>
+      <c r="H48" s="23" t="s">
+        <v>1168</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>1034</v>
+        <v>1169</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>18</v>
@@ -15439,19 +15421,19 @@
       <c r="G49" s="17" t="s">
         <v>1014</v>
       </c>
-      <c r="H49" s="21" t="s">
-        <v>1176</v>
+      <c r="H49" s="23" t="s">
+        <v>1171</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>18</v>
@@ -15459,19 +15441,19 @@
       <c r="G50" s="17" t="s">
         <v>1014</v>
       </c>
-      <c r="H50" s="24" t="s">
-        <v>1179</v>
+      <c r="H50" s="23" t="s">
+        <v>1174</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="17" t="s">
-        <v>1180</v>
+        <v>999</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>18</v>
@@ -15479,19 +15461,19 @@
       <c r="G51" s="17" t="s">
         <v>1014</v>
       </c>
-      <c r="H51" s="21" t="s">
-        <v>1182</v>
+      <c r="H51" s="24" t="s">
+        <v>1176</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="17" t="s">
-        <v>1183</v>
+        <v>1034</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>18</v>
@@ -15499,19 +15481,19 @@
       <c r="G52" s="17" t="s">
         <v>1014</v>
       </c>
-      <c r="H52" s="23" t="s">
-        <v>1185</v>
+      <c r="H52" s="21" t="s">
+        <v>1178</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>18</v>
@@ -15519,19 +15501,19 @@
       <c r="G53" s="17" t="s">
         <v>1014</v>
       </c>
-      <c r="H53" s="23" t="s">
-        <v>1188</v>
+      <c r="H53" s="24" t="s">
+        <v>1181</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="17" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>18</v>
@@ -15539,19 +15521,19 @@
       <c r="G54" s="17" t="s">
         <v>1014</v>
       </c>
-      <c r="H54" s="23" t="s">
-        <v>1191</v>
+      <c r="H54" s="21" t="s">
+        <v>1184</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>18</v>
@@ -15560,18 +15542,18 @@
         <v>1014</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>18</v>
@@ -15580,18 +15562,18 @@
         <v>1014</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>1197</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="17" t="s">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1199</v>
+        <v>1192</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>18</v>
@@ -15600,18 +15582,18 @@
         <v>1014</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>1200</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="17" t="s">
-        <v>1201</v>
+        <v>1194</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1202</v>
+        <v>1195</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>18</v>
@@ -15620,18 +15602,18 @@
         <v>1014</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>1203</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="17" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1205</v>
+        <v>1198</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>18</v>
@@ -15640,18 +15622,18 @@
         <v>1014</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="17" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>18</v>
@@ -15660,86 +15642,86 @@
         <v>1014</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="3"/>
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C61" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" s="17" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H61" s="23" t="s">
+        <v>1205</v>
+      </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="17" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1023</v>
+        <v>1207</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>1025</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="17" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1027</v>
+        <v>1210</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:8">
-      <c r="C64" s="17" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C65" s="17" t="s">
         <v>1212</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F64" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G64" s="17" t="s">
-        <v>1024</v>
-      </c>
-      <c r="H64" s="21" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:8">
-      <c r="C65" s="17" t="s">
-        <v>1215</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1216</v>
+        <v>1023</v>
       </c>
       <c r="F65" s="17" t="s">
         <v>18</v>
@@ -15747,256 +15729,316 @@
       <c r="G65" s="17" t="s">
         <v>1024</v>
       </c>
-      <c r="H65" s="21" t="s">
-        <v>1217</v>
+      <c r="H65" s="23" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C66" s="17" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" s="17" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H66" s="23" t="s">
+        <v>1028</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="17" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>1104</v>
+        <v>1024</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="17" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H68" s="21" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:8">
+      <c r="C70" s="17" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H70" s="21" t="s">
         <v>1222</v>
       </c>
-      <c r="F68" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" s="17" t="s">
-        <v>1104</v>
-      </c>
-      <c r="H68" s="21" t="s">
+    </row>
+    <row r="71" customHeight="1" spans="3:8">
+      <c r="C71" s="17" t="s">
         <v>1223</v>
       </c>
-    </row>
-    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C70" s="10" t="s">
+      <c r="D71" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E70" s="1" t="s">
+      <c r="F71" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H71" s="21" t="s">
         <v>1225</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H70" s="17" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C71" s="10" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>1229</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H71" s="17" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C72" s="10" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H72" s="17" t="s">
-        <v>1233</v>
-      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="3"/>
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C73" s="10" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C74" s="10" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C75" s="10" t="s">
-        <v>1240</v>
+        <v>1233</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1241</v>
+        <v>1234</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>1242</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C76" s="10" t="s">
-        <v>1243</v>
+        <v>1236</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1244</v>
+        <v>1237</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>1245</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C77" s="10" t="s">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1247</v>
+        <v>1240</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H77" s="23" t="s">
-        <v>1248</v>
+        <v>1228</v>
+      </c>
+      <c r="H77" s="17" t="s">
+        <v>1241</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C78" s="10" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H78" s="17" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C79" s="10" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C80" s="10" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>1249</v>
       </c>
-      <c r="D78" s="17" t="s">
+      <c r="F80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H80" s="23" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C81" s="10" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D81" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>1250</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H78" s="23" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C79" s="10">
+      <c r="E81" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H81" s="23" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C82" s="10">
         <v>300091</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D82" s="1">
         <v>100</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H79" s="23" t="s">
-        <v>1253</v>
+      <c r="E82" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H82" s="23" t="s">
+        <v>1255</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="1256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="1258">
   <si>
     <t>_id</t>
   </si>
@@ -3575,6 +3575,12 @@
   </si>
   <si>
     <t>4021</t>
+  </si>
+  <si>
+    <t>220042</t>
+  </si>
+  <si>
+    <t>暗金魂心</t>
   </si>
   <si>
     <t>220101</t>
@@ -14357,16 +14363,35 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="41" customFormat="1" customHeight="1"/>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C41" s="18" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1">
+        <v>4041</v>
+      </c>
+    </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="F43" s="1">
         <v>1</v>
@@ -14380,13 +14405,13 @@
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="F44" s="1">
         <v>1</v>
@@ -14400,13 +14425,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
@@ -14420,13 +14445,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -14440,13 +14465,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -14460,13 +14485,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="F48" s="1">
         <v>1</v>
@@ -14480,13 +14505,13 @@
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
@@ -14595,13 +14620,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="1" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
@@ -14610,18 +14635,18 @@
         <v>19</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -14630,18 +14655,18 @@
         <v>19</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>18</v>
@@ -14650,18 +14675,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>18</v>
@@ -14670,18 +14695,18 @@
         <v>19</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -14690,7 +14715,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -14701,7 +14726,7 @@
         <v>1012</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -14710,18 +14735,18 @@
         <v>19</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
@@ -14730,18 +14755,18 @@
         <v>16</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -14750,18 +14775,18 @@
         <v>16</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="17" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -14770,18 +14795,18 @@
         <v>16</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="17" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>18</v>
@@ -14790,18 +14815,18 @@
         <v>16</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
@@ -14810,18 +14835,18 @@
         <v>16</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>18</v>
@@ -14830,18 +14855,18 @@
         <v>16</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>18</v>
@@ -14850,7 +14875,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14869,7 +14894,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -14878,7 +14903,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14897,121 +14922,121 @@
         <v>1012</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="17" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="17" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="17" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="17" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="17" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>1012</v>
@@ -15031,62 +15056,62 @@
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="17" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="17" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15097,16 +15122,16 @@
         <v>1012</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15117,156 +15142,156 @@
         <v>1012</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="17" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="17" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15287,7 +15312,7 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>1012</v>
@@ -15307,7 +15332,7 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1012</v>
@@ -15327,13 +15352,13 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>18</v>
@@ -15342,12 +15367,12 @@
         <v>1014</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1012</v>
@@ -15367,13 +15392,13 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>18</v>
@@ -15382,18 +15407,18 @@
         <v>1014</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>18</v>
@@ -15402,18 +15427,18 @@
         <v>1014</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>18</v>
@@ -15422,18 +15447,18 @@
         <v>1014</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>18</v>
@@ -15442,7 +15467,7 @@
         <v>1014</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15453,7 +15478,7 @@
         <v>1012</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>18</v>
@@ -15462,7 +15487,7 @@
         <v>1014</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15473,7 +15498,7 @@
         <v>1012</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>18</v>
@@ -15482,18 +15507,18 @@
         <v>1014</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>18</v>
@@ -15502,18 +15527,18 @@
         <v>1014</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="17" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>18</v>
@@ -15522,18 +15547,18 @@
         <v>1014</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>18</v>
@@ -15542,18 +15567,18 @@
         <v>1014</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>18</v>
@@ -15562,18 +15587,18 @@
         <v>1014</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="17" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>18</v>
@@ -15582,18 +15607,18 @@
         <v>1014</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="17" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>18</v>
@@ -15602,18 +15627,18 @@
         <v>1014</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="17" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>18</v>
@@ -15622,18 +15647,18 @@
         <v>1014</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="17" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>18</v>
@@ -15642,18 +15667,18 @@
         <v>1014</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="17" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>18</v>
@@ -15662,18 +15687,18 @@
         <v>1014</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="17" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>18</v>
@@ -15682,18 +15707,18 @@
         <v>1014</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="17" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>18</v>
@@ -15702,7 +15727,7 @@
         <v>1014</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15715,7 +15740,7 @@
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="17" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>1012</v>
@@ -15735,7 +15760,7 @@
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="17" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>1012</v>
@@ -15755,13 +15780,13 @@
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="17" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>18</v>
@@ -15770,18 +15795,18 @@
         <v>1024</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="17" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>18</v>
@@ -15790,47 +15815,47 @@
         <v>1024</v>
       </c>
       <c r="H68" s="21" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="17" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H70" s="21" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="17" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="H71" s="21" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15843,182 +15868,182 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C73" s="10" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C74" s="10" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C75" s="10" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C76" s="10" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C77" s="10" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C78" s="10" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C79" s="10" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C80" s="10" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="H80" s="23" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C81" s="10" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="D81" s="17" t="s">
         <v>48</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="H81" s="23" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16029,16 +16054,16 @@
         <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="H82" s="23" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="1258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="1261">
   <si>
     <t>_id</t>
   </si>
@@ -3581,6 +3581,15 @@
   </si>
   <si>
     <t>暗金魂心</t>
+  </si>
+  <si>
+    <t>220043</t>
+  </si>
+  <si>
+    <t>六大极戒</t>
+  </si>
+  <si>
+    <t>190007,190008,190009,190010,190011,190012</t>
   </si>
   <si>
     <t>220101</t>
@@ -4891,8 +4900,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
@@ -5234,7 +5243,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" customHeight="1" spans="3:4">
+    <row r="2" customHeight="1" spans="3:8">
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
@@ -6158,7 +6167,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C49" s="1" t="s">
         <v>159</v>
       </c>
@@ -6178,7 +6187,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C50" s="1" t="s">
         <v>162</v>
       </c>
@@ -6198,7 +6207,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C51" s="1" t="s">
         <v>165</v>
       </c>
@@ -6218,7 +6227,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C52" s="1" t="s">
         <v>169</v>
       </c>
@@ -6238,7 +6247,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C53" s="1" t="s">
         <v>172</v>
       </c>
@@ -6258,7 +6267,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C54" s="1" t="s">
         <v>175</v>
       </c>
@@ -6278,7 +6287,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C55" s="1" t="s">
         <v>178</v>
       </c>
@@ -6298,7 +6307,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C56" s="1" t="s">
         <v>181</v>
       </c>
@@ -6318,7 +6327,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C57" s="1" t="s">
         <v>185</v>
       </c>
@@ -6338,7 +6347,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C58" s="1" t="s">
         <v>188</v>
       </c>
@@ -6358,7 +6367,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C59" s="1" t="s">
         <v>191</v>
       </c>
@@ -6378,7 +6387,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C60" s="1" t="s">
         <v>194</v>
       </c>
@@ -6440,7 +6449,7 @@
       </c>
       <c r="I62" s="7"/>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C63" s="1" t="s">
         <v>204</v>
       </c>
@@ -6460,7 +6469,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C64" s="1" t="s">
         <v>207</v>
       </c>
@@ -6480,7 +6489,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C65" s="1" t="s">
         <v>210</v>
       </c>
@@ -6500,7 +6509,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C66" s="1" t="s">
         <v>213</v>
       </c>
@@ -6520,7 +6529,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C67" s="1" t="s">
         <v>217</v>
       </c>
@@ -6540,7 +6549,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C68" s="1" t="s">
         <v>220</v>
       </c>
@@ -6560,7 +6569,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C69" s="1" t="s">
         <v>223</v>
       </c>
@@ -6580,7 +6589,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C70" s="1" t="s">
         <v>226</v>
       </c>
@@ -6690,7 +6699,7 @@
       <c r="H74" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="I74" s="16"/>
+      <c r="I74" s="15"/>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A75" s="10"/>
@@ -6713,9 +6722,9 @@
       <c r="H75" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="I75" s="16"/>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="I75" s="15"/>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C76" s="18" t="s">
         <v>245</v>
       </c>
@@ -6735,7 +6744,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C77" s="18" t="s">
         <v>249</v>
       </c>
@@ -6755,7 +6764,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C78" s="18" t="s">
         <v>252</v>
       </c>
@@ -6775,7 +6784,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C79" s="18" t="s">
         <v>255</v>
       </c>
@@ -6795,7 +6804,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C80" s="18" t="s">
         <v>258</v>
       </c>
@@ -6857,7 +6866,7 @@
       </c>
       <c r="I82" s="7"/>
     </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C83" s="1" t="s">
         <v>268</v>
       </c>
@@ -6877,7 +6886,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C84" s="1" t="s">
         <v>271</v>
       </c>
@@ -6897,7 +6906,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C85" s="1" t="s">
         <v>274</v>
       </c>
@@ -6959,7 +6968,7 @@
       </c>
       <c r="I87" s="7"/>
     </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C88" s="1">
         <v>200852</v>
       </c>
@@ -6979,7 +6988,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C89" s="1">
         <v>200853</v>
       </c>
@@ -6999,7 +7008,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C90" s="1">
         <v>200854</v>
       </c>
@@ -7061,7 +7070,7 @@
       </c>
       <c r="I92" s="7"/>
     </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C93" s="1">
         <v>200902</v>
       </c>
@@ -7081,7 +7090,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C94" s="1">
         <v>200903</v>
       </c>
@@ -7101,7 +7110,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C95" s="1">
         <v>200904</v>
       </c>
@@ -7163,7 +7172,7 @@
       </c>
       <c r="I97" s="7"/>
     </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C98" s="1" t="s">
         <v>296</v>
       </c>
@@ -7183,7 +7192,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C99" s="1" t="s">
         <v>299</v>
       </c>
@@ -7203,7 +7212,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C100" s="1" t="s">
         <v>302</v>
       </c>
@@ -7265,7 +7274,7 @@
       </c>
       <c r="I102" s="7"/>
     </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C103" s="1" t="s">
         <v>312</v>
       </c>
@@ -7285,7 +7294,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C104" s="1" t="s">
         <v>315</v>
       </c>
@@ -7305,7 +7314,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C105" s="1" t="s">
         <v>318</v>
       </c>
@@ -7367,7 +7376,7 @@
       </c>
       <c r="I107" s="7"/>
     </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C108" s="1" t="s">
         <v>328</v>
       </c>
@@ -7387,7 +7396,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C109" s="1" t="s">
         <v>331</v>
       </c>
@@ -7407,7 +7416,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="C110" s="1" t="s">
         <v>334</v>
       </c>
@@ -7427,7 +7436,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="3:8">
+    <row r="111" customHeight="1" spans="3:9">
       <c r="C111" s="1">
         <v>202001</v>
       </c>
@@ -7447,7 +7456,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="112" customHeight="1" spans="3:8">
+    <row r="112" customHeight="1" spans="3:9">
       <c r="C112" s="1">
         <v>202002</v>
       </c>
@@ -7595,7 +7604,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="8:8">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="H1" s="3"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -9543,7 +9552,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="3:3">
+    <row r="100" customHeight="1" spans="3:8">
       <c r="C100" s="10"/>
     </row>
   </sheetData>
@@ -9573,15 +9582,15 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="8:8">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="H1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -9601,7 +9610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
@@ -9621,7 +9630,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
@@ -9641,7 +9650,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C6" s="18" t="s">
         <v>633</v>
       </c>
@@ -9661,7 +9670,7 @@
         <v>40000051</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C7" s="18" t="s">
         <v>635</v>
       </c>
@@ -9681,7 +9690,7 @@
         <v>40000052</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C8" s="18" t="s">
         <v>637</v>
       </c>
@@ -9701,7 +9710,7 @@
         <v>40000053</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C9" s="18" t="s">
         <v>639</v>
       </c>
@@ -9721,7 +9730,7 @@
         <v>40000054</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C10" s="18" t="s">
         <v>641</v>
       </c>
@@ -9764,7 +9773,7 @@
       </c>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" customHeight="1" spans="3:8">
+    <row r="12" customHeight="1" spans="1:9">
       <c r="C12" s="18" t="s">
         <v>645</v>
       </c>
@@ -9784,7 +9793,7 @@
         <v>40000057</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:8">
+    <row r="13" customHeight="1" spans="1:9">
       <c r="C13" s="18" t="s">
         <v>647</v>
       </c>
@@ -9804,7 +9813,7 @@
         <v>40000058</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:8">
+    <row r="14" customHeight="1" spans="1:9">
       <c r="C14" s="18" t="s">
         <v>649</v>
       </c>
@@ -9824,7 +9833,7 @@
         <v>40000059</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:8">
+    <row r="15" customHeight="1" spans="1:9">
       <c r="C15" s="18" t="s">
         <v>651</v>
       </c>
@@ -9844,7 +9853,7 @@
         <v>40000060</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:8">
+    <row r="16" customHeight="1" spans="1:9">
       <c r="C16" s="18" t="s">
         <v>653</v>
       </c>
@@ -12824,7 +12833,7 @@
         <v>40000209</v>
       </c>
     </row>
-    <row r="165" customHeight="1" spans="3:3">
+    <row r="165" customHeight="1" spans="3:8">
       <c r="C165" s="10"/>
     </row>
   </sheetData>
@@ -12854,15 +12863,15 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="8:8">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="H1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -12882,7 +12891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
@@ -12902,7 +12911,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
@@ -12922,7 +12931,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C6" s="11">
         <v>180001</v>
       </c>
@@ -12942,7 +12951,7 @@
         <v>180001</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C7" s="11">
         <v>180002</v>
       </c>
@@ -12962,7 +12971,7 @@
         <v>180002</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C8" s="11">
         <v>180003</v>
       </c>
@@ -12982,7 +12991,7 @@
         <v>180003</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C9" s="11">
         <v>180004</v>
       </c>
@@ -13002,7 +13011,7 @@
         <v>180004</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C10" s="11">
         <v>180005</v>
       </c>
@@ -13045,7 +13054,7 @@
       </c>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C12" s="11">
         <v>180007</v>
       </c>
@@ -13065,7 +13074,7 @@
         <v>180007</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C13" s="11">
         <v>180008</v>
       </c>
@@ -13085,7 +13094,7 @@
         <v>180008</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C14" s="11">
         <v>180009</v>
       </c>
@@ -13105,7 +13114,7 @@
         <v>180009</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C15" s="11">
         <v>180010</v>
       </c>
@@ -13125,7 +13134,7 @@
         <v>180010</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C16" s="11">
         <v>180011</v>
       </c>
@@ -13365,7 +13374,7 @@
         <v>180022</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:3">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="10"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -13583,7 +13592,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H49"/>
+  <dimension ref="C1:H50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -13595,7 +13604,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="8:8">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="H1" s="3"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -14383,35 +14392,35 @@
         <v>4041</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="3:8">
-      <c r="C43" s="18" t="s">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C42" s="18" t="s">
         <v>1056</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E43" s="12" t="s">
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F42" s="1">
         <v>1</v>
       </c>
-      <c r="G43" s="1">
-        <v>16</v>
-      </c>
-      <c r="H43" s="1">
-        <v>8201</v>
+      <c r="G42" s="1">
+        <v>19</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>1058</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F44" s="1">
         <v>1</v>
@@ -14420,18 +14429,18 @@
         <v>16</v>
       </c>
       <c r="H44" s="1">
-        <v>8202</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
@@ -14440,18 +14449,18 @@
         <v>16</v>
       </c>
       <c r="H45" s="1">
-        <v>8203</v>
+        <v>8202</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -14460,18 +14469,18 @@
         <v>16</v>
       </c>
       <c r="H46" s="1">
-        <v>8204</v>
+        <v>8203</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -14480,18 +14489,18 @@
         <v>16</v>
       </c>
       <c r="H47" s="1">
-        <v>8205</v>
+        <v>8204</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F48" s="1">
         <v>1</v>
@@ -14500,18 +14509,18 @@
         <v>16</v>
       </c>
       <c r="H48" s="1">
-        <v>8206</v>
+        <v>8205</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
@@ -14520,6 +14529,26 @@
         <v>16</v>
       </c>
       <c r="H49" s="1">
+        <v>8206</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:8">
+      <c r="C50" s="18" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F50" s="1">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1">
+        <v>16</v>
+      </c>
+      <c r="H50" s="1">
         <v>8207</v>
       </c>
     </row>
@@ -14550,7 +14579,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="8:8">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="H1" s="3"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -14620,13 +14649,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="1" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
@@ -14635,18 +14664,18 @@
         <v>19</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -14655,18 +14684,18 @@
         <v>19</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>18</v>
@@ -14675,18 +14704,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>18</v>
@@ -14695,18 +14724,18 @@
         <v>19</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -14715,7 +14744,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -14726,7 +14755,7 @@
         <v>1012</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -14735,18 +14764,18 @@
         <v>19</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
@@ -14755,18 +14784,18 @@
         <v>16</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -14775,18 +14804,18 @@
         <v>16</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="17" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -14795,18 +14824,18 @@
         <v>16</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="17" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>18</v>
@@ -14815,18 +14844,18 @@
         <v>16</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
@@ -14835,18 +14864,18 @@
         <v>16</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>18</v>
@@ -14855,18 +14884,18 @@
         <v>16</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>18</v>
@@ -14875,7 +14904,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14894,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -14903,7 +14932,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14922,121 +14951,121 @@
         <v>1012</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="17" t="s">
         <v>1111</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>1108</v>
-      </c>
       <c r="H23" s="23" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="17" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="17" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="17" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="17" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="17" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>1012</v>
@@ -15056,62 +15085,62 @@
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="17" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="17" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15122,16 +15151,16 @@
         <v>1012</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15142,156 +15171,156 @@
         <v>1012</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="17" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="17" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15312,7 +15341,7 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>1012</v>
@@ -15332,7 +15361,7 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1012</v>
@@ -15352,13 +15381,13 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>18</v>
@@ -15367,12 +15396,12 @@
         <v>1014</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1012</v>
@@ -15392,13 +15421,13 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>18</v>
@@ -15407,18 +15436,18 @@
         <v>1014</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>18</v>
@@ -15427,18 +15456,18 @@
         <v>1014</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>18</v>
@@ -15447,18 +15476,18 @@
         <v>1014</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>18</v>
@@ -15467,7 +15496,7 @@
         <v>1014</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15478,7 +15507,7 @@
         <v>1012</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>18</v>
@@ -15487,7 +15516,7 @@
         <v>1014</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15498,7 +15527,7 @@
         <v>1012</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>18</v>
@@ -15507,18 +15536,18 @@
         <v>1014</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>18</v>
@@ -15527,18 +15556,18 @@
         <v>1014</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="17" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>18</v>
@@ -15547,18 +15576,18 @@
         <v>1014</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>18</v>
@@ -15567,18 +15596,18 @@
         <v>1014</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>18</v>
@@ -15587,18 +15616,18 @@
         <v>1014</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="17" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>18</v>
@@ -15607,18 +15636,18 @@
         <v>1014</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="17" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>18</v>
@@ -15627,18 +15656,18 @@
         <v>1014</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="17" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>18</v>
@@ -15647,18 +15676,18 @@
         <v>1014</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="17" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>18</v>
@@ -15667,18 +15696,18 @@
         <v>1014</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="17" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>18</v>
@@ -15687,18 +15716,18 @@
         <v>1014</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="17" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>18</v>
@@ -15707,18 +15736,18 @@
         <v>1014</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="17" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>18</v>
@@ -15727,7 +15756,7 @@
         <v>1014</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15740,7 +15769,7 @@
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="17" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>1012</v>
@@ -15760,7 +15789,7 @@
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="17" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>1012</v>
@@ -15780,13 +15809,13 @@
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="17" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>18</v>
@@ -15795,18 +15824,18 @@
         <v>1024</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="17" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>18</v>
@@ -15815,47 +15844,47 @@
         <v>1024</v>
       </c>
       <c r="H68" s="21" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="17" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H70" s="21" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="17" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="H71" s="21" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15868,182 +15897,182 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C73" s="10" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C74" s="10" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>1230</v>
-      </c>
       <c r="H74" s="17" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C75" s="10" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C76" s="10" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C77" s="10" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C78" s="10" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C79" s="10" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C80" s="10" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="H80" s="23" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C81" s="10" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="D81" s="17" t="s">
         <v>48</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="H81" s="23" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16054,16 +16083,16 @@
         <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="H82" s="23" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="1261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="1264">
   <si>
     <t>_id</t>
   </si>
@@ -3353,6 +3353,15 @@
   </si>
   <si>
     <t>极·金蛟剪</t>
+  </si>
+  <si>
+    <t>极·炼体证明</t>
+  </si>
+  <si>
+    <t>极·炼气证明</t>
+  </si>
+  <si>
+    <t>极·炼神证明</t>
   </si>
   <si>
     <t>220000</t>
@@ -12851,7 +12860,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -13575,6 +13584,66 @@
       </c>
       <c r="H38" s="11">
         <v>180039</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:8">
+      <c r="C39" s="11">
+        <v>180040</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="1">
+        <v>18</v>
+      </c>
+      <c r="H39" s="11">
+        <v>180040</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:8">
+      <c r="C40" s="11">
+        <v>180041</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="1">
+        <v>18</v>
+      </c>
+      <c r="H40" s="11">
+        <v>180041</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:8">
+      <c r="C41" s="11">
+        <v>180042</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="1">
+        <v>18</v>
+      </c>
+      <c r="H41" s="11">
+        <v>180042</v>
       </c>
     </row>
   </sheetData>
@@ -13674,13 +13743,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="18" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
@@ -13694,13 +13763,13 @@
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -13714,13 +13783,13 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="F8" s="1">
         <v>50</v>
@@ -13734,13 +13803,13 @@
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="F9" s="1">
         <v>20</v>
@@ -13754,13 +13823,13 @@
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -13774,13 +13843,13 @@
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -13794,13 +13863,13 @@
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
@@ -13814,13 +13883,13 @@
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -13829,18 +13898,18 @@
         <v>3</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -13849,18 +13918,18 @@
         <v>3</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -13869,18 +13938,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -13894,13 +13963,13 @@
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="F17" s="1">
         <v>40</v>
@@ -13914,13 +13983,13 @@
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="F18" s="1">
         <v>200</v>
@@ -13934,13 +14003,13 @@
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="F19" s="1">
         <v>80</v>
@@ -13954,13 +14023,13 @@
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>18</v>
@@ -13974,13 +14043,13 @@
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="F21" s="1">
         <v>500</v>
@@ -13994,13 +14063,13 @@
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="F22" s="1">
         <v>200</v>
@@ -14014,113 +14083,113 @@
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>18</v>
@@ -14129,18 +14198,18 @@
         <v>3</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>18</v>
@@ -14149,18 +14218,18 @@
         <v>3</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>18</v>
@@ -14169,18 +14238,18 @@
         <v>3</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="F31" s="1">
         <v>2</v>
@@ -14194,13 +14263,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="F32" s="1">
         <v>2</v>
@@ -14214,13 +14283,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="F33" s="1">
         <v>200</v>
@@ -14234,13 +14303,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="F34" s="1">
         <v>100</v>
@@ -14254,53 +14323,53 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="F35" s="1">
         <v>10</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>1046</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>1043</v>
       </c>
       <c r="F36" s="1">
         <v>15</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>18</v>
@@ -14314,13 +14383,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="F38" s="1">
         <v>1000</v>
@@ -14334,13 +14403,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="F39" s="1">
         <v>300</v>
@@ -14354,13 +14423,13 @@
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="F40" s="1">
         <v>1</v>
@@ -14369,18 +14438,18 @@
         <v>5</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="F41" s="1">
         <v>1</v>
@@ -14394,13 +14463,13 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="F42" s="1">
         <v>1</v>
@@ -14409,18 +14478,18 @@
         <v>19</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="F44" s="1">
         <v>1</v>
@@ -14434,13 +14503,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
@@ -14454,13 +14523,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -14474,13 +14543,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -14494,13 +14563,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="F48" s="1">
         <v>1</v>
@@ -14514,13 +14583,13 @@
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
@@ -14534,13 +14603,13 @@
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="F50" s="1">
         <v>1</v>
@@ -14649,13 +14718,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="1" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
@@ -14664,18 +14733,18 @@
         <v>19</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -14684,18 +14753,18 @@
         <v>19</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>18</v>
@@ -14704,18 +14773,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>18</v>
@@ -14724,18 +14793,18 @@
         <v>19</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -14744,7 +14813,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -14752,10 +14821,10 @@
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -14764,18 +14833,18 @@
         <v>19</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
@@ -14784,18 +14853,18 @@
         <v>16</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -14804,18 +14873,18 @@
         <v>16</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="17" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -14824,18 +14893,18 @@
         <v>16</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="17" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>18</v>
@@ -14844,18 +14913,18 @@
         <v>16</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
@@ -14864,18 +14933,18 @@
         <v>16</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>18</v>
@@ -14884,18 +14953,18 @@
         <v>16</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>18</v>
@@ -14904,7 +14973,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14923,7 +14992,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -14932,7 +15001,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -14948,199 +15017,199 @@
         <v>306</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="17" t="s">
         <v>1114</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>1111</v>
-      </c>
       <c r="H23" s="23" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="17" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="17" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="17" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="17" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="17" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="17" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="17" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15148,179 +15217,179 @@
         <v>310</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="17" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="17" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15341,422 +15410,422 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="17" t="s">
         <v>1017</v>
       </c>
-      <c r="F43" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G43" s="17" t="s">
-        <v>1014</v>
-      </c>
       <c r="H43" s="23" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="17" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="17" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="17" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="17" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="17" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G58" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="17" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="17" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="17" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="17" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="17" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15769,122 +15838,122 @@
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="17" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="F65" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="H65" s="23" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="17" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" s="17" t="s">
         <v>1027</v>
       </c>
-      <c r="F66" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G66" s="17" t="s">
-        <v>1024</v>
-      </c>
       <c r="H66" s="23" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="17" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="17" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="H68" s="21" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="17" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H70" s="21" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="17" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="H71" s="21" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15897,182 +15966,182 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C73" s="10" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C74" s="10" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>1233</v>
-      </c>
       <c r="H74" s="17" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C75" s="10" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C76" s="10" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C77" s="10" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C78" s="10" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C79" s="10" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C80" s="10" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="H80" s="23" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C81" s="10" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="D81" s="17" t="s">
         <v>48</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="H81" s="23" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16083,16 +16152,16 @@
         <v>100</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="H82" s="23" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="1264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="1280">
   <si>
     <t>_id</t>
   </si>
@@ -4073,6 +4073,54 @@
   </si>
   <si>
     <t>1998001,1998002,1998003,1998004,1998005</t>
+  </si>
+  <si>
+    <t>绿色英灵</t>
+  </si>
+  <si>
+    <t>2100023,2100024,2100025,2100026</t>
+  </si>
+  <si>
+    <t>蓝色英灵</t>
+  </si>
+  <si>
+    <t>2100019,2100020,2100021,2100022</t>
+  </si>
+  <si>
+    <t>紫色英灵</t>
+  </si>
+  <si>
+    <t>2100015,2100016,2100017,2100018</t>
+  </si>
+  <si>
+    <t>橙色英灵</t>
+  </si>
+  <si>
+    <t>2100012,2100013,2100014</t>
+  </si>
+  <si>
+    <t>红色英灵</t>
+  </si>
+  <si>
+    <t>2100009,2100010,2100011</t>
+  </si>
+  <si>
+    <t>金色英灵</t>
+  </si>
+  <si>
+    <t>2100006,2100007,2100008</t>
+  </si>
+  <si>
+    <t>暗金英灵</t>
+  </si>
+  <si>
+    <t>2100003,2100004,2100005</t>
+  </si>
+  <si>
+    <t>粉色英灵</t>
+  </si>
+  <si>
+    <t>2100001,2100002</t>
   </si>
   <si>
     <t>3001</t>
@@ -14636,7 +14684,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H82"/>
+  <dimension ref="C1:H92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -15836,72 +15884,72 @@
       <c r="G64" s="1"/>
       <c r="H64" s="3"/>
     </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C65" s="17" t="s">
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C65" s="1">
+        <v>2031</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>1220</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>1026</v>
-      </c>
       <c r="F65" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>1027</v>
+        <v>26</v>
       </c>
       <c r="H65" s="23" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C66" s="17" t="s">
         <v>1221</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>1015</v>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C66" s="1">
+        <v>2032</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1030</v>
+        <v>1222</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>1027</v>
+        <v>26</v>
       </c>
       <c r="H66" s="23" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:8">
-      <c r="C67" s="17" t="s">
-        <v>1222</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>1015</v>
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C67" s="1">
+        <v>2033</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H67" s="21" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:8">
-      <c r="C68" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H67" s="23" t="s">
         <v>1225</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>1015</v>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C68" s="1">
+        <v>2034</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>1226</v>
@@ -15910,38 +15958,58 @@
         <v>18</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H68" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H68" s="23" t="s">
         <v>1227</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="3:8">
-      <c r="C70" s="17" t="s">
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C69" s="1">
+        <v>2035</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>1015</v>
+      <c r="F69" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H69" s="23" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C70" s="1">
+        <v>2036</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H70" s="21" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:8">
-      <c r="C71" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H70" s="23" t="s">
         <v>1231</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>1015</v>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C71" s="1">
+        <v>2037</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>1232</v>
@@ -15950,218 +16018,374 @@
         <v>18</v>
       </c>
       <c r="G71" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H71" s="23" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C72" s="1">
+        <v>2038</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H72" s="23" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="3"/>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="3"/>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C75" s="17" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H75" s="23" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C76" s="17" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F76" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H76" s="23" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:8">
+      <c r="C77" s="17" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F77" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H77" s="21" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:8">
+      <c r="C78" s="17" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F78" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H78" s="21" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:8">
+      <c r="C80" s="17" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F80" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" s="17" t="s">
         <v>1114</v>
       </c>
-      <c r="H71" s="21" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="3"/>
-    </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C73" s="10" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D73" s="1" t="s">
+      <c r="H80" s="21" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:8">
+      <c r="C81" s="17" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F81" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="17" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="3"/>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C83" s="10" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>1235</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H73" s="17" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C74" s="10" t="s">
-        <v>1238</v>
-      </c>
-      <c r="D74" s="1" t="s">
+      <c r="E83" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H83" s="17" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C84" s="10" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>1239</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H74" s="17" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C75" s="10" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D75" s="1" t="s">
+      <c r="E84" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H84" s="17" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C85" s="10" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>1242</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H75" s="17" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C76" s="10" t="s">
-        <v>1244</v>
-      </c>
-      <c r="D76" s="1" t="s">
+      <c r="E85" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H85" s="17" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C86" s="10" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>1245</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H76" s="17" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C77" s="10" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D77" s="1" t="s">
+      <c r="E86" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H86" s="17" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C87" s="10" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>1248</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H77" s="17" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C78" s="10" t="s">
-        <v>1250</v>
-      </c>
-      <c r="D78" s="1" t="s">
+      <c r="E87" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H87" s="17" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C88" s="10" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>1251</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H78" s="17" t="s">
+      <c r="E88" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" s="1" t="s">
         <v>1252</v>
       </c>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C79" s="10" t="s">
-        <v>1253</v>
-      </c>
-      <c r="D79" s="1" t="s">
+      <c r="H88" s="17" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C89" s="10" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H79" s="17" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C80" s="10" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D80" s="1" t="s">
+      <c r="E89" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H89" s="17" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C90" s="10" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>1257</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H80" s="23" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C81" s="10" t="s">
-        <v>1259</v>
-      </c>
-      <c r="D81" s="17" t="s">
+      <c r="E90" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H90" s="23" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C91" s="10" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D91" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H81" s="23" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C82" s="10">
+      <c r="E91" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H91" s="23" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C92" s="10">
         <v>300091</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D92" s="1">
         <v>100</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>1262</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="H82" s="23" t="s">
-        <v>1263</v>
+      <c r="E92" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H92" s="23" t="s">
+        <v>1279</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4078,49 +4078,49 @@
     <t>绿色英灵</t>
   </si>
   <si>
-    <t>2100023,2100024,2100025,2100026</t>
+    <t>2100022,2100023,2100024,2100025,2100026,2100027</t>
   </si>
   <si>
     <t>蓝色英灵</t>
   </si>
   <si>
-    <t>2100019,2100020,2100021,2100022</t>
+    <t>2100019,2100020,2100021</t>
   </si>
   <si>
     <t>紫色英灵</t>
   </si>
   <si>
-    <t>2100015,2100016,2100017,2100018</t>
+    <t>2100016,2100017,2100018</t>
   </si>
   <si>
     <t>橙色英灵</t>
   </si>
   <si>
-    <t>2100012,2100013,2100014</t>
+    <t>2100013,2100014,2100015</t>
   </si>
   <si>
     <t>红色英灵</t>
   </si>
   <si>
-    <t>2100009,2100010,2100011</t>
+    <t>2100010,2100011,2100012</t>
   </si>
   <si>
     <t>金色英灵</t>
   </si>
   <si>
-    <t>2100006,2100007,2100008</t>
+    <t>2100007,2100008,2100009</t>
   </si>
   <si>
     <t>暗金英灵</t>
   </si>
   <si>
-    <t>2100003,2100004,2100005</t>
+    <t>2100004,2100005,2100006</t>
   </si>
   <si>
     <t>粉色英灵</t>
   </si>
   <si>
-    <t>2100001,2100002</t>
+    <t>2100001,2100002,2100003</t>
   </si>
   <si>
     <t>3001</t>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="1280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2273" uniqueCount="1286">
   <si>
     <t>_id</t>
   </si>
@@ -4145,6 +4145,24 @@
   </si>
   <si>
     <t>3000057,3000058,3000059,3000060,3000061,3000062,3000063,3000064</t>
+  </si>
+  <si>
+    <t>3005</t>
+  </si>
+  <si>
+    <t>第五时装</t>
+  </si>
+  <si>
+    <t>3000065,3000066,3000067,3000068,3000069,3000070,3000071,3000072</t>
+  </si>
+  <si>
+    <t>3006</t>
+  </si>
+  <si>
+    <t>第六时装</t>
+  </si>
+  <si>
+    <t>3000073,3000074,3000075,3000076,3000077,3000078,3000079,3000080</t>
   </si>
   <si>
     <t>4001</t>
@@ -14684,7 +14702,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H92"/>
+  <dimension ref="C1:H94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -16140,109 +16158,109 @@
         <v>1243</v>
       </c>
     </row>
+    <row r="79" customHeight="1" spans="3:8">
+      <c r="C79" s="17" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F79" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H79" s="21" t="s">
+        <v>1246</v>
+      </c>
+    </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="C80" s="17" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G80" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H80" s="21" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:8">
+      <c r="C82" s="17" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F82" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" s="17" t="s">
         <v>1114</v>
       </c>
-      <c r="H80" s="21" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="3:8">
-      <c r="C81" s="17" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D81" s="1" t="s">
+      <c r="H82" s="21" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:8">
+      <c r="C83" s="17" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>1248</v>
-      </c>
-      <c r="F81" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G81" s="17" t="s">
+      <c r="E83" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F83" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" s="17" t="s">
         <v>1114</v>
       </c>
-      <c r="H81" s="21" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="3"/>
-    </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C83" s="10" t="s">
-        <v>1250</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>1251</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H83" s="17" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C84" s="10" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="H83" s="21" t="s">
         <v>1255</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H84" s="17" t="s">
-        <v>1256</v>
-      </c>
+    </row>
+    <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="3"/>
     </row>
     <row r="85" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C85" s="10" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E85" s="1" t="s">
+      <c r="F85" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" s="1" t="s">
         <v>1258</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>1252</v>
       </c>
       <c r="H85" s="17" t="s">
         <v>1259</v>
@@ -16253,7 +16271,7 @@
         <v>1260</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>1261</v>
@@ -16262,7 +16280,7 @@
         <v>18</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="H86" s="17" t="s">
         <v>1262</v>
@@ -16273,7 +16291,7 @@
         <v>1263</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>1264</v>
@@ -16282,7 +16300,7 @@
         <v>18</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="H87" s="17" t="s">
         <v>1265</v>
@@ -16293,7 +16311,7 @@
         <v>1266</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>1267</v>
@@ -16302,7 +16320,7 @@
         <v>18</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="H88" s="17" t="s">
         <v>1268</v>
@@ -16313,7 +16331,7 @@
         <v>1269</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>1270</v>
@@ -16322,7 +16340,7 @@
         <v>18</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="H89" s="17" t="s">
         <v>1271</v>
@@ -16333,7 +16351,7 @@
         <v>1272</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>1273</v>
@@ -16342,9 +16360,9 @@
         <v>18</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H90" s="23" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H90" s="17" t="s">
         <v>1274</v>
       </c>
     </row>
@@ -16352,8 +16370,8 @@
       <c r="C91" s="10" t="s">
         <v>1275</v>
       </c>
-      <c r="D91" s="17" t="s">
-        <v>48</v>
+      <c r="D91" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>1276</v>
@@ -16362,30 +16380,70 @@
         <v>18</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H91" s="23" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H91" s="17" t="s">
         <v>1277</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C92" s="10">
+      <c r="C92" s="10" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H92" s="23" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C93" s="10" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D93" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H93" s="23" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C94" s="10">
         <v>300091</v>
       </c>
-      <c r="D92" s="1">
+      <c r="D94" s="1">
         <v>100</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="H92" s="23" t="s">
-        <v>1279</v>
+      <c r="E94" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H94" s="23" t="s">
+        <v>1285</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2273" uniqueCount="1286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="1288">
   <si>
     <t>_id</t>
   </si>
@@ -3641,6 +3641,12 @@
   </si>
   <si>
     <t>金色宠物</t>
+  </si>
+  <si>
+    <t>220109</t>
+  </si>
+  <si>
+    <t>粉色宠物</t>
   </si>
   <si>
     <t>101</t>
@@ -13727,7 +13733,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H50"/>
+  <dimension ref="C1:H51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -14685,6 +14691,26 @@
       </c>
       <c r="H50" s="1">
         <v>8207</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:8">
+      <c r="C51" s="18" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F51" s="1">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1">
+        <v>16</v>
+      </c>
+      <c r="H51" s="1">
+        <v>8209</v>
       </c>
     </row>
   </sheetData>
@@ -14784,13 +14810,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="1" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
@@ -14799,18 +14825,18 @@
         <v>19</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -14819,18 +14845,18 @@
         <v>19</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>18</v>
@@ -14839,18 +14865,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>18</v>
@@ -14859,18 +14885,18 @@
         <v>19</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -14879,7 +14905,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -14890,7 +14916,7 @@
         <v>1015</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -14899,18 +14925,18 @@
         <v>19</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
@@ -14919,18 +14945,18 @@
         <v>16</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -14939,18 +14965,18 @@
         <v>16</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="17" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -14959,18 +14985,18 @@
         <v>16</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="17" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>18</v>
@@ -14979,18 +15005,18 @@
         <v>16</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
@@ -14999,18 +15025,18 @@
         <v>16</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>18</v>
@@ -15019,18 +15045,18 @@
         <v>16</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>18</v>
@@ -15039,7 +15065,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15058,7 +15084,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -15067,7 +15093,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15086,121 +15112,121 @@
         <v>1015</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="17" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="17" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="17" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="17" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="17" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>1015</v>
@@ -15220,62 +15246,62 @@
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="17" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="17" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15286,16 +15312,16 @@
         <v>1015</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15306,156 +15332,156 @@
         <v>1015</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="17" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="17" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15476,7 +15502,7 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>1015</v>
@@ -15496,7 +15522,7 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1015</v>
@@ -15516,13 +15542,13 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>18</v>
@@ -15531,12 +15557,12 @@
         <v>1017</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1015</v>
@@ -15556,13 +15582,13 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>18</v>
@@ -15571,18 +15597,18 @@
         <v>1017</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>18</v>
@@ -15591,18 +15617,18 @@
         <v>1017</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>18</v>
@@ -15611,18 +15637,18 @@
         <v>1017</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>18</v>
@@ -15631,7 +15657,7 @@
         <v>1017</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15642,7 +15668,7 @@
         <v>1015</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>18</v>
@@ -15651,7 +15677,7 @@
         <v>1017</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15662,7 +15688,7 @@
         <v>1015</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>18</v>
@@ -15671,18 +15697,18 @@
         <v>1017</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>18</v>
@@ -15691,18 +15717,18 @@
         <v>1017</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="17" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>18</v>
@@ -15711,18 +15737,18 @@
         <v>1017</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>18</v>
@@ -15731,18 +15757,18 @@
         <v>1017</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>18</v>
@@ -15751,18 +15777,18 @@
         <v>1017</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="17" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>18</v>
@@ -15771,18 +15797,18 @@
         <v>1017</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="17" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>18</v>
@@ -15791,18 +15817,18 @@
         <v>1017</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="17" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>18</v>
@@ -15811,18 +15837,18 @@
         <v>1017</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="17" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>18</v>
@@ -15831,18 +15857,18 @@
         <v>1017</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="17" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>18</v>
@@ -15851,18 +15877,18 @@
         <v>1017</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="17" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>18</v>
@@ -15871,18 +15897,18 @@
         <v>1017</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="17" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>18</v>
@@ -15891,7 +15917,7 @@
         <v>1017</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15910,7 +15936,7 @@
         <v>0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="F65" s="17" t="s">
         <v>18</v>
@@ -15919,7 +15945,7 @@
         <v>26</v>
       </c>
       <c r="H65" s="23" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15930,7 +15956,7 @@
         <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>18</v>
@@ -15939,7 +15965,7 @@
         <v>26</v>
       </c>
       <c r="H66" s="23" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15950,7 +15976,7 @@
         <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>18</v>
@@ -15959,7 +15985,7 @@
         <v>26</v>
       </c>
       <c r="H67" s="23" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15970,7 +15996,7 @@
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>18</v>
@@ -15979,7 +16005,7 @@
         <v>26</v>
       </c>
       <c r="H68" s="23" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15990,7 +16016,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="F69" s="17" t="s">
         <v>18</v>
@@ -15999,7 +16025,7 @@
         <v>26</v>
       </c>
       <c r="H69" s="23" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16010,7 +16036,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>18</v>
@@ -16019,7 +16045,7 @@
         <v>26</v>
       </c>
       <c r="H70" s="23" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16030,7 +16056,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>18</v>
@@ -16039,7 +16065,7 @@
         <v>26</v>
       </c>
       <c r="H71" s="23" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16050,7 +16076,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="F72" s="17" t="s">
         <v>18</v>
@@ -16059,7 +16085,7 @@
         <v>26</v>
       </c>
       <c r="H72" s="23" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16080,7 +16106,7 @@
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C75" s="17" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>1015</v>
@@ -16100,7 +16126,7 @@
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C76" s="17" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>1015</v>
@@ -16120,13 +16146,13 @@
     </row>
     <row r="77" customHeight="1" spans="3:8">
       <c r="C77" s="17" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>18</v>
@@ -16135,18 +16161,18 @@
         <v>1027</v>
       </c>
       <c r="H77" s="21" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:8">
       <c r="C78" s="17" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="F78" s="17" t="s">
         <v>18</v>
@@ -16155,18 +16181,18 @@
         <v>1027</v>
       </c>
       <c r="H78" s="21" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:8">
       <c r="C79" s="17" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="F79" s="17" t="s">
         <v>18</v>
@@ -16175,18 +16201,18 @@
         <v>1027</v>
       </c>
       <c r="H79" s="21" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="C80" s="17" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>18</v>
@@ -16195,47 +16221,47 @@
         <v>1027</v>
       </c>
       <c r="H80" s="21" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:8">
       <c r="C82" s="17" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="F82" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H82" s="21" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:8">
       <c r="C83" s="17" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="F83" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="H83" s="21" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16248,182 +16274,182 @@
     </row>
     <row r="85" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C85" s="10" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H85" s="17" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C86" s="10" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C87" s="10" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C88" s="10" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H88" s="17" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C89" s="10" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C90" s="10" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C91" s="10" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C92" s="10" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H92" s="23" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C93" s="10" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D93" s="17" t="s">
         <v>48</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H93" s="23" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16434,16 +16460,16 @@
         <v>100</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H94" s="23" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="1288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="1296">
   <si>
     <t>_id</t>
   </si>
@@ -4127,6 +4127,30 @@
   </si>
   <si>
     <t>2100001,2100002,2100003</t>
+  </si>
+  <si>
+    <t>2100049,2100050,2100051,2100052,2100053,2100054</t>
+  </si>
+  <si>
+    <t>2100046,2100047,2100048</t>
+  </si>
+  <si>
+    <t>2100043,2100044,2100045</t>
+  </si>
+  <si>
+    <t>2100040,2100041,2100042</t>
+  </si>
+  <si>
+    <t>2100037,2100038,2100039</t>
+  </si>
+  <si>
+    <t>2100034,2100035,2100036</t>
+  </si>
+  <si>
+    <t>2100031,2100032,2100033</t>
+  </si>
+  <si>
+    <t>2100028,2100029,2100030</t>
   </si>
   <si>
     <t>3001</t>
@@ -14728,7 +14752,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H94"/>
+  <dimension ref="C1:H102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -16089,387 +16113,547 @@
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="3"/>
+      <c r="C73" s="1">
+        <v>2039</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H73" s="23" t="s">
+        <v>1238</v>
+      </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="3"/>
-    </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C75" s="17" t="s">
-        <v>1238</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>1015</v>
+      <c r="C74" s="1">
+        <v>2040</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H74" s="23" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C75" s="1">
+        <v>2041</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1026</v>
+        <v>1226</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>1027</v>
+        <v>26</v>
       </c>
       <c r="H75" s="23" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C76" s="17" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>1015</v>
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C76" s="1">
+        <v>2042</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1030</v>
+        <v>1228</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>1027</v>
+        <v>26</v>
       </c>
       <c r="H76" s="23" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:8">
-      <c r="C77" s="17" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>1015</v>
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C77" s="1">
+        <v>2043</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1241</v>
+        <v>1230</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H77" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="23" t="s">
         <v>1242</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="3:8">
-      <c r="C78" s="17" t="s">
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C78" s="1">
+        <v>2044</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F78" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H78" s="23" t="s">
         <v>1243</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E78" s="1" t="s">
+    </row>
+    <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C79" s="1">
+        <v>2045</v>
+      </c>
+      <c r="D79" s="1">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F79" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H79" s="23" t="s">
         <v>1244</v>
       </c>
-      <c r="F78" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G78" s="17" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H78" s="21" t="s">
+    </row>
+    <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C80" s="1">
+        <v>2046</v>
+      </c>
+      <c r="D80" s="1">
+        <v>0</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F80" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H80" s="23" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="3:8">
-      <c r="C79" s="17" t="s">
+    <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="3"/>
+    </row>
+    <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="3"/>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C83" s="17" t="s">
         <v>1246</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>1247</v>
-      </c>
-      <c r="F79" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G79" s="17" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H79" s="21" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:8">
-      <c r="C80" s="17" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>1250</v>
-      </c>
-      <c r="F80" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G80" s="17" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H80" s="21" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="3:8">
-      <c r="C82" s="17" t="s">
-        <v>1252</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>1253</v>
-      </c>
-      <c r="F82" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G82" s="17" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H82" s="21" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="3:8">
-      <c r="C83" s="17" t="s">
-        <v>1255</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>1015</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F83" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H83" s="23" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C84" s="17" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F84" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H84" s="23" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:8">
+      <c r="C85" s="17" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F85" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H85" s="21" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:8">
+      <c r="C86" s="17" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F86" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H86" s="21" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:8">
+      <c r="C87" s="17" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F87" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H87" s="21" t="s">
         <v>1256</v>
       </c>
-      <c r="F83" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G83" s="17" t="s">
+    </row>
+    <row r="88" customHeight="1" spans="3:8">
+      <c r="C88" s="17" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F88" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H88" s="21" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:8">
+      <c r="C90" s="17" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F90" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" s="17" t="s">
         <v>1116</v>
       </c>
-      <c r="H83" s="21" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="3"/>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C85" s="10" t="s">
-        <v>1258</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>1259</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H85" s="17" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C86" s="10" t="s">
+      <c r="H90" s="21" t="s">
         <v>1262</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E86" s="1" t="s">
+    </row>
+    <row r="91" customHeight="1" spans="3:8">
+      <c r="C91" s="17" t="s">
         <v>1263</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H86" s="17" t="s">
+      <c r="D91" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>1264</v>
       </c>
-    </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C87" s="10" t="s">
+      <c r="F91" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" s="17" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H91" s="21" t="s">
         <v>1265</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>1266</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H87" s="17" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C88" s="10" t="s">
-        <v>1268</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H88" s="17" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C89" s="10" t="s">
-        <v>1271</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>1272</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H89" s="17" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C90" s="10" t="s">
-        <v>1274</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H90" s="17" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C91" s="10" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H91" s="17" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C92" s="10" t="s">
-        <v>1280</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H92" s="23" t="s">
-        <v>1282</v>
-      </c>
+    </row>
+    <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="3"/>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C93" s="10" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H93" s="17" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C94" s="10" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H94" s="17" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C95" s="10" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H95" s="17" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C96" s="10" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H96" s="17" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C97" s="10" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H97" s="17" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C98" s="10" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="D93" s="17" t="s">
+      <c r="F98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H98" s="17" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C99" s="10" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H99" s="17" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C100" s="10" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H100" s="23" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C101" s="10" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D101" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>1284</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H93" s="23" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C94" s="10">
+      <c r="E101" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H101" s="23" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C102" s="10">
         <v>300091</v>
       </c>
-      <c r="D94" s="1">
+      <c r="D102" s="1">
         <v>100</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>1286</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H94" s="23" t="s">
-        <v>1287</v>
+      <c r="E102" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H102" s="23" t="s">
+        <v>1295</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="1296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2318" uniqueCount="1306">
   <si>
     <t>_id</t>
   </si>
@@ -1466,6 +1466,36 @@
   </si>
   <si>
     <t>21405809,21405810,22405809,22405810,23405809,23405810</t>
+  </si>
+  <si>
+    <t>虚无装备-全</t>
+  </si>
+  <si>
+    <t>21505801,21505802,21505803,21505804,21505805,21505807,21505809,21505810,22505801,22505802,22505803,22505804,22505805,22505807,22505809,22505810,23505801,23505802,23505803,23505804,23505805,23505807,23505809,23505810</t>
+  </si>
+  <si>
+    <t>虚无装备-剑甲</t>
+  </si>
+  <si>
+    <t>21505801,21505802,22505801,22505802,23505801,23505802</t>
+  </si>
+  <si>
+    <t>虚无装备-项链头盔</t>
+  </si>
+  <si>
+    <t>21505803,21505804,22505803,22505804,23505803,23505804</t>
+  </si>
+  <si>
+    <t>虚无装备-手镯戒指</t>
+  </si>
+  <si>
+    <t>21505805,21505807,22505805,22505807,23505805,23505807</t>
+  </si>
+  <si>
+    <t>虚无装备-鞋子腰带</t>
+  </si>
+  <si>
+    <t>21505809,21505810,22505809,22505810,23505809,23505810</t>
   </si>
   <si>
     <t>209990</t>
@@ -5336,7 +5366,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:I117"/>
+  <dimension ref="A2:I122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -7679,6 +7709,106 @@
       </c>
       <c r="H117" s="20" t="s">
         <v>350</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:8">
+      <c r="C118" s="1">
+        <v>202008</v>
+      </c>
+      <c r="D118" s="1">
+        <v>1800</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F118" s="1">
+        <v>1</v>
+      </c>
+      <c r="G118" s="1">
+        <v>2</v>
+      </c>
+      <c r="H118" s="20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:8">
+      <c r="C119" s="1">
+        <v>202009</v>
+      </c>
+      <c r="D119" s="1">
+        <v>1800</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F119" s="1">
+        <v>1</v>
+      </c>
+      <c r="G119" s="1">
+        <v>2</v>
+      </c>
+      <c r="H119" s="20" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:8">
+      <c r="C120" s="1">
+        <v>202010</v>
+      </c>
+      <c r="D120" s="1">
+        <v>1800</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F120" s="1">
+        <v>1</v>
+      </c>
+      <c r="G120" s="1">
+        <v>2</v>
+      </c>
+      <c r="H120" s="20" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:8">
+      <c r="C121" s="1">
+        <v>202011</v>
+      </c>
+      <c r="D121" s="1">
+        <v>1800</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F121" s="1">
+        <v>1</v>
+      </c>
+      <c r="G121" s="1">
+        <v>2</v>
+      </c>
+      <c r="H121" s="20" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:8">
+      <c r="C122" s="1">
+        <v>202012</v>
+      </c>
+      <c r="D122" s="1">
+        <v>1800</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F122" s="1">
+        <v>1</v>
+      </c>
+      <c r="G122" s="1">
+        <v>2</v>
+      </c>
+      <c r="H122" s="20" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -7779,13 +7909,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="18" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
@@ -7794,18 +7924,18 @@
         <v>19</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -7814,18 +7944,18 @@
         <v>19</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>18</v>
@@ -7834,18 +7964,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>18</v>
@@ -7854,18 +7984,18 @@
         <v>19</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -7874,18 +8004,18 @@
         <v>19</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -7894,18 +8024,18 @@
         <v>19</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
@@ -7914,18 +8044,18 @@
         <v>19</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -7934,18 +8064,18 @@
         <v>19</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -7954,18 +8084,18 @@
         <v>19</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>18</v>
@@ -7974,18 +8104,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
@@ -7994,18 +8124,18 @@
         <v>19</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>18</v>
@@ -8014,18 +8144,18 @@
         <v>19</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>18</v>
@@ -8034,18 +8164,18 @@
         <v>19</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>18</v>
@@ -8054,18 +8184,18 @@
         <v>19</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>18</v>
@@ -8074,18 +8204,18 @@
         <v>19</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>18</v>
@@ -8094,18 +8224,18 @@
         <v>5</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>18</v>
@@ -8114,18 +8244,18 @@
         <v>5</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>18</v>
@@ -8134,18 +8264,18 @@
         <v>5</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>18</v>
@@ -8154,18 +8284,18 @@
         <v>5</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>18</v>
@@ -8174,18 +8304,18 @@
         <v>5</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>18</v>
@@ -8194,18 +8324,18 @@
         <v>5</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>18</v>
@@ -8214,18 +8344,18 @@
         <v>5</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>18</v>
@@ -8234,18 +8364,18 @@
         <v>5</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>18</v>
@@ -8254,18 +8384,18 @@
         <v>5</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>18</v>
@@ -8274,18 +8404,18 @@
         <v>5</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>18</v>
@@ -8294,18 +8424,18 @@
         <v>5</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>18</v>
@@ -8314,18 +8444,18 @@
         <v>5</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>18</v>
@@ -8334,18 +8464,18 @@
         <v>5</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>18</v>
@@ -8354,18 +8484,18 @@
         <v>5</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>18</v>
@@ -8374,18 +8504,18 @@
         <v>5</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>18</v>
@@ -8394,18 +8524,18 @@
         <v>5</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>18</v>
@@ -8414,18 +8544,18 @@
         <v>5</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>18</v>
@@ -8434,18 +8564,18 @@
         <v>5</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>18</v>
@@ -8454,18 +8584,18 @@
         <v>5</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>18</v>
@@ -8474,18 +8604,18 @@
         <v>5</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>18</v>
@@ -8494,18 +8624,18 @@
         <v>5</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>18</v>
@@ -8514,18 +8644,18 @@
         <v>5</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>18</v>
@@ -8534,18 +8664,18 @@
         <v>5</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>18</v>
@@ -8554,18 +8684,18 @@
         <v>5</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>18</v>
@@ -8574,18 +8704,18 @@
         <v>5</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>18</v>
@@ -8594,18 +8724,18 @@
         <v>5</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>18</v>
@@ -8614,18 +8744,18 @@
         <v>5</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>18</v>
@@ -8634,18 +8764,18 @@
         <v>5</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>18</v>
@@ -8654,18 +8784,18 @@
         <v>5</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>18</v>
@@ -8674,18 +8804,18 @@
         <v>5</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>18</v>
@@ -8694,18 +8824,18 @@
         <v>5</v>
       </c>
       <c r="H51" s="21" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>18</v>
@@ -8714,18 +8844,18 @@
         <v>5</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>18</v>
@@ -8734,18 +8864,18 @@
         <v>5</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>18</v>
@@ -8754,18 +8884,18 @@
         <v>5</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>18</v>
@@ -8774,18 +8904,18 @@
         <v>5</v>
       </c>
       <c r="H55" s="21" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>18</v>
@@ -8794,18 +8924,18 @@
         <v>5</v>
       </c>
       <c r="H56" s="21" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>18</v>
@@ -8814,18 +8944,18 @@
         <v>5</v>
       </c>
       <c r="H57" s="21" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>18</v>
@@ -8834,18 +8964,18 @@
         <v>5</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>18</v>
@@ -8854,18 +8984,18 @@
         <v>5</v>
       </c>
       <c r="H59" s="21" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>18</v>
@@ -8874,18 +9004,18 @@
         <v>5</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>18</v>
@@ -8894,18 +9024,18 @@
         <v>5</v>
       </c>
       <c r="H61" s="21" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>18</v>
@@ -8914,18 +9044,18 @@
         <v>5</v>
       </c>
       <c r="H62" s="21" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>18</v>
@@ -8934,18 +9064,18 @@
         <v>5</v>
       </c>
       <c r="H63" s="21" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:8">
       <c r="C64" s="18" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>18</v>
@@ -8954,18 +9084,18 @@
         <v>5</v>
       </c>
       <c r="H64" s="21" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:8">
       <c r="C65" s="18" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>18</v>
@@ -8974,18 +9104,18 @@
         <v>5</v>
       </c>
       <c r="H65" s="21" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:8">
       <c r="C66" s="18" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>18</v>
@@ -8994,18 +9124,18 @@
         <v>5</v>
       </c>
       <c r="H66" s="21" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="18" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>18</v>
@@ -9014,18 +9144,18 @@
         <v>5</v>
       </c>
       <c r="H67" s="21" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="18" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>18</v>
@@ -9034,18 +9164,18 @@
         <v>5</v>
       </c>
       <c r="H68" s="21" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:8">
       <c r="C69" s="18" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>18</v>
@@ -9054,18 +9184,18 @@
         <v>5</v>
       </c>
       <c r="H69" s="21" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="18" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>18</v>
@@ -9074,18 +9204,18 @@
         <v>5</v>
       </c>
       <c r="H70" s="21" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="18" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>18</v>
@@ -9094,18 +9224,18 @@
         <v>5</v>
       </c>
       <c r="H71" s="21" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:8">
       <c r="C72" s="18" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>18</v>
@@ -9114,18 +9244,18 @@
         <v>5</v>
       </c>
       <c r="H72" s="21" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:8">
       <c r="C73" s="18" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>18</v>
@@ -9134,18 +9264,18 @@
         <v>5</v>
       </c>
       <c r="H73" s="21" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:8">
       <c r="C74" s="18" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>18</v>
@@ -9154,18 +9284,18 @@
         <v>5</v>
       </c>
       <c r="H74" s="21" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:8">
       <c r="C75" s="18" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>18</v>
@@ -9174,18 +9304,18 @@
         <v>5</v>
       </c>
       <c r="H75" s="21" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:8">
       <c r="C76" s="18" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>18</v>
@@ -9194,18 +9324,18 @@
         <v>5</v>
       </c>
       <c r="H76" s="21" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:8">
       <c r="C77" s="18" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>18</v>
@@ -9214,18 +9344,18 @@
         <v>5</v>
       </c>
       <c r="H77" s="21" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:8">
       <c r="C78" s="18" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>18</v>
@@ -9234,18 +9364,18 @@
         <v>5</v>
       </c>
       <c r="H78" s="21" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:8">
       <c r="C79" s="18" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>18</v>
@@ -9254,18 +9384,18 @@
         <v>5</v>
       </c>
       <c r="H79" s="21" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="C80" s="18" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>18</v>
@@ -9274,18 +9404,18 @@
         <v>5</v>
       </c>
       <c r="H80" s="21" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:8">
       <c r="C81" s="18" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>18</v>
@@ -9294,18 +9424,18 @@
         <v>5</v>
       </c>
       <c r="H81" s="21" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:8">
       <c r="C82" s="18" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>18</v>
@@ -9314,18 +9444,18 @@
         <v>5</v>
       </c>
       <c r="H82" s="21" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:8">
       <c r="C83" s="18" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>18</v>
@@ -9334,18 +9464,18 @@
         <v>5</v>
       </c>
       <c r="H83" s="21" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:8">
       <c r="C84" s="18" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>18</v>
@@ -9354,18 +9484,18 @@
         <v>5</v>
       </c>
       <c r="H84" s="21" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:8">
       <c r="C85" s="18" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>18</v>
@@ -9374,18 +9504,18 @@
         <v>5</v>
       </c>
       <c r="H85" s="21" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:8">
       <c r="C86" s="18" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>18</v>
@@ -9394,18 +9524,18 @@
         <v>5</v>
       </c>
       <c r="H86" s="21" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:8">
       <c r="C87" s="18" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>18</v>
@@ -9414,18 +9544,18 @@
         <v>5</v>
       </c>
       <c r="H87" s="21" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:8">
       <c r="C88" s="18" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>18</v>
@@ -9434,18 +9564,18 @@
         <v>5</v>
       </c>
       <c r="H88" s="21" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:8">
       <c r="C89" s="18" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>18</v>
@@ -9454,18 +9584,18 @@
         <v>5</v>
       </c>
       <c r="H89" s="21" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:8">
       <c r="C90" s="18" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>18</v>
@@ -9474,18 +9604,18 @@
         <v>5</v>
       </c>
       <c r="H90" s="21" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:8">
       <c r="C91" s="18" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>18</v>
@@ -9494,18 +9624,18 @@
         <v>5</v>
       </c>
       <c r="H91" s="21" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:8">
       <c r="C92" s="18" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>18</v>
@@ -9514,18 +9644,18 @@
         <v>5</v>
       </c>
       <c r="H92" s="21" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:8">
       <c r="C93" s="18" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>18</v>
@@ -9534,18 +9664,18 @@
         <v>5</v>
       </c>
       <c r="H93" s="21" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:8">
       <c r="C94" s="18" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>18</v>
@@ -9554,18 +9684,18 @@
         <v>5</v>
       </c>
       <c r="H94" s="21" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:8">
       <c r="C95" s="18" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>18</v>
@@ -9574,18 +9704,18 @@
         <v>5</v>
       </c>
       <c r="H95" s="21" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:8">
       <c r="C96" s="18" t="s">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>18</v>
@@ -9594,18 +9724,18 @@
         <v>5</v>
       </c>
       <c r="H96" s="21" t="s">
-        <v>623</v>
+        <v>633</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:8">
       <c r="C97" s="18" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>18</v>
@@ -9614,18 +9744,18 @@
         <v>5</v>
       </c>
       <c r="H97" s="21" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:8">
       <c r="C98" s="18" t="s">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>18</v>
@@ -9634,18 +9764,18 @@
         <v>5</v>
       </c>
       <c r="H98" s="21" t="s">
-        <v>629</v>
+        <v>639</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:8">
       <c r="C99" s="18" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>18</v>
@@ -9654,7 +9784,7 @@
         <v>5</v>
       </c>
       <c r="H99" s="21" t="s">
-        <v>632</v>
+        <v>642</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:8">
@@ -9757,13 +9887,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C6" s="18" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
@@ -9777,13 +9907,13 @@
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C7" s="18" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -9797,13 +9927,13 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C8" s="18" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>18</v>
@@ -9817,13 +9947,13 @@
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C9" s="18" t="s">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>18</v>
@@ -9837,13 +9967,13 @@
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="C10" s="18" t="s">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -9859,13 +9989,13 @@
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="18" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -9880,13 +10010,13 @@
     </row>
     <row r="12" customHeight="1" spans="1:9">
       <c r="C12" s="18" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
@@ -9900,13 +10030,13 @@
     </row>
     <row r="13" customHeight="1" spans="1:9">
       <c r="C13" s="18" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -9920,13 +10050,13 @@
     </row>
     <row r="14" customHeight="1" spans="1:9">
       <c r="C14" s="18" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -9940,13 +10070,13 @@
     </row>
     <row r="15" customHeight="1" spans="1:9">
       <c r="C15" s="18" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>18</v>
@@ -9960,13 +10090,13 @@
     </row>
     <row r="16" customHeight="1" spans="1:9">
       <c r="C16" s="18" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>654</v>
+        <v>664</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
@@ -9980,13 +10110,13 @@
     </row>
     <row r="17" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>18</v>
@@ -10000,13 +10130,13 @@
     </row>
     <row r="18" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>18</v>
@@ -10020,13 +10150,13 @@
     </row>
     <row r="19" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>18</v>
@@ -10040,13 +10170,13 @@
     </row>
     <row r="20" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>18</v>
@@ -10060,13 +10190,13 @@
     </row>
     <row r="21" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>18</v>
@@ -10080,13 +10210,13 @@
     </row>
     <row r="22" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>18</v>
@@ -10100,13 +10230,13 @@
     </row>
     <row r="23" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>18</v>
@@ -10120,13 +10250,13 @@
     </row>
     <row r="24" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>18</v>
@@ -10140,13 +10270,13 @@
     </row>
     <row r="25" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>18</v>
@@ -10160,13 +10290,13 @@
     </row>
     <row r="26" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>18</v>
@@ -10180,13 +10310,13 @@
     </row>
     <row r="27" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>18</v>
@@ -10200,13 +10330,13 @@
     </row>
     <row r="28" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>18</v>
@@ -10220,13 +10350,13 @@
     </row>
     <row r="29" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>18</v>
@@ -10240,13 +10370,13 @@
     </row>
     <row r="30" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>18</v>
@@ -10260,13 +10390,13 @@
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>18</v>
@@ -10280,13 +10410,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>18</v>
@@ -10300,13 +10430,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>18</v>
@@ -10320,13 +10450,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>18</v>
@@ -10340,13 +10470,13 @@
     </row>
     <row r="35" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>18</v>
@@ -10360,13 +10490,13 @@
     </row>
     <row r="36" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>18</v>
@@ -10380,13 +10510,13 @@
     </row>
     <row r="37" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>18</v>
@@ -10400,13 +10530,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>18</v>
@@ -10420,13 +10550,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>18</v>
@@ -10440,13 +10570,13 @@
     </row>
     <row r="40" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>18</v>
@@ -10460,13 +10590,13 @@
     </row>
     <row r="41" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>18</v>
@@ -10480,13 +10610,13 @@
     </row>
     <row r="42" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>18</v>
@@ -10500,13 +10630,13 @@
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>18</v>
@@ -10520,13 +10650,13 @@
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>18</v>
@@ -10540,13 +10670,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>18</v>
@@ -10560,13 +10690,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>18</v>
@@ -10580,13 +10710,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>18</v>
@@ -10600,13 +10730,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>18</v>
@@ -10620,13 +10750,13 @@
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>18</v>
@@ -10640,13 +10770,13 @@
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>18</v>
@@ -10660,13 +10790,13 @@
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>18</v>
@@ -10680,13 +10810,13 @@
     </row>
     <row r="52" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>18</v>
@@ -10700,13 +10830,13 @@
     </row>
     <row r="53" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>728</v>
+        <v>738</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>18</v>
@@ -10720,13 +10850,13 @@
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>18</v>
@@ -10740,13 +10870,13 @@
     </row>
     <row r="55" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>18</v>
@@ -10760,13 +10890,13 @@
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>18</v>
@@ -10780,13 +10910,13 @@
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>18</v>
@@ -10800,13 +10930,13 @@
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>18</v>
@@ -10820,13 +10950,13 @@
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>738</v>
+        <v>748</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>18</v>
@@ -10840,13 +10970,13 @@
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>741</v>
+        <v>751</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>18</v>
@@ -10860,13 +10990,13 @@
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>18</v>
@@ -10880,13 +11010,13 @@
     </row>
     <row r="62" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>18</v>
@@ -10900,13 +11030,13 @@
     </row>
     <row r="63" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>18</v>
@@ -10920,13 +11050,13 @@
     </row>
     <row r="64" customHeight="1" spans="3:8">
       <c r="C64" s="18" t="s">
-        <v>748</v>
+        <v>758</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>18</v>
@@ -10940,13 +11070,13 @@
     </row>
     <row r="65" customHeight="1" spans="3:8">
       <c r="C65" s="18" t="s">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>18</v>
@@ -10960,13 +11090,13 @@
     </row>
     <row r="66" customHeight="1" spans="3:8">
       <c r="C66" s="18" t="s">
-        <v>752</v>
+        <v>762</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>753</v>
+        <v>763</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>18</v>
@@ -10980,13 +11110,13 @@
     </row>
     <row r="67" customHeight="1" spans="3:8">
       <c r="C67" s="18" t="s">
-        <v>754</v>
+        <v>764</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>18</v>
@@ -11000,13 +11130,13 @@
     </row>
     <row r="68" customHeight="1" spans="3:8">
       <c r="C68" s="18" t="s">
-        <v>756</v>
+        <v>766</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>757</v>
+        <v>767</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>18</v>
@@ -11020,13 +11150,13 @@
     </row>
     <row r="69" customHeight="1" spans="3:8">
       <c r="C69" s="18" t="s">
-        <v>758</v>
+        <v>768</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>18</v>
@@ -11040,13 +11170,13 @@
     </row>
     <row r="70" customHeight="1" spans="3:8">
       <c r="C70" s="18" t="s">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>761</v>
+        <v>771</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>18</v>
@@ -11060,13 +11190,13 @@
     </row>
     <row r="71" customHeight="1" spans="3:8">
       <c r="C71" s="18" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>763</v>
+        <v>773</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>18</v>
@@ -11080,13 +11210,13 @@
     </row>
     <row r="72" customHeight="1" spans="3:8">
       <c r="C72" s="18" t="s">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>18</v>
@@ -11100,13 +11230,13 @@
     </row>
     <row r="73" customHeight="1" spans="3:8">
       <c r="C73" s="18" t="s">
-        <v>766</v>
+        <v>776</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>18</v>
@@ -11120,13 +11250,13 @@
     </row>
     <row r="74" customHeight="1" spans="3:8">
       <c r="C74" s="18" t="s">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>18</v>
@@ -11140,13 +11270,13 @@
     </row>
     <row r="75" customHeight="1" spans="3:8">
       <c r="C75" s="18" t="s">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>771</v>
+        <v>781</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>18</v>
@@ -11160,13 +11290,13 @@
     </row>
     <row r="76" customHeight="1" spans="3:8">
       <c r="C76" s="18" t="s">
-        <v>772</v>
+        <v>782</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>773</v>
+        <v>783</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>18</v>
@@ -11180,13 +11310,13 @@
     </row>
     <row r="77" customHeight="1" spans="3:8">
       <c r="C77" s="18" t="s">
-        <v>774</v>
+        <v>784</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>18</v>
@@ -11200,13 +11330,13 @@
     </row>
     <row r="78" customHeight="1" spans="3:8">
       <c r="C78" s="18" t="s">
-        <v>776</v>
+        <v>786</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>777</v>
+        <v>787</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>18</v>
@@ -11220,13 +11350,13 @@
     </row>
     <row r="79" customHeight="1" spans="3:8">
       <c r="C79" s="18" t="s">
-        <v>778</v>
+        <v>788</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>779</v>
+        <v>789</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>18</v>
@@ -11240,13 +11370,13 @@
     </row>
     <row r="80" customHeight="1" spans="3:8">
       <c r="C80" s="18" t="s">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>781</v>
+        <v>791</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>18</v>
@@ -11260,13 +11390,13 @@
     </row>
     <row r="81" customHeight="1" spans="3:8">
       <c r="C81" s="18" t="s">
-        <v>782</v>
+        <v>792</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>18</v>
@@ -11280,13 +11410,13 @@
     </row>
     <row r="82" customHeight="1" spans="3:8">
       <c r="C82" s="18" t="s">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>785</v>
+        <v>795</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>18</v>
@@ -11300,13 +11430,13 @@
     </row>
     <row r="83" customHeight="1" spans="3:8">
       <c r="C83" s="18" t="s">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>787</v>
+        <v>797</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>18</v>
@@ -11320,13 +11450,13 @@
     </row>
     <row r="84" customHeight="1" spans="3:8">
       <c r="C84" s="18" t="s">
-        <v>788</v>
+        <v>798</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>789</v>
+        <v>799</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>18</v>
@@ -11340,13 +11470,13 @@
     </row>
     <row r="85" customHeight="1" spans="3:8">
       <c r="C85" s="18" t="s">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>18</v>
@@ -11360,13 +11490,13 @@
     </row>
     <row r="86" customHeight="1" spans="3:8">
       <c r="C86" s="18" t="s">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>18</v>
@@ -11380,13 +11510,13 @@
     </row>
     <row r="87" customHeight="1" spans="3:8">
       <c r="C87" s="18" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>18</v>
@@ -11400,13 +11530,13 @@
     </row>
     <row r="88" customHeight="1" spans="3:8">
       <c r="C88" s="18" t="s">
-        <v>796</v>
+        <v>806</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>18</v>
@@ -11420,13 +11550,13 @@
     </row>
     <row r="89" customHeight="1" spans="3:8">
       <c r="C89" s="18" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>18</v>
@@ -11440,13 +11570,13 @@
     </row>
     <row r="90" customHeight="1" spans="3:8">
       <c r="C90" s="18" t="s">
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>18</v>
@@ -11460,13 +11590,13 @@
     </row>
     <row r="91" customHeight="1" spans="3:8">
       <c r="C91" s="18" t="s">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>803</v>
+        <v>813</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>18</v>
@@ -11480,13 +11610,13 @@
     </row>
     <row r="92" customHeight="1" spans="3:8">
       <c r="C92" s="18" t="s">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>18</v>
@@ -11500,13 +11630,13 @@
     </row>
     <row r="93" customHeight="1" spans="3:8">
       <c r="C93" s="18" t="s">
-        <v>806</v>
+        <v>816</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>18</v>
@@ -11520,13 +11650,13 @@
     </row>
     <row r="94" customHeight="1" spans="3:8">
       <c r="C94" s="18" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>809</v>
+        <v>819</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>18</v>
@@ -11540,13 +11670,13 @@
     </row>
     <row r="95" s="13" customFormat="1" customHeight="1" spans="3:8">
       <c r="C95" s="22" t="s">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="D95" s="13">
         <v>0</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>811</v>
+        <v>821</v>
       </c>
       <c r="F95" s="13" t="s">
         <v>18</v>
@@ -11560,13 +11690,13 @@
     </row>
     <row r="96" customHeight="1" spans="3:8">
       <c r="C96" s="18" t="s">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>18</v>
@@ -11580,13 +11710,13 @@
     </row>
     <row r="97" customHeight="1" spans="3:8">
       <c r="C97" s="18" t="s">
-        <v>814</v>
+        <v>824</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>815</v>
+        <v>825</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>18</v>
@@ -11600,13 +11730,13 @@
     </row>
     <row r="98" customHeight="1" spans="3:8">
       <c r="C98" s="18" t="s">
-        <v>816</v>
+        <v>826</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>18</v>
@@ -11620,13 +11750,13 @@
     </row>
     <row r="99" customHeight="1" spans="3:8">
       <c r="C99" s="18" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>18</v>
@@ -11640,13 +11770,13 @@
     </row>
     <row r="100" customHeight="1" spans="3:8">
       <c r="C100" s="18" t="s">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>18</v>
@@ -11660,13 +11790,13 @@
     </row>
     <row r="101" customHeight="1" spans="3:8">
       <c r="C101" s="18" t="s">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>823</v>
+        <v>833</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>18</v>
@@ -11680,13 +11810,13 @@
     </row>
     <row r="102" customHeight="1" spans="3:8">
       <c r="C102" s="18" t="s">
-        <v>824</v>
+        <v>834</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>18</v>
@@ -11700,13 +11830,13 @@
     </row>
     <row r="103" customHeight="1" spans="3:8">
       <c r="C103" s="18" t="s">
-        <v>826</v>
+        <v>836</v>
       </c>
       <c r="D103" s="1">
         <v>0</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>18</v>
@@ -11720,13 +11850,13 @@
     </row>
     <row r="104" customHeight="1" spans="3:8">
       <c r="C104" s="18" t="s">
-        <v>828</v>
+        <v>838</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>18</v>
@@ -11740,13 +11870,13 @@
     </row>
     <row r="105" customHeight="1" spans="3:8">
       <c r="C105" s="18" t="s">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>831</v>
+        <v>841</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>18</v>
@@ -11760,13 +11890,13 @@
     </row>
     <row r="106" customHeight="1" spans="3:8">
       <c r="C106" s="18" t="s">
-        <v>832</v>
+        <v>842</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>833</v>
+        <v>843</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>18</v>
@@ -11780,13 +11910,13 @@
     </row>
     <row r="107" customHeight="1" spans="3:8">
       <c r="C107" s="18" t="s">
-        <v>834</v>
+        <v>844</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>18</v>
@@ -11800,13 +11930,13 @@
     </row>
     <row r="108" customHeight="1" spans="3:8">
       <c r="C108" s="18" t="s">
-        <v>836</v>
+        <v>846</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>837</v>
+        <v>847</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>18</v>
@@ -11820,13 +11950,13 @@
     </row>
     <row r="109" customHeight="1" spans="3:8">
       <c r="C109" s="18" t="s">
-        <v>838</v>
+        <v>848</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>839</v>
+        <v>849</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>18</v>
@@ -11840,13 +11970,13 @@
     </row>
     <row r="110" customHeight="1" spans="3:8">
       <c r="C110" s="18" t="s">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>841</v>
+        <v>851</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>18</v>
@@ -11860,13 +11990,13 @@
     </row>
     <row r="111" customHeight="1" spans="3:8">
       <c r="C111" s="18" t="s">
-        <v>842</v>
+        <v>852</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>18</v>
@@ -11880,13 +12010,13 @@
     </row>
     <row r="112" customHeight="1" spans="3:8">
       <c r="C112" s="18" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>18</v>
@@ -11900,13 +12030,13 @@
     </row>
     <row r="113" customHeight="1" spans="3:8">
       <c r="C113" s="18" t="s">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>847</v>
+        <v>857</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>18</v>
@@ -11920,13 +12050,13 @@
     </row>
     <row r="114" customHeight="1" spans="3:8">
       <c r="C114" s="18" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>18</v>
@@ -11940,13 +12070,13 @@
     </row>
     <row r="115" customHeight="1" spans="3:8">
       <c r="C115" s="18" t="s">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>851</v>
+        <v>861</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>18</v>
@@ -11960,13 +12090,13 @@
     </row>
     <row r="116" customHeight="1" spans="3:8">
       <c r="C116" s="18" t="s">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>18</v>
@@ -11980,13 +12110,13 @@
     </row>
     <row r="117" customHeight="1" spans="3:8">
       <c r="C117" s="18" t="s">
-        <v>854</v>
+        <v>864</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>18</v>
@@ -12000,13 +12130,13 @@
     </row>
     <row r="118" customHeight="1" spans="3:8">
       <c r="C118" s="18" t="s">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="D118" s="1">
         <v>0</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>18</v>
@@ -12020,13 +12150,13 @@
     </row>
     <row r="119" customHeight="1" spans="3:8">
       <c r="C119" s="18" t="s">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>18</v>
@@ -12040,13 +12170,13 @@
     </row>
     <row r="120" customHeight="1" spans="3:8">
       <c r="C120" s="18" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>861</v>
+        <v>871</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>18</v>
@@ -12060,13 +12190,13 @@
     </row>
     <row r="121" customHeight="1" spans="3:8">
       <c r="C121" s="18" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="D121" s="1">
         <v>0</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>863</v>
+        <v>873</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>18</v>
@@ -12080,13 +12210,13 @@
     </row>
     <row r="122" customHeight="1" spans="3:8">
       <c r="C122" s="18" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="D122" s="1">
         <v>0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>865</v>
+        <v>875</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>18</v>
@@ -12100,13 +12230,13 @@
     </row>
     <row r="123" customHeight="1" spans="3:8">
       <c r="C123" s="18" t="s">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>18</v>
@@ -12120,13 +12250,13 @@
     </row>
     <row r="124" customHeight="1" spans="3:8">
       <c r="C124" s="18" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="D124" s="1">
         <v>0</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>18</v>
@@ -12140,13 +12270,13 @@
     </row>
     <row r="125" customHeight="1" spans="3:8">
       <c r="C125" s="18" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="D125" s="1">
         <v>0</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>18</v>
@@ -12160,13 +12290,13 @@
     </row>
     <row r="126" customHeight="1" spans="3:8">
       <c r="C126" s="18" t="s">
-        <v>872</v>
+        <v>882</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>873</v>
+        <v>883</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>18</v>
@@ -12180,13 +12310,13 @@
     </row>
     <row r="127" customHeight="1" spans="3:8">
       <c r="C127" s="18" t="s">
-        <v>874</v>
+        <v>884</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>875</v>
+        <v>885</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>18</v>
@@ -12200,13 +12330,13 @@
     </row>
     <row r="128" customHeight="1" spans="3:8">
       <c r="C128" s="18" t="s">
-        <v>876</v>
+        <v>886</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>18</v>
@@ -12220,13 +12350,13 @@
     </row>
     <row r="129" customHeight="1" spans="3:8">
       <c r="C129" s="18" t="s">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="D129" s="1">
         <v>0</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>18</v>
@@ -12240,13 +12370,13 @@
     </row>
     <row r="130" s="13" customFormat="1" customHeight="1" spans="3:8">
       <c r="C130" s="22" t="s">
-        <v>880</v>
+        <v>890</v>
       </c>
       <c r="D130" s="13">
         <v>0</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>881</v>
+        <v>891</v>
       </c>
       <c r="F130" s="13" t="s">
         <v>18</v>
@@ -12260,13 +12390,13 @@
     </row>
     <row r="131" customHeight="1" spans="3:8">
       <c r="C131" s="18" t="s">
-        <v>882</v>
+        <v>892</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>883</v>
+        <v>893</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>18</v>
@@ -12280,13 +12410,13 @@
     </row>
     <row r="132" customHeight="1" spans="3:8">
       <c r="C132" s="18" t="s">
-        <v>884</v>
+        <v>894</v>
       </c>
       <c r="D132" s="1">
         <v>0</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>18</v>
@@ -12300,13 +12430,13 @@
     </row>
     <row r="133" customHeight="1" spans="3:8">
       <c r="C133" s="18" t="s">
-        <v>886</v>
+        <v>896</v>
       </c>
       <c r="D133" s="1">
         <v>0</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>887</v>
+        <v>897</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>18</v>
@@ -12320,13 +12450,13 @@
     </row>
     <row r="134" customHeight="1" spans="3:8">
       <c r="C134" s="18" t="s">
-        <v>888</v>
+        <v>898</v>
       </c>
       <c r="D134" s="1">
         <v>0</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>889</v>
+        <v>899</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>18</v>
@@ -12340,13 +12470,13 @@
     </row>
     <row r="135" customHeight="1" spans="3:8">
       <c r="C135" s="18" t="s">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="D135" s="1">
         <v>0</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>891</v>
+        <v>901</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>18</v>
@@ -12360,13 +12490,13 @@
     </row>
     <row r="136" customHeight="1" spans="3:8">
       <c r="C136" s="18" t="s">
-        <v>892</v>
+        <v>902</v>
       </c>
       <c r="D136" s="1">
         <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>893</v>
+        <v>903</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>18</v>
@@ -12380,13 +12510,13 @@
     </row>
     <row r="137" customHeight="1" spans="3:8">
       <c r="C137" s="18" t="s">
-        <v>894</v>
+        <v>904</v>
       </c>
       <c r="D137" s="1">
         <v>0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>18</v>
@@ -12400,13 +12530,13 @@
     </row>
     <row r="138" customHeight="1" spans="3:8">
       <c r="C138" s="18" t="s">
-        <v>896</v>
+        <v>906</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>897</v>
+        <v>907</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>18</v>
@@ -12420,13 +12550,13 @@
     </row>
     <row r="139" customHeight="1" spans="3:8">
       <c r="C139" s="18" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="D139" s="1">
         <v>0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>18</v>
@@ -12440,13 +12570,13 @@
     </row>
     <row r="140" customHeight="1" spans="3:8">
       <c r="C140" s="18" t="s">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="D140" s="1">
         <v>0</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>18</v>
@@ -12460,13 +12590,13 @@
     </row>
     <row r="141" customHeight="1" spans="3:8">
       <c r="C141" s="18" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="D141" s="1">
         <v>0</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>18</v>
@@ -12480,13 +12610,13 @@
     </row>
     <row r="142" customHeight="1" spans="3:8">
       <c r="C142" s="18" t="s">
-        <v>904</v>
+        <v>914</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>18</v>
@@ -12500,13 +12630,13 @@
     </row>
     <row r="143" customHeight="1" spans="3:8">
       <c r="C143" s="18" t="s">
-        <v>906</v>
+        <v>916</v>
       </c>
       <c r="D143" s="1">
         <v>0</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>907</v>
+        <v>917</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>18</v>
@@ -12520,13 +12650,13 @@
     </row>
     <row r="144" customHeight="1" spans="3:8">
       <c r="C144" s="18" t="s">
-        <v>908</v>
+        <v>918</v>
       </c>
       <c r="D144" s="1">
         <v>0</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>909</v>
+        <v>919</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>18</v>
@@ -12540,13 +12670,13 @@
     </row>
     <row r="145" customHeight="1" spans="3:8">
       <c r="C145" s="18" t="s">
-        <v>910</v>
+        <v>920</v>
       </c>
       <c r="D145" s="1">
         <v>0</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>911</v>
+        <v>921</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>18</v>
@@ -12560,13 +12690,13 @@
     </row>
     <row r="146" customHeight="1" spans="3:8">
       <c r="C146" s="18" t="s">
-        <v>912</v>
+        <v>922</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>913</v>
+        <v>923</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>18</v>
@@ -12580,13 +12710,13 @@
     </row>
     <row r="147" customHeight="1" spans="3:8">
       <c r="C147" s="18" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="D147" s="1">
         <v>0</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>915</v>
+        <v>925</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>18</v>
@@ -12600,13 +12730,13 @@
     </row>
     <row r="148" customHeight="1" spans="3:8">
       <c r="C148" s="18" t="s">
-        <v>916</v>
+        <v>926</v>
       </c>
       <c r="D148" s="1">
         <v>0</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>917</v>
+        <v>927</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>18</v>
@@ -12620,13 +12750,13 @@
     </row>
     <row r="149" customHeight="1" spans="3:8">
       <c r="C149" s="18" t="s">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="D149" s="1">
         <v>0</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>18</v>
@@ -12640,13 +12770,13 @@
     </row>
     <row r="150" customHeight="1" spans="3:8">
       <c r="C150" s="18" t="s">
-        <v>920</v>
+        <v>930</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>18</v>
@@ -12660,13 +12790,13 @@
     </row>
     <row r="151" customHeight="1" spans="3:8">
       <c r="C151" s="18" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="D151" s="1">
         <v>0</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>18</v>
@@ -12680,13 +12810,13 @@
     </row>
     <row r="152" customHeight="1" spans="3:8">
       <c r="C152" s="18" t="s">
-        <v>924</v>
+        <v>934</v>
       </c>
       <c r="D152" s="1">
         <v>0</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>18</v>
@@ -12700,13 +12830,13 @@
     </row>
     <row r="153" customHeight="1" spans="3:8">
       <c r="C153" s="18" t="s">
-        <v>926</v>
+        <v>936</v>
       </c>
       <c r="D153" s="1">
         <v>0</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>927</v>
+        <v>937</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>18</v>
@@ -12720,13 +12850,13 @@
     </row>
     <row r="154" customHeight="1" spans="3:8">
       <c r="C154" s="18" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="D154" s="1">
         <v>0</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>929</v>
+        <v>939</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>18</v>
@@ -12740,13 +12870,13 @@
     </row>
     <row r="155" customHeight="1" spans="3:8">
       <c r="C155" s="18" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="D155" s="1">
         <v>0</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>18</v>
@@ -12760,13 +12890,13 @@
     </row>
     <row r="156" customHeight="1" spans="3:8">
       <c r="C156" s="18" t="s">
-        <v>932</v>
+        <v>942</v>
       </c>
       <c r="D156" s="1">
         <v>0</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>933</v>
+        <v>943</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>18</v>
@@ -12780,13 +12910,13 @@
     </row>
     <row r="157" customHeight="1" spans="3:8">
       <c r="C157" s="18" t="s">
-        <v>934</v>
+        <v>944</v>
       </c>
       <c r="D157" s="1">
         <v>0</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>935</v>
+        <v>945</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>18</v>
@@ -12800,13 +12930,13 @@
     </row>
     <row r="158" customHeight="1" spans="3:8">
       <c r="C158" s="18" t="s">
-        <v>936</v>
+        <v>946</v>
       </c>
       <c r="D158" s="1">
         <v>0</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>937</v>
+        <v>947</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>18</v>
@@ -12820,13 +12950,13 @@
     </row>
     <row r="159" customHeight="1" spans="3:8">
       <c r="C159" s="18" t="s">
-        <v>938</v>
+        <v>948</v>
       </c>
       <c r="D159" s="1">
         <v>0</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>939</v>
+        <v>949</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>18</v>
@@ -12840,13 +12970,13 @@
     </row>
     <row r="160" customHeight="1" spans="3:8">
       <c r="C160" s="18" t="s">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="D160" s="1">
         <v>0</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>941</v>
+        <v>951</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>18</v>
@@ -12860,13 +12990,13 @@
     </row>
     <row r="161" customHeight="1" spans="3:8">
       <c r="C161" s="18" t="s">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="D161" s="1">
         <v>0</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>943</v>
+        <v>953</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>18</v>
@@ -12880,13 +13010,13 @@
     </row>
     <row r="162" customHeight="1" spans="3:8">
       <c r="C162" s="18" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="D162" s="1">
         <v>0</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>945</v>
+        <v>955</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>18</v>
@@ -12900,13 +13030,13 @@
     </row>
     <row r="163" customHeight="1" spans="3:8">
       <c r="C163" s="18" t="s">
-        <v>946</v>
+        <v>956</v>
       </c>
       <c r="D163" s="1">
         <v>0</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>947</v>
+        <v>957</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>18</v>
@@ -12920,13 +13050,13 @@
     </row>
     <row r="164" customHeight="1" spans="3:8">
       <c r="C164" s="18" t="s">
-        <v>948</v>
+        <v>958</v>
       </c>
       <c r="D164" s="1">
         <v>0</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>18</v>
@@ -13044,7 +13174,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
@@ -13064,7 +13194,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -13084,7 +13214,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>18</v>
@@ -13104,7 +13234,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>953</v>
+        <v>963</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>18</v>
@@ -13124,7 +13254,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>954</v>
+        <v>964</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -13146,7 +13276,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>955</v>
+        <v>965</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -13167,7 +13297,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
@@ -13187,7 +13317,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -13207,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -13227,7 +13357,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>18</v>
@@ -13247,7 +13377,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
@@ -13267,7 +13397,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>18</v>
@@ -13287,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>962</v>
+        <v>972</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>18</v>
@@ -13307,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>18</v>
@@ -13327,7 +13457,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>18</v>
@@ -13347,7 +13477,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>18</v>
@@ -13367,7 +13497,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>18</v>
@@ -13387,7 +13517,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>18</v>
@@ -13407,7 +13537,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>18</v>
@@ -13427,7 +13557,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>18</v>
@@ -13447,7 +13577,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>18</v>
@@ -13467,7 +13597,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>18</v>
@@ -13490,7 +13620,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>18</v>
@@ -13510,7 +13640,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>18</v>
@@ -13530,7 +13660,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>18</v>
@@ -13550,7 +13680,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>18</v>
@@ -13570,7 +13700,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>18</v>
@@ -13590,7 +13720,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>18</v>
@@ -13610,7 +13740,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>18</v>
@@ -13630,7 +13760,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>18</v>
@@ -13650,7 +13780,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>18</v>
@@ -13670,7 +13800,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>18</v>
@@ -13690,7 +13820,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>18</v>
@@ -13710,7 +13840,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>18</v>
@@ -13730,7 +13860,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>18</v>
@@ -13839,13 +13969,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="18" t="s">
-        <v>983</v>
+        <v>993</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
@@ -13859,13 +13989,13 @@
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -13879,13 +14009,13 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="F8" s="1">
         <v>50</v>
@@ -13899,13 +14029,13 @@
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>989</v>
+        <v>999</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="F9" s="1">
         <v>20</v>
@@ -13919,13 +14049,13 @@
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>992</v>
+        <v>1002</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -13939,13 +14069,13 @@
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>993</v>
+        <v>1003</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -13959,13 +14089,13 @@
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
@@ -13979,13 +14109,13 @@
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>998</v>
+        <v>1008</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -13994,18 +14124,18 @@
         <v>3</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>999</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1001</v>
+        <v>1011</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -14014,18 +14144,18 @@
         <v>3</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>1003</v>
+        <v>1013</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1004</v>
+        <v>1014</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -14034,18 +14164,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>1005</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>1006</v>
+        <v>1016</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -14059,13 +14189,13 @@
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>1007</v>
+        <v>1017</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="F17" s="1">
         <v>40</v>
@@ -14079,13 +14209,13 @@
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>1008</v>
+        <v>1018</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="F18" s="1">
         <v>200</v>
@@ -14099,13 +14229,13 @@
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>1009</v>
+        <v>1019</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="F19" s="1">
         <v>80</v>
@@ -14119,13 +14249,13 @@
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>18</v>
@@ -14139,13 +14269,13 @@
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="F21" s="1">
         <v>500</v>
@@ -14159,13 +14289,13 @@
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="18" t="s">
-        <v>1013</v>
+        <v>1023</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="F22" s="1">
         <v>200</v>
@@ -14179,113 +14309,113 @@
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>1014</v>
+        <v>1024</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1016</v>
+        <v>1026</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>1018</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>1021</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>1022</v>
+        <v>1032</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>1025</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>1015</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>1028</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>1029</v>
+        <v>1039</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>1031</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>1032</v>
+        <v>1042</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1033</v>
+        <v>1043</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>18</v>
@@ -14294,18 +14424,18 @@
         <v>3</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>1035</v>
+        <v>1045</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1036</v>
+        <v>1046</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>18</v>
@@ -14314,18 +14444,18 @@
         <v>3</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>1038</v>
+        <v>1048</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1039</v>
+        <v>1049</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>18</v>
@@ -14334,18 +14464,18 @@
         <v>3</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>1040</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1041</v>
+        <v>1051</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="F31" s="1">
         <v>2</v>
@@ -14359,13 +14489,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1042</v>
+        <v>1052</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="F32" s="1">
         <v>2</v>
@@ -14379,13 +14509,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="F33" s="1">
         <v>200</v>
@@ -14399,13 +14529,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1044</v>
+        <v>1054</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="F34" s="1">
         <v>100</v>
@@ -14419,53 +14549,53 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1045</v>
+        <v>1055</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1046</v>
+        <v>1056</v>
       </c>
       <c r="F35" s="1">
         <v>10</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1047</v>
+        <v>1057</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>1048</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1049</v>
+        <v>1059</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1046</v>
+        <v>1056</v>
       </c>
       <c r="F36" s="1">
         <v>15</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1047</v>
+        <v>1057</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>1048</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1051</v>
+        <v>1061</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>18</v>
@@ -14479,13 +14609,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1052</v>
+        <v>1062</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="F38" s="1">
         <v>1000</v>
@@ -14499,13 +14629,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1053</v>
+        <v>1063</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="F39" s="1">
         <v>300</v>
@@ -14519,13 +14649,13 @@
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>1054</v>
+        <v>1064</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1055</v>
+        <v>1065</v>
       </c>
       <c r="F40" s="1">
         <v>1</v>
@@ -14534,18 +14664,18 @@
         <v>5</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>1057</v>
+        <v>1067</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="F41" s="1">
         <v>1</v>
@@ -14559,13 +14689,13 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1059</v>
+        <v>1069</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="F42" s="1">
         <v>1</v>
@@ -14574,18 +14704,18 @@
         <v>19</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>1061</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1062</v>
+        <v>1072</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1063</v>
+        <v>1073</v>
       </c>
       <c r="F44" s="1">
         <v>1</v>
@@ -14599,13 +14729,13 @@
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1064</v>
+        <v>1074</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1065</v>
+        <v>1075</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
@@ -14619,13 +14749,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1066</v>
+        <v>1076</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1067</v>
+        <v>1077</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -14639,13 +14769,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1068</v>
+        <v>1078</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1069</v>
+        <v>1079</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -14659,13 +14789,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="F48" s="1">
         <v>1</v>
@@ -14679,13 +14809,13 @@
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1072</v>
+        <v>1082</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1073</v>
+        <v>1083</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
@@ -14699,13 +14829,13 @@
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1074</v>
+        <v>1084</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1075</v>
+        <v>1085</v>
       </c>
       <c r="F50" s="1">
         <v>1</v>
@@ -14719,13 +14849,13 @@
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>1076</v>
+        <v>1086</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1077</v>
+        <v>1087</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -14834,13 +14964,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="1" t="s">
-        <v>1078</v>
+        <v>1088</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1079</v>
+        <v>1089</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>18</v>
@@ -14849,18 +14979,18 @@
         <v>19</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1080</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="17" t="s">
-        <v>1081</v>
+        <v>1091</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1082</v>
+        <v>1092</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -14869,18 +14999,18 @@
         <v>19</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>1083</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="17" t="s">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1085</v>
+        <v>1095</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>18</v>
@@ -14889,18 +15019,18 @@
         <v>19</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>1086</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="17" t="s">
-        <v>1087</v>
+        <v>1097</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1088</v>
+        <v>1098</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>18</v>
@@ -14909,18 +15039,18 @@
         <v>19</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>1089</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="17" t="s">
-        <v>1090</v>
+        <v>1100</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1091</v>
+        <v>1101</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -14929,7 +15059,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>1092</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -14937,10 +15067,10 @@
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>18</v>
@@ -14949,18 +15079,18 @@
         <v>19</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>1094</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="17" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>18</v>
@@ -14969,18 +15099,18 @@
         <v>16</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>1097</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="17" t="s">
-        <v>1098</v>
+        <v>1108</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -14989,18 +15119,18 @@
         <v>16</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>1099</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="17" t="s">
-        <v>1100</v>
+        <v>1110</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -15009,18 +15139,18 @@
         <v>16</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>1101</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="17" t="s">
-        <v>1102</v>
+        <v>1112</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>18</v>
@@ -15029,18 +15159,18 @@
         <v>16</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>1103</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="17" t="s">
-        <v>1104</v>
+        <v>1114</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1105</v>
+        <v>1115</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>18</v>
@@ -15049,18 +15179,18 @@
         <v>16</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>1106</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="17" t="s">
-        <v>1107</v>
+        <v>1117</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1108</v>
+        <v>1118</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>18</v>
@@ -15069,18 +15199,18 @@
         <v>16</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>1109</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="17" t="s">
-        <v>1110</v>
+        <v>1120</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1111</v>
+        <v>1121</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>18</v>
@@ -15089,7 +15219,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>1112</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15108,7 +15238,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -15117,7 +15247,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>1114</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15133,199 +15263,199 @@
         <v>306</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1115</v>
+        <v>1125</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>1117</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="17" t="s">
-        <v>1118</v>
+        <v>1128</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1119</v>
+        <v>1129</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>1120</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="17" t="s">
-        <v>1121</v>
+        <v>1131</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1122</v>
+        <v>1132</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>1120</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="17" t="s">
-        <v>1123</v>
+        <v>1133</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1124</v>
+        <v>1134</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>1125</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="17" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="17" t="s">
         <v>1126</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>1116</v>
-      </c>
       <c r="H26" s="23" t="s">
-        <v>1128</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="17" t="s">
-        <v>1129</v>
+        <v>1139</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>1131</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="17" t="s">
-        <v>1132</v>
+        <v>1142</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1046</v>
+        <v>1056</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>1047</v>
+        <v>1057</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>1048</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="17" t="s">
-        <v>1133</v>
+        <v>1143</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1134</v>
+        <v>1144</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>1135</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="17" t="s">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1137</v>
+        <v>1147</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>1138</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="17" t="s">
-        <v>1139</v>
+        <v>1149</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>1141</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -15333,179 +15463,179 @@
         <v>310</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1142</v>
+        <v>1152</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>1143</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="17" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1144</v>
+        <v>1154</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>1145</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="17" t="s">
-        <v>1146</v>
+        <v>1156</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1147</v>
+        <v>1157</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>1148</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="17" t="s">
-        <v>1149</v>
+        <v>1159</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1150</v>
+        <v>1160</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>1151</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="17" t="s">
-        <v>1152</v>
+        <v>1162</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1153</v>
+        <v>1163</v>
       </c>
       <c r="F36" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>1154</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="17" t="s">
-        <v>1155</v>
+        <v>1165</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="17" t="s">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1159</v>
+        <v>1169</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>1160</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="17" t="s">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1162</v>
+        <v>1172</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>1163</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="17" t="s">
-        <v>1164</v>
+        <v>1174</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1165</v>
+        <v>1175</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>1166</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15526,422 +15656,422 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="17" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="F43" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>1021</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="17" t="s">
-        <v>1168</v>
+        <v>1178</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1016</v>
+        <v>1026</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>1018</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="17" t="s">
-        <v>1169</v>
+        <v>1179</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1170</v>
+        <v>1180</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>1171</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="17" t="s">
-        <v>1172</v>
+        <v>1182</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="17" t="s">
-        <v>1173</v>
+        <v>1183</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1174</v>
+        <v>1184</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>1175</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="17" t="s">
-        <v>1176</v>
+        <v>1186</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>1178</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="17" t="s">
-        <v>1179</v>
+        <v>1189</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1180</v>
+        <v>1190</v>
       </c>
       <c r="F49" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>1181</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="17" t="s">
-        <v>1182</v>
+        <v>1192</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1183</v>
+        <v>1193</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>1184</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="17" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1185</v>
+        <v>1195</v>
       </c>
       <c r="F51" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>1186</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="17" t="s">
-        <v>1037</v>
+        <v>1047</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1187</v>
+        <v>1197</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>1188</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="17" t="s">
-        <v>1189</v>
+        <v>1199</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>1191</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="17" t="s">
-        <v>1192</v>
+        <v>1202</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1193</v>
+        <v>1203</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>1194</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="17" t="s">
-        <v>1195</v>
+        <v>1205</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1196</v>
+        <v>1206</v>
       </c>
       <c r="F55" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>1197</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="17" t="s">
-        <v>1198</v>
+        <v>1208</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1199</v>
+        <v>1209</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>1200</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="17" t="s">
-        <v>1201</v>
+        <v>1211</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1202</v>
+        <v>1212</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>1203</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="17" t="s">
-        <v>1204</v>
+        <v>1214</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1205</v>
+        <v>1215</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G58" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>1206</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="17" t="s">
-        <v>1207</v>
+        <v>1217</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1208</v>
+        <v>1218</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>1209</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="17" t="s">
-        <v>1210</v>
+        <v>1220</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1211</v>
+        <v>1221</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>1212</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="17" t="s">
-        <v>1213</v>
+        <v>1223</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1214</v>
+        <v>1224</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="17" t="s">
-        <v>1216</v>
+        <v>1226</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1217</v>
+        <v>1227</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>1218</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="17" t="s">
-        <v>1219</v>
+        <v>1229</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15960,7 +16090,7 @@
         <v>0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
       <c r="F65" s="17" t="s">
         <v>18</v>
@@ -15969,7 +16099,7 @@
         <v>26</v>
       </c>
       <c r="H65" s="23" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -15980,7 +16110,7 @@
         <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1224</v>
+        <v>1234</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>18</v>
@@ -15989,7 +16119,7 @@
         <v>26</v>
       </c>
       <c r="H66" s="23" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16000,7 +16130,7 @@
         <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>18</v>
@@ -16009,7 +16139,7 @@
         <v>26</v>
       </c>
       <c r="H67" s="23" t="s">
-        <v>1227</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16020,7 +16150,7 @@
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>18</v>
@@ -16029,7 +16159,7 @@
         <v>26</v>
       </c>
       <c r="H68" s="23" t="s">
-        <v>1229</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16040,7 +16170,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="F69" s="17" t="s">
         <v>18</v>
@@ -16049,7 +16179,7 @@
         <v>26</v>
       </c>
       <c r="H69" s="23" t="s">
-        <v>1231</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16060,7 +16190,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1232</v>
+        <v>1242</v>
       </c>
       <c r="F70" s="17" t="s">
         <v>18</v>
@@ -16069,7 +16199,7 @@
         <v>26</v>
       </c>
       <c r="H70" s="23" t="s">
-        <v>1233</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16080,7 +16210,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1234</v>
+        <v>1244</v>
       </c>
       <c r="F71" s="17" t="s">
         <v>18</v>
@@ -16089,7 +16219,7 @@
         <v>26</v>
       </c>
       <c r="H71" s="23" t="s">
-        <v>1235</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16100,7 +16230,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1236</v>
+        <v>1246</v>
       </c>
       <c r="F72" s="17" t="s">
         <v>18</v>
@@ -16109,7 +16239,7 @@
         <v>26</v>
       </c>
       <c r="H72" s="23" t="s">
-        <v>1237</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16120,7 +16250,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1222</v>
+        <v>1232</v>
       </c>
       <c r="F73" s="17" t="s">
         <v>18</v>
@@ -16129,7 +16259,7 @@
         <v>26</v>
       </c>
       <c r="H73" s="23" t="s">
-        <v>1238</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16140,7 +16270,7 @@
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1224</v>
+        <v>1234</v>
       </c>
       <c r="F74" s="17" t="s">
         <v>18</v>
@@ -16149,7 +16279,7 @@
         <v>26</v>
       </c>
       <c r="H74" s="23" t="s">
-        <v>1239</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16160,7 +16290,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>18</v>
@@ -16169,7 +16299,7 @@
         <v>26</v>
       </c>
       <c r="H75" s="23" t="s">
-        <v>1240</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16180,7 +16310,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>18</v>
@@ -16189,7 +16319,7 @@
         <v>26</v>
       </c>
       <c r="H76" s="23" t="s">
-        <v>1241</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16200,7 +16330,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>18</v>
@@ -16209,7 +16339,7 @@
         <v>26</v>
       </c>
       <c r="H77" s="23" t="s">
-        <v>1242</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16220,7 +16350,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1232</v>
+        <v>1242</v>
       </c>
       <c r="F78" s="17" t="s">
         <v>18</v>
@@ -16229,7 +16359,7 @@
         <v>26</v>
       </c>
       <c r="H78" s="23" t="s">
-        <v>1243</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16240,7 +16370,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1234</v>
+        <v>1244</v>
       </c>
       <c r="F79" s="17" t="s">
         <v>18</v>
@@ -16249,7 +16379,7 @@
         <v>26</v>
       </c>
       <c r="H79" s="23" t="s">
-        <v>1244</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16260,7 +16390,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1236</v>
+        <v>1246</v>
       </c>
       <c r="F80" s="17" t="s">
         <v>18</v>
@@ -16269,7 +16399,7 @@
         <v>26</v>
       </c>
       <c r="H80" s="23" t="s">
-        <v>1245</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16290,162 +16420,162 @@
     </row>
     <row r="83" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C83" s="17" t="s">
-        <v>1246</v>
+        <v>1256</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="F83" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="H83" s="23" t="s">
-        <v>1028</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C84" s="17" t="s">
-        <v>1247</v>
+        <v>1257</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="F84" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="H84" s="23" t="s">
-        <v>1031</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:8">
       <c r="C85" s="17" t="s">
-        <v>1248</v>
+        <v>1258</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1249</v>
+        <v>1259</v>
       </c>
       <c r="F85" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="H85" s="21" t="s">
-        <v>1250</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:8">
       <c r="C86" s="17" t="s">
-        <v>1251</v>
+        <v>1261</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1252</v>
+        <v>1262</v>
       </c>
       <c r="F86" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="H86" s="21" t="s">
-        <v>1253</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:8">
       <c r="C87" s="17" t="s">
-        <v>1254</v>
+        <v>1264</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1255</v>
+        <v>1265</v>
       </c>
       <c r="F87" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G87" s="17" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="H87" s="21" t="s">
-        <v>1256</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:8">
       <c r="C88" s="17" t="s">
-        <v>1257</v>
+        <v>1267</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1258</v>
+        <v>1268</v>
       </c>
       <c r="F88" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="H88" s="21" t="s">
-        <v>1259</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:8">
       <c r="C90" s="17" t="s">
-        <v>1260</v>
+        <v>1270</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1261</v>
+        <v>1271</v>
       </c>
       <c r="F90" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G90" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H90" s="21" t="s">
-        <v>1262</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:8">
       <c r="C91" s="17" t="s">
-        <v>1263</v>
+        <v>1273</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1264</v>
+        <v>1274</v>
       </c>
       <c r="F91" s="17" t="s">
         <v>18</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="H91" s="21" t="s">
-        <v>1265</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16458,182 +16588,182 @@
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C93" s="10" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H93" s="17" t="s">
-        <v>1269</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C94" s="10" t="s">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H94" s="17" t="s">
-        <v>1272</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C95" s="10" t="s">
-        <v>1273</v>
+        <v>1283</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1274</v>
+        <v>1284</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H95" s="17" t="s">
-        <v>1275</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C96" s="10" t="s">
-        <v>1276</v>
+        <v>1286</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1277</v>
+        <v>1287</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H96" s="17" t="s">
-        <v>1278</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C97" s="10" t="s">
-        <v>1279</v>
+        <v>1289</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H97" s="17" t="s">
-        <v>1281</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C98" s="10" t="s">
-        <v>1282</v>
+        <v>1292</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1283</v>
+        <v>1293</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H98" s="17" t="s">
-        <v>1284</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C99" s="10" t="s">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H99" s="17" t="s">
-        <v>1287</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C100" s="10" t="s">
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1289</v>
+        <v>1299</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H100" s="23" t="s">
-        <v>1290</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C101" s="10" t="s">
-        <v>1291</v>
+        <v>1301</v>
       </c>
       <c r="D101" s="17" t="s">
         <v>48</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1292</v>
+        <v>1302</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H101" s="23" t="s">
-        <v>1293</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16644,16 +16774,16 @@
         <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1294</v>
+        <v>1304</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="H102" s="23" t="s">
-        <v>1295</v>
+        <v>1305</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -4000,7 +4000,7 @@
     <t>六阶四格</t>
   </si>
   <si>
-    <t>106,205,306,406</t>
+    <t>106,206,306,406</t>
   </si>
   <si>
     <t>501</t>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2450" uniqueCount="1397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2468" uniqueCount="1409">
   <si>
     <t>_id</t>
   </si>
@@ -3947,6 +3947,42 @@
   </si>
   <si>
     <t>粉色宠物</t>
+  </si>
+  <si>
+    <t>220303</t>
+  </si>
+  <si>
+    <t>蓝色坐骑</t>
+  </si>
+  <si>
+    <t>220304</t>
+  </si>
+  <si>
+    <t>紫色坐骑</t>
+  </si>
+  <si>
+    <t>220305</t>
+  </si>
+  <si>
+    <t>橙色坐骑</t>
+  </si>
+  <si>
+    <t>220306</t>
+  </si>
+  <si>
+    <t>红色坐骑</t>
+  </si>
+  <si>
+    <t>220307</t>
+  </si>
+  <si>
+    <t>金色坐骑</t>
+  </si>
+  <si>
+    <t>220308</t>
+  </si>
+  <si>
+    <t>暗金坐骑</t>
   </si>
   <si>
     <t>101</t>
@@ -15000,7 +15036,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H51"/>
+  <dimension ref="C1:H60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -15978,6 +16014,142 @@
       </c>
       <c r="H51" s="1">
         <v>8209</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:8">
+      <c r="C53" s="10"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="3:8">
+      <c r="C54" s="10"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="3:8">
+      <c r="C55" s="19" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F55" s="1">
+        <v>1</v>
+      </c>
+      <c r="G55" s="1">
+        <v>23</v>
+      </c>
+      <c r="H55" s="1">
+        <v>8303</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:8">
+      <c r="C56" s="19" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F56" s="1">
+        <v>1</v>
+      </c>
+      <c r="G56" s="1">
+        <v>23</v>
+      </c>
+      <c r="H56" s="1">
+        <v>8304</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:8">
+      <c r="C57" s="19" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F57" s="1">
+        <v>1</v>
+      </c>
+      <c r="G57" s="1">
+        <v>23</v>
+      </c>
+      <c r="H57" s="1">
+        <v>8305</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:8">
+      <c r="C58" s="19" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F58" s="1">
+        <v>1</v>
+      </c>
+      <c r="G58" s="1">
+        <v>23</v>
+      </c>
+      <c r="H58" s="1">
+        <v>8306</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:8">
+      <c r="C59" s="19" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F59" s="1">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1">
+        <v>23</v>
+      </c>
+      <c r="H59" s="1">
+        <v>8307</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:8">
+      <c r="C60" s="19" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F60" s="1">
+        <v>1</v>
+      </c>
+      <c r="G60" s="1">
+        <v>23</v>
+      </c>
+      <c r="H60" s="1">
+        <v>8308</v>
       </c>
     </row>
   </sheetData>
@@ -16077,13 +16249,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="1" t="s">
-        <v>1178</v>
+        <v>1190</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1179</v>
+        <v>1191</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>17</v>
@@ -16092,18 +16264,18 @@
         <v>18</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>1181</v>
+        <v>1193</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>17</v>
@@ -16112,18 +16284,18 @@
         <v>18</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>1183</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>1184</v>
+        <v>1196</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1185</v>
+        <v>1197</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>17</v>
@@ -16132,18 +16304,18 @@
         <v>18</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>17</v>
@@ -16152,18 +16324,18 @@
         <v>18</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>1189</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>1190</v>
+        <v>1202</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1191</v>
+        <v>1203</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
@@ -16172,18 +16344,18 @@
         <v>18</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>1192</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>1193</v>
+        <v>1205</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1194</v>
+        <v>1206</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>17</v>
@@ -16192,18 +16364,18 @@
         <v>18</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>1195</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>1196</v>
+        <v>1208</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1197</v>
+        <v>1209</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>17</v>
@@ -16212,18 +16384,18 @@
         <v>15</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>1198</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1197</v>
+        <v>1209</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>17</v>
@@ -16232,18 +16404,18 @@
         <v>15</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>1200</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>1201</v>
+        <v>1213</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1197</v>
+        <v>1209</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>17</v>
@@ -16252,18 +16424,18 @@
         <v>15</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>1202</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1197</v>
+        <v>1209</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>17</v>
@@ -16272,18 +16444,18 @@
         <v>15</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>17</v>
@@ -16292,18 +16464,18 @@
         <v>15</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>1207</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>1208</v>
+        <v>1220</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1209</v>
+        <v>1221</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>17</v>
@@ -16312,18 +16484,18 @@
         <v>15</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>1211</v>
+        <v>1223</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>17</v>
@@ -16332,7 +16504,7 @@
         <v>15</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>1213</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16351,7 +16523,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1214</v>
+        <v>1226</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -16360,7 +16532,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>1215</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16379,121 +16551,121 @@
         <v>1115</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1216</v>
+        <v>1228</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>1219</v>
+        <v>1231</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1220</v>
+        <v>1232</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>1221</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1223</v>
+        <v>1235</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>21</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>1221</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>1224</v>
+        <v>1236</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1225</v>
+        <v>1237</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>1226</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>1227</v>
+        <v>1239</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1228</v>
+        <v>1240</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>1229</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>1230</v>
+        <v>1242</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1231</v>
+        <v>1243</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>1232</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>1115</v>
@@ -16513,62 +16685,62 @@
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>1234</v>
+        <v>1246</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1235</v>
+        <v>1247</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>1237</v>
+        <v>1249</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1238</v>
+        <v>1250</v>
       </c>
       <c r="F30" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>1239</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1240</v>
+        <v>1252</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1241</v>
+        <v>1253</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>1242</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16579,16 +16751,16 @@
         <v>1115</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1243</v>
+        <v>1255</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16599,156 +16771,156 @@
         <v>1115</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1245</v>
+        <v>1257</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>1246</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1248</v>
+        <v>1260</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>1249</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1250</v>
+        <v>1262</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1251</v>
+        <v>1263</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>1252</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1253</v>
+        <v>1265</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1254</v>
+        <v>1266</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>1255</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1256</v>
+        <v>1268</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1257</v>
+        <v>1269</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>1258</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1259</v>
+        <v>1271</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1260</v>
+        <v>1272</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>1261</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1262</v>
+        <v>1274</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1263</v>
+        <v>1275</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>1264</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>1265</v>
+        <v>1277</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1266</v>
+        <v>1278</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>1267</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16769,7 +16941,7 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C43" s="18" t="s">
-        <v>1268</v>
+        <v>1280</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>1115</v>
@@ -16789,7 +16961,7 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1269</v>
+        <v>1281</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1115</v>
@@ -16809,13 +16981,13 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1270</v>
+        <v>1282</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1271</v>
+        <v>1283</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>17</v>
@@ -16824,12 +16996,12 @@
         <v>1117</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>1272</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1273</v>
+        <v>1285</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1115</v>
@@ -16849,13 +17021,13 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1274</v>
+        <v>1286</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1275</v>
+        <v>1287</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>17</v>
@@ -16864,18 +17036,18 @@
         <v>1117</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>1276</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1277</v>
+        <v>1289</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1278</v>
+        <v>1290</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>17</v>
@@ -16884,18 +17056,18 @@
         <v>1117</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>1279</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1280</v>
+        <v>1292</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1281</v>
+        <v>1293</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>17</v>
@@ -16904,18 +17076,18 @@
         <v>1117</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>1282</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1283</v>
+        <v>1295</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1284</v>
+        <v>1296</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>17</v>
@@ -16924,7 +17096,7 @@
         <v>1117</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>1285</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16935,7 +17107,7 @@
         <v>1115</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1286</v>
+        <v>1298</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>17</v>
@@ -16944,7 +17116,7 @@
         <v>1117</v>
       </c>
       <c r="H51" s="25" t="s">
-        <v>1287</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16955,7 +17127,7 @@
         <v>1115</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1288</v>
+        <v>1300</v>
       </c>
       <c r="F52" s="18" t="s">
         <v>17</v>
@@ -16964,18 +17136,18 @@
         <v>1117</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>1289</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1290</v>
+        <v>1302</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1291</v>
+        <v>1303</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>17</v>
@@ -16984,18 +17156,18 @@
         <v>1117</v>
       </c>
       <c r="H53" s="25" t="s">
-        <v>1292</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>1293</v>
+        <v>1305</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1294</v>
+        <v>1306</v>
       </c>
       <c r="F54" s="18" t="s">
         <v>17</v>
@@ -17004,18 +17176,18 @@
         <v>1117</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>1295</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>1296</v>
+        <v>1308</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1297</v>
+        <v>1309</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>17</v>
@@ -17024,18 +17196,18 @@
         <v>1117</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>1298</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1299</v>
+        <v>1311</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1300</v>
+        <v>1312</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>17</v>
@@ -17044,18 +17216,18 @@
         <v>1117</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>1301</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>1302</v>
+        <v>1314</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1303</v>
+        <v>1315</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>17</v>
@@ -17064,18 +17236,18 @@
         <v>1117</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>1304</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>1305</v>
+        <v>1317</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1306</v>
+        <v>1318</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>17</v>
@@ -17084,18 +17256,18 @@
         <v>1117</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>1307</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>1308</v>
+        <v>1320</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1309</v>
+        <v>1321</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>17</v>
@@ -17104,18 +17276,18 @@
         <v>1117</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>1310</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>1311</v>
+        <v>1323</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1312</v>
+        <v>1324</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>17</v>
@@ -17124,18 +17296,18 @@
         <v>1117</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>1313</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>1314</v>
+        <v>1326</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1315</v>
+        <v>1327</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>17</v>
@@ -17144,18 +17316,18 @@
         <v>1117</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>1316</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>1317</v>
+        <v>1329</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1318</v>
+        <v>1330</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>17</v>
@@ -17164,18 +17336,18 @@
         <v>1117</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>1319</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>1320</v>
+        <v>1332</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1321</v>
+        <v>1333</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>17</v>
@@ -17184,7 +17356,7 @@
         <v>1117</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>1322</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17203,7 +17375,7 @@
         <v>0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1323</v>
+        <v>1335</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>17</v>
@@ -17212,7 +17384,7 @@
         <v>25</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>1324</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17223,7 +17395,7 @@
         <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1325</v>
+        <v>1337</v>
       </c>
       <c r="F66" s="18" t="s">
         <v>17</v>
@@ -17232,7 +17404,7 @@
         <v>25</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>1326</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17243,7 +17415,7 @@
         <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1327</v>
+        <v>1339</v>
       </c>
       <c r="F67" s="18" t="s">
         <v>17</v>
@@ -17252,7 +17424,7 @@
         <v>25</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>1328</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17263,7 +17435,7 @@
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1329</v>
+        <v>1341</v>
       </c>
       <c r="F68" s="18" t="s">
         <v>17</v>
@@ -17272,7 +17444,7 @@
         <v>25</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>1330</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17283,7 +17455,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1331</v>
+        <v>1343</v>
       </c>
       <c r="F69" s="18" t="s">
         <v>17</v>
@@ -17292,7 +17464,7 @@
         <v>25</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>1332</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17303,7 +17475,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1333</v>
+        <v>1345</v>
       </c>
       <c r="F70" s="18" t="s">
         <v>17</v>
@@ -17312,7 +17484,7 @@
         <v>25</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>1334</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17323,7 +17495,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1335</v>
+        <v>1347</v>
       </c>
       <c r="F71" s="18" t="s">
         <v>17</v>
@@ -17332,7 +17504,7 @@
         <v>25</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>1336</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17343,7 +17515,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1337</v>
+        <v>1349</v>
       </c>
       <c r="F72" s="18" t="s">
         <v>17</v>
@@ -17352,7 +17524,7 @@
         <v>25</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>1338</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17363,7 +17535,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1323</v>
+        <v>1335</v>
       </c>
       <c r="F73" s="18" t="s">
         <v>17</v>
@@ -17372,7 +17544,7 @@
         <v>25</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>1339</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17383,7 +17555,7 @@
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1325</v>
+        <v>1337</v>
       </c>
       <c r="F74" s="18" t="s">
         <v>17</v>
@@ -17392,7 +17564,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>1340</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17403,7 +17575,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1327</v>
+        <v>1339</v>
       </c>
       <c r="F75" s="18" t="s">
         <v>17</v>
@@ -17412,7 +17584,7 @@
         <v>25</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>1341</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17423,7 +17595,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1329</v>
+        <v>1341</v>
       </c>
       <c r="F76" s="18" t="s">
         <v>17</v>
@@ -17432,7 +17604,7 @@
         <v>25</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>1342</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17443,7 +17615,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1331</v>
+        <v>1343</v>
       </c>
       <c r="F77" s="18" t="s">
         <v>17</v>
@@ -17452,7 +17624,7 @@
         <v>25</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>1343</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17463,7 +17635,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1333</v>
+        <v>1345</v>
       </c>
       <c r="F78" s="18" t="s">
         <v>17</v>
@@ -17472,7 +17644,7 @@
         <v>25</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>1344</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17483,7 +17655,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1335</v>
+        <v>1347</v>
       </c>
       <c r="F79" s="18" t="s">
         <v>17</v>
@@ -17492,7 +17664,7 @@
         <v>25</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>1345</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17503,7 +17675,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1337</v>
+        <v>1349</v>
       </c>
       <c r="F80" s="18" t="s">
         <v>17</v>
@@ -17512,7 +17684,7 @@
         <v>25</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>1346</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17533,7 +17705,7 @@
     </row>
     <row r="83" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C83" s="18" t="s">
-        <v>1347</v>
+        <v>1359</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>1115</v>
@@ -17553,7 +17725,7 @@
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C84" s="18" t="s">
-        <v>1348</v>
+        <v>1360</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>1115</v>
@@ -17573,13 +17745,13 @@
     </row>
     <row r="85" customHeight="1" spans="3:8">
       <c r="C85" s="18" t="s">
-        <v>1349</v>
+        <v>1361</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1350</v>
+        <v>1362</v>
       </c>
       <c r="F85" s="18" t="s">
         <v>17</v>
@@ -17588,18 +17760,18 @@
         <v>1127</v>
       </c>
       <c r="H85" s="22" t="s">
-        <v>1351</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:8">
       <c r="C86" s="18" t="s">
-        <v>1352</v>
+        <v>1364</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1353</v>
+        <v>1365</v>
       </c>
       <c r="F86" s="18" t="s">
         <v>17</v>
@@ -17608,18 +17780,18 @@
         <v>1127</v>
       </c>
       <c r="H86" s="22" t="s">
-        <v>1354</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:8">
       <c r="C87" s="18" t="s">
-        <v>1355</v>
+        <v>1367</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1356</v>
+        <v>1368</v>
       </c>
       <c r="F87" s="18" t="s">
         <v>17</v>
@@ -17628,18 +17800,18 @@
         <v>1127</v>
       </c>
       <c r="H87" s="22" t="s">
-        <v>1357</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:8">
       <c r="C88" s="18" t="s">
-        <v>1358</v>
+        <v>1370</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1359</v>
+        <v>1371</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>17</v>
@@ -17648,47 +17820,47 @@
         <v>1127</v>
       </c>
       <c r="H88" s="22" t="s">
-        <v>1360</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:8">
       <c r="C90" s="18" t="s">
-        <v>1361</v>
+        <v>1373</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1362</v>
+        <v>1374</v>
       </c>
       <c r="F90" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H90" s="22" t="s">
-        <v>1363</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:8">
       <c r="C91" s="18" t="s">
-        <v>1364</v>
+        <v>1376</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F91" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="H91" s="22" t="s">
-        <v>1366</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17701,182 +17873,182 @@
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C93" s="10" t="s">
-        <v>1367</v>
+        <v>1379</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1368</v>
+        <v>1380</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="H93" s="18" t="s">
-        <v>1370</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C94" s="10" t="s">
-        <v>1371</v>
+        <v>1383</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1372</v>
+        <v>1384</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="H94" s="18" t="s">
-        <v>1373</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C95" s="10" t="s">
-        <v>1374</v>
+        <v>1386</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1375</v>
+        <v>1387</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="H95" s="18" t="s">
-        <v>1376</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C96" s="10" t="s">
-        <v>1377</v>
+        <v>1389</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>1379</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C97" s="10" t="s">
-        <v>1380</v>
+        <v>1392</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G97" s="1" t="s">
         <v>1381</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>1369</v>
-      </c>
       <c r="H97" s="18" t="s">
-        <v>1382</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C98" s="10" t="s">
-        <v>1383</v>
+        <v>1395</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1384</v>
+        <v>1396</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>1385</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C99" s="10" t="s">
-        <v>1386</v>
+        <v>1398</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="H99" s="18" t="s">
-        <v>1388</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C100" s="10" t="s">
-        <v>1389</v>
+        <v>1401</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1390</v>
+        <v>1402</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>1391</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C101" s="10" t="s">
-        <v>1392</v>
+        <v>1404</v>
       </c>
       <c r="D101" s="18" t="s">
         <v>47</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1393</v>
+        <v>1405</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="H101" s="24" t="s">
-        <v>1394</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -17887,16 +18059,16 @@
         <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1395</v>
+        <v>1407</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1369</v>
+        <v>1381</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>1396</v>
+        <v>1408</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -16018,18 +16018,12 @@
     </row>
     <row r="53" customHeight="1" spans="3:8">
       <c r="C53" s="10"/>
-      <c r="D53" s="1"/>
       <c r="E53" s="12"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
       <c r="H53" s="1"/>
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="10"/>
-      <c r="D54" s="1"/>
       <c r="E54" s="12"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
       <c r="H54" s="1"/>
     </row>
     <row r="55" customHeight="1" spans="3:8">
@@ -16046,7 +16040,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="1">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H55" s="1">
         <v>8303</v>
@@ -16066,7 +16060,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="1">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H56" s="1">
         <v>8304</v>
@@ -16086,7 +16080,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="1">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H57" s="1">
         <v>8305</v>
@@ -16106,7 +16100,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="1">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H58" s="1">
         <v>8306</v>
@@ -16126,7 +16120,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="1">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H59" s="1">
         <v>8307</v>
@@ -16146,7 +16140,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="1">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H60" s="1">
         <v>8308</v>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2468" uniqueCount="1409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="1411">
   <si>
     <t>_id</t>
   </si>
@@ -4097,6 +4097,12 @@
   </si>
   <si>
     <t>60000001,60000002,60000003,60000004,60000005,60000006,60000007,60000008,60000009,60000010</t>
+  </si>
+  <si>
+    <t>极宝石随机</t>
+  </si>
+  <si>
+    <t>60000011,60000012,60000013,60000014,60000015,60000016,60000017,60000018,60000019,60000020,60000021,60000022,60000023</t>
   </si>
   <si>
     <t>特殊图鉴碎片</t>
@@ -16161,7 +16167,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H102"/>
+  <dimension ref="C1:H103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -16530,71 +16536,71 @@
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C22" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="C21" s="1">
+        <v>602</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="F22" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="18" t="s">
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>5</v>
+      </c>
+      <c r="H21" s="22" t="s">
         <v>1229</v>
       </c>
-      <c r="H22" s="24" t="s">
-        <v>1230</v>
-      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="3"/>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="18" t="s">
-        <v>1231</v>
+        <v>305</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H23" s="24" t="s">
         <v>1232</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H24" s="24" t="s">
         <v>1235</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H24" s="24" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16608,138 +16614,138 @@
         <v>1237</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H26" s="24" t="s">
         <v>1240</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H27" s="24" t="s">
         <v>1243</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H27" s="24" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1146</v>
+        <v>1245</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>1147</v>
+        <v>1231</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>1148</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1247</v>
+        <v>1146</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>1229</v>
+        <v>1147</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>1248</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H30" s="24" t="s">
         <v>1250</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H30" s="24" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H31" s="24" t="s">
         <v>1253</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H31" s="24" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>309</v>
+        <v>1254</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1115</v>
@@ -16751,7 +16757,7 @@
         <v>17</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="H32" s="24" t="s">
         <v>1256</v>
@@ -16759,7 +16765,7 @@
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C33" s="18" t="s">
-        <v>1134</v>
+        <v>309</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>1115</v>
@@ -16771,7 +16777,7 @@
         <v>17</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="H33" s="24" t="s">
         <v>1258</v>
@@ -16779,151 +16785,163 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1259</v>
+        <v>1134</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H34" s="24" t="s">
         <v>1260</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H35" s="18" t="s">
         <v>1263</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H36" s="18" t="s">
         <v>1266</v>
       </c>
-      <c r="F36" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H36" s="18" t="s">
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C37" s="18" t="s">
         <v>1267</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C37" s="18" t="s">
-        <v>1268</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H37" s="18" t="s">
         <v>1269</v>
-      </c>
-      <c r="F37" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H37" s="18" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E38" s="8" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H38" s="18" t="s">
         <v>1272</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E39" s="8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H39" s="18" t="s">
         <v>1275</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H39" s="18" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E40" s="8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H40" s="18" t="s">
         <v>1278</v>
       </c>
-      <c r="F40" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H40" s="3" t="s">
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C41" s="18" t="s">
         <v>1279</v>
       </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="3"/>
+      <c r="D41" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>1281</v>
+      </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="1"/>
@@ -16933,35 +16951,23 @@
       <c r="G42" s="1"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C43" s="18" t="s">
-        <v>1280</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>1120</v>
-      </c>
-      <c r="F43" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>1117</v>
-      </c>
-      <c r="H43" s="24" t="s">
-        <v>1121</v>
-      </c>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="3"/>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>17</v>
@@ -16970,18 +16976,18 @@
         <v>1117</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C45" s="18" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1283</v>
+        <v>1116</v>
       </c>
       <c r="F45" s="18" t="s">
         <v>17</v>
@@ -16990,18 +16996,18 @@
         <v>1117</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>1284</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1123</v>
+        <v>1285</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>17</v>
@@ -17010,18 +17016,18 @@
         <v>1117</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>1124</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1287</v>
+        <v>1123</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>17</v>
@@ -17030,18 +17036,18 @@
         <v>1117</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>1288</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>17</v>
@@ -17050,18 +17056,18 @@
         <v>1117</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>17</v>
@@ -17070,18 +17076,18 @@
         <v>1117</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>17</v>
@@ -17090,12 +17096,12 @@
         <v>1117</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>1102</v>
+        <v>1297</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>1115</v>
@@ -17109,13 +17115,13 @@
       <c r="G51" s="18" t="s">
         <v>1117</v>
       </c>
-      <c r="H51" s="25" t="s">
+      <c r="H51" s="24" t="s">
         <v>1299</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>1137</v>
+        <v>1102</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>1115</v>
@@ -17129,19 +17135,19 @@
       <c r="G52" s="18" t="s">
         <v>1117</v>
       </c>
-      <c r="H52" s="22" t="s">
+      <c r="H52" s="25" t="s">
         <v>1301</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1302</v>
+        <v>1137</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>17</v>
@@ -17149,19 +17155,19 @@
       <c r="G53" s="18" t="s">
         <v>1117</v>
       </c>
-      <c r="H53" s="25" t="s">
-        <v>1304</v>
+      <c r="H53" s="22" t="s">
+        <v>1303</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F54" s="18" t="s">
         <v>17</v>
@@ -17169,19 +17175,19 @@
       <c r="G54" s="18" t="s">
         <v>1117</v>
       </c>
-      <c r="H54" s="22" t="s">
-        <v>1307</v>
+      <c r="H54" s="25" t="s">
+        <v>1306</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>17</v>
@@ -17189,19 +17195,19 @@
       <c r="G55" s="18" t="s">
         <v>1117</v>
       </c>
-      <c r="H55" s="24" t="s">
-        <v>1310</v>
+      <c r="H55" s="22" t="s">
+        <v>1309</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>17</v>
@@ -17210,18 +17216,18 @@
         <v>1117</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>17</v>
@@ -17230,18 +17236,18 @@
         <v>1117</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>17</v>
@@ -17250,18 +17256,18 @@
         <v>1117</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>17</v>
@@ -17270,18 +17276,18 @@
         <v>1117</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>17</v>
@@ -17290,18 +17296,18 @@
         <v>1117</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>17</v>
@@ -17310,18 +17316,18 @@
         <v>1117</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>17</v>
@@ -17330,18 +17336,18 @@
         <v>1117</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>17</v>
@@ -17350,40 +17356,40 @@
         <v>1117</v>
       </c>
       <c r="H63" s="24" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C64" s="18" t="s">
         <v>1334</v>
       </c>
-    </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="3"/>
+      <c r="D64" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G64" s="18" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H64" s="24" t="s">
+        <v>1336</v>
+      </c>
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C65" s="1">
-        <v>2031</v>
-      </c>
-      <c r="D65" s="1">
-        <v>0</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>1335</v>
-      </c>
-      <c r="F65" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G65" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H65" s="24" t="s">
-        <v>1336</v>
-      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="3"/>
     </row>
     <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="1">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
@@ -17403,7 +17409,7 @@
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C67" s="1">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
@@ -17423,7 +17429,7 @@
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C68" s="1">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
@@ -17443,7 +17449,7 @@
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C69" s="1">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
@@ -17463,7 +17469,7 @@
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C70" s="1">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
@@ -17483,7 +17489,7 @@
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C71" s="1">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
@@ -17503,7 +17509,7 @@
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C72" s="1">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
@@ -17523,13 +17529,13 @@
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C73" s="1">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1335</v>
+        <v>1351</v>
       </c>
       <c r="F73" s="18" t="s">
         <v>17</v>
@@ -17538,12 +17544,12 @@
         <v>25</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C74" s="1">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
@@ -17558,12 +17564,12 @@
         <v>25</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C75" s="1">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
@@ -17578,12 +17584,12 @@
         <v>25</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C76" s="1">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
@@ -17598,12 +17604,12 @@
         <v>25</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C77" s="1">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
@@ -17618,12 +17624,12 @@
         <v>25</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C78" s="1">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
@@ -17638,12 +17644,12 @@
         <v>25</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C79" s="1">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
@@ -17658,12 +17664,12 @@
         <v>25</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C80" s="1">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
@@ -17678,16 +17684,28 @@
         <v>25</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="3"/>
+      <c r="C81" s="1">
+        <v>2046</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H81" s="24" t="s">
+        <v>1360</v>
+      </c>
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C82" s="1"/>
@@ -17697,35 +17715,23 @@
       <c r="G82" s="1"/>
       <c r="H82" s="3"/>
     </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C83" s="18" t="s">
-        <v>1359</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>1126</v>
-      </c>
-      <c r="F83" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G83" s="18" t="s">
-        <v>1127</v>
-      </c>
-      <c r="H83" s="24" t="s">
-        <v>1128</v>
-      </c>
+    <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="3"/>
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C84" s="18" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="F84" s="18" t="s">
         <v>17</v>
@@ -17734,18 +17740,18 @@
         <v>1127</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="3:8">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C85" s="18" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1362</v>
+        <v>1130</v>
       </c>
       <c r="F85" s="18" t="s">
         <v>17</v>
@@ -17753,19 +17759,19 @@
       <c r="G85" s="18" t="s">
         <v>1127</v>
       </c>
-      <c r="H85" s="22" t="s">
-        <v>1363</v>
+      <c r="H85" s="24" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:8">
       <c r="C86" s="18" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="F86" s="18" t="s">
         <v>17</v>
@@ -17774,18 +17780,18 @@
         <v>1127</v>
       </c>
       <c r="H86" s="22" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:8">
       <c r="C87" s="18" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="F87" s="18" t="s">
         <v>17</v>
@@ -17794,18 +17800,18 @@
         <v>1127</v>
       </c>
       <c r="H87" s="22" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:8">
       <c r="C88" s="18" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>17</v>
@@ -17814,243 +17820,243 @@
         <v>1127</v>
       </c>
       <c r="H88" s="22" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:8">
+      <c r="C89" s="18" t="s">
         <v>1372</v>
       </c>
-    </row>
-    <row r="90" customHeight="1" spans="3:8">
-      <c r="C90" s="18" t="s">
+      <c r="D89" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>1373</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E90" s="1" t="s">
+      <c r="F89" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" s="18" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H89" s="22" t="s">
         <v>1374</v>
-      </c>
-      <c r="F90" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G90" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H90" s="22" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:8">
       <c r="C91" s="18" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E91" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F91" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H91" s="22" t="s">
         <v>1377</v>
       </c>
-      <c r="F91" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G91" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="H91" s="22" t="s">
+    </row>
+    <row r="92" customHeight="1" spans="3:8">
+      <c r="C92" s="18" t="s">
         <v>1378</v>
       </c>
-    </row>
-    <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="3"/>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C93" s="10" t="s">
+      <c r="D92" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E93" s="1" t="s">
+      <c r="F92" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G92" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H92" s="22" t="s">
         <v>1380</v>
       </c>
-      <c r="F93" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="H93" s="18" t="s">
-        <v>1382</v>
-      </c>
+    </row>
+    <row r="93" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="3"/>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C94" s="10" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>1383</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E94" s="1" t="s">
+      <c r="H94" s="18" t="s">
         <v>1384</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="H94" s="18" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C95" s="10" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E95" s="1" t="s">
+      <c r="F95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H95" s="18" t="s">
         <v>1387</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="H95" s="18" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C96" s="10" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>1389</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E96" s="1" t="s">
+      <c r="F96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H96" s="18" t="s">
         <v>1390</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="H96" s="18" t="s">
-        <v>1391</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C97" s="10" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E97" s="1" t="s">
+      <c r="F97" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H97" s="18" t="s">
         <v>1393</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="H97" s="18" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C98" s="10" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E98" s="1" t="s">
+      <c r="F98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H98" s="18" t="s">
         <v>1396</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="H98" s="18" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C99" s="10" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E99" s="1" t="s">
+      <c r="F99" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H99" s="18" t="s">
         <v>1399</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="H99" s="18" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C100" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>1401</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E100" s="1" t="s">
+      <c r="F100" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H100" s="18" t="s">
         <v>1402</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="H100" s="24" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C101" s="10" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="D101" s="18" t="s">
+      <c r="F101" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H101" s="24" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C102" s="10" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D102" s="18" t="s">
         <v>47</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>1405</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="H101" s="24" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C102" s="10">
-        <v>300091</v>
-      </c>
-      <c r="D102" s="1">
-        <v>100</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>1407</v>
@@ -18059,10 +18065,30 @@
         <v>17</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="H102" s="24" t="s">
         <v>1408</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C103" s="10">
+        <v>300091</v>
+      </c>
+      <c r="D103" s="1">
+        <v>100</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H103" s="24" t="s">
+        <v>1410</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="1411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="1435">
   <si>
     <t>_id</t>
   </si>
@@ -4474,28 +4474,100 @@
     <t>2100001,2100002,2100003</t>
   </si>
   <si>
+    <t>绿色英灵-吴国</t>
+  </si>
+  <si>
     <t>2100049,2100050,2100051,2100052,2100053,2100054</t>
   </si>
   <si>
+    <t>蓝色英灵-吴国</t>
+  </si>
+  <si>
     <t>2100046,2100047,2100048</t>
   </si>
   <si>
+    <t>紫色英灵-吴国</t>
+  </si>
+  <si>
     <t>2100043,2100044,2100045</t>
   </si>
   <si>
+    <t>橙色英灵-吴国</t>
+  </si>
+  <si>
     <t>2100040,2100041,2100042</t>
   </si>
   <si>
+    <t>红色英灵-吴国</t>
+  </si>
+  <si>
     <t>2100037,2100038,2100039</t>
   </si>
   <si>
+    <t>金色英灵-吴国</t>
+  </si>
+  <si>
     <t>2100034,2100035,2100036</t>
   </si>
   <si>
+    <t>暗金英灵-吴国</t>
+  </si>
+  <si>
     <t>2100031,2100032,2100033</t>
   </si>
   <si>
+    <t>粉色英灵-吴国</t>
+  </si>
+  <si>
     <t>2100028,2100029,2100030</t>
+  </si>
+  <si>
+    <t>绿色英灵-魏国</t>
+  </si>
+  <si>
+    <t>2100076,2100077,2100078,2100079,2100080,2100081</t>
+  </si>
+  <si>
+    <t>蓝色英灵-魏国</t>
+  </si>
+  <si>
+    <t>2100073,2100074,2100075</t>
+  </si>
+  <si>
+    <t>紫色英灵-魏国</t>
+  </si>
+  <si>
+    <t>2100070,2100071,2100072</t>
+  </si>
+  <si>
+    <t>橙色英灵-魏国</t>
+  </si>
+  <si>
+    <t>2100067,2100068,2100069</t>
+  </si>
+  <si>
+    <t>红色英灵-魏国</t>
+  </si>
+  <si>
+    <t>2100064,2100065,2100066</t>
+  </si>
+  <si>
+    <t>金色英灵-魏国</t>
+  </si>
+  <si>
+    <t>2100061,2100062,2100063</t>
+  </si>
+  <si>
+    <t>暗金英灵-魏国</t>
+  </si>
+  <si>
+    <t>2100058,2100059,2100060</t>
+  </si>
+  <si>
+    <t>粉色英灵-魏国</t>
+  </si>
+  <si>
+    <t>2100055,2100056,2100057</t>
   </si>
   <si>
     <t>3001</t>
@@ -16167,7 +16239,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H103"/>
+  <dimension ref="C1:H110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -17555,7 +17627,7 @@
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1337</v>
+        <v>1353</v>
       </c>
       <c r="F74" s="18" t="s">
         <v>17</v>
@@ -17564,7 +17636,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17575,7 +17647,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1339</v>
+        <v>1355</v>
       </c>
       <c r="F75" s="18" t="s">
         <v>17</v>
@@ -17584,7 +17656,7 @@
         <v>25</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17595,7 +17667,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1341</v>
+        <v>1357</v>
       </c>
       <c r="F76" s="18" t="s">
         <v>17</v>
@@ -17604,7 +17676,7 @@
         <v>25</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17615,7 +17687,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1343</v>
+        <v>1359</v>
       </c>
       <c r="F77" s="18" t="s">
         <v>17</v>
@@ -17624,7 +17696,7 @@
         <v>25</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17635,7 +17707,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1345</v>
+        <v>1361</v>
       </c>
       <c r="F78" s="18" t="s">
         <v>17</v>
@@ -17644,7 +17716,7 @@
         <v>25</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17655,7 +17727,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1347</v>
+        <v>1363</v>
       </c>
       <c r="F79" s="18" t="s">
         <v>17</v>
@@ -17664,7 +17736,7 @@
         <v>25</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17675,7 +17747,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1349</v>
+        <v>1365</v>
       </c>
       <c r="F80" s="18" t="s">
         <v>17</v>
@@ -17684,7 +17756,7 @@
         <v>25</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>1359</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17695,7 +17767,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1351</v>
+        <v>1367</v>
       </c>
       <c r="F81" s="18" t="s">
         <v>17</v>
@@ -17704,391 +17776,543 @@
         <v>25</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="3"/>
+      <c r="C82" s="1">
+        <v>2047</v>
+      </c>
+      <c r="D82" s="1">
+        <v>0</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G82" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H82" s="24" t="s">
+        <v>1370</v>
+      </c>
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="3"/>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C84" s="18" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>1115</v>
+      <c r="C83" s="1">
+        <v>2048</v>
+      </c>
+      <c r="D83" s="1">
+        <v>0</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H83" s="24" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C84" s="1">
+        <v>2049</v>
+      </c>
+      <c r="D84" s="1">
+        <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1126</v>
+        <v>1373</v>
       </c>
       <c r="F84" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>1127</v>
+        <v>25</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C85" s="18" t="s">
-        <v>1362</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>1115</v>
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="85" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C85" s="1">
+        <v>2050</v>
+      </c>
+      <c r="D85" s="1">
+        <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1130</v>
+        <v>1375</v>
       </c>
       <c r="F85" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G85" s="18" t="s">
-        <v>1127</v>
+        <v>25</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="3:8">
-      <c r="C86" s="18" t="s">
-        <v>1363</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>1115</v>
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="86" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C86" s="1">
+        <v>2051</v>
+      </c>
+      <c r="D86" s="1">
+        <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1364</v>
+        <v>1377</v>
       </c>
       <c r="F86" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>1127</v>
-      </c>
-      <c r="H86" s="22" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="3:8">
-      <c r="C87" s="18" t="s">
-        <v>1366</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>1115</v>
+        <v>25</v>
+      </c>
+      <c r="H86" s="24" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="87" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C87" s="1">
+        <v>2052</v>
+      </c>
+      <c r="D87" s="1">
+        <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1367</v>
+        <v>1379</v>
       </c>
       <c r="F87" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>1127</v>
-      </c>
-      <c r="H87" s="22" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="3:8">
-      <c r="C88" s="18" t="s">
-        <v>1369</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>1115</v>
+        <v>25</v>
+      </c>
+      <c r="H87" s="24" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C88" s="1">
+        <v>2053</v>
+      </c>
+      <c r="D88" s="1">
+        <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1370</v>
+        <v>1381</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>1127</v>
-      </c>
-      <c r="H88" s="22" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" spans="3:8">
-      <c r="C89" s="18" t="s">
-        <v>1372</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>1115</v>
+        <v>25</v>
+      </c>
+      <c r="H88" s="24" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="89" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C89" s="1">
+        <v>2054</v>
+      </c>
+      <c r="D89" s="1">
+        <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1373</v>
+        <v>1383</v>
       </c>
       <c r="F89" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G89" s="18" t="s">
-        <v>1127</v>
-      </c>
-      <c r="H89" s="22" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="3:8">
+        <v>25</v>
+      </c>
+      <c r="H89" s="24" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="90" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C91" s="18" t="s">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1376</v>
+        <v>1126</v>
       </c>
       <c r="F91" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>1231</v>
-      </c>
-      <c r="H91" s="22" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" spans="3:8">
+        <v>1127</v>
+      </c>
+      <c r="H91" s="24" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C92" s="18" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1379</v>
+        <v>1130</v>
       </c>
       <c r="F92" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G92" s="18" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H92" s="24" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:8">
+      <c r="C93" s="18" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F93" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G93" s="18" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H93" s="22" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:8">
+      <c r="C94" s="18" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F94" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="18" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H94" s="22" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:8">
+      <c r="C95" s="18" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F95" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G95" s="18" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H95" s="22" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:8">
+      <c r="C96" s="18" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="18" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H96" s="22" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:8">
+      <c r="C98" s="18" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" s="18" t="s">
         <v>1231</v>
       </c>
-      <c r="H92" s="22" t="s">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="93" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="3"/>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C94" s="10" t="s">
-        <v>1381</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>1382</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H94" s="18" t="s">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C95" s="10" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>1386</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H95" s="18" t="s">
-        <v>1387</v>
-      </c>
-    </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C96" s="10" t="s">
-        <v>1388</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>1389</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H96" s="18" t="s">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C97" s="10" t="s">
-        <v>1391</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>1392</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H97" s="18" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C98" s="10" t="s">
-        <v>1394</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>1395</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H98" s="18" t="s">
-        <v>1396</v>
-      </c>
-    </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C99" s="10" t="s">
-        <v>1397</v>
+      <c r="H98" s="22" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:8">
+      <c r="C99" s="18" t="s">
+        <v>1402</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>37</v>
+        <v>1115</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>1398</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H99" s="18" t="s">
-        <v>1399</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C100" s="10" t="s">
-        <v>1400</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>1401</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H100" s="18" t="s">
-        <v>1402</v>
-      </c>
+        <v>1403</v>
+      </c>
+      <c r="F99" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H99" s="22" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="3"/>
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C101" s="10" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H101" s="24" t="s">
-        <v>1405</v>
+        <v>1407</v>
+      </c>
+      <c r="H101" s="18" t="s">
+        <v>1408</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C102" s="10" t="s">
-        <v>1406</v>
-      </c>
-      <c r="D102" s="18" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H102" s="18" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C103" s="10" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H103" s="18" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C104" s="10" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H104" s="18" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C105" s="10" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H105" s="18" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C106" s="10" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H106" s="18" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C107" s="10" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H107" s="18" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C108" s="10" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H108" s="24" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C109" s="10" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D109" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E109" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G109" s="1" t="s">
         <v>1407</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H102" s="24" t="s">
-        <v>1408</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C103" s="10">
+      <c r="H109" s="24" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C110" s="10">
         <v>300091</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D110" s="1">
         <v>100</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>1409</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>1383</v>
-      </c>
-      <c r="H103" s="24" t="s">
-        <v>1410</v>
+      <c r="E110" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H110" s="24" t="s">
+        <v>1434</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="1435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="1443">
   <si>
     <t>_id</t>
   </si>
@@ -4259,6 +4259,30 @@
   </si>
   <si>
     <t>4038</t>
+  </si>
+  <si>
+    <t>1019</t>
+  </si>
+  <si>
+    <t>虚无精华</t>
+  </si>
+  <si>
+    <t>4046</t>
+  </si>
+  <si>
+    <t>兽粮</t>
+  </si>
+  <si>
+    <t>4051</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>红色魂心</t>
+  </si>
+  <si>
+    <t>4024</t>
   </si>
   <si>
     <t>2000</t>
@@ -16239,7 +16263,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H110"/>
+  <dimension ref="C1:H112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -17016,70 +17040,82 @@
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="3"/>
+      <c r="C42" s="18" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>1284</v>
+      </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C43" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H43" s="24" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1120</v>
+        <v>1288</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>1117</v>
+        <v>1231</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C45" s="18" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F45" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G45" s="18" t="s">
-        <v>1117</v>
-      </c>
-      <c r="H45" s="24" t="s">
-        <v>1118</v>
-      </c>
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="3"/>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1285</v>
+        <v>1120</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>17</v>
@@ -17088,18 +17124,18 @@
         <v>1117</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>1286</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>17</v>
@@ -17108,18 +17144,18 @@
         <v>1117</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>17</v>
@@ -17128,18 +17164,18 @@
         <v>1117</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1292</v>
+        <v>1123</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>17</v>
@@ -17148,18 +17184,18 @@
         <v>1117</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>1293</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>17</v>
@@ -17168,18 +17204,18 @@
         <v>1117</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>17</v>
@@ -17188,18 +17224,18 @@
         <v>1117</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>1102</v>
+        <v>1302</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F52" s="18" t="s">
         <v>17</v>
@@ -17207,19 +17243,19 @@
       <c r="G52" s="18" t="s">
         <v>1117</v>
       </c>
-      <c r="H52" s="25" t="s">
-        <v>1301</v>
+      <c r="H52" s="24" t="s">
+        <v>1304</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1137</v>
+        <v>1305</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>17</v>
@@ -17227,19 +17263,19 @@
       <c r="G53" s="18" t="s">
         <v>1117</v>
       </c>
-      <c r="H53" s="22" t="s">
-        <v>1303</v>
+      <c r="H53" s="24" t="s">
+        <v>1307</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>1304</v>
+        <v>1102</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="F54" s="18" t="s">
         <v>17</v>
@@ -17248,18 +17284,18 @@
         <v>1117</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>1307</v>
+        <v>1137</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>17</v>
@@ -17268,18 +17304,18 @@
         <v>1117</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>17</v>
@@ -17287,19 +17323,19 @@
       <c r="G56" s="18" t="s">
         <v>1117</v>
       </c>
-      <c r="H56" s="24" t="s">
-        <v>1312</v>
+      <c r="H56" s="25" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>17</v>
@@ -17307,19 +17343,19 @@
       <c r="G57" s="18" t="s">
         <v>1117</v>
       </c>
-      <c r="H57" s="24" t="s">
-        <v>1315</v>
+      <c r="H57" s="22" t="s">
+        <v>1317</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>17</v>
@@ -17328,18 +17364,18 @@
         <v>1117</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>17</v>
@@ -17348,18 +17384,18 @@
         <v>1117</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>17</v>
@@ -17368,18 +17404,18 @@
         <v>1117</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>17</v>
@@ -17388,18 +17424,18 @@
         <v>1117</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>17</v>
@@ -17408,18 +17444,18 @@
         <v>1117</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>17</v>
@@ -17428,18 +17464,18 @@
         <v>1117</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="18" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="F64" s="18" t="s">
         <v>17</v>
@@ -17448,66 +17484,66 @@
         <v>1117</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="3"/>
-    </row>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C66" s="1">
-        <v>2031</v>
-      </c>
-      <c r="D66" s="1">
-        <v>0</v>
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C65" s="18" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" s="18" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H65" s="24" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C66" s="18" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>1115</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="F66" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>25</v>
+        <v>1117</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C67" s="1">
-        <v>2032</v>
-      </c>
-      <c r="D67" s="1">
-        <v>0</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>1339</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G67" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H67" s="24" t="s">
-        <v>1340</v>
-      </c>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="3"/>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C68" s="1">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="F68" s="18" t="s">
         <v>17</v>
@@ -17516,18 +17552,18 @@
         <v>25</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C69" s="1">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="F69" s="18" t="s">
         <v>17</v>
@@ -17536,18 +17572,18 @@
         <v>25</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C70" s="1">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="F70" s="18" t="s">
         <v>17</v>
@@ -17556,18 +17592,18 @@
         <v>25</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C71" s="1">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="F71" s="18" t="s">
         <v>17</v>
@@ -17576,18 +17612,18 @@
         <v>25</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C72" s="1">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="F72" s="18" t="s">
         <v>17</v>
@@ -17596,18 +17632,18 @@
         <v>25</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C73" s="1">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="F73" s="18" t="s">
         <v>17</v>
@@ -17616,18 +17652,18 @@
         <v>25</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C74" s="1">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="F74" s="18" t="s">
         <v>17</v>
@@ -17636,18 +17672,18 @@
         <v>25</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C75" s="1">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="F75" s="18" t="s">
         <v>17</v>
@@ -17656,18 +17692,18 @@
         <v>25</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C76" s="1">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="F76" s="18" t="s">
         <v>17</v>
@@ -17676,18 +17712,18 @@
         <v>25</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C77" s="1">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="F77" s="18" t="s">
         <v>17</v>
@@ -17696,18 +17732,18 @@
         <v>25</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C78" s="1">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="F78" s="18" t="s">
         <v>17</v>
@@ -17716,18 +17752,18 @@
         <v>25</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C79" s="1">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="F79" s="18" t="s">
         <v>17</v>
@@ -17736,18 +17772,18 @@
         <v>25</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C80" s="1">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="F80" s="18" t="s">
         <v>17</v>
@@ -17756,18 +17792,18 @@
         <v>25</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C81" s="1">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="F81" s="18" t="s">
         <v>17</v>
@@ -17776,18 +17812,18 @@
         <v>25</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C82" s="1">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="F82" s="18" t="s">
         <v>17</v>
@@ -17796,18 +17832,18 @@
         <v>25</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C83" s="1">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="F83" s="18" t="s">
         <v>17</v>
@@ -17816,18 +17852,18 @@
         <v>25</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C84" s="1">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="F84" s="18" t="s">
         <v>17</v>
@@ -17836,18 +17872,18 @@
         <v>25</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="85" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C85" s="1">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="F85" s="18" t="s">
         <v>17</v>
@@ -17856,18 +17892,18 @@
         <v>25</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="86" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C86" s="1">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="F86" s="18" t="s">
         <v>17</v>
@@ -17876,18 +17912,18 @@
         <v>25</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C87" s="1">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="F87" s="18" t="s">
         <v>17</v>
@@ -17896,18 +17932,18 @@
         <v>25</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="88" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C88" s="1">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>17</v>
@@ -17916,18 +17952,18 @@
         <v>25</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C89" s="1">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="F89" s="18" t="s">
         <v>17</v>
@@ -17936,66 +17972,66 @@
         <v>25</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="90" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="3"/>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C91" s="18" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>1115</v>
+      <c r="C90" s="1">
+        <v>2053</v>
+      </c>
+      <c r="D90" s="1">
+        <v>0</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F90" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H90" s="24" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="91" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C91" s="1">
+        <v>2054</v>
+      </c>
+      <c r="D91" s="1">
+        <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1126</v>
+        <v>1391</v>
       </c>
       <c r="F91" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>1127</v>
+        <v>25</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C92" s="18" t="s">
-        <v>1386</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>1130</v>
-      </c>
-      <c r="F92" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G92" s="18" t="s">
-        <v>1127</v>
-      </c>
-      <c r="H92" s="24" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" spans="3:8">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C93" s="18" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1388</v>
+        <v>1126</v>
       </c>
       <c r="F93" s="18" t="s">
         <v>17</v>
@@ -18003,19 +18039,19 @@
       <c r="G93" s="18" t="s">
         <v>1127</v>
       </c>
-      <c r="H93" s="22" t="s">
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="3:8">
+      <c r="H93" s="24" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C94" s="18" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1391</v>
+        <v>1130</v>
       </c>
       <c r="F94" s="18" t="s">
         <v>17</v>
@@ -18023,19 +18059,19 @@
       <c r="G94" s="18" t="s">
         <v>1127</v>
       </c>
-      <c r="H94" s="22" t="s">
-        <v>1392</v>
+      <c r="H94" s="24" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:8">
       <c r="C95" s="18" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="F95" s="18" t="s">
         <v>17</v>
@@ -18044,18 +18080,18 @@
         <v>1127</v>
       </c>
       <c r="H95" s="22" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:8">
       <c r="C96" s="18" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="F96" s="18" t="s">
         <v>17</v>
@@ -18064,255 +18100,295 @@
         <v>1127</v>
       </c>
       <c r="H96" s="22" t="s">
-        <v>1398</v>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:8">
+      <c r="C97" s="18" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="F97" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G97" s="18" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H97" s="22" t="s">
+        <v>1403</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:8">
       <c r="C98" s="18" t="s">
-        <v>1399</v>
+        <v>1404</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="F98" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G98" s="18" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H98" s="22" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:8">
+      <c r="C100" s="18" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F100" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="18" t="s">
         <v>1231</v>
       </c>
-      <c r="H98" s="22" t="s">
-        <v>1401</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" spans="3:8">
-      <c r="C99" s="18" t="s">
-        <v>1402</v>
-      </c>
-      <c r="D99" s="1" t="s">
+      <c r="H100" s="22" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:8">
+      <c r="C101" s="18" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>1403</v>
-      </c>
-      <c r="F99" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G99" s="18" t="s">
+      <c r="E101" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F101" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="18" t="s">
         <v>1231</v>
       </c>
-      <c r="H99" s="22" t="s">
-        <v>1404</v>
-      </c>
-    </row>
-    <row r="100" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="3"/>
-    </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C101" s="10" t="s">
-        <v>1405</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>1406</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>1407</v>
-      </c>
-      <c r="H101" s="18" t="s">
-        <v>1408</v>
-      </c>
-    </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C102" s="10" t="s">
-        <v>1409</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>1410</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>1407</v>
-      </c>
-      <c r="H102" s="18" t="s">
-        <v>1411</v>
-      </c>
+      <c r="H101" s="22" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="102" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="3"/>
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C103" s="10" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="H103" s="18" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C104" s="10" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G104" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>1416</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>1407</v>
-      </c>
       <c r="H104" s="18" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C105" s="10" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C106" s="10" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="H106" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C107" s="10" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="H107" s="18" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C108" s="10" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>1407</v>
-      </c>
-      <c r="H108" s="24" t="s">
-        <v>1429</v>
+        <v>1415</v>
+      </c>
+      <c r="H108" s="18" t="s">
+        <v>1431</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C109" s="10" t="s">
-        <v>1430</v>
-      </c>
-      <c r="D109" s="18" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H109" s="18" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C110" s="10" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H110" s="24" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C111" s="10" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D111" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>1431</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>1407</v>
-      </c>
-      <c r="H109" s="24" t="s">
-        <v>1432</v>
-      </c>
-    </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C110" s="10">
+      <c r="E111" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H111" s="24" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="112" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C112" s="10">
         <v>300091</v>
       </c>
-      <c r="D110" s="1">
+      <c r="D112" s="1">
         <v>100</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>1433</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>1407</v>
-      </c>
-      <c r="H110" s="24" t="s">
-        <v>1434</v>
+      <c r="E112" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H112" s="24" t="s">
+        <v>1442</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="1443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2525" uniqueCount="1447">
   <si>
     <t>_id</t>
   </si>
@@ -3664,6 +3664,9 @@
     <t>极·炼神证明</t>
   </si>
   <si>
+    <t>极·炼魂证明</t>
+  </si>
+  <si>
     <t>220000</t>
   </si>
   <si>
@@ -3899,6 +3902,15 @@
   </si>
   <si>
     <t>190007,190008,190009,190010,190011,190012</t>
+  </si>
+  <si>
+    <t>220044</t>
+  </si>
+  <si>
+    <t>六大道戒</t>
+  </si>
+  <si>
+    <t>190013,190014,190015,190016,190017,190018</t>
   </si>
   <si>
     <t>220101</t>
@@ -4956,12 +4968,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -14337,7 +14349,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -15121,6 +15133,26 @@
       </c>
       <c r="H41" s="11">
         <v>180042</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:8">
+      <c r="C42" s="11">
+        <v>180043</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42" s="1">
+        <v>18</v>
+      </c>
+      <c r="H42" s="11">
+        <v>180043</v>
       </c>
     </row>
   </sheetData>
@@ -15138,7 +15170,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H60"/>
+  <dimension ref="C1:H61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -15220,13 +15252,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="19" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>17</v>
@@ -15240,13 +15272,13 @@
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="19" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>17</v>
@@ -15260,13 +15292,13 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="19" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F8" s="1">
         <v>50</v>
@@ -15280,13 +15312,13 @@
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="19" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F9" s="1">
         <v>20</v>
@@ -15300,13 +15332,13 @@
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="19" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
@@ -15320,13 +15352,13 @@
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="19" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>17</v>
@@ -15340,13 +15372,13 @@
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="19" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>17</v>
@@ -15360,13 +15392,13 @@
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="19" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>17</v>
@@ -15375,18 +15407,18 @@
         <v>3</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="19" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>17</v>
@@ -15395,18 +15427,18 @@
         <v>3</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="19" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -15415,18 +15447,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="19" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -15440,13 +15472,13 @@
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="19" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F17" s="1">
         <v>40</v>
@@ -15460,13 +15492,13 @@
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="19" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F18" s="1">
         <v>200</v>
@@ -15480,13 +15512,13 @@
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="19" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F19" s="1">
         <v>80</v>
@@ -15500,13 +15532,13 @@
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="19" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>17</v>
@@ -15520,13 +15552,13 @@
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="19" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F21" s="1">
         <v>500</v>
@@ -15540,13 +15572,13 @@
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="19" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F22" s="1">
         <v>200</v>
@@ -15560,113 +15592,113 @@
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="19" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="19" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="19" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="19" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="19" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="19" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>17</v>
@@ -15675,18 +15707,18 @@
         <v>3</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="19" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>17</v>
@@ -15695,18 +15727,18 @@
         <v>3</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="19" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>17</v>
@@ -15715,18 +15747,18 @@
         <v>3</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="19" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F31" s="1">
         <v>2</v>
@@ -15740,13 +15772,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="19" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F32" s="1">
         <v>2</v>
@@ -15760,13 +15792,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="19" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F33" s="1">
         <v>200</v>
@@ -15780,13 +15812,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="19" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F34" s="1">
         <v>100</v>
@@ -15800,53 +15832,53 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="19" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="F35" s="1">
         <v>10</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="19" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="F36" s="1">
         <v>15</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="19" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>17</v>
@@ -15860,13 +15892,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="19" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F38" s="1">
         <v>1000</v>
@@ -15880,13 +15912,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="19" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F39" s="1">
         <v>300</v>
@@ -15900,13 +15932,13 @@
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="19" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="F40" s="1">
         <v>1</v>
@@ -15915,18 +15947,18 @@
         <v>5</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="19" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="F41" s="1">
         <v>1</v>
@@ -15940,13 +15972,13 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="19" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="F42" s="1">
         <v>1</v>
@@ -15955,38 +15987,38 @@
         <v>19</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:8">
-      <c r="C44" s="19" t="s">
         <v>1162</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E44" s="12" t="s">
+    </row>
+    <row r="43" customHeight="1" spans="3:8">
+      <c r="C43" s="19" t="s">
         <v>1163</v>
       </c>
-      <c r="F44" s="1">
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F43" s="1">
         <v>1</v>
       </c>
-      <c r="G44" s="1">
-        <v>16</v>
-      </c>
-      <c r="H44" s="1">
-        <v>8201</v>
+      <c r="G43" s="1">
+        <v>19</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>1165</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="19" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
@@ -15995,18 +16027,18 @@
         <v>16</v>
       </c>
       <c r="H45" s="1">
-        <v>8202</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="19" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -16015,18 +16047,18 @@
         <v>16</v>
       </c>
       <c r="H46" s="1">
-        <v>8203</v>
+        <v>8202</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="19" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -16035,18 +16067,18 @@
         <v>16</v>
       </c>
       <c r="H47" s="1">
-        <v>8204</v>
+        <v>8203</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="19" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="F48" s="1">
         <v>1</v>
@@ -16055,18 +16087,18 @@
         <v>16</v>
       </c>
       <c r="H48" s="1">
-        <v>8205</v>
+        <v>8204</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="19" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
@@ -16075,18 +16107,18 @@
         <v>16</v>
       </c>
       <c r="H49" s="1">
-        <v>8206</v>
+        <v>8205</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="19" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="F50" s="1">
         <v>1</v>
@@ -16095,18 +16127,18 @@
         <v>16</v>
       </c>
       <c r="H50" s="1">
-        <v>8207</v>
+        <v>8206</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="19" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -16115,13 +16147,28 @@
         <v>16</v>
       </c>
       <c r="H51" s="1">
+        <v>8207</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:8">
+      <c r="C52" s="19" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F52" s="1">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1">
+        <v>16</v>
+      </c>
+      <c r="H52" s="1">
         <v>8209</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:8">
-      <c r="C53" s="10"/>
-      <c r="E53" s="12"/>
-      <c r="H53" s="1"/>
     </row>
     <row r="54" customHeight="1" spans="3:8">
       <c r="C54" s="10"/>
@@ -16129,34 +16176,19 @@
       <c r="H54" s="1"/>
     </row>
     <row r="55" customHeight="1" spans="3:8">
-      <c r="C55" s="19" t="s">
-        <v>1178</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>1179</v>
-      </c>
-      <c r="F55" s="1">
-        <v>1</v>
-      </c>
-      <c r="G55" s="1">
-        <v>31</v>
-      </c>
-      <c r="H55" s="1">
-        <v>8303</v>
-      </c>
+      <c r="C55" s="10"/>
+      <c r="E55" s="12"/>
+      <c r="H55" s="1"/>
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="19" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="F56" s="1">
         <v>1</v>
@@ -16165,18 +16197,18 @@
         <v>31</v>
       </c>
       <c r="H56" s="1">
-        <v>8304</v>
+        <v>8303</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="19" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="F57" s="1">
         <v>1</v>
@@ -16185,18 +16217,18 @@
         <v>31</v>
       </c>
       <c r="H57" s="1">
-        <v>8305</v>
+        <v>8304</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="19" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="F58" s="1">
         <v>1</v>
@@ -16205,18 +16237,18 @@
         <v>31</v>
       </c>
       <c r="H58" s="1">
-        <v>8306</v>
+        <v>8305</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="19" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="F59" s="1">
         <v>1</v>
@@ -16225,18 +16257,18 @@
         <v>31</v>
       </c>
       <c r="H59" s="1">
-        <v>8307</v>
+        <v>8306</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="19" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="F60" s="1">
         <v>1</v>
@@ -16245,6 +16277,26 @@
         <v>31</v>
       </c>
       <c r="H60" s="1">
+        <v>8307</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:8">
+      <c r="C61" s="19" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F61" s="1">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1">
+        <v>31</v>
+      </c>
+      <c r="H61" s="1">
         <v>8308</v>
       </c>
     </row>
@@ -16345,13 +16397,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="1" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>17</v>
@@ -16360,18 +16412,18 @@
         <v>18</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>17</v>
@@ -16380,18 +16432,18 @@
         <v>18</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>17</v>
@@ -16400,18 +16452,18 @@
         <v>18</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>17</v>
@@ -16420,18 +16472,18 @@
         <v>18</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
@@ -16440,18 +16492,18 @@
         <v>18</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>17</v>
@@ -16460,18 +16512,18 @@
         <v>18</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>17</v>
@@ -16480,18 +16532,18 @@
         <v>15</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>17</v>
@@ -16500,18 +16552,18 @@
         <v>15</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>1213</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>1209</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>17</v>
@@ -16520,18 +16572,18 @@
         <v>15</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>17</v>
@@ -16540,18 +16592,18 @@
         <v>15</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>17</v>
@@ -16560,18 +16612,18 @@
         <v>15</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>17</v>
@@ -16580,18 +16632,18 @@
         <v>15</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>17</v>
@@ -16600,7 +16652,7 @@
         <v>15</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16619,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -16628,7 +16680,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16639,7 +16691,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
@@ -16648,7 +16700,7 @@
         <v>5</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16664,199 +16716,199 @@
         <v>305</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>21</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="F28" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="F30" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16864,199 +16916,199 @@
         <v>309</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17064,39 +17116,39 @@
         <v>312</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17109,422 +17161,422 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G50" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="F52" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="F54" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H56" s="25" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G62" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="18" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="F64" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="18" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="18" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="F66" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17543,7 +17595,7 @@
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="F68" s="18" t="s">
         <v>17</v>
@@ -17552,7 +17604,7 @@
         <v>25</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17563,7 +17615,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="F69" s="18" t="s">
         <v>17</v>
@@ -17572,7 +17624,7 @@
         <v>25</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17583,7 +17635,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="F70" s="18" t="s">
         <v>17</v>
@@ -17592,7 +17644,7 @@
         <v>25</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17603,7 +17655,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="F71" s="18" t="s">
         <v>17</v>
@@ -17612,7 +17664,7 @@
         <v>25</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17623,7 +17675,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="F72" s="18" t="s">
         <v>17</v>
@@ -17632,7 +17684,7 @@
         <v>25</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17643,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="F73" s="18" t="s">
         <v>17</v>
@@ -17652,7 +17704,7 @@
         <v>25</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17663,7 +17715,7 @@
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="F74" s="18" t="s">
         <v>17</v>
@@ -17672,7 +17724,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17683,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="F75" s="18" t="s">
         <v>17</v>
@@ -17692,7 +17744,7 @@
         <v>25</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17703,7 +17755,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="F76" s="18" t="s">
         <v>17</v>
@@ -17712,7 +17764,7 @@
         <v>25</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17723,7 +17775,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="F77" s="18" t="s">
         <v>17</v>
@@ -17732,7 +17784,7 @@
         <v>25</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17743,7 +17795,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="F78" s="18" t="s">
         <v>17</v>
@@ -17752,7 +17804,7 @@
         <v>25</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17763,7 +17815,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="F79" s="18" t="s">
         <v>17</v>
@@ -17772,7 +17824,7 @@
         <v>25</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17783,7 +17835,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="F80" s="18" t="s">
         <v>17</v>
@@ -17792,7 +17844,7 @@
         <v>25</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17803,7 +17855,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="F81" s="18" t="s">
         <v>17</v>
@@ -17812,7 +17864,7 @@
         <v>25</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17823,7 +17875,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="F82" s="18" t="s">
         <v>17</v>
@@ -17832,7 +17884,7 @@
         <v>25</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17843,7 +17895,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="F83" s="18" t="s">
         <v>17</v>
@@ -17852,7 +17904,7 @@
         <v>25</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17863,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="F84" s="18" t="s">
         <v>17</v>
@@ -17872,7 +17924,7 @@
         <v>25</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="85" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17883,7 +17935,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="F85" s="18" t="s">
         <v>17</v>
@@ -17892,7 +17944,7 @@
         <v>25</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="86" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17903,7 +17955,7 @@
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="F86" s="18" t="s">
         <v>17</v>
@@ -17912,7 +17964,7 @@
         <v>25</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17923,7 +17975,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="F87" s="18" t="s">
         <v>17</v>
@@ -17932,7 +17984,7 @@
         <v>25</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="88" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17943,7 +17995,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>17</v>
@@ -17952,7 +18004,7 @@
         <v>25</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17963,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="F89" s="18" t="s">
         <v>17</v>
@@ -17972,7 +18024,7 @@
         <v>25</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="90" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17983,7 +18035,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="F90" s="18" t="s">
         <v>17</v>
@@ -17992,7 +18044,7 @@
         <v>25</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="91" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18003,7 +18055,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="F91" s="18" t="s">
         <v>17</v>
@@ -18012,7 +18064,7 @@
         <v>25</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18025,162 +18077,162 @@
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C93" s="18" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="F93" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C94" s="18" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="F94" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G94" s="18" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:8">
       <c r="C95" s="18" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="F95" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G95" s="18" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H95" s="22" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:8">
       <c r="C96" s="18" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="F96" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H96" s="22" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:8">
       <c r="C97" s="18" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="F97" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H97" s="22" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:8">
       <c r="C98" s="18" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="F98" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G98" s="18" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H98" s="22" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:8">
       <c r="C100" s="18" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="F100" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G100" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H100" s="22" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:8">
       <c r="C101" s="18" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="F101" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G101" s="18" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18193,182 +18245,182 @@
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C103" s="10" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="H103" s="18" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C104" s="10" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="H104" s="18" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C105" s="10" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C106" s="10" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="H106" s="18" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C107" s="10" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="H107" s="18" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C108" s="10" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="H108" s="18" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C109" s="10" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="H109" s="18" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C110" s="10" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="H110" s="24" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C111" s="10" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="D111" s="18" t="s">
         <v>47</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="H111" s="24" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -18379,16 +18431,16 @@
         <v>100</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="H112" s="24" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -413,7 +418,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2525" uniqueCount="1447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="1449">
   <si>
     <t>_id</t>
   </si>
@@ -3665,6 +3670,12 @@
   </si>
   <si>
     <t>极·炼魂证明</t>
+  </si>
+  <si>
+    <t>极戒之源</t>
+  </si>
+  <si>
+    <t>道戒之源</t>
   </si>
   <si>
     <t>220000</t>
@@ -4968,12 +4979,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -14349,7 +14360,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -15153,6 +15164,46 @@
       </c>
       <c r="H42" s="11">
         <v>180043</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:8">
+      <c r="C43" s="11">
+        <v>180044</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" s="1">
+        <v>18</v>
+      </c>
+      <c r="H43" s="11">
+        <v>180044</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:8">
+      <c r="C44" s="11">
+        <v>180045</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="1">
+        <v>18</v>
+      </c>
+      <c r="H44" s="11">
+        <v>180045</v>
       </c>
     </row>
   </sheetData>
@@ -15252,13 +15303,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="19" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>17</v>
@@ -15272,13 +15323,13 @@
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="19" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>17</v>
@@ -15292,13 +15343,13 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="19" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F8" s="1">
         <v>50</v>
@@ -15312,13 +15363,13 @@
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="19" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F9" s="1">
         <v>20</v>
@@ -15332,13 +15383,13 @@
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="19" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
@@ -15352,13 +15403,13 @@
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="19" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>17</v>
@@ -15372,13 +15423,13 @@
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="19" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>17</v>
@@ -15392,13 +15443,13 @@
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="19" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>17</v>
@@ -15407,18 +15458,18 @@
         <v>3</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="19" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>17</v>
@@ -15427,18 +15478,18 @@
         <v>3</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="19" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -15447,18 +15498,18 @@
         <v>19</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="19" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -15472,13 +15523,13 @@
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="19" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F17" s="1">
         <v>40</v>
@@ -15492,13 +15543,13 @@
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="19" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F18" s="1">
         <v>200</v>
@@ -15512,13 +15563,13 @@
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="19" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F19" s="1">
         <v>80</v>
@@ -15532,13 +15583,13 @@
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="19" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>17</v>
@@ -15552,13 +15603,13 @@
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="19" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F21" s="1">
         <v>500</v>
@@ -15572,13 +15623,13 @@
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C22" s="19" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F22" s="1">
         <v>200</v>
@@ -15592,113 +15643,113 @@
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C23" s="19" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="19" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="19" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="19" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="19" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="19" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>17</v>
@@ -15707,18 +15758,18 @@
         <v>3</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="19" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>17</v>
@@ -15727,18 +15778,18 @@
         <v>3</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="19" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>17</v>
@@ -15747,18 +15798,18 @@
         <v>3</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:8">
       <c r="C31" s="19" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="F31" s="1">
         <v>2</v>
@@ -15772,13 +15823,13 @@
     </row>
     <row r="32" customHeight="1" spans="3:8">
       <c r="C32" s="19" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="F32" s="1">
         <v>2</v>
@@ -15792,13 +15843,13 @@
     </row>
     <row r="33" customHeight="1" spans="3:8">
       <c r="C33" s="19" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F33" s="1">
         <v>200</v>
@@ -15812,13 +15863,13 @@
     </row>
     <row r="34" customHeight="1" spans="3:8">
       <c r="C34" s="19" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F34" s="1">
         <v>100</v>
@@ -15832,53 +15883,53 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="19" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="F35" s="1">
         <v>10</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="19" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="F36" s="1">
         <v>15</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="19" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>17</v>
@@ -15892,13 +15943,13 @@
     </row>
     <row r="38" customHeight="1" spans="3:8">
       <c r="C38" s="19" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F38" s="1">
         <v>1000</v>
@@ -15912,13 +15963,13 @@
     </row>
     <row r="39" customHeight="1" spans="3:8">
       <c r="C39" s="19" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F39" s="1">
         <v>300</v>
@@ -15932,13 +15983,13 @@
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="19" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="F40" s="1">
         <v>1</v>
@@ -15947,18 +15998,18 @@
         <v>5</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="19" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="F41" s="1">
         <v>1</v>
@@ -15972,13 +16023,13 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="19" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="F42" s="1">
         <v>1</v>
@@ -15987,18 +16038,18 @@
         <v>19</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:8">
       <c r="C43" s="19" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="F43" s="1">
         <v>1</v>
@@ -16007,18 +16058,18 @@
         <v>19</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="19" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
@@ -16032,13 +16083,13 @@
     </row>
     <row r="46" customHeight="1" spans="3:8">
       <c r="C46" s="19" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -16052,13 +16103,13 @@
     </row>
     <row r="47" customHeight="1" spans="3:8">
       <c r="C47" s="19" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -16072,13 +16123,13 @@
     </row>
     <row r="48" customHeight="1" spans="3:8">
       <c r="C48" s="19" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="F48" s="1">
         <v>1</v>
@@ -16092,13 +16143,13 @@
     </row>
     <row r="49" customHeight="1" spans="3:8">
       <c r="C49" s="19" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
@@ -16112,13 +16163,13 @@
     </row>
     <row r="50" customHeight="1" spans="3:8">
       <c r="C50" s="19" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F50" s="1">
         <v>1</v>
@@ -16132,13 +16183,13 @@
     </row>
     <row r="51" customHeight="1" spans="3:8">
       <c r="C51" s="19" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -16152,13 +16203,13 @@
     </row>
     <row r="52" customHeight="1" spans="3:8">
       <c r="C52" s="19" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="F52" s="1">
         <v>1</v>
@@ -16182,13 +16233,13 @@
     </row>
     <row r="56" customHeight="1" spans="3:8">
       <c r="C56" s="19" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="F56" s="1">
         <v>1</v>
@@ -16202,13 +16253,13 @@
     </row>
     <row r="57" customHeight="1" spans="3:8">
       <c r="C57" s="19" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="F57" s="1">
         <v>1</v>
@@ -16222,13 +16273,13 @@
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="19" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="F58" s="1">
         <v>1</v>
@@ -16242,13 +16293,13 @@
     </row>
     <row r="59" customHeight="1" spans="3:8">
       <c r="C59" s="19" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="F59" s="1">
         <v>1</v>
@@ -16262,13 +16313,13 @@
     </row>
     <row r="60" customHeight="1" spans="3:8">
       <c r="C60" s="19" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="F60" s="1">
         <v>1</v>
@@ -16282,13 +16333,13 @@
     </row>
     <row r="61" customHeight="1" spans="3:8">
       <c r="C61" s="19" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="F61" s="1">
         <v>1</v>
@@ -16397,13 +16448,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="1" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>17</v>
@@ -16412,18 +16463,18 @@
         <v>18</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>17</v>
@@ -16432,18 +16483,18 @@
         <v>18</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>17</v>
@@ -16452,18 +16503,18 @@
         <v>18</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>17</v>
@@ -16472,18 +16523,18 @@
         <v>18</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
@@ -16492,18 +16543,18 @@
         <v>18</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>17</v>
@@ -16512,18 +16563,18 @@
         <v>18</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>17</v>
@@ -16532,18 +16583,18 @@
         <v>15</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>1215</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>1213</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>17</v>
@@ -16552,18 +16603,18 @@
         <v>15</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>17</v>
@@ -16572,18 +16623,18 @@
         <v>15</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>17</v>
@@ -16592,18 +16643,18 @@
         <v>15</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>17</v>
@@ -16612,18 +16663,18 @@
         <v>15</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>17</v>
@@ -16632,18 +16683,18 @@
         <v>15</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>17</v>
@@ -16652,7 +16703,7 @@
         <v>15</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16671,7 +16722,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -16680,7 +16731,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16691,7 +16742,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
@@ -16700,7 +16751,7 @@
         <v>5</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16716,199 +16767,199 @@
         <v>305</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="18" t="s">
         <v>1237</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>1235</v>
-      </c>
       <c r="H24" s="24" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>21</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="F28" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>15</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="F30" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16916,199 +16967,199 @@
         <v>309</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C34" s="18" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17116,39 +17167,39 @@
         <v>312</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17161,422 +17212,422 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="F46" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="F47" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="F49" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G50" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="F52" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C54" s="18" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="F54" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C55" s="18" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H56" s="25" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G62" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="18" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="F64" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="18" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="18" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="F66" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17595,7 +17646,7 @@
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="F68" s="18" t="s">
         <v>17</v>
@@ -17604,7 +17655,7 @@
         <v>25</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17615,7 +17666,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="F69" s="18" t="s">
         <v>17</v>
@@ -17624,7 +17675,7 @@
         <v>25</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17635,7 +17686,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="F70" s="18" t="s">
         <v>17</v>
@@ -17644,7 +17695,7 @@
         <v>25</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17655,7 +17706,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="F71" s="18" t="s">
         <v>17</v>
@@ -17664,7 +17715,7 @@
         <v>25</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17675,7 +17726,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="F72" s="18" t="s">
         <v>17</v>
@@ -17684,7 +17735,7 @@
         <v>25</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17695,7 +17746,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F73" s="18" t="s">
         <v>17</v>
@@ -17704,7 +17755,7 @@
         <v>25</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17715,7 +17766,7 @@
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="F74" s="18" t="s">
         <v>17</v>
@@ -17724,7 +17775,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17735,7 +17786,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="F75" s="18" t="s">
         <v>17</v>
@@ -17744,7 +17795,7 @@
         <v>25</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17755,7 +17806,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F76" s="18" t="s">
         <v>17</v>
@@ -17764,7 +17815,7 @@
         <v>25</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17775,7 +17826,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="F77" s="18" t="s">
         <v>17</v>
@@ -17784,7 +17835,7 @@
         <v>25</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17795,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="F78" s="18" t="s">
         <v>17</v>
@@ -17804,7 +17855,7 @@
         <v>25</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17815,7 +17866,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="F79" s="18" t="s">
         <v>17</v>
@@ -17824,7 +17875,7 @@
         <v>25</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17835,7 +17886,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="F80" s="18" t="s">
         <v>17</v>
@@ -17844,7 +17895,7 @@
         <v>25</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17855,7 +17906,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="F81" s="18" t="s">
         <v>17</v>
@@ -17864,7 +17915,7 @@
         <v>25</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17875,7 +17926,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="F82" s="18" t="s">
         <v>17</v>
@@ -17884,7 +17935,7 @@
         <v>25</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17895,7 +17946,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="F83" s="18" t="s">
         <v>17</v>
@@ -17904,7 +17955,7 @@
         <v>25</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17915,7 +17966,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="F84" s="18" t="s">
         <v>17</v>
@@ -17924,7 +17975,7 @@
         <v>25</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="85" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17935,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="F85" s="18" t="s">
         <v>17</v>
@@ -17944,7 +17995,7 @@
         <v>25</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="86" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17955,7 +18006,7 @@
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="F86" s="18" t="s">
         <v>17</v>
@@ -17964,7 +18015,7 @@
         <v>25</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17975,7 +18026,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="F87" s="18" t="s">
         <v>17</v>
@@ -17984,7 +18035,7 @@
         <v>25</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="88" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17995,7 +18046,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>17</v>
@@ -18004,7 +18055,7 @@
         <v>25</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18015,7 +18066,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F89" s="18" t="s">
         <v>17</v>
@@ -18024,7 +18075,7 @@
         <v>25</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="90" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18035,7 +18086,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F90" s="18" t="s">
         <v>17</v>
@@ -18044,7 +18095,7 @@
         <v>25</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="91" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18055,7 +18106,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="F91" s="18" t="s">
         <v>17</v>
@@ -18064,7 +18115,7 @@
         <v>25</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18077,162 +18128,162 @@
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C93" s="18" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="F93" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C94" s="18" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="F94" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G94" s="18" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:8">
       <c r="C95" s="18" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="F95" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G95" s="18" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="H95" s="22" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:8">
       <c r="C96" s="18" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="F96" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="H96" s="22" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:8">
       <c r="C97" s="18" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="F97" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="H97" s="22" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:8">
       <c r="C98" s="18" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="F98" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G98" s="18" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="H98" s="22" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:8">
       <c r="C100" s="18" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="F100" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G100" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H100" s="22" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:8">
       <c r="C101" s="18" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="F101" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G101" s="18" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H101" s="22" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18245,182 +18296,182 @@
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C103" s="10" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="H103" s="18" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C104" s="10" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="H104" s="18" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C105" s="10" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C106" s="10" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="H106" s="18" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C107" s="10" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="H107" s="18" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C108" s="10" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="H108" s="18" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C109" s="10" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="H109" s="18" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C110" s="10" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="H110" s="24" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C111" s="10" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="D111" s="18" t="s">
         <v>47</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="H111" s="24" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -18431,16 +18482,16 @@
         <v>100</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="H112" s="24" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -418,7 +418,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="1449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="1457">
   <si>
     <t>_id</t>
   </si>
@@ -4569,52 +4569,76 @@
     <t>2100028,2100029,2100030</t>
   </si>
   <si>
-    <t>绿色英灵-魏国</t>
+    <t>绿色英灵-群雄</t>
   </si>
   <si>
     <t>2100076,2100077,2100078,2100079,2100080,2100081</t>
   </si>
   <si>
-    <t>蓝色英灵-魏国</t>
+    <t>蓝色英灵-群雄</t>
   </si>
   <si>
     <t>2100073,2100074,2100075</t>
   </si>
   <si>
-    <t>紫色英灵-魏国</t>
+    <t>紫色英灵-群雄</t>
   </si>
   <si>
     <t>2100070,2100071,2100072</t>
   </si>
   <si>
-    <t>橙色英灵-魏国</t>
+    <t>橙色英灵-群雄</t>
   </si>
   <si>
     <t>2100067,2100068,2100069</t>
   </si>
   <si>
-    <t>红色英灵-魏国</t>
+    <t>红色英灵-群雄</t>
   </si>
   <si>
     <t>2100064,2100065,2100066</t>
   </si>
   <si>
-    <t>金色英灵-魏国</t>
+    <t>金色英灵-群雄</t>
   </si>
   <si>
     <t>2100061,2100062,2100063</t>
   </si>
   <si>
-    <t>暗金英灵-魏国</t>
+    <t>暗金英灵-群雄</t>
   </si>
   <si>
     <t>2100058,2100059,2100060</t>
   </si>
   <si>
-    <t>粉色英灵-魏国</t>
+    <t>粉色英灵-群雄</t>
   </si>
   <si>
     <t>2100055,2100056,2100057</t>
+  </si>
+  <si>
+    <t>2100103,2100104,2100105,2100106,2100107,2100108</t>
+  </si>
+  <si>
+    <t>2100100,2100101,2100102</t>
+  </si>
+  <si>
+    <t>2100097,2100098,2100099</t>
+  </si>
+  <si>
+    <t>2100094,2100095,2100096</t>
+  </si>
+  <si>
+    <t>2100091,2100092,2100093</t>
+  </si>
+  <si>
+    <t>2100088,2100089,2100090</t>
+  </si>
+  <si>
+    <t>2100085,2100086,2100087</t>
+  </si>
+  <si>
+    <t>2100082,2100083,2100084</t>
   </si>
   <si>
     <t>3001</t>
@@ -16366,7 +16390,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H112"/>
+  <dimension ref="C1:H122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -18126,165 +18150,173 @@
       <c r="G92" s="1"/>
       <c r="H92" s="3"/>
     </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C93" s="18" t="s">
+    <row r="93" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C93" s="1">
+        <v>2055</v>
+      </c>
+      <c r="D93" s="1">
+        <v>0</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F93" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G93" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H93" s="24" t="s">
         <v>1399</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F93" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G93" s="18" t="s">
-        <v>1130</v>
-      </c>
-      <c r="H93" s="24" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C94" s="18" t="s">
+    </row>
+    <row r="94" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C94" s="1">
+        <v>2056</v>
+      </c>
+      <c r="D94" s="1">
+        <v>0</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F94" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H94" s="24" t="s">
         <v>1400</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F94" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G94" s="18" t="s">
-        <v>1130</v>
-      </c>
-      <c r="H94" s="24" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="95" customHeight="1" spans="3:8">
-      <c r="C95" s="18" t="s">
+    </row>
+    <row r="95" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C95" s="1">
+        <v>2057</v>
+      </c>
+      <c r="D95" s="1">
+        <v>0</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F95" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G95" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H95" s="24" t="s">
         <v>1401</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E95" s="1" t="s">
+    </row>
+    <row r="96" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C96" s="1">
+        <v>2058</v>
+      </c>
+      <c r="D96" s="1">
+        <v>0</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H96" s="24" t="s">
         <v>1402</v>
       </c>
-      <c r="F95" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G95" s="18" t="s">
-        <v>1130</v>
-      </c>
-      <c r="H95" s="22" t="s">
+    </row>
+    <row r="97" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C97" s="1">
+        <v>2059</v>
+      </c>
+      <c r="D97" s="1">
+        <v>0</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F97" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G97" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H97" s="24" t="s">
         <v>1403</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="3:8">
-      <c r="C96" s="18" t="s">
+    <row r="98" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C98" s="1">
+        <v>2060</v>
+      </c>
+      <c r="D98" s="1">
+        <v>0</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H98" s="24" t="s">
         <v>1404</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E96" s="1" t="s">
+    </row>
+    <row r="99" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C99" s="1">
+        <v>2061</v>
+      </c>
+      <c r="D99" s="1">
+        <v>0</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F99" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H99" s="24" t="s">
         <v>1405</v>
       </c>
-      <c r="F96" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G96" s="18" t="s">
-        <v>1130</v>
-      </c>
-      <c r="H96" s="22" t="s">
+    </row>
+    <row r="100" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C100" s="1">
+        <v>2062</v>
+      </c>
+      <c r="D100" s="1">
+        <v>0</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F100" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H100" s="24" t="s">
         <v>1406</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="3:8">
-      <c r="C97" s="18" t="s">
-        <v>1407</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>1408</v>
-      </c>
-      <c r="F97" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G97" s="18" t="s">
-        <v>1130</v>
-      </c>
-      <c r="H97" s="22" t="s">
-        <v>1409</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" spans="3:8">
-      <c r="C98" s="18" t="s">
-        <v>1410</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>1411</v>
-      </c>
-      <c r="F98" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G98" s="18" t="s">
-        <v>1130</v>
-      </c>
-      <c r="H98" s="22" t="s">
-        <v>1412</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="3:8">
-      <c r="C100" s="18" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>1414</v>
-      </c>
-      <c r="F100" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G100" s="18" t="s">
-        <v>1237</v>
-      </c>
-      <c r="H100" s="22" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="3:8">
-      <c r="C101" s="18" t="s">
-        <v>1416</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>1417</v>
-      </c>
-      <c r="F101" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G101" s="18" t="s">
-        <v>1237</v>
-      </c>
-      <c r="H101" s="22" t="s">
-        <v>1418</v>
-      </c>
+    <row r="101" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="3"/>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C102" s="1"/>
@@ -18295,203 +18327,371 @@
       <c r="H102" s="3"/>
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C103" s="10" t="s">
+      <c r="C103" s="18" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F103" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="18" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H103" s="24" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C104" s="18" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G104" s="18" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H104" s="24" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:8">
+      <c r="C105" s="18" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F105" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G105" s="18" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H105" s="22" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:8">
+      <c r="C106" s="18" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F106" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G106" s="18" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H106" s="22" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:8">
+      <c r="C107" s="18" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F107" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G107" s="18" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H107" s="22" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:8">
+      <c r="C108" s="18" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="F108" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G108" s="18" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H108" s="22" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:8">
+      <c r="C110" s="18" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F110" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G110" s="18" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H110" s="22" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:8">
+      <c r="C111" s="18" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F111" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G111" s="18" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H111" s="22" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="112" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="3"/>
+    </row>
+    <row r="113" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C113" s="10" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H103" s="18" t="s">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C104" s="10" t="s">
-        <v>1423</v>
-      </c>
-      <c r="D104" s="1" t="s">
+      <c r="E113" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H113" s="18" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="114" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C114" s="10" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>1424</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H104" s="18" t="s">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C105" s="10" t="s">
-        <v>1426</v>
-      </c>
-      <c r="D105" s="1" t="s">
+      <c r="E114" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H114" s="18" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C115" s="10" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>1427</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H105" s="18" t="s">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C106" s="10" t="s">
+      <c r="E115" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G115" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="H115" s="18" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="116" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C116" s="10" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>1430</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H106" s="18" t="s">
-        <v>1431</v>
-      </c>
-    </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C107" s="10" t="s">
-        <v>1432</v>
-      </c>
-      <c r="D107" s="1" t="s">
+      <c r="E116" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H116" s="18" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="117" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C117" s="10" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>1433</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H107" s="18" t="s">
-        <v>1434</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C108" s="10" t="s">
-        <v>1435</v>
-      </c>
-      <c r="D108" s="1" t="s">
+      <c r="E117" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H117" s="18" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="118" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C118" s="10" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>1436</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H108" s="18" t="s">
-        <v>1437</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C109" s="10" t="s">
-        <v>1438</v>
-      </c>
-      <c r="D109" s="1" t="s">
+      <c r="E118" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H118" s="18" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="119" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C119" s="10" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>1439</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H109" s="18" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C110" s="10" t="s">
-        <v>1441</v>
-      </c>
-      <c r="D110" s="1" t="s">
+      <c r="E119" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H119" s="18" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="120" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C120" s="10" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>1442</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H110" s="24" t="s">
-        <v>1443</v>
-      </c>
-    </row>
-    <row r="111" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C111" s="10" t="s">
-        <v>1444</v>
-      </c>
-      <c r="D111" s="18" t="s">
+      <c r="E120" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H120" s="24" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="121" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C121" s="10" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D121" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>1445</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H111" s="24" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="112" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C112" s="10">
+      <c r="E121" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H121" s="24" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="122" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C122" s="10">
         <v>300091</v>
       </c>
-      <c r="D112" s="1">
+      <c r="D122" s="1">
         <v>100</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>1447</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="H112" s="24" t="s">
-        <v>1448</v>
+      <c r="E122" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H122" s="24" t="s">
+        <v>1456</v>
       </c>
     </row>
   </sheetData>
